--- a/artfynd/A 18040-2021 artfynd.xlsx
+++ b/artfynd/A 18040-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 18040-2021 artfynd.xlsx
+++ b/artfynd/A 18040-2021 artfynd.xlsx
@@ -13563,7 +13563,7 @@
         <v>112248564</v>
       </c>
       <c r="B119" t="n">
-        <v>91262</v>
+        <v>91272</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>

--- a/artfynd/A 18040-2021 artfynd.xlsx
+++ b/artfynd/A 18040-2021 artfynd.xlsx
@@ -13563,7 +13563,7 @@
         <v>112248564</v>
       </c>
       <c r="B119" t="n">
-        <v>91272</v>
+        <v>91284</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>

--- a/artfynd/A 18040-2021 artfynd.xlsx
+++ b/artfynd/A 18040-2021 artfynd.xlsx
@@ -13563,7 +13563,7 @@
         <v>112248564</v>
       </c>
       <c r="B119" t="n">
-        <v>91284</v>
+        <v>91285</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>

--- a/artfynd/A 18040-2021 artfynd.xlsx
+++ b/artfynd/A 18040-2021 artfynd.xlsx
@@ -13563,7 +13563,7 @@
         <v>112248564</v>
       </c>
       <c r="B119" t="n">
-        <v>91285</v>
+        <v>91288</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>

--- a/artfynd/A 18040-2021 artfynd.xlsx
+++ b/artfynd/A 18040-2021 artfynd.xlsx
@@ -1361,7 +1361,7 @@
         <v>109652943</v>
       </c>
       <c r="B8" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>553442.584477419</v>
+        <v>553443</v>
       </c>
       <c r="R8" t="n">
-        <v>6705068.108341484</v>
+        <v>6705068</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1484,7 +1484,7 @@
         <v>109653351</v>
       </c>
       <c r="B9" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1527,10 +1527,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>553523.3591971713</v>
+        <v>553523</v>
       </c>
       <c r="R9" t="n">
-        <v>6705083.108098233</v>
+        <v>6705084</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1607,7 +1607,7 @@
         <v>109666258</v>
       </c>
       <c r="B10" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>553491.6787896904</v>
+        <v>553492</v>
       </c>
       <c r="R10" t="n">
-        <v>6704920.908280238</v>
+        <v>6704921</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -4367,7 +4367,7 @@
         <v>109536413</v>
       </c>
       <c r="B34" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4410,10 +4410,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>553505.9765261939</v>
+        <v>553506</v>
       </c>
       <c r="R34" t="n">
-        <v>6705457.07394894</v>
+        <v>6705457</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -6052,7 +6052,7 @@
         <v>112254000</v>
       </c>
       <c r="B49" t="n">
-        <v>56461</v>
+        <v>57478</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>112253990</v>
       </c>
       <c r="B78" t="n">
-        <v>56461</v>
+        <v>57478</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9997,7 +9997,7 @@
         <v>112249635</v>
       </c>
       <c r="B86" t="n">
-        <v>56461</v>
+        <v>57478</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10036,14 +10036,14 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Morkullbergets naturreservat (Morkullbergets naturreservat), Dlr</t>
+          <t>Morkullbergets naturreservat, Morkullbergets naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
         <v>553482</v>
       </c>
       <c r="R86" t="n">
-        <v>6705517</v>
+        <v>6705518</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10550,7 +10550,7 @@
         <v>112253999</v>
       </c>
       <c r="B91" t="n">
-        <v>56461</v>
+        <v>57478</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>553502</v>
+        <v>553501</v>
       </c>
       <c r="R91" t="n">
         <v>6704909</v>
@@ -11175,7 +11175,7 @@
         <v>112253993</v>
       </c>
       <c r="B97" t="n">
-        <v>56461</v>
+        <v>57478</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>112326464</v>
       </c>
       <c r="B116" t="n">
-        <v>56461</v>
+        <v>57478</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>

--- a/artfynd/A 18040-2021 artfynd.xlsx
+++ b/artfynd/A 18040-2021 artfynd.xlsx
@@ -1361,7 +1361,7 @@
         <v>109652943</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>109653351</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>109666258</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>109536413</v>
       </c>
       <c r="B34" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>112254000</v>
       </c>
       <c r="B49" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>112253990</v>
       </c>
       <c r="B78" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9997,7 +9997,7 @@
         <v>112249635</v>
       </c>
       <c r="B86" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>112253999</v>
       </c>
       <c r="B91" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>112253993</v>
       </c>
       <c r="B97" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>112326464</v>
       </c>
       <c r="B116" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>

--- a/artfynd/A 18040-2021 artfynd.xlsx
+++ b/artfynd/A 18040-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY121"/>
+  <dimension ref="A1:AY120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1729,10 +1729,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>109536801</v>
+        <v>112254012</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
+        <v>96783</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1763,20 +1763,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Morkullbergets naturreservat, Dlr</t>
+          <t>Morkullberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>553479.7989116225</v>
+        <v>553479</v>
       </c>
       <c r="R11" t="n">
-        <v>6705223.480163005</v>
+        <v>6705223</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1800,22 +1799,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-05-26</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>18:35</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-05-26</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>18:35</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,7 +1824,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Philipp Weiss, fanny westling</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -7334,10 +7323,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>112254012</v>
+        <v>112253987</v>
       </c>
       <c r="B61" t="n">
-        <v>96783</v>
+        <v>89594</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7346,25 +7335,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7374,10 +7363,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>553479</v>
+        <v>553525</v>
       </c>
       <c r="R61" t="n">
-        <v>6705223</v>
+        <v>6705418</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7436,10 +7425,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>112253987</v>
+        <v>112253994</v>
       </c>
       <c r="B62" t="n">
-        <v>89594</v>
+        <v>96783</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7448,25 +7437,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7476,10 +7465,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>553525</v>
+        <v>553513</v>
       </c>
       <c r="R62" t="n">
-        <v>6705418</v>
+        <v>6705290</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7538,7 +7527,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>112253994</v>
+        <v>112254011</v>
       </c>
       <c r="B63" t="n">
         <v>96783</v>
@@ -7578,10 +7567,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>553513</v>
+        <v>553479</v>
       </c>
       <c r="R63" t="n">
-        <v>6705290</v>
+        <v>6704917</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7640,7 +7629,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>112254011</v>
+        <v>112254025</v>
       </c>
       <c r="B64" t="n">
         <v>96783</v>
@@ -7680,10 +7669,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>553479</v>
+        <v>553447</v>
       </c>
       <c r="R64" t="n">
-        <v>6704917</v>
+        <v>6704809</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7742,7 +7731,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>112254025</v>
+        <v>112254037</v>
       </c>
       <c r="B65" t="n">
         <v>96783</v>
@@ -7782,10 +7771,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>553447</v>
+        <v>553386</v>
       </c>
       <c r="R65" t="n">
-        <v>6704809</v>
+        <v>6704753</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7844,7 +7833,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>112254037</v>
+        <v>112254006</v>
       </c>
       <c r="B66" t="n">
         <v>96783</v>
@@ -7877,17 +7866,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>553386</v>
+        <v>553489</v>
       </c>
       <c r="R66" t="n">
-        <v>6704753</v>
+        <v>6704972</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7928,6 +7929,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7946,7 +7948,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>112254006</v>
+        <v>112254021</v>
       </c>
       <c r="B67" t="n">
         <v>96783</v>
@@ -7989,7 +7991,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
@@ -7998,10 +8004,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>553489</v>
+        <v>553450</v>
       </c>
       <c r="R67" t="n">
-        <v>6704972</v>
+        <v>6705143</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -8061,7 +8067,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>112254021</v>
+        <v>112254016</v>
       </c>
       <c r="B68" t="n">
         <v>96783</v>
@@ -8094,33 +8100,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>553450</v>
+        <v>553476</v>
       </c>
       <c r="R68" t="n">
-        <v>6705143</v>
+        <v>6704913</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -8161,7 +8151,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8180,7 +8169,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>112254016</v>
+        <v>112253986</v>
       </c>
       <c r="B69" t="n">
         <v>96783</v>
@@ -8213,17 +8202,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>553476</v>
+        <v>553531</v>
       </c>
       <c r="R69" t="n">
-        <v>6704913</v>
+        <v>6705311</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -8264,6 +8265,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8282,7 +8284,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>112253986</v>
+        <v>112253995</v>
       </c>
       <c r="B70" t="n">
         <v>96783</v>
@@ -8317,7 +8319,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8334,10 +8336,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>553531</v>
+        <v>553512</v>
       </c>
       <c r="R70" t="n">
-        <v>6705311</v>
+        <v>6705338</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -8397,7 +8399,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>112253995</v>
+        <v>112254026</v>
       </c>
       <c r="B71" t="n">
         <v>96783</v>
@@ -8430,29 +8432,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>553512</v>
+        <v>553439</v>
       </c>
       <c r="R71" t="n">
-        <v>6705338</v>
+        <v>6705097</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8493,7 +8483,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8512,10 +8501,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>112254026</v>
+        <v>112253978</v>
       </c>
       <c r="B72" t="n">
-        <v>96783</v>
+        <v>89594</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8524,25 +8513,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8552,10 +8541,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>553439</v>
+        <v>553546</v>
       </c>
       <c r="R72" t="n">
-        <v>6705097</v>
+        <v>6705297</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8614,10 +8603,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>112253978</v>
+        <v>112254009</v>
       </c>
       <c r="B73" t="n">
-        <v>89594</v>
+        <v>96783</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8626,38 +8615,50 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>553546</v>
+        <v>553483</v>
       </c>
       <c r="R73" t="n">
-        <v>6705297</v>
+        <v>6704957</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8698,6 +8699,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8716,10 +8718,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>112254009</v>
+        <v>112253991</v>
       </c>
       <c r="B74" t="n">
-        <v>96783</v>
+        <v>8387</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8728,50 +8730,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>553483</v>
+        <v>553522</v>
       </c>
       <c r="R74" t="n">
-        <v>6704957</v>
+        <v>6705362</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8812,7 +8802,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8831,10 +8820,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>112253991</v>
+        <v>112254015</v>
       </c>
       <c r="B75" t="n">
-        <v>8387</v>
+        <v>5145</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8847,34 +8836,43 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>553522</v>
+        <v>553476</v>
       </c>
       <c r="R75" t="n">
-        <v>6705362</v>
+        <v>6704913</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8915,6 +8913,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8933,10 +8932,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>112254015</v>
+        <v>112254047</v>
       </c>
       <c r="B76" t="n">
-        <v>5145</v>
+        <v>96783</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8945,47 +8944,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>553476</v>
+        <v>553343</v>
       </c>
       <c r="R76" t="n">
-        <v>6704913</v>
+        <v>6704939</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -9026,7 +9016,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -9045,10 +9034,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>112254047</v>
+        <v>112253990</v>
       </c>
       <c r="B77" t="n">
-        <v>96783</v>
+        <v>57481</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9057,38 +9046,46 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>553343</v>
+        <v>553523</v>
       </c>
       <c r="R77" t="n">
-        <v>6704939</v>
+        <v>6705360</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -9121,6 +9118,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9147,10 +9149,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>112253990</v>
+        <v>112254023</v>
       </c>
       <c r="B78" t="n">
-        <v>57481</v>
+        <v>89594</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9163,42 +9165,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>553523</v>
+        <v>553449</v>
       </c>
       <c r="R78" t="n">
-        <v>6705360</v>
+        <v>6705492</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -9231,11 +9225,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2023-09-22</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9262,10 +9251,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>112254023</v>
+        <v>112253992</v>
       </c>
       <c r="B79" t="n">
-        <v>89594</v>
+        <v>96783</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9274,38 +9263,54 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>553449</v>
+        <v>553517</v>
       </c>
       <c r="R79" t="n">
-        <v>6705492</v>
+        <v>6705425</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -9346,6 +9351,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -9364,10 +9370,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>112253992</v>
+        <v>112254020</v>
       </c>
       <c r="B80" t="n">
-        <v>96783</v>
+        <v>89934</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9380,50 +9386,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>553517</v>
+        <v>553455</v>
       </c>
       <c r="R80" t="n">
-        <v>6705425</v>
+        <v>6705497</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -9483,10 +9473,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>112254020</v>
+        <v>112254010</v>
       </c>
       <c r="B81" t="n">
-        <v>89934</v>
+        <v>89113</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9495,25 +9485,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2062</v>
+        <v>256703</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9523,10 +9513,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>553455</v>
+        <v>553481</v>
       </c>
       <c r="R81" t="n">
-        <v>6705497</v>
+        <v>6705395</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -9567,7 +9557,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9586,10 +9575,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>112254010</v>
+        <v>112254029</v>
       </c>
       <c r="B82" t="n">
-        <v>89113</v>
+        <v>96783</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9598,25 +9587,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>256703</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9626,10 +9615,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>553481</v>
+        <v>553417</v>
       </c>
       <c r="R82" t="n">
-        <v>6705395</v>
+        <v>6704775</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9688,10 +9677,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>112254029</v>
+        <v>112254005</v>
       </c>
       <c r="B83" t="n">
-        <v>96783</v>
+        <v>89558</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9700,25 +9689,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9728,10 +9717,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>553417</v>
+        <v>553494</v>
       </c>
       <c r="R83" t="n">
-        <v>6704775</v>
+        <v>6705017</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9790,10 +9779,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>112254005</v>
+        <v>112254001</v>
       </c>
       <c r="B84" t="n">
-        <v>89558</v>
+        <v>96783</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9802,25 +9791,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9830,10 +9819,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>553494</v>
+        <v>553497</v>
       </c>
       <c r="R84" t="n">
-        <v>6705017</v>
+        <v>6705035</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9892,10 +9881,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>112254001</v>
+        <v>112249635</v>
       </c>
       <c r="B85" t="n">
-        <v>96783</v>
+        <v>57481</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9904,41 +9893,47 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Morkullberget, Dlr</t>
+          <t>Morkullbergets naturreservat, Morkullbergets naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>553497</v>
+        <v>553482</v>
       </c>
       <c r="R85" t="n">
-        <v>6705035</v>
+        <v>6705518</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9965,9 +9960,24 @@
           <t>2023-09-22</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9982,22 +9992,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Philipp Weiss, fanny westling</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>112249635</v>
+        <v>112254035</v>
       </c>
       <c r="B86" t="n">
-        <v>57481</v>
+        <v>89594</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10010,43 +10020,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Morkullbergets naturreservat, Morkullbergets naturreservat, Dlr</t>
+          <t>Morkullberget, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>553482</v>
+        <v>553389</v>
       </c>
       <c r="R86" t="n">
-        <v>6705518</v>
+        <v>6704754</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10073,24 +10077,9 @@
           <t>2023-09-22</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2023-09-22</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10105,22 +10094,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t>Philipp Weiss, fanny westling</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>112254035</v>
+        <v>112254049</v>
       </c>
       <c r="B87" t="n">
-        <v>89594</v>
+        <v>96783</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10129,25 +10118,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10157,10 +10146,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>553389</v>
+        <v>553333</v>
       </c>
       <c r="R87" t="n">
-        <v>6704754</v>
+        <v>6704880</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -10219,7 +10208,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>112254049</v>
+        <v>112254022</v>
       </c>
       <c r="B88" t="n">
         <v>96783</v>
@@ -10252,17 +10241,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>553333</v>
+        <v>553450</v>
       </c>
       <c r="R88" t="n">
-        <v>6704880</v>
+        <v>6705147</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -10303,6 +10304,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -10321,7 +10323,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>112254022</v>
+        <v>112253977</v>
       </c>
       <c r="B89" t="n">
         <v>96783</v>
@@ -10354,17 +10356,13 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
@@ -10373,10 +10371,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>553450</v>
+        <v>553575</v>
       </c>
       <c r="R89" t="n">
-        <v>6705147</v>
+        <v>6705296</v>
       </c>
       <c r="S89" t="n">
         <v>15</v>
@@ -10436,10 +10434,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>112253977</v>
+        <v>112253999</v>
       </c>
       <c r="B90" t="n">
-        <v>96783</v>
+        <v>57481</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10448,35 +10446,35 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -10484,10 +10482,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>553575</v>
+        <v>553501</v>
       </c>
       <c r="R90" t="n">
-        <v>6705296</v>
+        <v>6704909</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -10522,13 +10520,17 @@
           <t>2023-09-22</t>
         </is>
       </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -10547,10 +10549,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>112253999</v>
+        <v>112253981</v>
       </c>
       <c r="B91" t="n">
-        <v>57481</v>
+        <v>89594</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10563,42 +10565,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>553501</v>
+        <v>553541</v>
       </c>
       <c r="R91" t="n">
-        <v>6704909</v>
+        <v>6705249</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -10631,11 +10625,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2023-09-22</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10662,10 +10651,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>112253981</v>
+        <v>112253996</v>
       </c>
       <c r="B92" t="n">
-        <v>89594</v>
+        <v>96783</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10674,25 +10663,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10702,10 +10691,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>553541</v>
+        <v>553511</v>
       </c>
       <c r="R92" t="n">
-        <v>6705249</v>
+        <v>6705107</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -10764,7 +10753,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>112253996</v>
+        <v>112254046</v>
       </c>
       <c r="B93" t="n">
         <v>96783</v>
@@ -10804,10 +10793,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>553511</v>
+        <v>553347</v>
       </c>
       <c r="R93" t="n">
-        <v>6705107</v>
+        <v>6704930</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -10866,7 +10855,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>112254046</v>
+        <v>112254014</v>
       </c>
       <c r="B94" t="n">
         <v>96783</v>
@@ -10906,10 +10895,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>553347</v>
+        <v>553479</v>
       </c>
       <c r="R94" t="n">
-        <v>6704930</v>
+        <v>6705174</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -10968,7 +10957,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>112254014</v>
+        <v>112254013</v>
       </c>
       <c r="B95" t="n">
         <v>96783</v>
@@ -11011,7 +11000,7 @@
         <v>553479</v>
       </c>
       <c r="R95" t="n">
-        <v>6705174</v>
+        <v>6705228</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -11070,10 +11059,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>112254013</v>
+        <v>112253993</v>
       </c>
       <c r="B96" t="n">
-        <v>96783</v>
+        <v>57481</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11082,38 +11071,46 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>553479</v>
+        <v>553514</v>
       </c>
       <c r="R96" t="n">
-        <v>6705228</v>
+        <v>6705442</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -11146,6 +11143,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11172,10 +11174,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>112253993</v>
+        <v>112254002</v>
       </c>
       <c r="B97" t="n">
-        <v>57481</v>
+        <v>96783</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11184,46 +11186,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>553514</v>
+        <v>553497</v>
       </c>
       <c r="R97" t="n">
-        <v>6705442</v>
+        <v>6705280</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -11256,11 +11250,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2023-09-22</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11287,10 +11276,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>112254002</v>
+        <v>112254031</v>
       </c>
       <c r="B98" t="n">
-        <v>96783</v>
+        <v>5145</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11299,38 +11288,47 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>553497</v>
+        <v>553400</v>
       </c>
       <c r="R98" t="n">
-        <v>6705280</v>
+        <v>6704775</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -11371,6 +11369,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11389,10 +11388,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>112254031</v>
+        <v>112254032</v>
       </c>
       <c r="B99" t="n">
-        <v>5145</v>
+        <v>89594</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11401,47 +11400,38 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>553400</v>
+        <v>553397</v>
       </c>
       <c r="R99" t="n">
-        <v>6704775</v>
+        <v>6705068</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -11482,7 +11472,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -11501,10 +11490,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>112254032</v>
+        <v>112254044</v>
       </c>
       <c r="B100" t="n">
-        <v>89594</v>
+        <v>96783</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11513,38 +11502,50 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>553397</v>
+        <v>553351</v>
       </c>
       <c r="R100" t="n">
-        <v>6705068</v>
+        <v>6704849</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>
@@ -11585,6 +11586,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11603,10 +11605,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>112254044</v>
+        <v>112253988</v>
       </c>
       <c r="B101" t="n">
-        <v>96783</v>
+        <v>90034</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11619,46 +11621,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>553351</v>
+        <v>553525</v>
       </c>
       <c r="R101" t="n">
-        <v>6704849</v>
+        <v>6705427</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -11699,7 +11689,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11718,10 +11707,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>112253988</v>
+        <v>112254028</v>
       </c>
       <c r="B102" t="n">
-        <v>90034</v>
+        <v>89594</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11730,25 +11719,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11758,10 +11747,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>553525</v>
+        <v>553418</v>
       </c>
       <c r="R102" t="n">
-        <v>6705427</v>
+        <v>6705049</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -11820,10 +11809,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>112254028</v>
+        <v>112253998</v>
       </c>
       <c r="B103" t="n">
-        <v>89594</v>
+        <v>96783</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11832,25 +11821,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11860,10 +11849,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>553418</v>
+        <v>553506</v>
       </c>
       <c r="R103" t="n">
-        <v>6705049</v>
+        <v>6705290</v>
       </c>
       <c r="S103" t="n">
         <v>15</v>
@@ -11922,7 +11911,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>112253998</v>
+        <v>112254052</v>
       </c>
       <c r="B104" t="n">
         <v>96783</v>
@@ -11955,17 +11944,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>553506</v>
+        <v>553330</v>
       </c>
       <c r="R104" t="n">
-        <v>6705290</v>
+        <v>6704878</v>
       </c>
       <c r="S104" t="n">
         <v>15</v>
@@ -12006,6 +12007,7 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -12024,7 +12026,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>112254052</v>
+        <v>112254045</v>
       </c>
       <c r="B105" t="n">
         <v>96783</v>
@@ -12057,29 +12059,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Morkullberget, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>553330</v>
+        <v>553351</v>
       </c>
       <c r="R105" t="n">
-        <v>6704878</v>
+        <v>6704833</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -12120,7 +12110,6 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -12139,7 +12128,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>112254045</v>
+        <v>112254039</v>
       </c>
       <c r="B106" t="n">
         <v>96783</v>
@@ -12179,10 +12168,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>553351</v>
+        <v>553361</v>
       </c>
       <c r="R106" t="n">
-        <v>6704833</v>
+        <v>6704802</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -12241,7 +12230,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>112254039</v>
+        <v>112248365</v>
       </c>
       <c r="B107" t="n">
         <v>96783</v>
@@ -12275,19 +12264,20 @@
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Morkullberget, Dlr</t>
+          <t>Morkullbergets naturreservat (Morkullbergets naturreservat), Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>553361</v>
+        <v>553493</v>
       </c>
       <c r="R107" t="n">
-        <v>6704802</v>
+        <v>6705276</v>
       </c>
       <c r="S107" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12314,9 +12304,19 @@
           <t>2023-09-22</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12331,19 +12331,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Philipp Weiss, fanny westling</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>112248365</v>
+        <v>112248387</v>
       </c>
       <c r="B108" t="n">
         <v>96783</v>
@@ -12384,10 +12384,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>553493</v>
+        <v>553501</v>
       </c>
       <c r="R108" t="n">
-        <v>6705276</v>
+        <v>6705280</v>
       </c>
       <c r="S108" t="n">
         <v>1</v>
@@ -12456,7 +12456,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>112248387</v>
+        <v>112326482</v>
       </c>
       <c r="B109" t="n">
         <v>96783</v>
@@ -12490,20 +12490,23 @@
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Morkullbergets naturreservat (Morkullbergets naturreservat), Dlr</t>
+          <t>Amshyttan, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>553501</v>
+        <v>553444</v>
       </c>
       <c r="R109" t="n">
-        <v>6705280</v>
+        <v>6705045</v>
       </c>
       <c r="S109" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12530,27 +12533,18 @@
           <t>2023-09-22</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2023-09-22</t>
         </is>
       </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -12569,10 +12563,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>112326482</v>
+        <v>112249511</v>
       </c>
       <c r="B110" t="n">
-        <v>96783</v>
+        <v>90034</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12585,41 +12579,38 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Amshyttan, Dlr</t>
+          <t>Morkullbergets naturreservat (Morkullbergets naturreservat), Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>553444</v>
+        <v>553517</v>
       </c>
       <c r="R110" t="n">
-        <v>6705045</v>
+        <v>6705424</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12646,18 +12637,27 @@
           <t>2023-09-22</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2023-09-22</t>
         </is>
       </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -12676,10 +12676,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>112249511</v>
+        <v>112326437</v>
       </c>
       <c r="B111" t="n">
-        <v>90034</v>
+        <v>96783</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12692,38 +12692,41 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Morkullbergets naturreservat (Morkullbergets naturreservat), Dlr</t>
+          <t>Amshyttan, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>553517</v>
+        <v>553404</v>
       </c>
       <c r="R111" t="n">
-        <v>6705424</v>
+        <v>6705030</v>
       </c>
       <c r="S111" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12750,27 +12753,18 @@
           <t>2023-09-22</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2023-09-22</t>
         </is>
       </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12789,7 +12783,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>112326437</v>
+        <v>112326491</v>
       </c>
       <c r="B112" t="n">
         <v>96783</v>
@@ -12833,10 +12827,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>553404</v>
+        <v>553456</v>
       </c>
       <c r="R112" t="n">
-        <v>6705030</v>
+        <v>6704987</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12896,10 +12890,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>112326491</v>
+        <v>112337718</v>
       </c>
       <c r="B113" t="n">
-        <v>96783</v>
+        <v>89875</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12908,45 +12902,42 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Amshyttan, Dlr</t>
+          <t>Flyttjesundet (Flyttjesundet), Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>553456</v>
+        <v>553390</v>
       </c>
       <c r="R113" t="n">
-        <v>6704987</v>
+        <v>6704781</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12970,12 +12961,22 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2023-05-30</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2023-05-30</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12984,29 +12985,28 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>112337718</v>
+        <v>112326426</v>
       </c>
       <c r="B114" t="n">
-        <v>89875</v>
+        <v>96783</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13015,42 +13015,45 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Flyttjesundet (Flyttjesundet), Dlr</t>
+          <t>Amshyttan, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>553390</v>
+        <v>553407</v>
       </c>
       <c r="R114" t="n">
-        <v>6704781</v>
+        <v>6705043</v>
       </c>
       <c r="S114" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13074,22 +13077,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2023-05-30</t>
-        </is>
-      </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>20:16</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2023-05-30</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>20:16</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13098,28 +13091,29 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>112326426</v>
+        <v>112326464</v>
       </c>
       <c r="B115" t="n">
-        <v>96783</v>
+        <v>57481</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13128,31 +13122,31 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -13160,10 +13154,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>553407</v>
+        <v>553445</v>
       </c>
       <c r="R115" t="n">
-        <v>6705043</v>
+        <v>6705069</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13198,13 +13192,17 @@
           <t>2023-09-22</t>
         </is>
       </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -13223,10 +13221,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>112326464</v>
+        <v>112248468</v>
       </c>
       <c r="B116" t="n">
-        <v>57481</v>
+        <v>96783</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13235,45 +13233,42 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Amshyttan, Dlr</t>
+          <t>Morkullbergets naturreservat (Morkullbergets naturreservat), Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>553445</v>
+        <v>553472</v>
       </c>
       <c r="R116" t="n">
-        <v>6705069</v>
+        <v>6705237</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13300,14 +13295,19 @@
           <t>2023-09-22</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2023-09-22</t>
         </is>
       </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13334,7 +13334,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>112248468</v>
+        <v>112248494</v>
       </c>
       <c r="B117" t="n">
         <v>96783</v>
@@ -13375,10 +13375,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>553472</v>
+        <v>553470</v>
       </c>
       <c r="R117" t="n">
-        <v>6705237</v>
+        <v>6705210</v>
       </c>
       <c r="S117" t="n">
         <v>1</v>
@@ -13447,14 +13447,14 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>112248494</v>
+        <v>112248564</v>
       </c>
       <c r="B118" t="n">
-        <v>96783</v>
+        <v>91288</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -13463,35 +13463,37 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>1179</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Morkullbergets naturreservat (Morkullbergets naturreservat), Dlr</t>
+          <t>Morkullbergets naturreservat, Morkullbergets naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>553470</v>
+        <v>553474</v>
       </c>
       <c r="R118" t="n">
-        <v>6705210</v>
+        <v>6705181</v>
       </c>
       <c r="S118" t="n">
         <v>1</v>
@@ -13536,12 +13538,18 @@
           <t>13:47</t>
         </is>
       </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Resipunat på mossbevuxen granlåga</t>
+        </is>
+      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -13560,37 +13568,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>112248564</v>
+        <v>112253984</v>
       </c>
       <c r="B119" t="n">
-        <v>91288</v>
+        <v>89979</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1179</v>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Gräddticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13599,17 +13602,17 @@
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Morkullbergets naturreservat, Morkullbergets naturreservat, Dlr</t>
+          <t>Morkullberget, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>553474</v>
+        <v>553540</v>
       </c>
       <c r="R119" t="n">
-        <v>6705181</v>
+        <v>6705286</v>
       </c>
       <c r="S119" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13636,24 +13639,9 @@
           <t>2023-09-22</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2023-09-22</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Resipunat på mossbevuxen granlåga</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13669,22 +13657,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t>Philipp Weiss, fanny westling</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>112253984</v>
+        <v>112326395</v>
       </c>
       <c r="B120" t="n">
-        <v>89979</v>
+        <v>96783</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13693,39 +13681,45 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Morkullberget, Dlr</t>
+          <t>Amshyttan, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>553540</v>
+        <v>553409</v>
       </c>
       <c r="R120" t="n">
-        <v>6705286</v>
+        <v>6705092</v>
       </c>
       <c r="S120" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13770,122 +13764,15 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Philipp Weiss, fanny westling</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" t="n">
-        <v>112326395</v>
-      </c>
-      <c r="B121" t="n">
-        <v>96783</v>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E121" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
-      <c r="P121" t="inlineStr">
-        <is>
-          <t>Amshyttan, Dlr</t>
-        </is>
-      </c>
-      <c r="Q121" t="n">
-        <v>553409</v>
-      </c>
-      <c r="R121" t="n">
-        <v>6705092</v>
-      </c>
-      <c r="S121" t="n">
-        <v>10</v>
-      </c>
-      <c r="T121" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U121" t="inlineStr">
-        <is>
-          <t>Hedemora</t>
-        </is>
-      </c>
-      <c r="V121" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W121" t="inlineStr">
-        <is>
-          <t>Husby</t>
-        </is>
-      </c>
-      <c r="Y121" t="inlineStr">
-        <is>
-          <t>2023-09-22</t>
-        </is>
-      </c>
-      <c r="AA121" t="inlineStr">
-        <is>
-          <t>2023-09-22</t>
-        </is>
-      </c>
-      <c r="AD121" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE121" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF121" t="inlineStr"/>
-      <c r="AG121" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT121" t="inlineStr"/>
-      <c r="AW121" t="inlineStr">
-        <is>
-          <t>fanny westling</t>
-        </is>
-      </c>
-      <c r="AX121" t="inlineStr">
-        <is>
-          <t>fanny westling</t>
-        </is>
-      </c>
-      <c r="AY121" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18040-2021 artfynd.xlsx
+++ b/artfynd/A 18040-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY233"/>
+  <dimension ref="A1:AY234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13776,50 +13776,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127314375</v>
+        <v>127314388</v>
       </c>
       <c r="B121" t="n">
-        <v>57654</v>
+        <v>91779</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>553537</v>
+        <v>553411</v>
       </c>
       <c r="R121" t="n">
-        <v>6705403</v>
+        <v>6705072</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13878,38 +13873,38 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127314407</v>
+        <v>127314375</v>
       </c>
       <c r="B122" t="n">
-        <v>98442</v>
+        <v>57654</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -13918,10 +13913,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>553477</v>
+        <v>553537</v>
       </c>
       <c r="R122" t="n">
-        <v>6705175</v>
+        <v>6705403</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13954,11 +13949,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>få synliga bladrosetter</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13985,45 +13975,50 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127314398</v>
+        <v>127314407</v>
       </c>
       <c r="B123" t="n">
-        <v>97320</v>
+        <v>98442</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>553472</v>
+        <v>553477</v>
       </c>
       <c r="R123" t="n">
-        <v>6705479</v>
+        <v>6705175</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14056,6 +14051,11 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>få synliga bladrosetter</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14082,32 +14082,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127314388</v>
+        <v>127314398</v>
       </c>
       <c r="B124" t="n">
-        <v>91779</v>
+        <v>97320</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1209</v>
+        <v>221945</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14117,10 +14117,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>553411</v>
+        <v>553472</v>
       </c>
       <c r="R124" t="n">
-        <v>6705072</v>
+        <v>6705479</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14276,47 +14276,38 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127314416</v>
+        <v>127314372</v>
       </c>
       <c r="B126" t="n">
-        <v>98442</v>
+        <v>57654</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -14325,10 +14316,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>553356</v>
+        <v>553488</v>
       </c>
       <c r="R126" t="n">
-        <v>6704786</v>
+        <v>6705460</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14361,11 +14352,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14392,7 +14378,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127314415</v>
+        <v>127314435</v>
       </c>
       <c r="B127" t="n">
         <v>98442</v>
@@ -14422,7 +14408,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -14441,10 +14427,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>553463</v>
+        <v>553476</v>
       </c>
       <c r="R127" t="n">
-        <v>6705155</v>
+        <v>6705068</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14481,7 +14467,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>4 blomstjälkar</t>
+          <t>12 blomstjälkar</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14508,7 +14494,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127314432</v>
+        <v>127314415</v>
       </c>
       <c r="B128" t="n">
         <v>98442</v>
@@ -14538,7 +14524,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -14546,16 +14532,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>553508</v>
+        <v>553463</v>
       </c>
       <c r="R128" t="n">
-        <v>6705194</v>
+        <v>6705155</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14588,6 +14579,11 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14614,38 +14610,47 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127314372</v>
+        <v>127314416</v>
       </c>
       <c r="B129" t="n">
-        <v>57654</v>
+        <v>98442</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -14654,10 +14659,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>553488</v>
+        <v>553356</v>
       </c>
       <c r="R129" t="n">
-        <v>6705460</v>
+        <v>6704786</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14690,6 +14695,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14716,7 +14726,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127314435</v>
+        <v>127314432</v>
       </c>
       <c r="B130" t="n">
         <v>98442</v>
@@ -14746,7 +14756,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -14754,21 +14764,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>553476</v>
+        <v>553508</v>
       </c>
       <c r="R130" t="n">
-        <v>6705068</v>
+        <v>6705194</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14801,11 +14806,6 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>12 blomstjälkar</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14832,32 +14832,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127314336</v>
+        <v>127314347</v>
       </c>
       <c r="B131" t="n">
-        <v>91683</v>
+        <v>91325</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14867,10 +14867,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>553429</v>
+        <v>553419</v>
       </c>
       <c r="R131" t="n">
-        <v>6705077</v>
+        <v>6705073</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14929,32 +14929,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127314341</v>
+        <v>127314336</v>
       </c>
       <c r="B132" t="n">
-        <v>91325</v>
+        <v>91683</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -15000,11 +15000,6 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15128,54 +15123,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127314465</v>
+        <v>127314341</v>
       </c>
       <c r="B134" t="n">
-        <v>98442</v>
+        <v>91325</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>553488</v>
+        <v>553429</v>
       </c>
       <c r="R134" t="n">
-        <v>6705263</v>
+        <v>6705077</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15208,6 +15194,11 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15234,54 +15225,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127314410</v>
+        <v>127314350</v>
       </c>
       <c r="B135" t="n">
-        <v>98442</v>
+        <v>91325</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>553422</v>
+        <v>553465</v>
       </c>
       <c r="R135" t="n">
-        <v>6705072</v>
+        <v>6705219</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15340,10 +15322,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127314452</v>
+        <v>127314468</v>
       </c>
       <c r="B136" t="n">
-        <v>98442</v>
+        <v>91912</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15351,48 +15333,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220787</v>
+        <v>1179</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Peck) Donk</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>553418</v>
+        <v>553482</v>
       </c>
       <c r="R136" t="n">
-        <v>6705084</v>
+        <v>6705183</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15425,6 +15393,11 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Återfynd</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15451,10 +15424,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127314468</v>
+        <v>127314452</v>
       </c>
       <c r="B137" t="n">
-        <v>91912</v>
+        <v>98442</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15462,34 +15435,48 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1179</v>
+        <v>220787</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>553482</v>
+        <v>553418</v>
       </c>
       <c r="R137" t="n">
-        <v>6705183</v>
+        <v>6705084</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15522,11 +15509,6 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Återfynd</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15553,45 +15535,54 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127314347</v>
+        <v>127314465</v>
       </c>
       <c r="B138" t="n">
-        <v>91325</v>
+        <v>98442</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>553419</v>
+        <v>553488</v>
       </c>
       <c r="R138" t="n">
-        <v>6705073</v>
+        <v>6705263</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15650,45 +15641,54 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127314350</v>
+        <v>127314410</v>
       </c>
       <c r="B139" t="n">
-        <v>91325</v>
+        <v>98442</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>553465</v>
+        <v>553422</v>
       </c>
       <c r="R139" t="n">
-        <v>6705219</v>
+        <v>6705072</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15853,53 +15853,59 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127314370</v>
+        <v>127314417</v>
       </c>
       <c r="B141" t="n">
-        <v>57654</v>
+        <v>98442</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>553311</v>
+        <v>553413</v>
       </c>
       <c r="R141" t="n">
-        <v>6704717</v>
+        <v>6704868</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15932,6 +15938,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15958,38 +15969,42 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127314473</v>
+        <v>127314442</v>
       </c>
       <c r="B142" t="n">
-        <v>57578</v>
+        <v>98442</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -15998,10 +16013,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>553415</v>
+        <v>553423</v>
       </c>
       <c r="R142" t="n">
-        <v>6705462</v>
+        <v>6704914</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16034,11 +16049,6 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Fjädrar på "slaktbord"</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16065,59 +16075,53 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127314417</v>
+        <v>127314370</v>
       </c>
       <c r="B143" t="n">
-        <v>98442</v>
+        <v>57654</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>553413</v>
+        <v>553311</v>
       </c>
       <c r="R143" t="n">
-        <v>6704868</v>
+        <v>6704717</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16150,11 +16154,6 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16181,42 +16180,38 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127314442</v>
+        <v>127314473</v>
       </c>
       <c r="B144" t="n">
-        <v>98442</v>
+        <v>57578</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -16225,10 +16220,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>553423</v>
+        <v>553415</v>
       </c>
       <c r="R144" t="n">
-        <v>6704914</v>
+        <v>6705462</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16261,6 +16256,11 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Fjädrar på "slaktbord"</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16287,7 +16287,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127314380</v>
+        <v>127314376</v>
       </c>
       <c r="B145" t="n">
         <v>57654</v>
@@ -16327,10 +16327,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>553479</v>
+        <v>553380</v>
       </c>
       <c r="R145" t="n">
-        <v>6705480</v>
+        <v>6704935</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16389,47 +16389,38 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127314424</v>
+        <v>127314380</v>
       </c>
       <c r="B146" t="n">
-        <v>98442</v>
+        <v>57654</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -16438,10 +16429,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>553422</v>
+        <v>553479</v>
       </c>
       <c r="R146" t="n">
-        <v>6704824</v>
+        <v>6705480</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16616,38 +16607,47 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127314376</v>
+        <v>127314424</v>
       </c>
       <c r="B148" t="n">
-        <v>57654</v>
+        <v>98442</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -16656,10 +16656,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>553380</v>
+        <v>553422</v>
       </c>
       <c r="R148" t="n">
-        <v>6704935</v>
+        <v>6704824</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16718,45 +16718,50 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127314342</v>
+        <v>127314405</v>
       </c>
       <c r="B149" t="n">
-        <v>91325</v>
+        <v>8447</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>553347</v>
+        <v>553521</v>
       </c>
       <c r="R149" t="n">
-        <v>6704783</v>
+        <v>6705364</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16815,59 +16820,45 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127314450</v>
+        <v>127314343</v>
       </c>
       <c r="B150" t="n">
-        <v>98442</v>
+        <v>91325</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>553340</v>
+        <v>553388</v>
       </c>
       <c r="R150" t="n">
-        <v>6704784</v>
+        <v>6704753</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16926,59 +16917,45 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127314411</v>
+        <v>127314342</v>
       </c>
       <c r="B151" t="n">
-        <v>98442</v>
+        <v>91325</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>553500</v>
+        <v>553347</v>
       </c>
       <c r="R151" t="n">
-        <v>6705175</v>
+        <v>6704783</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17037,7 +17014,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127314419</v>
+        <v>127314450</v>
       </c>
       <c r="B152" t="n">
         <v>98442</v>
@@ -17067,7 +17044,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -17086,10 +17063,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>553343</v>
+        <v>553340</v>
       </c>
       <c r="R152" t="n">
-        <v>6704786</v>
+        <v>6704784</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17122,11 +17099,6 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17153,38 +17125,47 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>127314405</v>
+        <v>127314419</v>
       </c>
       <c r="B153" t="n">
-        <v>8447</v>
+        <v>98442</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
@@ -17193,10 +17174,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>553521</v>
+        <v>553343</v>
       </c>
       <c r="R153" t="n">
-        <v>6705364</v>
+        <v>6704786</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17229,6 +17210,11 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17255,45 +17241,59 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127314343</v>
+        <v>127314411</v>
       </c>
       <c r="B154" t="n">
-        <v>91325</v>
+        <v>98442</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>553388</v>
+        <v>553500</v>
       </c>
       <c r="R154" t="n">
-        <v>6704753</v>
+        <v>6705175</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17352,38 +17352,47 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127314391</v>
+        <v>127314447</v>
       </c>
       <c r="B155" t="n">
-        <v>57657</v>
+        <v>98442</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
@@ -17392,10 +17401,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>553375</v>
+        <v>553387</v>
       </c>
       <c r="R155" t="n">
-        <v>6705433</v>
+        <v>6704938</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17428,11 +17437,6 @@
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17565,53 +17569,45 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127314374</v>
+        <v>127314385</v>
       </c>
       <c r="B157" t="n">
-        <v>57654</v>
+        <v>56953</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100049</v>
+        <v>100038</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>553523</v>
+        <v>553426</v>
       </c>
       <c r="R157" t="n">
-        <v>6705404</v>
+        <v>6704786</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17670,45 +17666,53 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127314385</v>
+        <v>127314374</v>
       </c>
       <c r="B158" t="n">
-        <v>56953</v>
+        <v>57654</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100038</v>
+        <v>100049</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>553426</v>
+        <v>553523</v>
       </c>
       <c r="R158" t="n">
-        <v>6704786</v>
+        <v>6705404</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17767,47 +17771,38 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127314447</v>
+        <v>127314391</v>
       </c>
       <c r="B159" t="n">
-        <v>98442</v>
+        <v>57657</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
@@ -17816,10 +17811,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>553387</v>
+        <v>553375</v>
       </c>
       <c r="R159" t="n">
-        <v>6704938</v>
+        <v>6705433</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17852,6 +17847,11 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17878,50 +17878,45 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127314362</v>
+        <v>127314387</v>
       </c>
       <c r="B160" t="n">
-        <v>4772</v>
+        <v>91779</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100299</v>
+        <v>1209</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>553526</v>
+        <v>553517</v>
       </c>
       <c r="R160" t="n">
-        <v>6705221</v>
+        <v>6705421</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17980,45 +17975,50 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127314387</v>
+        <v>127314362</v>
       </c>
       <c r="B161" t="n">
-        <v>91779</v>
+        <v>4772</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1209</v>
+        <v>100299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>553517</v>
+        <v>553526</v>
       </c>
       <c r="R161" t="n">
-        <v>6705421</v>
+        <v>6705221</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18077,7 +18077,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127314451</v>
+        <v>127314443</v>
       </c>
       <c r="B162" t="n">
         <v>98442</v>
@@ -18107,7 +18107,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -18115,21 +18115,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>553427</v>
+        <v>553338</v>
       </c>
       <c r="R162" t="n">
-        <v>6704914</v>
+        <v>6705039</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18188,7 +18183,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>127314448</v>
+        <v>127314451</v>
       </c>
       <c r="B163" t="n">
         <v>98442</v>
@@ -18237,10 +18232,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>553342</v>
+        <v>553427</v>
       </c>
       <c r="R163" t="n">
-        <v>6704852</v>
+        <v>6704914</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18299,7 +18294,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>127314443</v>
+        <v>127314448</v>
       </c>
       <c r="B164" t="n">
         <v>98442</v>
@@ -18329,7 +18324,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -18337,16 +18332,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>553338</v>
+        <v>553342</v>
       </c>
       <c r="R164" t="n">
-        <v>6705039</v>
+        <v>6704852</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18521,7 +18521,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>127314409</v>
+        <v>127314439</v>
       </c>
       <c r="B166" t="n">
         <v>98442</v>
@@ -18549,7 +18549,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr"/>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K166" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -18561,10 +18570,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>553478</v>
+        <v>553525</v>
       </c>
       <c r="R166" t="n">
-        <v>6705174</v>
+        <v>6705250</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18601,7 +18610,7 @@
       </c>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>få synliga bladrosetter</t>
+          <t>6 blomstjälkar</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18734,7 +18743,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>127314439</v>
+        <v>127314409</v>
       </c>
       <c r="B168" t="n">
         <v>98442</v>
@@ -18762,16 +18771,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I168" t="inlineStr"/>
       <c r="K168" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -18783,10 +18783,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>553525</v>
+        <v>553478</v>
       </c>
       <c r="R168" t="n">
-        <v>6705250</v>
+        <v>6705174</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18823,7 +18823,7 @@
       </c>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>6 blomstjälkar</t>
+          <t>få synliga bladrosetter</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18961,47 +18961,38 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>127314455</v>
+        <v>127314393</v>
       </c>
       <c r="B170" t="n">
-        <v>98442</v>
+        <v>57657</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
@@ -19010,10 +19001,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>553431</v>
+        <v>553521</v>
       </c>
       <c r="R170" t="n">
-        <v>6704842</v>
+        <v>6705364</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19050,7 +19041,7 @@
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>3 blomstjälkar</t>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19289,38 +19280,47 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127314393</v>
+        <v>127314455</v>
       </c>
       <c r="B173" t="n">
-        <v>57657</v>
+        <v>98442</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr"/>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
@@ -19329,10 +19329,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>553521</v>
+        <v>553431</v>
       </c>
       <c r="R173" t="n">
-        <v>6705364</v>
+        <v>6704842</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19369,7 +19369,7 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19396,50 +19396,45 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127314482</v>
+        <v>127314355</v>
       </c>
       <c r="B174" t="n">
-        <v>5176</v>
+        <v>91683</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>100526</v>
+        <v>2062</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P174" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>553322</v>
+        <v>553451</v>
       </c>
       <c r="R174" t="n">
-        <v>6704727</v>
+        <v>6705503</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19498,47 +19493,38 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127314438</v>
+        <v>127314482</v>
       </c>
       <c r="B175" t="n">
-        <v>98442</v>
+        <v>5176</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
@@ -19547,10 +19533,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>553407</v>
+        <v>553322</v>
       </c>
       <c r="R175" t="n">
-        <v>6704816</v>
+        <v>6704727</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19583,11 +19569,6 @@
       <c r="AA175" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19614,42 +19595,38 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>127314459</v>
+        <v>127314392</v>
       </c>
       <c r="B176" t="n">
-        <v>98442</v>
+        <v>57657</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
@@ -19658,10 +19635,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>553508</v>
+        <v>553395</v>
       </c>
       <c r="R176" t="n">
-        <v>6705196</v>
+        <v>6704765</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19694,6 +19671,11 @@
       <c r="AA176" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19720,10 +19702,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>127314355</v>
+        <v>127314438</v>
       </c>
       <c r="B177" t="n">
-        <v>91683</v>
+        <v>98442</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19731,34 +19713,48 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P177" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>553451</v>
+        <v>553407</v>
       </c>
       <c r="R177" t="n">
-        <v>6705503</v>
+        <v>6704816</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19791,6 +19787,11 @@
       <c r="AA177" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19817,38 +19818,42 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>127314392</v>
+        <v>127314459</v>
       </c>
       <c r="B178" t="n">
-        <v>57657</v>
+        <v>98442</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr"/>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
@@ -19857,10 +19862,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>553395</v>
+        <v>553508</v>
       </c>
       <c r="R178" t="n">
-        <v>6704765</v>
+        <v>6705196</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19893,11 +19898,6 @@
       <c r="AA178" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19924,38 +19924,38 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>127314378</v>
+        <v>127314484</v>
       </c>
       <c r="B179" t="n">
-        <v>57654</v>
+        <v>5176</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="M179" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
@@ -19964,10 +19964,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>553468</v>
+        <v>553430</v>
       </c>
       <c r="R179" t="n">
-        <v>6705210</v>
+        <v>6705087</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20026,38 +20026,47 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>127314484</v>
+        <v>127314413</v>
       </c>
       <c r="B180" t="n">
-        <v>5176</v>
+        <v>98442</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr"/>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
@@ -20066,10 +20075,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>553430</v>
+        <v>553349</v>
       </c>
       <c r="R180" t="n">
-        <v>6705087</v>
+        <v>6704994</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20102,6 +20111,11 @@
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>5 blomstjälkar</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20128,38 +20142,47 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>127314381</v>
+        <v>127314418</v>
       </c>
       <c r="B181" t="n">
-        <v>57654</v>
+        <v>98442</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr"/>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
@@ -20168,10 +20191,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>553468</v>
+        <v>553496</v>
       </c>
       <c r="R181" t="n">
-        <v>6705451</v>
+        <v>6705280</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20204,6 +20227,11 @@
       <c r="AA181" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20230,7 +20258,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127314418</v>
+        <v>127314430</v>
       </c>
       <c r="B182" t="n">
         <v>98442</v>
@@ -20268,21 +20296,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>553496</v>
+        <v>553358</v>
       </c>
       <c r="R182" t="n">
-        <v>6705280</v>
+        <v>6705058</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20315,11 +20338,6 @@
       <c r="AA182" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC182" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20346,47 +20364,38 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>127314413</v>
+        <v>127314381</v>
       </c>
       <c r="B183" t="n">
-        <v>98442</v>
+        <v>57654</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
@@ -20395,10 +20404,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>553349</v>
+        <v>553468</v>
       </c>
       <c r="R183" t="n">
-        <v>6704994</v>
+        <v>6705451</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20431,11 +20440,6 @@
       <c r="AA183" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>5 blomstjälkar</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -20462,42 +20466,38 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>127314430</v>
+        <v>127314378</v>
       </c>
       <c r="B184" t="n">
-        <v>98442</v>
+        <v>57654</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
@@ -20506,10 +20506,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>553358</v>
+        <v>553468</v>
       </c>
       <c r="R184" t="n">
-        <v>6705058</v>
+        <v>6705210</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20859,7 +20859,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>127314436</v>
+        <v>127314461</v>
       </c>
       <c r="B188" t="n">
         <v>98442</v>
@@ -20889,7 +20889,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -20897,21 +20897,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P188" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>553571</v>
+        <v>553335</v>
       </c>
       <c r="R188" t="n">
-        <v>6705315</v>
+        <v>6704846</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20944,11 +20939,6 @@
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC188" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20975,7 +20965,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>127314461</v>
+        <v>127314453</v>
       </c>
       <c r="B189" t="n">
         <v>98442</v>
@@ -21013,16 +21003,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P189" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>553335</v>
+        <v>553477</v>
       </c>
       <c r="R189" t="n">
-        <v>6704846</v>
+        <v>6705197</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21081,7 +21076,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>127314453</v>
+        <v>127314464</v>
       </c>
       <c r="B190" t="n">
         <v>98442</v>
@@ -21119,21 +21114,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P190" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>553477</v>
+        <v>553470</v>
       </c>
       <c r="R190" t="n">
-        <v>6705197</v>
+        <v>6705234</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21192,7 +21182,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>127314464</v>
+        <v>127314436</v>
       </c>
       <c r="B191" t="n">
         <v>98442</v>
@@ -21222,7 +21212,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -21230,16 +21220,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P191" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>553470</v>
+        <v>553571</v>
       </c>
       <c r="R191" t="n">
-        <v>6705234</v>
+        <v>6705315</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21272,6 +21267,11 @@
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21298,10 +21298,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>127314423</v>
+        <v>127314339</v>
       </c>
       <c r="B192" t="n">
-        <v>98442</v>
+        <v>91683</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21309,48 +21309,34 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J192" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>553338</v>
+        <v>553347</v>
       </c>
       <c r="R192" t="n">
-        <v>6704806</v>
+        <v>6704783</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21409,7 +21395,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>127314408</v>
+        <v>127314423</v>
       </c>
       <c r="B193" t="n">
         <v>98442</v>
@@ -21437,7 +21423,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K193" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -21449,10 +21444,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>553400</v>
+        <v>553338</v>
       </c>
       <c r="R193" t="n">
-        <v>6705072</v>
+        <v>6704806</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21485,11 +21480,6 @@
       <c r="AA193" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>få synliga bladrosetter</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21516,10 +21506,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>127314339</v>
+        <v>127314408</v>
       </c>
       <c r="B194" t="n">
-        <v>91683</v>
+        <v>98442</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21527,34 +21517,39 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>553347</v>
+        <v>553400</v>
       </c>
       <c r="R194" t="n">
-        <v>6704783</v>
+        <v>6705072</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21587,6 +21582,11 @@
       <c r="AA194" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>få synliga bladrosetter</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21727,50 +21727,45 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>127314325</v>
+        <v>127314389</v>
       </c>
       <c r="B196" t="n">
-        <v>5196</v>
+        <v>91621</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>105930</v>
+        <v>658</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>553508</v>
+        <v>553364</v>
       </c>
       <c r="R196" t="n">
-        <v>6705185</v>
+        <v>6704790</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21829,7 +21824,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>127314420</v>
+        <v>127314445</v>
       </c>
       <c r="B197" t="n">
         <v>98442</v>
@@ -21859,7 +21854,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -21869,7 +21864,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
@@ -21878,10 +21873,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>553426</v>
+        <v>553364</v>
       </c>
       <c r="R197" t="n">
-        <v>6704821</v>
+        <v>6704996</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21914,11 +21909,6 @@
       <c r="AA197" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC197" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21945,53 +21935,54 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>127314363</v>
+        <v>127314425</v>
       </c>
       <c r="B198" t="n">
-        <v>57817</v>
+        <v>98442</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr"/>
-      <c r="K198" t="inlineStr"/>
-      <c r="L198" t="inlineStr"/>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N198" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>553336</v>
+        <v>553466</v>
       </c>
       <c r="R198" t="n">
-        <v>6704944</v>
+        <v>6705077</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22050,7 +22041,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>127314445</v>
+        <v>127314429</v>
       </c>
       <c r="B199" t="n">
         <v>98442</v>
@@ -22080,7 +22071,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -22088,21 +22079,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P199" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>553364</v>
+        <v>553414</v>
       </c>
       <c r="R199" t="n">
-        <v>6704996</v>
+        <v>6704864</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22161,45 +22147,59 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127314389</v>
+        <v>127314420</v>
       </c>
       <c r="B200" t="n">
-        <v>91621</v>
+        <v>98442</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P200" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>553364</v>
+        <v>553426</v>
       </c>
       <c r="R200" t="n">
-        <v>6704790</v>
+        <v>6704821</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22232,6 +22232,11 @@
       <c r="AA200" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22462,54 +22467,53 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>127314425</v>
+        <v>127314363</v>
       </c>
       <c r="B203" t="n">
-        <v>98442</v>
+        <v>57817</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>553466</v>
+        <v>553336</v>
       </c>
       <c r="R203" t="n">
-        <v>6705077</v>
+        <v>6704944</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22568,42 +22572,38 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>127314429</v>
+        <v>127314325</v>
       </c>
       <c r="B204" t="n">
-        <v>98442</v>
+        <v>5196</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
@@ -22612,10 +22612,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>553414</v>
+        <v>553508</v>
       </c>
       <c r="R204" t="n">
-        <v>6704864</v>
+        <v>6705185</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22674,59 +22674,45 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>127314412</v>
+        <v>127314354</v>
       </c>
       <c r="B205" t="n">
-        <v>98442</v>
+        <v>91325</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J205" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>553337</v>
+        <v>553517</v>
       </c>
       <c r="R205" t="n">
-        <v>6704813</v>
+        <v>6705421</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22891,40 +22877,54 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>127314406</v>
+        <v>127314431</v>
       </c>
       <c r="B207" t="n">
-        <v>91732</v>
+        <v>98442</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P207" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>553517</v>
+        <v>553442</v>
       </c>
       <c r="R207" t="n">
-        <v>6705421</v>
+        <v>6705095</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22983,54 +22983,40 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>127314431</v>
+        <v>127314406</v>
       </c>
       <c r="B208" t="n">
-        <v>98442</v>
+        <v>91732</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J208" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>553442</v>
+        <v>553517</v>
       </c>
       <c r="R208" t="n">
-        <v>6705095</v>
+        <v>6705421</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23089,45 +23075,59 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>127314354</v>
+        <v>127314412</v>
       </c>
       <c r="B209" t="n">
-        <v>91325</v>
+        <v>98442</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P209" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>553517</v>
+        <v>553337</v>
       </c>
       <c r="R209" t="n">
-        <v>6705421</v>
+        <v>6704813</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23186,42 +23186,38 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>127314428</v>
+        <v>127314368</v>
       </c>
       <c r="B210" t="n">
-        <v>98442</v>
+        <v>57654</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I210" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J210" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr"/>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
@@ -23230,10 +23226,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>553336</v>
+        <v>553500</v>
       </c>
       <c r="R210" t="n">
-        <v>6704827</v>
+        <v>6705249</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23292,50 +23288,45 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>127314368</v>
+        <v>127314477</v>
       </c>
       <c r="B211" t="n">
-        <v>57654</v>
+        <v>92615</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
-      <c r="M211" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P211" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>553500</v>
+        <v>553371</v>
       </c>
       <c r="R211" t="n">
-        <v>6705249</v>
+        <v>6704731</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23368,6 +23359,11 @@
       <c r="AA211" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>Många gamla fruktkroppar i häxring</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -23394,38 +23390,42 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>127314480</v>
+        <v>127314428</v>
       </c>
       <c r="B212" t="n">
-        <v>5176</v>
+        <v>98442</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr"/>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
@@ -23434,10 +23434,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>553399</v>
+        <v>553336</v>
       </c>
       <c r="R212" t="n">
-        <v>6704947</v>
+        <v>6704827</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23496,48 +23496,51 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>127314477</v>
+        <v>127310539</v>
       </c>
       <c r="B213" t="n">
-        <v>92615</v>
+        <v>91537</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>4364</v>
+        <v>1106</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
+      <c r="N213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Morkullberget södra, Dlr</t>
+          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>553371</v>
+        <v>553483</v>
       </c>
       <c r="R213" t="n">
-        <v>6704731</v>
+        <v>6705051</v>
       </c>
       <c r="S213" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -23569,80 +23572,78 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC213" t="inlineStr">
-        <is>
-          <t>Många gamla fruktkroppar i häxring</t>
-        </is>
-      </c>
       <c r="AD213" t="b">
         <v>0</v>
       </c>
       <c r="AE213" t="b">
         <v>0</v>
       </c>
+      <c r="AF213" t="inlineStr"/>
       <c r="AG213" t="b">
         <v>0</v>
       </c>
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>127310539</v>
+        <v>127314480</v>
       </c>
       <c r="B214" t="n">
-        <v>91537</v>
+        <v>5176</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>1106</v>
+        <v>100526</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
-      <c r="J214" t="inlineStr"/>
-      <c r="K214" t="inlineStr"/>
-      <c r="N214" t="inlineStr"/>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
+          <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>553483</v>
+        <v>553399</v>
       </c>
       <c r="R214" t="n">
-        <v>6705051</v>
+        <v>6704947</v>
       </c>
       <c r="S214" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -23680,26 +23681,25 @@
       <c r="AE214" t="b">
         <v>0</v>
       </c>
-      <c r="AF214" t="inlineStr"/>
       <c r="AG214" t="b">
         <v>0</v>
       </c>
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>127314348</v>
+        <v>127314351</v>
       </c>
       <c r="B215" t="n">
         <v>91325</v>
@@ -23734,10 +23734,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>553499</v>
+        <v>553533</v>
       </c>
       <c r="R215" t="n">
-        <v>6705218</v>
+        <v>6705296</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -23796,7 +23796,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>127314351</v>
+        <v>127314348</v>
       </c>
       <c r="B216" t="n">
         <v>91325</v>
@@ -23831,10 +23831,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>553533</v>
+        <v>553499</v>
       </c>
       <c r="R216" t="n">
-        <v>6705296</v>
+        <v>6705218</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -23990,54 +23990,45 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>127314463</v>
+        <v>127314471</v>
       </c>
       <c r="B218" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J218" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>553433</v>
+        <v>553406</v>
       </c>
       <c r="R218" t="n">
-        <v>6704902</v>
+        <v>6705479</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24096,32 +24087,32 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127314394</v>
+        <v>127314337</v>
       </c>
       <c r="B219" t="n">
-        <v>97320</v>
+        <v>91683</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>221945</v>
+        <v>2062</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -24131,10 +24122,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>553498</v>
+        <v>553419</v>
       </c>
       <c r="R219" t="n">
-        <v>6705418</v>
+        <v>6705073</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24167,6 +24158,11 @@
       <c r="AA219" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>Eventuellt S. delicata</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -24193,47 +24189,38 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127314437</v>
+        <v>127314377</v>
       </c>
       <c r="B220" t="n">
-        <v>98442</v>
+        <v>57654</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J220" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr"/>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -24242,10 +24229,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>553333</v>
+        <v>553336</v>
       </c>
       <c r="R220" t="n">
-        <v>6704814</v>
+        <v>6704827</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24304,45 +24291,54 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>127314471</v>
+        <v>127314463</v>
       </c>
       <c r="B221" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>553406</v>
+        <v>553433</v>
       </c>
       <c r="R221" t="n">
-        <v>6705479</v>
+        <v>6704902</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24401,7 +24397,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>127314458</v>
+        <v>127314456</v>
       </c>
       <c r="B222" t="n">
         <v>98442</v>
@@ -24439,16 +24435,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P222" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>553526</v>
+        <v>553437</v>
       </c>
       <c r="R222" t="n">
-        <v>6705245</v>
+        <v>6704997</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24481,6 +24482,11 @@
       <c r="AA222" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -24507,10 +24513,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>127314337</v>
+        <v>127314422</v>
       </c>
       <c r="B223" t="n">
-        <v>91683</v>
+        <v>98442</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -24518,34 +24524,48 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>553419</v>
+        <v>553445</v>
       </c>
       <c r="R223" t="n">
-        <v>6705073</v>
+        <v>6704996</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24578,11 +24598,6 @@
       <c r="AA223" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC223" t="inlineStr">
-        <is>
-          <t>Eventuellt S. delicata</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -24609,7 +24624,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127314457</v>
+        <v>127314437</v>
       </c>
       <c r="B224" t="n">
         <v>98442</v>
@@ -24639,7 +24654,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -24647,16 +24662,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P224" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>553442</v>
+        <v>553333</v>
       </c>
       <c r="R224" t="n">
-        <v>6705078</v>
+        <v>6704814</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24715,7 +24735,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127314422</v>
+        <v>127314457</v>
       </c>
       <c r="B225" t="n">
         <v>98442</v>
@@ -24745,7 +24765,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -24753,21 +24773,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P225" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>553445</v>
+        <v>553442</v>
       </c>
       <c r="R225" t="n">
-        <v>6704996</v>
+        <v>6705078</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24826,7 +24841,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127314456</v>
+        <v>127314458</v>
       </c>
       <c r="B226" t="n">
         <v>98442</v>
@@ -24864,21 +24879,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P226" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>553437</v>
+        <v>553526</v>
       </c>
       <c r="R226" t="n">
-        <v>6704997</v>
+        <v>6705245</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24911,11 +24921,6 @@
       <c r="AA226" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC226" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -24942,50 +24947,45 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127314377</v>
+        <v>127314394</v>
       </c>
       <c r="B227" t="n">
-        <v>57654</v>
+        <v>97320</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>553336</v>
+        <v>553498</v>
       </c>
       <c r="R227" t="n">
-        <v>6704827</v>
+        <v>6705418</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25044,10 +25044,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127314326</v>
+        <v>127314479</v>
       </c>
       <c r="B228" t="n">
-        <v>5196</v>
+        <v>5176</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -25055,27 +25055,27 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
       <c r="M228" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
@@ -25084,10 +25084,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>553527</v>
+        <v>553496</v>
       </c>
       <c r="R228" t="n">
-        <v>6705221</v>
+        <v>6705218</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25146,10 +25146,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127314479</v>
+        <v>127314326</v>
       </c>
       <c r="B229" t="n">
-        <v>5176</v>
+        <v>5196</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -25157,27 +25157,27 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
       <c r="M229" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -25186,10 +25186,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>553496</v>
+        <v>553527</v>
       </c>
       <c r="R229" t="n">
-        <v>6705218</v>
+        <v>6705221</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25354,7 +25354,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>127314444</v>
+        <v>127314414</v>
       </c>
       <c r="B231" t="n">
         <v>98442</v>
@@ -25384,7 +25384,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -25392,16 +25392,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P231" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>553489</v>
+        <v>553341</v>
       </c>
       <c r="R231" t="n">
-        <v>6705294</v>
+        <v>6704994</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -25434,6 +25439,11 @@
       <c r="AA231" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -25460,38 +25470,42 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>127314371</v>
+        <v>127314444</v>
       </c>
       <c r="B232" t="n">
-        <v>57654</v>
+        <v>98442</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I232" t="inlineStr"/>
-      <c r="M232" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P232" t="inlineStr">
@@ -25500,10 +25514,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>553336</v>
+        <v>553489</v>
       </c>
       <c r="R232" t="n">
-        <v>6704723</v>
+        <v>6705294</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -25562,47 +25576,38 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>127314414</v>
+        <v>127314371</v>
       </c>
       <c r="B233" t="n">
-        <v>98442</v>
+        <v>57654</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J233" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr"/>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
@@ -25611,10 +25616,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>553341</v>
+        <v>553336</v>
       </c>
       <c r="R233" t="n">
-        <v>6704994</v>
+        <v>6704723</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -25649,11 +25654,6 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC233" t="inlineStr">
-        <is>
-          <t>4 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD233" t="b">
         <v>0</v>
       </c>
@@ -25675,6 +25675,109 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>127314486</v>
+      </c>
+      <c r="B234" t="n">
+        <v>91697</v>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>1505</v>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Kristallticka</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Skeletocutis stellae</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>(Pilát) Jean Keller</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr"/>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>Morkullberget södra, Dlr</t>
+        </is>
+      </c>
+      <c r="Q234" t="n">
+        <v>553465</v>
+      </c>
+      <c r="R234" t="n">
+        <v>6705219</v>
+      </c>
+      <c r="S234" t="n">
+        <v>10</v>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC234" t="inlineStr">
+        <is>
+          <t>Mycket finporig, resupinat fruktkropp. Tydlig doft av Skeletocutis. Blev smutsbrun efter tumning. Inget gelatinös skikt som finporing har. På murken granlåga tillsammans med gammal ullticka i grannaturskog med fler naturvårdsintressanta vedsvampar. Kommer att mikroskoperas.</t>
+        </is>
+      </c>
+      <c r="AD234" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE234" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF234" t="inlineStr"/>
+      <c r="AG234" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT234" t="inlineStr"/>
+      <c r="AW234" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX234" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY234" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18040-2021 artfynd.xlsx
+++ b/artfynd/A 18040-2021 artfynd.xlsx
@@ -15747,54 +15747,53 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127314441</v>
+        <v>127314370</v>
       </c>
       <c r="B140" t="n">
-        <v>98442</v>
+        <v>57654</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>553422</v>
+        <v>553311</v>
       </c>
       <c r="R140" t="n">
-        <v>6704986</v>
+        <v>6704717</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15853,47 +15852,38 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127314417</v>
+        <v>127314473</v>
       </c>
       <c r="B141" t="n">
-        <v>98442</v>
+        <v>57578</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -15902,10 +15892,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>553413</v>
+        <v>553415</v>
       </c>
       <c r="R141" t="n">
-        <v>6704868</v>
+        <v>6705462</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15942,7 +15932,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>3 blomstjälkar</t>
+          <t>Fjädrar på "slaktbord"</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15969,7 +15959,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127314442</v>
+        <v>127314441</v>
       </c>
       <c r="B142" t="n">
         <v>98442</v>
@@ -16013,10 +16003,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>553423</v>
+        <v>553422</v>
       </c>
       <c r="R142" t="n">
-        <v>6704914</v>
+        <v>6704986</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16075,53 +16065,59 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127314370</v>
+        <v>127314417</v>
       </c>
       <c r="B143" t="n">
-        <v>57654</v>
+        <v>98442</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>553311</v>
+        <v>553413</v>
       </c>
       <c r="R143" t="n">
-        <v>6704717</v>
+        <v>6704868</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16154,6 +16150,11 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16180,38 +16181,42 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127314473</v>
+        <v>127314442</v>
       </c>
       <c r="B144" t="n">
-        <v>57578</v>
+        <v>98442</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -16220,10 +16225,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>553415</v>
+        <v>553423</v>
       </c>
       <c r="R144" t="n">
-        <v>6705462</v>
+        <v>6704914</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16256,11 +16261,6 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>Fjädrar på "slaktbord"</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -19924,38 +19924,38 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>127314484</v>
+        <v>127314378</v>
       </c>
       <c r="B179" t="n">
-        <v>5176</v>
+        <v>57654</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="M179" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
@@ -19964,10 +19964,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>553430</v>
+        <v>553468</v>
       </c>
       <c r="R179" t="n">
-        <v>6705087</v>
+        <v>6705210</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20026,59 +20026,45 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>127314413</v>
+        <v>127314467</v>
       </c>
       <c r="B180" t="n">
-        <v>98442</v>
+        <v>105477</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>553349</v>
+        <v>553468</v>
       </c>
       <c r="R180" t="n">
-        <v>6704994</v>
+        <v>6705155</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20111,11 +20097,6 @@
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>5 blomstjälkar</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20142,47 +20123,38 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>127314418</v>
+        <v>127314381</v>
       </c>
       <c r="B181" t="n">
-        <v>98442</v>
+        <v>57654</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
@@ -20191,10 +20163,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>553496</v>
+        <v>553468</v>
       </c>
       <c r="R181" t="n">
-        <v>6705280</v>
+        <v>6705451</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20227,11 +20199,6 @@
       <c r="AA181" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20258,42 +20225,38 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127314430</v>
+        <v>127314484</v>
       </c>
       <c r="B182" t="n">
-        <v>98442</v>
+        <v>5176</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
@@ -20302,10 +20265,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>553358</v>
+        <v>553430</v>
       </c>
       <c r="R182" t="n">
-        <v>6705058</v>
+        <v>6705087</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20364,38 +20327,47 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>127314381</v>
+        <v>127314413</v>
       </c>
       <c r="B183" t="n">
-        <v>57654</v>
+        <v>98442</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr"/>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
@@ -20404,10 +20376,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>553468</v>
+        <v>553349</v>
       </c>
       <c r="R183" t="n">
-        <v>6705451</v>
+        <v>6704994</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20440,6 +20412,11 @@
       <c r="AA183" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>5 blomstjälkar</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -20466,38 +20443,47 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>127314378</v>
+        <v>127314418</v>
       </c>
       <c r="B184" t="n">
-        <v>57654</v>
+        <v>98442</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr"/>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
@@ -20506,10 +20492,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>553468</v>
+        <v>553496</v>
       </c>
       <c r="R184" t="n">
-        <v>6705210</v>
+        <v>6705280</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20542,6 +20528,11 @@
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20568,45 +20559,54 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>127314467</v>
+        <v>127314430</v>
       </c>
       <c r="B185" t="n">
-        <v>105477</v>
+        <v>98442</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P185" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>553468</v>
+        <v>553358</v>
       </c>
       <c r="R185" t="n">
-        <v>6705155</v>
+        <v>6705058</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -21824,47 +21824,38 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>127314445</v>
+        <v>127314379</v>
       </c>
       <c r="B197" t="n">
-        <v>98442</v>
+        <v>57654</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
@@ -21873,10 +21864,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>553364</v>
+        <v>553485</v>
       </c>
       <c r="R197" t="n">
-        <v>6704996</v>
+        <v>6705230</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21935,42 +21926,38 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>127314425</v>
+        <v>127314382</v>
       </c>
       <c r="B198" t="n">
-        <v>98442</v>
+        <v>57307</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>220787</v>
+        <v>100063</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
@@ -21979,10 +21966,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>553466</v>
+        <v>553494</v>
       </c>
       <c r="R198" t="n">
-        <v>6705077</v>
+        <v>6705461</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22041,54 +22028,53 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>127314429</v>
+        <v>127314363</v>
       </c>
       <c r="B199" t="n">
-        <v>98442</v>
+        <v>57817</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>553414</v>
+        <v>553336</v>
       </c>
       <c r="R199" t="n">
-        <v>6704864</v>
+        <v>6704944</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22147,47 +22133,38 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127314420</v>
+        <v>127314325</v>
       </c>
       <c r="B200" t="n">
-        <v>98442</v>
+        <v>5196</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -22196,10 +22173,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>553426</v>
+        <v>553508</v>
       </c>
       <c r="R200" t="n">
-        <v>6704821</v>
+        <v>6705185</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22232,11 +22209,6 @@
       <c r="AA200" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22263,38 +22235,47 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>127314379</v>
+        <v>127314445</v>
       </c>
       <c r="B201" t="n">
-        <v>57654</v>
+        <v>98442</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr"/>
-      <c r="M201" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
@@ -22303,10 +22284,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>553485</v>
+        <v>553364</v>
       </c>
       <c r="R201" t="n">
-        <v>6705230</v>
+        <v>6704996</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22365,38 +22346,42 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127314382</v>
+        <v>127314425</v>
       </c>
       <c r="B202" t="n">
-        <v>57307</v>
+        <v>98442</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>100063</v>
+        <v>220787</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr"/>
-      <c r="M202" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
@@ -22405,10 +22390,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>553494</v>
+        <v>553466</v>
       </c>
       <c r="R202" t="n">
-        <v>6705461</v>
+        <v>6705077</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22467,53 +22452,54 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>127314363</v>
+        <v>127314429</v>
       </c>
       <c r="B203" t="n">
-        <v>57817</v>
+        <v>98442</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr"/>
-      <c r="K203" t="inlineStr"/>
-      <c r="L203" t="inlineStr"/>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N203" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P203" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>553336</v>
+        <v>553414</v>
       </c>
       <c r="R203" t="n">
-        <v>6704944</v>
+        <v>6704864</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22572,38 +22558,47 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>127314325</v>
+        <v>127314420</v>
       </c>
       <c r="B204" t="n">
-        <v>5196</v>
+        <v>98442</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr"/>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
@@ -22612,10 +22607,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>553508</v>
+        <v>553426</v>
       </c>
       <c r="R204" t="n">
-        <v>6705185</v>
+        <v>6704821</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22648,6 +22643,11 @@
       <c r="AA204" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -25044,38 +25044,38 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127314479</v>
+        <v>127314371</v>
       </c>
       <c r="B228" t="n">
-        <v>5176</v>
+        <v>57654</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
       <c r="M228" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
@@ -25084,10 +25084,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>553496</v>
+        <v>553336</v>
       </c>
       <c r="R228" t="n">
-        <v>6705218</v>
+        <v>6704723</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25146,10 +25146,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127314326</v>
+        <v>127314479</v>
       </c>
       <c r="B229" t="n">
-        <v>5196</v>
+        <v>5176</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -25157,27 +25157,27 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
       <c r="M229" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -25186,10 +25186,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>553527</v>
+        <v>553496</v>
       </c>
       <c r="R229" t="n">
-        <v>6705221</v>
+        <v>6705218</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25248,42 +25248,38 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>127314440</v>
+        <v>127314326</v>
       </c>
       <c r="B230" t="n">
-        <v>98442</v>
+        <v>5196</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J230" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr"/>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
@@ -25292,10 +25288,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>553571</v>
+        <v>553527</v>
       </c>
       <c r="R230" t="n">
-        <v>6705297</v>
+        <v>6705221</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -25354,7 +25350,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>127314414</v>
+        <v>127314440</v>
       </c>
       <c r="B231" t="n">
         <v>98442</v>
@@ -25384,7 +25380,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -25392,21 +25388,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P231" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>553341</v>
+        <v>553571</v>
       </c>
       <c r="R231" t="n">
-        <v>6704994</v>
+        <v>6705297</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -25439,11 +25430,6 @@
       <c r="AA231" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC231" t="inlineStr">
-        <is>
-          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -25470,7 +25456,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>127314444</v>
+        <v>127314414</v>
       </c>
       <c r="B232" t="n">
         <v>98442</v>
@@ -25500,7 +25486,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -25508,16 +25494,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P232" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>553489</v>
+        <v>553341</v>
       </c>
       <c r="R232" t="n">
-        <v>6705294</v>
+        <v>6704994</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -25550,6 +25541,11 @@
       <c r="AA232" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -25576,38 +25572,42 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>127314371</v>
+        <v>127314444</v>
       </c>
       <c r="B233" t="n">
-        <v>57654</v>
+        <v>98442</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr"/>
-      <c r="M233" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
@@ -25616,10 +25616,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>553336</v>
+        <v>553489</v>
       </c>
       <c r="R233" t="n">
-        <v>6704723</v>
+        <v>6705294</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>

--- a/artfynd/A 18040-2021 artfynd.xlsx
+++ b/artfynd/A 18040-2021 artfynd.xlsx
@@ -13776,10 +13776,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127314388</v>
+        <v>127314407</v>
       </c>
       <c r="B121" t="n">
-        <v>91779</v>
+        <v>98443</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13787,34 +13787,39 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>553411</v>
+        <v>553477</v>
       </c>
       <c r="R121" t="n">
-        <v>6705072</v>
+        <v>6705175</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13847,6 +13852,11 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>få synliga bladrosetter</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13975,10 +13985,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127314407</v>
+        <v>127314388</v>
       </c>
       <c r="B123" t="n">
-        <v>98442</v>
+        <v>91780</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13986,39 +13996,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>553477</v>
+        <v>553411</v>
       </c>
       <c r="R123" t="n">
-        <v>6705175</v>
+        <v>6705072</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14051,11 +14056,6 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>få synliga bladrosetter</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14085,7 +14085,7 @@
         <v>127314398</v>
       </c>
       <c r="B124" t="n">
-        <v>97320</v>
+        <v>97321</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         <v>127314397</v>
       </c>
       <c r="B125" t="n">
-        <v>97320</v>
+        <v>97321</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14378,10 +14378,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127314435</v>
+        <v>127314416</v>
       </c>
       <c r="B127" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14408,7 +14408,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -14427,10 +14427,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>553476</v>
+        <v>553356</v>
       </c>
       <c r="R127" t="n">
-        <v>6705068</v>
+        <v>6704786</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14467,7 +14467,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>12 blomstjälkar</t>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14494,10 +14494,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127314415</v>
+        <v>127314432</v>
       </c>
       <c r="B128" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -14532,21 +14532,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>553463</v>
+        <v>553508</v>
       </c>
       <c r="R128" t="n">
-        <v>6705155</v>
+        <v>6705194</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14579,11 +14574,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14610,10 +14600,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127314416</v>
+        <v>127314435</v>
       </c>
       <c r="B129" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14640,7 +14630,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -14659,10 +14649,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>553356</v>
+        <v>553476</v>
       </c>
       <c r="R129" t="n">
-        <v>6704786</v>
+        <v>6705068</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14699,7 +14689,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>3 blomstjälkar</t>
+          <t>12 blomstjälkar</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14726,10 +14716,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127314432</v>
+        <v>127314415</v>
       </c>
       <c r="B130" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14756,7 +14746,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -14764,16 +14754,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>553508</v>
+        <v>553463</v>
       </c>
       <c r="R130" t="n">
-        <v>6705194</v>
+        <v>6705155</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14806,6 +14801,11 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14835,7 +14835,7 @@
         <v>127314347</v>
       </c>
       <c r="B131" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14932,7 +14932,7 @@
         <v>127314336</v>
       </c>
       <c r="B132" t="n">
-        <v>91683</v>
+        <v>91684</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15029,7 +15029,7 @@
         <v>127314345</v>
       </c>
       <c r="B133" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15126,7 +15126,7 @@
         <v>127314341</v>
       </c>
       <c r="B134" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15228,7 +15228,7 @@
         <v>127314350</v>
       </c>
       <c r="B135" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15325,7 +15325,7 @@
         <v>127314468</v>
       </c>
       <c r="B136" t="n">
-        <v>91912</v>
+        <v>91913</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>127314452</v>
       </c>
       <c r="B137" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>127314465</v>
       </c>
       <c r="B138" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15644,7 +15644,7 @@
         <v>127314410</v>
       </c>
       <c r="B139" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15747,10 +15747,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127314370</v>
+        <v>127314473</v>
       </c>
       <c r="B140" t="n">
-        <v>57654</v>
+        <v>57578</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15758,16 +15758,16 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -15776,24 +15776,21 @@
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>553311</v>
+        <v>553415</v>
       </c>
       <c r="R140" t="n">
-        <v>6704717</v>
+        <v>6705462</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15826,6 +15823,11 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Fjädrar på "slaktbord"</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15852,38 +15854,42 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127314473</v>
+        <v>127314441</v>
       </c>
       <c r="B141" t="n">
-        <v>57578</v>
+        <v>98443</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -15892,10 +15898,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>553415</v>
+        <v>553422</v>
       </c>
       <c r="R141" t="n">
-        <v>6705462</v>
+        <v>6704986</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15928,11 +15934,6 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Fjädrar på "slaktbord"</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15959,10 +15960,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127314441</v>
+        <v>127314442</v>
       </c>
       <c r="B142" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16003,10 +16004,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>553422</v>
+        <v>553423</v>
       </c>
       <c r="R142" t="n">
-        <v>6704986</v>
+        <v>6704914</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16068,7 +16069,7 @@
         <v>127314417</v>
       </c>
       <c r="B143" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16181,54 +16182,53 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127314442</v>
+        <v>127314370</v>
       </c>
       <c r="B144" t="n">
-        <v>98442</v>
+        <v>57654</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>553423</v>
+        <v>553311</v>
       </c>
       <c r="R144" t="n">
-        <v>6704914</v>
+        <v>6704717</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16491,10 +16491,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127314454</v>
+        <v>127314424</v>
       </c>
       <c r="B147" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -16540,10 +16540,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>553347</v>
+        <v>553422</v>
       </c>
       <c r="R147" t="n">
-        <v>6705040</v>
+        <v>6704824</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16576,11 +16576,6 @@
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>7 blomstjälkar</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16607,10 +16602,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127314424</v>
+        <v>127314454</v>
       </c>
       <c r="B148" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16637,7 +16632,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -16656,10 +16651,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>553422</v>
+        <v>553347</v>
       </c>
       <c r="R148" t="n">
-        <v>6704824</v>
+        <v>6705040</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16692,6 +16687,11 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>7 blomstjälkar</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16820,45 +16820,59 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127314343</v>
+        <v>127314411</v>
       </c>
       <c r="B150" t="n">
-        <v>91325</v>
+        <v>98443</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>553388</v>
+        <v>553500</v>
       </c>
       <c r="R150" t="n">
-        <v>6704753</v>
+        <v>6705175</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16917,45 +16931,59 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127314342</v>
+        <v>127314419</v>
       </c>
       <c r="B151" t="n">
-        <v>91325</v>
+        <v>98443</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>553347</v>
+        <v>553343</v>
       </c>
       <c r="R151" t="n">
-        <v>6704783</v>
+        <v>6704786</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16988,6 +17016,11 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17017,7 +17050,7 @@
         <v>127314450</v>
       </c>
       <c r="B152" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17125,59 +17158,45 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>127314419</v>
+        <v>127314343</v>
       </c>
       <c r="B153" t="n">
-        <v>98442</v>
+        <v>91326</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>553343</v>
+        <v>553388</v>
       </c>
       <c r="R153" t="n">
-        <v>6704786</v>
+        <v>6704753</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17210,11 +17229,6 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17241,59 +17255,45 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127314411</v>
+        <v>127314342</v>
       </c>
       <c r="B154" t="n">
-        <v>98442</v>
+        <v>91326</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>553500</v>
+        <v>553347</v>
       </c>
       <c r="R154" t="n">
-        <v>6705175</v>
+        <v>6704783</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17352,59 +17352,53 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127314447</v>
+        <v>127314374</v>
       </c>
       <c r="B155" t="n">
-        <v>98442</v>
+        <v>57654</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>553387</v>
+        <v>553523</v>
       </c>
       <c r="R155" t="n">
-        <v>6704938</v>
+        <v>6705404</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17463,42 +17457,38 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127314433</v>
+        <v>127314391</v>
       </c>
       <c r="B156" t="n">
-        <v>98442</v>
+        <v>57657</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -17507,10 +17497,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>553366</v>
+        <v>553375</v>
       </c>
       <c r="R156" t="n">
-        <v>6704886</v>
+        <v>6705433</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17543,6 +17533,11 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17569,32 +17564,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127314385</v>
+        <v>127314387</v>
       </c>
       <c r="B157" t="n">
-        <v>56953</v>
+        <v>91780</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100038</v>
+        <v>1209</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17604,10 +17599,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>553426</v>
+        <v>553517</v>
       </c>
       <c r="R157" t="n">
-        <v>6704786</v>
+        <v>6705421</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17666,53 +17661,50 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127314374</v>
+        <v>127314362</v>
       </c>
       <c r="B158" t="n">
-        <v>57654</v>
+        <v>4772</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100049</v>
+        <v>100299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N158" t="inlineStr"/>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>553523</v>
+        <v>553526</v>
       </c>
       <c r="R158" t="n">
-        <v>6705404</v>
+        <v>6705221</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17771,50 +17763,45 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127314391</v>
+        <v>127314385</v>
       </c>
       <c r="B159" t="n">
-        <v>57657</v>
+        <v>56953</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100109</v>
+        <v>100038</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>553375</v>
+        <v>553426</v>
       </c>
       <c r="R159" t="n">
-        <v>6705433</v>
+        <v>6704786</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17847,11 +17834,6 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17878,10 +17860,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127314387</v>
+        <v>127314447</v>
       </c>
       <c r="B160" t="n">
-        <v>91779</v>
+        <v>98443</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17889,34 +17871,48 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>553517</v>
+        <v>553387</v>
       </c>
       <c r="R160" t="n">
-        <v>6705421</v>
+        <v>6704938</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17975,38 +17971,42 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127314362</v>
+        <v>127314433</v>
       </c>
       <c r="B161" t="n">
-        <v>4772</v>
+        <v>98443</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
@@ -18015,10 +18015,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>553526</v>
+        <v>553366</v>
       </c>
       <c r="R161" t="n">
-        <v>6705221</v>
+        <v>6704886</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18080,7 +18080,7 @@
         <v>127314443</v>
       </c>
       <c r="B162" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18183,10 +18183,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>127314451</v>
+        <v>127314448</v>
       </c>
       <c r="B163" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18232,10 +18232,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>553427</v>
+        <v>553342</v>
       </c>
       <c r="R163" t="n">
-        <v>6704914</v>
+        <v>6704852</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18294,10 +18294,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>127314448</v>
+        <v>127314451</v>
       </c>
       <c r="B164" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18343,10 +18343,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>553342</v>
+        <v>553427</v>
       </c>
       <c r="R164" t="n">
-        <v>6704852</v>
+        <v>6704914</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18408,7 +18408,7 @@
         <v>127314434</v>
       </c>
       <c r="B165" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18521,10 +18521,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>127314439</v>
+        <v>127314409</v>
       </c>
       <c r="B166" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18549,16 +18549,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I166" t="inlineStr"/>
       <c r="K166" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -18570,10 +18561,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>553525</v>
+        <v>553478</v>
       </c>
       <c r="R166" t="n">
-        <v>6705250</v>
+        <v>6705174</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18610,7 +18601,7 @@
       </c>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>6 blomstjälkar</t>
+          <t>få synliga bladrosetter</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18640,7 +18631,7 @@
         <v>127314460</v>
       </c>
       <c r="B167" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18743,10 +18734,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>127314409</v>
+        <v>127314421</v>
       </c>
       <c r="B168" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18771,7 +18762,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr"/>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K168" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -18783,10 +18783,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>553478</v>
+        <v>553457</v>
       </c>
       <c r="R168" t="n">
-        <v>6705174</v>
+        <v>6705062</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18819,11 +18819,6 @@
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>få synliga bladrosetter</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18850,10 +18845,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>127314421</v>
+        <v>127314439</v>
       </c>
       <c r="B169" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18880,7 +18875,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -18899,10 +18894,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>553457</v>
+        <v>553525</v>
       </c>
       <c r="R169" t="n">
-        <v>6705062</v>
+        <v>6705250</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18935,6 +18930,11 @@
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>6 blomstjälkar</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18961,38 +18961,42 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>127314393</v>
+        <v>127314386</v>
       </c>
       <c r="B170" t="n">
-        <v>57657</v>
+        <v>92628</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
@@ -19001,10 +19005,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>553521</v>
+        <v>553414</v>
       </c>
       <c r="R170" t="n">
-        <v>6705364</v>
+        <v>6704970</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19037,11 +19041,6 @@
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19068,42 +19067,38 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127314386</v>
+        <v>127314393</v>
       </c>
       <c r="B171" t="n">
-        <v>92627</v>
+        <v>57657</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
@@ -19112,10 +19107,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>553414</v>
+        <v>553521</v>
       </c>
       <c r="R171" t="n">
-        <v>6704970</v>
+        <v>6705364</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19148,6 +19143,11 @@
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19177,7 +19177,7 @@
         <v>127314426</v>
       </c>
       <c r="B172" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>127314455</v>
       </c>
       <c r="B173" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19396,45 +19396,50 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127314355</v>
+        <v>127314392</v>
       </c>
       <c r="B174" t="n">
-        <v>91683</v>
+        <v>57657</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P174" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>553451</v>
+        <v>553395</v>
       </c>
       <c r="R174" t="n">
-        <v>6705503</v>
+        <v>6704765</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19467,6 +19472,11 @@
       <c r="AA174" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19493,50 +19503,45 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127314482</v>
+        <v>127314355</v>
       </c>
       <c r="B175" t="n">
-        <v>5176</v>
+        <v>91684</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>100526</v>
+        <v>2062</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P175" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>553322</v>
+        <v>553451</v>
       </c>
       <c r="R175" t="n">
-        <v>6704727</v>
+        <v>6705503</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19595,38 +19600,38 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>127314392</v>
+        <v>127314482</v>
       </c>
       <c r="B176" t="n">
-        <v>57657</v>
+        <v>5176</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="M176" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
@@ -19635,10 +19640,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>553395</v>
+        <v>553322</v>
       </c>
       <c r="R176" t="n">
-        <v>6704765</v>
+        <v>6704727</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19671,11 +19676,6 @@
       <c r="AA176" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19705,7 +19705,7 @@
         <v>127314438</v>
       </c>
       <c r="B177" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>127314459</v>
       </c>
       <c r="B178" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19924,38 +19924,47 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>127314378</v>
+        <v>127314413</v>
       </c>
       <c r="B179" t="n">
-        <v>57654</v>
+        <v>98443</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr"/>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
@@ -19964,10 +19973,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>553468</v>
+        <v>553349</v>
       </c>
       <c r="R179" t="n">
-        <v>6705210</v>
+        <v>6704994</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20000,6 +20009,11 @@
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>5 blomstjälkar</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20026,45 +20040,59 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>127314467</v>
+        <v>127314418</v>
       </c>
       <c r="B180" t="n">
-        <v>105477</v>
+        <v>98443</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>553468</v>
+        <v>553496</v>
       </c>
       <c r="R180" t="n">
-        <v>6705155</v>
+        <v>6705280</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20097,6 +20125,11 @@
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20123,38 +20156,42 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>127314381</v>
+        <v>127314430</v>
       </c>
       <c r="B181" t="n">
-        <v>57654</v>
+        <v>98443</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr"/>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
@@ -20163,10 +20200,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>553468</v>
+        <v>553358</v>
       </c>
       <c r="R181" t="n">
-        <v>6705451</v>
+        <v>6705058</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20225,10 +20262,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127314484</v>
+        <v>127314395</v>
       </c>
       <c r="B182" t="n">
-        <v>5176</v>
+        <v>97321</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20236,39 +20273,34 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>553430</v>
+        <v>553357</v>
       </c>
       <c r="R182" t="n">
-        <v>6705087</v>
+        <v>6704877</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20327,47 +20359,38 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>127314413</v>
+        <v>127314381</v>
       </c>
       <c r="B183" t="n">
-        <v>98442</v>
+        <v>57654</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
@@ -20376,10 +20399,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>553349</v>
+        <v>553468</v>
       </c>
       <c r="R183" t="n">
-        <v>6704994</v>
+        <v>6705451</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20412,11 +20435,6 @@
       <c r="AA183" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>5 blomstjälkar</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -20443,47 +20461,38 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>127314418</v>
+        <v>127314378</v>
       </c>
       <c r="B184" t="n">
-        <v>98442</v>
+        <v>57654</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
@@ -20492,10 +20501,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>553496</v>
+        <v>553468</v>
       </c>
       <c r="R184" t="n">
-        <v>6705280</v>
+        <v>6705210</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20528,11 +20537,6 @@
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20559,42 +20563,38 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>127314430</v>
+        <v>127314484</v>
       </c>
       <c r="B185" t="n">
-        <v>98442</v>
+        <v>5176</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
@@ -20603,10 +20603,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>553358</v>
+        <v>553430</v>
       </c>
       <c r="R185" t="n">
-        <v>6705058</v>
+        <v>6705087</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20665,10 +20665,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>127314395</v>
+        <v>127314467</v>
       </c>
       <c r="B186" t="n">
-        <v>97320</v>
+        <v>105478</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20676,21 +20676,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -20700,10 +20700,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>553357</v>
+        <v>553468</v>
       </c>
       <c r="R186" t="n">
-        <v>6704877</v>
+        <v>6705155</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20762,45 +20762,59 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>127314390</v>
+        <v>127314436</v>
       </c>
       <c r="B187" t="n">
-        <v>91621</v>
+        <v>98443</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P187" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>553386</v>
+        <v>553571</v>
       </c>
       <c r="R187" t="n">
-        <v>6704777</v>
+        <v>6705315</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20833,6 +20847,11 @@
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20859,10 +20878,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>127314461</v>
+        <v>127314464</v>
       </c>
       <c r="B188" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20903,10 +20922,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>553335</v>
+        <v>553470</v>
       </c>
       <c r="R188" t="n">
-        <v>6704846</v>
+        <v>6705234</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20965,10 +20984,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>127314453</v>
+        <v>127314461</v>
       </c>
       <c r="B189" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21003,21 +21022,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P189" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>553477</v>
+        <v>553335</v>
       </c>
       <c r="R189" t="n">
-        <v>6705197</v>
+        <v>6704846</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21076,54 +21090,45 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>127314464</v>
+        <v>127314390</v>
       </c>
       <c r="B190" t="n">
-        <v>98442</v>
+        <v>91622</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>553470</v>
+        <v>553386</v>
       </c>
       <c r="R190" t="n">
-        <v>6705234</v>
+        <v>6704777</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21182,10 +21187,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>127314436</v>
+        <v>127314453</v>
       </c>
       <c r="B191" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21212,7 +21217,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -21231,10 +21236,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>553571</v>
+        <v>553477</v>
       </c>
       <c r="R191" t="n">
-        <v>6705315</v>
+        <v>6705197</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21267,11 +21272,6 @@
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC191" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21301,7 +21301,7 @@
         <v>127314339</v>
       </c>
       <c r="B192" t="n">
-        <v>91683</v>
+        <v>91684</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21395,10 +21395,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>127314423</v>
+        <v>127314408</v>
       </c>
       <c r="B193" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21423,16 +21423,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -21444,10 +21435,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>553338</v>
+        <v>553400</v>
       </c>
       <c r="R193" t="n">
-        <v>6704806</v>
+        <v>6705072</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21480,6 +21471,11 @@
       <c r="AA193" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>få synliga bladrosetter</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21506,10 +21502,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>127314408</v>
+        <v>127314423</v>
       </c>
       <c r="B194" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21534,7 +21530,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K194" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -21546,10 +21551,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>553400</v>
+        <v>553338</v>
       </c>
       <c r="R194" t="n">
-        <v>6705072</v>
+        <v>6704806</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21582,11 +21587,6 @@
       <c r="AA194" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>få synliga bladrosetter</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21616,7 +21616,7 @@
         <v>127310426</v>
       </c>
       <c r="B195" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21727,10 +21727,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>127314389</v>
+        <v>127314382</v>
       </c>
       <c r="B196" t="n">
-        <v>91621</v>
+        <v>57307</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21738,34 +21738,39 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>658</v>
+        <v>100063</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>553364</v>
+        <v>553494</v>
       </c>
       <c r="R196" t="n">
-        <v>6704790</v>
+        <v>6705461</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21824,10 +21829,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>127314379</v>
+        <v>127314389</v>
       </c>
       <c r="B197" t="n">
-        <v>57654</v>
+        <v>91622</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21835,39 +21840,34 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>553485</v>
+        <v>553364</v>
       </c>
       <c r="R197" t="n">
-        <v>6705230</v>
+        <v>6704790</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21926,10 +21926,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>127314382</v>
+        <v>127314379</v>
       </c>
       <c r="B198" t="n">
-        <v>57307</v>
+        <v>57654</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21937,27 +21937,27 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>100063</v>
+        <v>100049</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="M198" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
@@ -21966,10 +21966,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>553494</v>
+        <v>553485</v>
       </c>
       <c r="R198" t="n">
-        <v>6705461</v>
+        <v>6705230</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22028,53 +22028,54 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>127314363</v>
+        <v>127314425</v>
       </c>
       <c r="B199" t="n">
-        <v>57817</v>
+        <v>98443</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr"/>
-      <c r="K199" t="inlineStr"/>
-      <c r="L199" t="inlineStr"/>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N199" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P199" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>553336</v>
+        <v>553466</v>
       </c>
       <c r="R199" t="n">
-        <v>6704944</v>
+        <v>6705077</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22133,38 +22134,47 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127314325</v>
+        <v>127314420</v>
       </c>
       <c r="B200" t="n">
-        <v>5196</v>
+        <v>98443</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr"/>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -22173,10 +22183,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>553508</v>
+        <v>553426</v>
       </c>
       <c r="R200" t="n">
-        <v>6705185</v>
+        <v>6704821</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22209,6 +22219,11 @@
       <c r="AA200" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22238,7 +22253,7 @@
         <v>127314445</v>
       </c>
       <c r="B201" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22346,10 +22361,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127314425</v>
+        <v>127314429</v>
       </c>
       <c r="B202" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22390,10 +22405,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>553466</v>
+        <v>553414</v>
       </c>
       <c r="R202" t="n">
-        <v>6705077</v>
+        <v>6704864</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22452,54 +22467,53 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>127314429</v>
+        <v>127314363</v>
       </c>
       <c r="B203" t="n">
-        <v>98442</v>
+        <v>57817</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>553414</v>
+        <v>553336</v>
       </c>
       <c r="R203" t="n">
-        <v>6704864</v>
+        <v>6704944</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22558,47 +22572,38 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>127314420</v>
+        <v>127314325</v>
       </c>
       <c r="B204" t="n">
-        <v>98442</v>
+        <v>5196</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
@@ -22607,10 +22612,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>553426</v>
+        <v>553508</v>
       </c>
       <c r="R204" t="n">
-        <v>6704821</v>
+        <v>6705185</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22643,11 +22648,6 @@
       <c r="AA204" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -22677,7 +22677,7 @@
         <v>127314354</v>
       </c>
       <c r="B205" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -22877,10 +22877,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>127314431</v>
+        <v>127314412</v>
       </c>
       <c r="B207" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -22907,7 +22907,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -22915,16 +22915,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P207" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>553442</v>
+        <v>553337</v>
       </c>
       <c r="R207" t="n">
-        <v>6705095</v>
+        <v>6704813</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22983,40 +22988,54 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>127314406</v>
+        <v>127314431</v>
       </c>
       <c r="B208" t="n">
-        <v>91732</v>
+        <v>98443</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P208" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>553517</v>
+        <v>553442</v>
       </c>
       <c r="R208" t="n">
-        <v>6705421</v>
+        <v>6705095</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23075,59 +23094,40 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>127314412</v>
+        <v>127314406</v>
       </c>
       <c r="B209" t="n">
-        <v>98442</v>
+        <v>91733</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J209" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>553337</v>
+        <v>553517</v>
       </c>
       <c r="R209" t="n">
-        <v>6704813</v>
+        <v>6705421</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23288,48 +23288,51 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>127314477</v>
+        <v>127310539</v>
       </c>
       <c r="B211" t="n">
-        <v>92615</v>
+        <v>91538</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>4364</v>
+        <v>1106</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Morkullberget södra, Dlr</t>
+          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>553371</v>
+        <v>553483</v>
       </c>
       <c r="R211" t="n">
-        <v>6704731</v>
+        <v>6705051</v>
       </c>
       <c r="S211" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -23361,71 +23364,63 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC211" t="inlineStr">
-        <is>
-          <t>Många gamla fruktkroppar i häxring</t>
-        </is>
-      </c>
       <c r="AD211" t="b">
         <v>0</v>
       </c>
       <c r="AE211" t="b">
         <v>0</v>
       </c>
+      <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="b">
         <v>0</v>
       </c>
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>127314428</v>
+        <v>127314480</v>
       </c>
       <c r="B212" t="n">
-        <v>98442</v>
+        <v>5176</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J212" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr"/>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
@@ -23434,10 +23429,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>553336</v>
+        <v>553399</v>
       </c>
       <c r="R212" t="n">
-        <v>6704827</v>
+        <v>6704947</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23496,10 +23491,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>127310539</v>
+        <v>127314428</v>
       </c>
       <c r="B213" t="n">
-        <v>91537</v>
+        <v>98443</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -23507,40 +23502,46 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>1106</v>
+        <v>220787</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr"/>
-      <c r="J213" t="inlineStr"/>
-      <c r="K213" t="inlineStr"/>
-      <c r="N213" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
+          <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>553483</v>
+        <v>553336</v>
       </c>
       <c r="R213" t="n">
-        <v>6705051</v>
+        <v>6704827</v>
       </c>
       <c r="S213" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -23578,29 +23579,28 @@
       <c r="AE213" t="b">
         <v>0</v>
       </c>
-      <c r="AF213" t="inlineStr"/>
       <c r="AG213" t="b">
         <v>0</v>
       </c>
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>127314480</v>
+        <v>127314477</v>
       </c>
       <c r="B214" t="n">
-        <v>5176</v>
+        <v>92616</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -23608,39 +23608,34 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P214" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>553399</v>
+        <v>553371</v>
       </c>
       <c r="R214" t="n">
-        <v>6704947</v>
+        <v>6704731</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23673,6 +23668,11 @@
       <c r="AA214" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>Många gamla fruktkroppar i häxring</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -23699,32 +23699,32 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>127314351</v>
+        <v>127314396</v>
       </c>
       <c r="B215" t="n">
-        <v>91325</v>
+        <v>97321</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -23734,10 +23734,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>553533</v>
+        <v>553521</v>
       </c>
       <c r="R215" t="n">
-        <v>6705296</v>
+        <v>6705212</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -23799,7 +23799,7 @@
         <v>127314348</v>
       </c>
       <c r="B216" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -23893,32 +23893,32 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>127314396</v>
+        <v>127314351</v>
       </c>
       <c r="B217" t="n">
-        <v>97320</v>
+        <v>91326</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -23928,10 +23928,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>553521</v>
+        <v>553533</v>
       </c>
       <c r="R217" t="n">
-        <v>6705212</v>
+        <v>6705296</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -23990,10 +23990,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>127314471</v>
+        <v>127314377</v>
       </c>
       <c r="B218" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24001,34 +24001,39 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P218" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>553406</v>
+        <v>553336</v>
       </c>
       <c r="R218" t="n">
-        <v>6705479</v>
+        <v>6704827</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24090,7 +24095,7 @@
         <v>127314337</v>
       </c>
       <c r="B219" t="n">
-        <v>91683</v>
+        <v>91684</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24189,10 +24194,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127314377</v>
+        <v>127314471</v>
       </c>
       <c r="B220" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24200,39 +24205,34 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P220" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>553336</v>
+        <v>553406</v>
       </c>
       <c r="R220" t="n">
-        <v>6704827</v>
+        <v>6705479</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24291,10 +24291,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>127314463</v>
+        <v>127314422</v>
       </c>
       <c r="B221" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -24329,16 +24329,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>553433</v>
+        <v>553445</v>
       </c>
       <c r="R221" t="n">
-        <v>6704902</v>
+        <v>6704996</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24397,10 +24402,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>127314456</v>
+        <v>127314437</v>
       </c>
       <c r="B222" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -24427,7 +24432,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -24446,10 +24451,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>553437</v>
+        <v>553333</v>
       </c>
       <c r="R222" t="n">
-        <v>6704997</v>
+        <v>6704814</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24482,11 +24487,6 @@
       <c r="AA222" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC222" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -24513,10 +24513,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>127314422</v>
+        <v>127314456</v>
       </c>
       <c r="B223" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -24543,7 +24543,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -24562,10 +24562,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>553445</v>
+        <v>553437</v>
       </c>
       <c r="R223" t="n">
-        <v>6704996</v>
+        <v>6704997</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24598,6 +24598,11 @@
       <c r="AA223" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -24624,10 +24629,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127314437</v>
+        <v>127314457</v>
       </c>
       <c r="B224" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -24654,7 +24659,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -24662,21 +24667,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P224" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>553333</v>
+        <v>553442</v>
       </c>
       <c r="R224" t="n">
-        <v>6704814</v>
+        <v>6705078</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24735,10 +24735,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127314457</v>
+        <v>127314458</v>
       </c>
       <c r="B225" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -24779,10 +24779,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>553442</v>
+        <v>553526</v>
       </c>
       <c r="R225" t="n">
-        <v>6705078</v>
+        <v>6705245</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24841,54 +24841,45 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127314458</v>
+        <v>127314394</v>
       </c>
       <c r="B226" t="n">
-        <v>98442</v>
+        <v>97321</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J226" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>553526</v>
+        <v>553498</v>
       </c>
       <c r="R226" t="n">
-        <v>6705245</v>
+        <v>6705418</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24947,45 +24938,54 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127314394</v>
+        <v>127314463</v>
       </c>
       <c r="B227" t="n">
-        <v>97320</v>
+        <v>98443</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>553498</v>
+        <v>553433</v>
       </c>
       <c r="R227" t="n">
-        <v>6705418</v>
+        <v>6704902</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25350,10 +25350,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>127314440</v>
+        <v>127314414</v>
       </c>
       <c r="B231" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -25380,7 +25380,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -25388,16 +25388,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P231" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>553571</v>
+        <v>553341</v>
       </c>
       <c r="R231" t="n">
-        <v>6705297</v>
+        <v>6704994</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -25430,6 +25435,11 @@
       <c r="AA231" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -25456,10 +25466,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>127314414</v>
+        <v>127314444</v>
       </c>
       <c r="B232" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -25486,7 +25496,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -25494,21 +25504,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P232" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>553341</v>
+        <v>553489</v>
       </c>
       <c r="R232" t="n">
-        <v>6704994</v>
+        <v>6705294</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -25541,11 +25546,6 @@
       <c r="AA232" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC232" t="inlineStr">
-        <is>
-          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -25572,10 +25572,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>127314444</v>
+        <v>127314440</v>
       </c>
       <c r="B233" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -25616,10 +25616,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>553489</v>
+        <v>553571</v>
       </c>
       <c r="R233" t="n">
-        <v>6705294</v>
+        <v>6705297</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -25681,7 +25681,7 @@
         <v>127314486</v>
       </c>
       <c r="B234" t="n">
-        <v>91697</v>
+        <v>91698</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>

--- a/artfynd/A 18040-2021 artfynd.xlsx
+++ b/artfynd/A 18040-2021 artfynd.xlsx
@@ -15747,10 +15747,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127314473</v>
+        <v>127314370</v>
       </c>
       <c r="B140" t="n">
-        <v>57578</v>
+        <v>57654</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15758,16 +15758,16 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100001</v>
+        <v>100049</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -15776,21 +15776,24 @@
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>553415</v>
+        <v>553311</v>
       </c>
       <c r="R140" t="n">
-        <v>6705462</v>
+        <v>6704717</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15823,11 +15826,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Fjädrar på "slaktbord"</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15854,42 +15852,38 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127314441</v>
+        <v>127314473</v>
       </c>
       <c r="B141" t="n">
-        <v>98443</v>
+        <v>57578</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -15898,10 +15892,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>553422</v>
+        <v>553415</v>
       </c>
       <c r="R141" t="n">
-        <v>6704986</v>
+        <v>6705462</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15934,6 +15928,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Fjädrar på "slaktbord"</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15960,7 +15959,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127314442</v>
+        <v>127314441</v>
       </c>
       <c r="B142" t="n">
         <v>98443</v>
@@ -16004,10 +16003,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>553423</v>
+        <v>553422</v>
       </c>
       <c r="R142" t="n">
-        <v>6704914</v>
+        <v>6704986</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16066,7 +16065,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127314417</v>
+        <v>127314442</v>
       </c>
       <c r="B143" t="n">
         <v>98443</v>
@@ -16096,7 +16095,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -16104,21 +16103,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>553413</v>
+        <v>553423</v>
       </c>
       <c r="R143" t="n">
-        <v>6704868</v>
+        <v>6704914</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16151,11 +16145,6 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16182,53 +16171,59 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127314370</v>
+        <v>127314417</v>
       </c>
       <c r="B144" t="n">
-        <v>57654</v>
+        <v>98443</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N144" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>553311</v>
+        <v>553413</v>
       </c>
       <c r="R144" t="n">
-        <v>6704717</v>
+        <v>6704868</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16261,6 +16256,11 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16718,50 +16718,45 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127314405</v>
+        <v>127314343</v>
       </c>
       <c r="B149" t="n">
-        <v>8447</v>
+        <v>91326</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>553521</v>
+        <v>553388</v>
       </c>
       <c r="R149" t="n">
-        <v>6705364</v>
+        <v>6704753</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16820,59 +16815,45 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127314411</v>
+        <v>127314342</v>
       </c>
       <c r="B150" t="n">
-        <v>98443</v>
+        <v>91326</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>553500</v>
+        <v>553347</v>
       </c>
       <c r="R150" t="n">
-        <v>6705175</v>
+        <v>6704783</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16931,47 +16912,38 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127314419</v>
+        <v>127314405</v>
       </c>
       <c r="B151" t="n">
-        <v>98443</v>
+        <v>8447</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -16980,10 +16952,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>553343</v>
+        <v>553521</v>
       </c>
       <c r="R151" t="n">
-        <v>6704786</v>
+        <v>6705364</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17016,11 +16988,6 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17047,7 +17014,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127314450</v>
+        <v>127314411</v>
       </c>
       <c r="B152" t="n">
         <v>98443</v>
@@ -17077,7 +17044,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -17096,10 +17063,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>553340</v>
+        <v>553500</v>
       </c>
       <c r="R152" t="n">
-        <v>6704784</v>
+        <v>6705175</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17158,45 +17125,59 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>127314343</v>
+        <v>127314419</v>
       </c>
       <c r="B153" t="n">
-        <v>91326</v>
+        <v>98443</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>553388</v>
+        <v>553343</v>
       </c>
       <c r="R153" t="n">
-        <v>6704753</v>
+        <v>6704786</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17229,6 +17210,11 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17255,45 +17241,59 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127314342</v>
+        <v>127314450</v>
       </c>
       <c r="B154" t="n">
-        <v>91326</v>
+        <v>98443</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>553347</v>
+        <v>553340</v>
       </c>
       <c r="R154" t="n">
-        <v>6704783</v>
+        <v>6704784</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -19396,38 +19396,47 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127314392</v>
+        <v>127314438</v>
       </c>
       <c r="B174" t="n">
-        <v>57657</v>
+        <v>98443</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr"/>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
@@ -19436,10 +19445,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>553395</v>
+        <v>553407</v>
       </c>
       <c r="R174" t="n">
-        <v>6704765</v>
+        <v>6704816</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19476,7 +19485,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19503,10 +19512,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127314355</v>
+        <v>127314459</v>
       </c>
       <c r="B175" t="n">
-        <v>91684</v>
+        <v>98443</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19514,34 +19523,43 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P175" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>553451</v>
+        <v>553508</v>
       </c>
       <c r="R175" t="n">
-        <v>6705503</v>
+        <v>6705196</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19600,38 +19618,38 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>127314482</v>
+        <v>127314392</v>
       </c>
       <c r="B176" t="n">
-        <v>5176</v>
+        <v>57657</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="M176" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
@@ -19640,10 +19658,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>553322</v>
+        <v>553395</v>
       </c>
       <c r="R176" t="n">
-        <v>6704727</v>
+        <v>6704765</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19676,6 +19694,11 @@
       <c r="AA176" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19702,47 +19725,38 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>127314438</v>
+        <v>127314482</v>
       </c>
       <c r="B177" t="n">
-        <v>98443</v>
+        <v>5176</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
@@ -19751,10 +19765,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>553407</v>
+        <v>553322</v>
       </c>
       <c r="R177" t="n">
-        <v>6704816</v>
+        <v>6704727</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19787,11 +19801,6 @@
       <c r="AA177" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19818,10 +19827,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>127314459</v>
+        <v>127314355</v>
       </c>
       <c r="B178" t="n">
-        <v>98443</v>
+        <v>91684</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19829,43 +19838,34 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>553508</v>
+        <v>553451</v>
       </c>
       <c r="R178" t="n">
-        <v>6705196</v>
+        <v>6705503</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19924,59 +19924,45 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>127314413</v>
+        <v>127314395</v>
       </c>
       <c r="B179" t="n">
-        <v>98443</v>
+        <v>97321</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>553349</v>
+        <v>553357</v>
       </c>
       <c r="R179" t="n">
-        <v>6704994</v>
+        <v>6704877</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20009,11 +19995,6 @@
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>5 blomstjälkar</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20040,59 +20021,45 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>127314418</v>
+        <v>127314467</v>
       </c>
       <c r="B180" t="n">
-        <v>98443</v>
+        <v>105478</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>553496</v>
+        <v>553468</v>
       </c>
       <c r="R180" t="n">
-        <v>6705280</v>
+        <v>6705155</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20125,11 +20092,6 @@
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20156,42 +20118,38 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>127314430</v>
+        <v>127314381</v>
       </c>
       <c r="B181" t="n">
-        <v>98443</v>
+        <v>57654</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
@@ -20200,10 +20158,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>553358</v>
+        <v>553468</v>
       </c>
       <c r="R181" t="n">
-        <v>6705058</v>
+        <v>6705451</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20262,45 +20220,50 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127314395</v>
+        <v>127314378</v>
       </c>
       <c r="B182" t="n">
-        <v>97321</v>
+        <v>57654</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>553357</v>
+        <v>553468</v>
       </c>
       <c r="R182" t="n">
-        <v>6704877</v>
+        <v>6705210</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20359,38 +20322,38 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>127314381</v>
+        <v>127314484</v>
       </c>
       <c r="B183" t="n">
-        <v>57654</v>
+        <v>5176</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="M183" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
@@ -20399,10 +20362,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>553468</v>
+        <v>553430</v>
       </c>
       <c r="R183" t="n">
-        <v>6705451</v>
+        <v>6705087</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20461,38 +20424,47 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>127314378</v>
+        <v>127314413</v>
       </c>
       <c r="B184" t="n">
-        <v>57654</v>
+        <v>98443</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr"/>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
@@ -20501,10 +20473,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>553468</v>
+        <v>553349</v>
       </c>
       <c r="R184" t="n">
-        <v>6705210</v>
+        <v>6704994</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20537,6 +20509,11 @@
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>5 blomstjälkar</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20563,38 +20540,47 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>127314484</v>
+        <v>127314418</v>
       </c>
       <c r="B185" t="n">
-        <v>5176</v>
+        <v>98443</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr"/>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
@@ -20603,10 +20589,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>553430</v>
+        <v>553496</v>
       </c>
       <c r="R185" t="n">
-        <v>6705087</v>
+        <v>6705280</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20639,6 +20625,11 @@
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -20665,45 +20656,54 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>127314467</v>
+        <v>127314430</v>
       </c>
       <c r="B186" t="n">
-        <v>105478</v>
+        <v>98443</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>553468</v>
+        <v>553358</v>
       </c>
       <c r="R186" t="n">
-        <v>6705155</v>
+        <v>6705058</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -21395,7 +21395,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>127314408</v>
+        <v>127310426</v>
       </c>
       <c r="B193" t="n">
         <v>98443</v>
@@ -21423,25 +21423,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K193" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
+      <c r="L193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Morkullberget södra, Dlr</t>
+          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>553400</v>
+        <v>553479</v>
       </c>
       <c r="R193" t="n">
-        <v>6705072</v>
+        <v>6705057</v>
       </c>
       <c r="S193" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -21473,36 +21484,32 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>få synliga bladrosetter</t>
-        </is>
-      </c>
       <c r="AD193" t="b">
         <v>0</v>
       </c>
       <c r="AE193" t="b">
         <v>0</v>
       </c>
+      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>127314423</v>
+        <v>127314408</v>
       </c>
       <c r="B194" t="n">
         <v>98443</v>
@@ -21530,16 +21537,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -21551,10 +21549,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>553338</v>
+        <v>553400</v>
       </c>
       <c r="R194" t="n">
-        <v>6704806</v>
+        <v>6705072</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21587,6 +21585,11 @@
       <c r="AA194" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>få synliga bladrosetter</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21613,7 +21616,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>127310426</v>
+        <v>127314423</v>
       </c>
       <c r="B195" t="n">
         <v>98443</v>
@@ -21643,12 +21646,12 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -21656,21 +21659,19 @@
           <t>blomning</t>
         </is>
       </c>
-      <c r="L195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
+          <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>553479</v>
+        <v>553338</v>
       </c>
       <c r="R195" t="n">
-        <v>6705057</v>
+        <v>6704806</v>
       </c>
       <c r="S195" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -21708,29 +21709,28 @@
       <c r="AE195" t="b">
         <v>0</v>
       </c>
-      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>127314382</v>
+        <v>127314363</v>
       </c>
       <c r="B196" t="n">
-        <v>57307</v>
+        <v>57817</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21738,39 +21738,42 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>100063</v>
+        <v>103021</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
       <c r="M196" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>553494</v>
+        <v>553336</v>
       </c>
       <c r="R196" t="n">
-        <v>6705461</v>
+        <v>6704944</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21829,45 +21832,50 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>127314389</v>
+        <v>127314325</v>
       </c>
       <c r="B197" t="n">
-        <v>91622</v>
+        <v>5196</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>658</v>
+        <v>105930</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>553364</v>
+        <v>553508</v>
       </c>
       <c r="R197" t="n">
-        <v>6704790</v>
+        <v>6705185</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21926,10 +21934,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>127314379</v>
+        <v>127314382</v>
       </c>
       <c r="B198" t="n">
-        <v>57654</v>
+        <v>57307</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21937,27 +21945,27 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>100049</v>
+        <v>100063</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="M198" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
@@ -21966,10 +21974,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>553485</v>
+        <v>553494</v>
       </c>
       <c r="R198" t="n">
-        <v>6705230</v>
+        <v>6705461</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22028,54 +22036,45 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>127314425</v>
+        <v>127314389</v>
       </c>
       <c r="B199" t="n">
-        <v>98443</v>
+        <v>91622</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>553466</v>
+        <v>553364</v>
       </c>
       <c r="R199" t="n">
-        <v>6705077</v>
+        <v>6704790</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22134,47 +22133,38 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127314420</v>
+        <v>127314379</v>
       </c>
       <c r="B200" t="n">
-        <v>98443</v>
+        <v>57654</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -22183,10 +22173,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>553426</v>
+        <v>553485</v>
       </c>
       <c r="R200" t="n">
-        <v>6704821</v>
+        <v>6705230</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22219,11 +22209,6 @@
       <c r="AA200" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22250,7 +22235,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>127314445</v>
+        <v>127314425</v>
       </c>
       <c r="B201" t="n">
         <v>98443</v>
@@ -22280,7 +22265,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -22288,21 +22273,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P201" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>553364</v>
+        <v>553466</v>
       </c>
       <c r="R201" t="n">
-        <v>6704996</v>
+        <v>6705077</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22361,7 +22341,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127314429</v>
+        <v>127314420</v>
       </c>
       <c r="B202" t="n">
         <v>98443</v>
@@ -22399,16 +22379,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P202" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>553414</v>
+        <v>553426</v>
       </c>
       <c r="R202" t="n">
-        <v>6704864</v>
+        <v>6704821</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22441,6 +22426,11 @@
       <c r="AA202" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22467,53 +22457,59 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>127314363</v>
+        <v>127314445</v>
       </c>
       <c r="B203" t="n">
-        <v>57817</v>
+        <v>98443</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr"/>
-      <c r="K203" t="inlineStr"/>
-      <c r="L203" t="inlineStr"/>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N203" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P203" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>553336</v>
+        <v>553364</v>
       </c>
       <c r="R203" t="n">
-        <v>6704944</v>
+        <v>6704996</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22572,38 +22568,42 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>127314325</v>
+        <v>127314429</v>
       </c>
       <c r="B204" t="n">
-        <v>5196</v>
+        <v>98443</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr"/>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
@@ -22612,10 +22612,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>553508</v>
+        <v>553414</v>
       </c>
       <c r="R204" t="n">
-        <v>6705185</v>
+        <v>6704864</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -23389,10 +23389,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>127314480</v>
+        <v>127314477</v>
       </c>
       <c r="B212" t="n">
-        <v>5176</v>
+        <v>92616</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -23400,39 +23400,34 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P212" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>553399</v>
+        <v>553371</v>
       </c>
       <c r="R212" t="n">
-        <v>6704947</v>
+        <v>6704731</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23465,6 +23460,11 @@
       <c r="AA212" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>Många gamla fruktkroppar i häxring</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -23491,42 +23491,38 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>127314428</v>
+        <v>127314480</v>
       </c>
       <c r="B213" t="n">
-        <v>98443</v>
+        <v>5176</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J213" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr"/>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -23535,10 +23531,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>553336</v>
+        <v>553399</v>
       </c>
       <c r="R213" t="n">
-        <v>6704827</v>
+        <v>6704947</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -23597,45 +23593,54 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>127314477</v>
+        <v>127314428</v>
       </c>
       <c r="B214" t="n">
-        <v>92616</v>
+        <v>98443</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P214" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>553371</v>
+        <v>553336</v>
       </c>
       <c r="R214" t="n">
-        <v>6704731</v>
+        <v>6704827</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23668,11 +23673,6 @@
       <c r="AA214" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC214" t="inlineStr">
-        <is>
-          <t>Många gamla fruktkroppar i häxring</t>
         </is>
       </c>
       <c r="AD214" t="b">

--- a/artfynd/A 18040-2021 artfynd.xlsx
+++ b/artfynd/A 18040-2021 artfynd.xlsx
@@ -13776,10 +13776,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127314407</v>
+        <v>127314388</v>
       </c>
       <c r="B121" t="n">
-        <v>98443</v>
+        <v>91780</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13787,39 +13787,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>553477</v>
+        <v>553411</v>
       </c>
       <c r="R121" t="n">
-        <v>6705175</v>
+        <v>6705072</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13852,11 +13847,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>få synliga bladrosetter</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13985,10 +13975,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127314388</v>
+        <v>127314407</v>
       </c>
       <c r="B123" t="n">
-        <v>91780</v>
+        <v>98443</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13996,34 +13986,39 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>553411</v>
+        <v>553477</v>
       </c>
       <c r="R123" t="n">
-        <v>6705072</v>
+        <v>6705175</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14056,6 +14051,11 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>få synliga bladrosetter</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14494,7 +14494,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127314432</v>
+        <v>127314435</v>
       </c>
       <c r="B128" t="n">
         <v>98443</v>
@@ -14524,7 +14524,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -14532,16 +14532,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>553508</v>
+        <v>553476</v>
       </c>
       <c r="R128" t="n">
-        <v>6705194</v>
+        <v>6705068</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14574,6 +14579,11 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>12 blomstjälkar</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14600,7 +14610,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127314435</v>
+        <v>127314415</v>
       </c>
       <c r="B129" t="n">
         <v>98443</v>
@@ -14630,7 +14640,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -14649,10 +14659,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>553476</v>
+        <v>553463</v>
       </c>
       <c r="R129" t="n">
-        <v>6705068</v>
+        <v>6705155</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14689,7 +14699,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>12 blomstjälkar</t>
+          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14716,7 +14726,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127314415</v>
+        <v>127314432</v>
       </c>
       <c r="B130" t="n">
         <v>98443</v>
@@ -14746,7 +14756,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -14754,21 +14764,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>553463</v>
+        <v>553508</v>
       </c>
       <c r="R130" t="n">
-        <v>6705155</v>
+        <v>6705194</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14801,11 +14806,6 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14832,7 +14832,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127314347</v>
+        <v>127314350</v>
       </c>
       <c r="B131" t="n">
         <v>91326</v>
@@ -14867,10 +14867,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>553419</v>
+        <v>553465</v>
       </c>
       <c r="R131" t="n">
-        <v>6705073</v>
+        <v>6705219</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15026,7 +15026,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127314345</v>
+        <v>127314347</v>
       </c>
       <c r="B133" t="n">
         <v>91326</v>
@@ -15061,10 +15061,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>553386</v>
+        <v>553419</v>
       </c>
       <c r="R133" t="n">
-        <v>6704777</v>
+        <v>6705073</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15123,7 +15123,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127314341</v>
+        <v>127314345</v>
       </c>
       <c r="B134" t="n">
         <v>91326</v>
@@ -15158,10 +15158,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>553429</v>
+        <v>553386</v>
       </c>
       <c r="R134" t="n">
-        <v>6705077</v>
+        <v>6704777</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15194,11 +15194,6 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15225,7 +15220,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127314350</v>
+        <v>127314341</v>
       </c>
       <c r="B135" t="n">
         <v>91326</v>
@@ -15260,10 +15255,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>553465</v>
+        <v>553429</v>
       </c>
       <c r="R135" t="n">
-        <v>6705219</v>
+        <v>6705077</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15296,6 +15291,11 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15535,7 +15535,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127314465</v>
+        <v>127314410</v>
       </c>
       <c r="B138" t="n">
         <v>98443</v>
@@ -15565,7 +15565,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15579,10 +15579,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>553488</v>
+        <v>553422</v>
       </c>
       <c r="R138" t="n">
-        <v>6705263</v>
+        <v>6705072</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15641,7 +15641,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127314410</v>
+        <v>127314465</v>
       </c>
       <c r="B139" t="n">
         <v>98443</v>
@@ -15671,7 +15671,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -15685,10 +15685,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>553422</v>
+        <v>553488</v>
       </c>
       <c r="R139" t="n">
-        <v>6705072</v>
+        <v>6705263</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15747,10 +15747,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127314370</v>
+        <v>127314473</v>
       </c>
       <c r="B140" t="n">
-        <v>57654</v>
+        <v>57578</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15758,16 +15758,16 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -15776,24 +15776,21 @@
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>553311</v>
+        <v>553415</v>
       </c>
       <c r="R140" t="n">
-        <v>6704717</v>
+        <v>6705462</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15826,6 +15823,11 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Fjädrar på "slaktbord"</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15852,10 +15854,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127314473</v>
+        <v>127314370</v>
       </c>
       <c r="B141" t="n">
-        <v>57578</v>
+        <v>57654</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15863,16 +15865,16 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100001</v>
+        <v>100049</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -15881,21 +15883,24 @@
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>553415</v>
+        <v>553311</v>
       </c>
       <c r="R141" t="n">
-        <v>6705462</v>
+        <v>6704717</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15928,11 +15933,6 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Fjädrar på "slaktbord"</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16287,38 +16287,47 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127314376</v>
+        <v>127314424</v>
       </c>
       <c r="B145" t="n">
-        <v>57654</v>
+        <v>98443</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -16327,10 +16336,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>553380</v>
+        <v>553422</v>
       </c>
       <c r="R145" t="n">
-        <v>6704935</v>
+        <v>6704824</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16389,38 +16398,47 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127314380</v>
+        <v>127314454</v>
       </c>
       <c r="B146" t="n">
-        <v>57654</v>
+        <v>98443</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -16429,10 +16447,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>553479</v>
+        <v>553347</v>
       </c>
       <c r="R146" t="n">
-        <v>6705480</v>
+        <v>6705040</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16465,6 +16483,11 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>7 blomstjälkar</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16491,47 +16514,38 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127314424</v>
+        <v>127314376</v>
       </c>
       <c r="B147" t="n">
-        <v>98443</v>
+        <v>57654</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -16540,10 +16554,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>553422</v>
+        <v>553380</v>
       </c>
       <c r="R147" t="n">
-        <v>6704824</v>
+        <v>6704935</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16602,47 +16616,38 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127314454</v>
+        <v>127314380</v>
       </c>
       <c r="B148" t="n">
-        <v>98443</v>
+        <v>57654</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -16651,10 +16656,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>553347</v>
+        <v>553479</v>
       </c>
       <c r="R148" t="n">
-        <v>6705040</v>
+        <v>6705480</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16687,11 +16692,6 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>7 blomstjälkar</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17661,10 +17661,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127314362</v>
+        <v>127314385</v>
       </c>
       <c r="B158" t="n">
-        <v>4772</v>
+        <v>56953</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17672,39 +17672,34 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100299</v>
+        <v>100038</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>553526</v>
+        <v>553426</v>
       </c>
       <c r="R158" t="n">
-        <v>6705221</v>
+        <v>6704786</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17763,10 +17758,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127314385</v>
+        <v>127314362</v>
       </c>
       <c r="B159" t="n">
-        <v>56953</v>
+        <v>4772</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17774,34 +17769,39 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100038</v>
+        <v>100299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>553426</v>
+        <v>553526</v>
       </c>
       <c r="R159" t="n">
-        <v>6704786</v>
+        <v>6705221</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18077,7 +18077,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127314443</v>
+        <v>127314451</v>
       </c>
       <c r="B162" t="n">
         <v>98443</v>
@@ -18107,7 +18107,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -18115,16 +18115,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>553338</v>
+        <v>553427</v>
       </c>
       <c r="R162" t="n">
-        <v>6705039</v>
+        <v>6704914</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18183,7 +18188,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>127314448</v>
+        <v>127314443</v>
       </c>
       <c r="B163" t="n">
         <v>98443</v>
@@ -18213,7 +18218,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -18221,21 +18226,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P163" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>553342</v>
+        <v>553338</v>
       </c>
       <c r="R163" t="n">
-        <v>6704852</v>
+        <v>6705039</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18294,7 +18294,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>127314451</v>
+        <v>127314448</v>
       </c>
       <c r="B164" t="n">
         <v>98443</v>
@@ -18343,10 +18343,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>553427</v>
+        <v>553342</v>
       </c>
       <c r="R164" t="n">
-        <v>6704914</v>
+        <v>6704852</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18521,7 +18521,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>127314409</v>
+        <v>127314421</v>
       </c>
       <c r="B166" t="n">
         <v>98443</v>
@@ -18549,7 +18549,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr"/>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K166" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -18561,10 +18570,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>553478</v>
+        <v>553457</v>
       </c>
       <c r="R166" t="n">
-        <v>6705174</v>
+        <v>6705062</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18597,11 +18606,6 @@
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>få synliga bladrosetter</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18628,7 +18632,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>127314460</v>
+        <v>127314439</v>
       </c>
       <c r="B167" t="n">
         <v>98443</v>
@@ -18658,7 +18662,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -18666,16 +18670,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>553444</v>
+        <v>553525</v>
       </c>
       <c r="R167" t="n">
-        <v>6705056</v>
+        <v>6705250</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18708,6 +18717,11 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>6 blomstjälkar</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18734,7 +18748,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>127314421</v>
+        <v>127314409</v>
       </c>
       <c r="B168" t="n">
         <v>98443</v>
@@ -18762,16 +18776,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I168" t="inlineStr"/>
       <c r="K168" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -18783,10 +18788,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>553457</v>
+        <v>553478</v>
       </c>
       <c r="R168" t="n">
-        <v>6705062</v>
+        <v>6705174</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18819,6 +18824,11 @@
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>få synliga bladrosetter</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18845,7 +18855,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>127314439</v>
+        <v>127314460</v>
       </c>
       <c r="B169" t="n">
         <v>98443</v>
@@ -18875,7 +18885,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -18883,21 +18893,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P169" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>553525</v>
+        <v>553444</v>
       </c>
       <c r="R169" t="n">
-        <v>6705250</v>
+        <v>6705056</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18930,11 +18935,6 @@
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>6 blomstjälkar</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -19396,10 +19396,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127314438</v>
+        <v>127314355</v>
       </c>
       <c r="B174" t="n">
-        <v>98443</v>
+        <v>91684</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19407,48 +19407,34 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>553407</v>
+        <v>553451</v>
       </c>
       <c r="R174" t="n">
-        <v>6704816</v>
+        <v>6705503</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19481,11 +19467,6 @@
       <c r="AA174" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19512,42 +19493,38 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127314459</v>
+        <v>127314392</v>
       </c>
       <c r="B175" t="n">
-        <v>98443</v>
+        <v>57657</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
@@ -19556,10 +19533,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>553508</v>
+        <v>553395</v>
       </c>
       <c r="R175" t="n">
-        <v>6705196</v>
+        <v>6704765</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19592,6 +19569,11 @@
       <c r="AA175" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19618,38 +19600,38 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>127314392</v>
+        <v>127314482</v>
       </c>
       <c r="B176" t="n">
-        <v>57657</v>
+        <v>5176</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="M176" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
@@ -19658,10 +19640,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>553395</v>
+        <v>553322</v>
       </c>
       <c r="R176" t="n">
-        <v>6704765</v>
+        <v>6704727</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19694,11 +19676,6 @@
       <c r="AA176" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19725,38 +19702,47 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>127314482</v>
+        <v>127314438</v>
       </c>
       <c r="B177" t="n">
-        <v>5176</v>
+        <v>98443</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr"/>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
@@ -19765,10 +19751,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>553322</v>
+        <v>553407</v>
       </c>
       <c r="R177" t="n">
-        <v>6704727</v>
+        <v>6704816</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19801,6 +19787,11 @@
       <c r="AA177" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19827,10 +19818,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>127314355</v>
+        <v>127314459</v>
       </c>
       <c r="B178" t="n">
-        <v>91684</v>
+        <v>98443</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19838,34 +19829,43 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>553451</v>
+        <v>553508</v>
       </c>
       <c r="R178" t="n">
-        <v>6705503</v>
+        <v>6705196</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19924,10 +19924,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>127314395</v>
+        <v>127314467</v>
       </c>
       <c r="B179" t="n">
-        <v>97321</v>
+        <v>105478</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19935,21 +19935,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19959,10 +19959,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>553357</v>
+        <v>553468</v>
       </c>
       <c r="R179" t="n">
-        <v>6704877</v>
+        <v>6705155</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20021,10 +20021,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>127314467</v>
+        <v>127314395</v>
       </c>
       <c r="B180" t="n">
-        <v>105478</v>
+        <v>97321</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20032,21 +20032,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -20056,10 +20056,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>553468</v>
+        <v>553357</v>
       </c>
       <c r="R180" t="n">
-        <v>6705155</v>
+        <v>6704877</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20118,38 +20118,38 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>127314381</v>
+        <v>127314484</v>
       </c>
       <c r="B181" t="n">
-        <v>57654</v>
+        <v>5176</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="M181" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
@@ -20158,10 +20158,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>553468</v>
+        <v>553430</v>
       </c>
       <c r="R181" t="n">
-        <v>6705451</v>
+        <v>6705087</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20220,38 +20220,47 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127314378</v>
+        <v>127314413</v>
       </c>
       <c r="B182" t="n">
-        <v>57654</v>
+        <v>98443</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr"/>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
@@ -20260,10 +20269,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>553468</v>
+        <v>553349</v>
       </c>
       <c r="R182" t="n">
-        <v>6705210</v>
+        <v>6704994</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20296,6 +20305,11 @@
       <c r="AA182" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>5 blomstjälkar</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20322,38 +20336,47 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>127314484</v>
+        <v>127314418</v>
       </c>
       <c r="B183" t="n">
-        <v>5176</v>
+        <v>98443</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr"/>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
@@ -20362,10 +20385,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>553430</v>
+        <v>553496</v>
       </c>
       <c r="R183" t="n">
-        <v>6705087</v>
+        <v>6705280</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20398,6 +20421,11 @@
       <c r="AA183" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -20424,7 +20452,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>127314413</v>
+        <v>127314430</v>
       </c>
       <c r="B184" t="n">
         <v>98443</v>
@@ -20454,7 +20482,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -20462,21 +20490,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P184" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>553349</v>
+        <v>553358</v>
       </c>
       <c r="R184" t="n">
-        <v>6704994</v>
+        <v>6705058</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20509,11 +20532,6 @@
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>5 blomstjälkar</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20540,47 +20558,38 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>127314418</v>
+        <v>127314381</v>
       </c>
       <c r="B185" t="n">
-        <v>98443</v>
+        <v>57654</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
@@ -20589,10 +20598,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>553496</v>
+        <v>553468</v>
       </c>
       <c r="R185" t="n">
-        <v>6705280</v>
+        <v>6705451</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20625,11 +20634,6 @@
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -20656,42 +20660,38 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>127314430</v>
+        <v>127314378</v>
       </c>
       <c r="B186" t="n">
-        <v>98443</v>
+        <v>57654</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J186" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
@@ -20700,10 +20700,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>553358</v>
+        <v>553468</v>
       </c>
       <c r="R186" t="n">
-        <v>6705058</v>
+        <v>6705210</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20762,59 +20762,45 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>127314436</v>
+        <v>127314390</v>
       </c>
       <c r="B187" t="n">
-        <v>98443</v>
+        <v>91622</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J187" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>553571</v>
+        <v>553386</v>
       </c>
       <c r="R187" t="n">
-        <v>6705315</v>
+        <v>6704777</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20847,11 +20833,6 @@
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC187" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20878,7 +20859,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>127314464</v>
+        <v>127314436</v>
       </c>
       <c r="B188" t="n">
         <v>98443</v>
@@ -20908,7 +20889,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -20916,16 +20897,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P188" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>553470</v>
+        <v>553571</v>
       </c>
       <c r="R188" t="n">
-        <v>6705234</v>
+        <v>6705315</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20958,6 +20944,11 @@
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20984,7 +20975,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>127314461</v>
+        <v>127314453</v>
       </c>
       <c r="B189" t="n">
         <v>98443</v>
@@ -21022,16 +21013,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P189" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>553335</v>
+        <v>553477</v>
       </c>
       <c r="R189" t="n">
-        <v>6704846</v>
+        <v>6705197</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21090,45 +21086,54 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>127314390</v>
+        <v>127314461</v>
       </c>
       <c r="B190" t="n">
-        <v>91622</v>
+        <v>98443</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P190" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>553386</v>
+        <v>553335</v>
       </c>
       <c r="R190" t="n">
-        <v>6704777</v>
+        <v>6704846</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21187,7 +21192,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>127314453</v>
+        <v>127314464</v>
       </c>
       <c r="B191" t="n">
         <v>98443</v>
@@ -21225,21 +21230,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P191" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>553477</v>
+        <v>553470</v>
       </c>
       <c r="R191" t="n">
-        <v>6705197</v>
+        <v>6705234</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21727,10 +21727,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>127314363</v>
+        <v>127314389</v>
       </c>
       <c r="B196" t="n">
-        <v>57817</v>
+        <v>91622</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21738,42 +21738,34 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
-      <c r="L196" t="inlineStr"/>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>553336</v>
+        <v>553364</v>
       </c>
       <c r="R196" t="n">
-        <v>6704944</v>
+        <v>6704790</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21832,50 +21824,53 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>127314325</v>
+        <v>127314363</v>
       </c>
       <c r="B197" t="n">
-        <v>5196</v>
+        <v>57817</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
       <c r="M197" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>553508</v>
+        <v>553336</v>
       </c>
       <c r="R197" t="n">
-        <v>6705185</v>
+        <v>6704944</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21934,38 +21929,42 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>127314382</v>
+        <v>127314425</v>
       </c>
       <c r="B198" t="n">
-        <v>57307</v>
+        <v>98443</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>100063</v>
+        <v>220787</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr"/>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
@@ -21974,10 +21973,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>553494</v>
+        <v>553466</v>
       </c>
       <c r="R198" t="n">
-        <v>6705461</v>
+        <v>6705077</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22036,45 +22035,59 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>127314389</v>
+        <v>127314420</v>
       </c>
       <c r="B199" t="n">
-        <v>91622</v>
+        <v>98443</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P199" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>553364</v>
+        <v>553426</v>
       </c>
       <c r="R199" t="n">
-        <v>6704790</v>
+        <v>6704821</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22107,6 +22120,11 @@
       <c r="AA199" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22133,38 +22151,42 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127314379</v>
+        <v>127314429</v>
       </c>
       <c r="B200" t="n">
-        <v>57654</v>
+        <v>98443</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr"/>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -22173,10 +22195,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>553485</v>
+        <v>553414</v>
       </c>
       <c r="R200" t="n">
-        <v>6705230</v>
+        <v>6704864</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22235,7 +22257,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>127314425</v>
+        <v>127314445</v>
       </c>
       <c r="B201" t="n">
         <v>98443</v>
@@ -22265,7 +22287,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -22273,16 +22295,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P201" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>553466</v>
+        <v>553364</v>
       </c>
       <c r="R201" t="n">
-        <v>6705077</v>
+        <v>6704996</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22341,47 +22368,38 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127314420</v>
+        <v>127314379</v>
       </c>
       <c r="B202" t="n">
-        <v>98443</v>
+        <v>57654</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
@@ -22390,10 +22408,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>553426</v>
+        <v>553485</v>
       </c>
       <c r="R202" t="n">
-        <v>6704821</v>
+        <v>6705230</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22426,11 +22444,6 @@
       <c r="AA202" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22457,47 +22470,38 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>127314445</v>
+        <v>127314382</v>
       </c>
       <c r="B203" t="n">
-        <v>98443</v>
+        <v>57307</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>220787</v>
+        <v>100063</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr"/>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
@@ -22506,10 +22510,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>553364</v>
+        <v>553494</v>
       </c>
       <c r="R203" t="n">
-        <v>6704996</v>
+        <v>6705461</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22568,42 +22572,38 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>127314429</v>
+        <v>127314325</v>
       </c>
       <c r="B204" t="n">
-        <v>98443</v>
+        <v>5196</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
@@ -22612,10 +22612,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>553414</v>
+        <v>553508</v>
       </c>
       <c r="R204" t="n">
-        <v>6704864</v>
+        <v>6705185</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -23186,53 +23186,51 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>127314368</v>
+        <v>127310539</v>
       </c>
       <c r="B210" t="n">
-        <v>57654</v>
+        <v>91538</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>100049</v>
+        <v>1106</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="J210" t="inlineStr"/>
+      <c r="K210" t="inlineStr"/>
+      <c r="N210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Morkullberget södra, Dlr</t>
+          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>553500</v>
+        <v>553483</v>
       </c>
       <c r="R210" t="n">
-        <v>6705249</v>
+        <v>6705051</v>
       </c>
       <c r="S210" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -23270,69 +23268,67 @@
       <c r="AE210" t="b">
         <v>0</v>
       </c>
+      <c r="AF210" t="inlineStr"/>
       <c r="AG210" t="b">
         <v>0</v>
       </c>
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>127310539</v>
+        <v>127314477</v>
       </c>
       <c r="B211" t="n">
-        <v>91538</v>
+        <v>92616</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>1106</v>
+        <v>4364</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
-      <c r="J211" t="inlineStr"/>
-      <c r="K211" t="inlineStr"/>
-      <c r="N211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
+          <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>553483</v>
+        <v>553371</v>
       </c>
       <c r="R211" t="n">
-        <v>6705051</v>
+        <v>6704731</v>
       </c>
       <c r="S211" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -23364,70 +23360,79 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>Många gamla fruktkroppar i häxring</t>
+        </is>
+      </c>
       <c r="AD211" t="b">
         <v>0</v>
       </c>
       <c r="AE211" t="b">
         <v>0</v>
       </c>
-      <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="b">
         <v>0</v>
       </c>
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>127314477</v>
+        <v>127314368</v>
       </c>
       <c r="B212" t="n">
-        <v>92616</v>
+        <v>57654</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P212" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>553371</v>
+        <v>553500</v>
       </c>
       <c r="R212" t="n">
-        <v>6704731</v>
+        <v>6705249</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23460,11 +23465,6 @@
       <c r="AA212" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC212" t="inlineStr">
-        <is>
-          <t>Många gamla fruktkroppar i häxring</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -23796,7 +23796,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>127314348</v>
+        <v>127314351</v>
       </c>
       <c r="B216" t="n">
         <v>91326</v>
@@ -23831,10 +23831,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>553499</v>
+        <v>553533</v>
       </c>
       <c r="R216" t="n">
-        <v>6705218</v>
+        <v>6705296</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -23893,7 +23893,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>127314351</v>
+        <v>127314348</v>
       </c>
       <c r="B217" t="n">
         <v>91326</v>
@@ -23928,10 +23928,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>553533</v>
+        <v>553499</v>
       </c>
       <c r="R217" t="n">
-        <v>6705296</v>
+        <v>6705218</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24092,10 +24092,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127314337</v>
+        <v>127314422</v>
       </c>
       <c r="B219" t="n">
-        <v>91684</v>
+        <v>98443</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24103,34 +24103,48 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>553419</v>
+        <v>553445</v>
       </c>
       <c r="R219" t="n">
-        <v>6705073</v>
+        <v>6704996</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24163,11 +24177,6 @@
       <c r="AA219" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC219" t="inlineStr">
-        <is>
-          <t>Eventuellt S. delicata</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -24194,45 +24203,59 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127314471</v>
+        <v>127314437</v>
       </c>
       <c r="B220" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P220" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>553406</v>
+        <v>553333</v>
       </c>
       <c r="R220" t="n">
-        <v>6705479</v>
+        <v>6704814</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24291,7 +24314,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>127314422</v>
+        <v>127314456</v>
       </c>
       <c r="B221" t="n">
         <v>98443</v>
@@ -24321,7 +24344,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -24340,10 +24363,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>553445</v>
+        <v>553437</v>
       </c>
       <c r="R221" t="n">
-        <v>6704996</v>
+        <v>6704997</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24376,6 +24399,11 @@
       <c r="AA221" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -24402,7 +24430,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>127314437</v>
+        <v>127314457</v>
       </c>
       <c r="B222" t="n">
         <v>98443</v>
@@ -24432,7 +24460,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -24440,21 +24468,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P222" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>553333</v>
+        <v>553442</v>
       </c>
       <c r="R222" t="n">
-        <v>6704814</v>
+        <v>6705078</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24513,7 +24536,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>127314456</v>
+        <v>127314463</v>
       </c>
       <c r="B223" t="n">
         <v>98443</v>
@@ -24543,7 +24566,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -24551,21 +24574,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>553437</v>
+        <v>553433</v>
       </c>
       <c r="R223" t="n">
-        <v>6704997</v>
+        <v>6704902</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24598,11 +24616,6 @@
       <c r="AA223" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC223" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -24629,7 +24642,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127314457</v>
+        <v>127314458</v>
       </c>
       <c r="B224" t="n">
         <v>98443</v>
@@ -24673,10 +24686,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>553442</v>
+        <v>553526</v>
       </c>
       <c r="R224" t="n">
-        <v>6705078</v>
+        <v>6705245</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24735,54 +24748,45 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127314458</v>
+        <v>127314394</v>
       </c>
       <c r="B225" t="n">
-        <v>98443</v>
+        <v>97321</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J225" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>553526</v>
+        <v>553498</v>
       </c>
       <c r="R225" t="n">
-        <v>6705245</v>
+        <v>6705418</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24841,32 +24845,32 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127314394</v>
+        <v>127314337</v>
       </c>
       <c r="B226" t="n">
-        <v>97321</v>
+        <v>91684</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>221945</v>
+        <v>2062</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -24876,10 +24880,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>553498</v>
+        <v>553419</v>
       </c>
       <c r="R226" t="n">
-        <v>6705418</v>
+        <v>6705073</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24912,6 +24916,11 @@
       <c r="AA226" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>Eventuellt S. delicata</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -24938,54 +24947,45 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127314463</v>
+        <v>127314471</v>
       </c>
       <c r="B227" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J227" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>553433</v>
+        <v>553406</v>
       </c>
       <c r="R227" t="n">
-        <v>6704902</v>
+        <v>6705479</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>

--- a/artfynd/A 18040-2021 artfynd.xlsx
+++ b/artfynd/A 18040-2021 artfynd.xlsx
@@ -13776,45 +13776,50 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127314388</v>
+        <v>127314375</v>
       </c>
       <c r="B121" t="n">
-        <v>91780</v>
+        <v>57654</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>553411</v>
+        <v>553537</v>
       </c>
       <c r="R121" t="n">
-        <v>6705072</v>
+        <v>6705403</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13873,50 +13878,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127314375</v>
+        <v>127314388</v>
       </c>
       <c r="B122" t="n">
-        <v>57654</v>
+        <v>91780</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>553537</v>
+        <v>553411</v>
       </c>
       <c r="R122" t="n">
-        <v>6705403</v>
+        <v>6705072</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14832,7 +14832,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127314350</v>
+        <v>127314347</v>
       </c>
       <c r="B131" t="n">
         <v>91326</v>
@@ -14867,10 +14867,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>553465</v>
+        <v>553419</v>
       </c>
       <c r="R131" t="n">
-        <v>6705219</v>
+        <v>6705073</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14929,32 +14929,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127314336</v>
+        <v>127314345</v>
       </c>
       <c r="B132" t="n">
-        <v>91684</v>
+        <v>91326</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14964,10 +14964,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>553429</v>
+        <v>553386</v>
       </c>
       <c r="R132" t="n">
-        <v>6705077</v>
+        <v>6704777</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15026,7 +15026,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127314347</v>
+        <v>127314341</v>
       </c>
       <c r="B133" t="n">
         <v>91326</v>
@@ -15061,10 +15061,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>553419</v>
+        <v>553429</v>
       </c>
       <c r="R133" t="n">
-        <v>6705073</v>
+        <v>6705077</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15097,6 +15097,11 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15123,7 +15128,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127314345</v>
+        <v>127314350</v>
       </c>
       <c r="B134" t="n">
         <v>91326</v>
@@ -15158,10 +15163,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>553386</v>
+        <v>553465</v>
       </c>
       <c r="R134" t="n">
-        <v>6704777</v>
+        <v>6705219</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15220,32 +15225,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127314341</v>
+        <v>127314468</v>
       </c>
       <c r="B135" t="n">
-        <v>91326</v>
+        <v>91913</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1202</v>
+        <v>1179</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15255,10 +15260,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>553429</v>
+        <v>553482</v>
       </c>
       <c r="R135" t="n">
-        <v>6705077</v>
+        <v>6705183</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15295,7 +15300,7 @@
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>Gammal fruktkropp</t>
+          <t>Återfynd</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15322,10 +15327,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127314468</v>
+        <v>127314452</v>
       </c>
       <c r="B136" t="n">
-        <v>91913</v>
+        <v>98443</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15333,34 +15338,48 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1179</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>553482</v>
+        <v>553418</v>
       </c>
       <c r="R136" t="n">
-        <v>6705183</v>
+        <v>6705084</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15393,11 +15412,6 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Återfynd</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15424,7 +15438,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127314452</v>
+        <v>127314410</v>
       </c>
       <c r="B137" t="n">
         <v>98443</v>
@@ -15454,7 +15468,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -15462,21 +15476,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>553418</v>
+        <v>553422</v>
       </c>
       <c r="R137" t="n">
-        <v>6705084</v>
+        <v>6705072</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15535,7 +15544,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127314410</v>
+        <v>127314465</v>
       </c>
       <c r="B138" t="n">
         <v>98443</v>
@@ -15565,7 +15574,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15579,10 +15588,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>553422</v>
+        <v>553488</v>
       </c>
       <c r="R138" t="n">
-        <v>6705072</v>
+        <v>6705263</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15641,10 +15650,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127314465</v>
+        <v>127314336</v>
       </c>
       <c r="B139" t="n">
-        <v>98443</v>
+        <v>91684</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15652,43 +15661,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>553488</v>
+        <v>553429</v>
       </c>
       <c r="R139" t="n">
-        <v>6705263</v>
+        <v>6705077</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -17352,53 +17352,45 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127314374</v>
+        <v>127314387</v>
       </c>
       <c r="B155" t="n">
-        <v>57654</v>
+        <v>91780</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>553523</v>
+        <v>553517</v>
       </c>
       <c r="R155" t="n">
-        <v>6705404</v>
+        <v>6705421</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17457,38 +17449,47 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127314391</v>
+        <v>127314447</v>
       </c>
       <c r="B156" t="n">
-        <v>57657</v>
+        <v>98443</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -17497,10 +17498,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>553375</v>
+        <v>553387</v>
       </c>
       <c r="R156" t="n">
-        <v>6705433</v>
+        <v>6704938</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17533,11 +17534,6 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17564,10 +17560,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127314387</v>
+        <v>127314433</v>
       </c>
       <c r="B157" t="n">
-        <v>91780</v>
+        <v>98443</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17575,34 +17571,43 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>553517</v>
+        <v>553366</v>
       </c>
       <c r="R157" t="n">
-        <v>6705421</v>
+        <v>6704886</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17758,50 +17763,53 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127314362</v>
+        <v>127314374</v>
       </c>
       <c r="B159" t="n">
-        <v>4772</v>
+        <v>57654</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
       <c r="M159" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>553526</v>
+        <v>553523</v>
       </c>
       <c r="R159" t="n">
-        <v>6705221</v>
+        <v>6705404</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17860,47 +17868,38 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127314447</v>
+        <v>127314391</v>
       </c>
       <c r="B160" t="n">
-        <v>98443</v>
+        <v>57657</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -17909,10 +17908,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>553387</v>
+        <v>553375</v>
       </c>
       <c r="R160" t="n">
-        <v>6704938</v>
+        <v>6705433</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17945,6 +17944,11 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17971,42 +17975,38 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127314433</v>
+        <v>127314362</v>
       </c>
       <c r="B161" t="n">
-        <v>98443</v>
+        <v>4772</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
@@ -18015,10 +18015,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>553366</v>
+        <v>553526</v>
       </c>
       <c r="R161" t="n">
-        <v>6704886</v>
+        <v>6705221</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18077,7 +18077,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127314451</v>
+        <v>127314443</v>
       </c>
       <c r="B162" t="n">
         <v>98443</v>
@@ -18107,7 +18107,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -18115,21 +18115,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>553427</v>
+        <v>553338</v>
       </c>
       <c r="R162" t="n">
-        <v>6704914</v>
+        <v>6705039</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18188,7 +18183,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>127314443</v>
+        <v>127314448</v>
       </c>
       <c r="B163" t="n">
         <v>98443</v>
@@ -18218,7 +18213,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -18226,16 +18221,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>553338</v>
+        <v>553342</v>
       </c>
       <c r="R163" t="n">
-        <v>6705039</v>
+        <v>6704852</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18294,7 +18294,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>127314448</v>
+        <v>127314434</v>
       </c>
       <c r="B164" t="n">
         <v>98443</v>
@@ -18324,7 +18324,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -18343,10 +18343,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>553342</v>
+        <v>553416</v>
       </c>
       <c r="R164" t="n">
-        <v>6704852</v>
+        <v>6704816</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18379,6 +18379,11 @@
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18405,7 +18410,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>127314434</v>
+        <v>127314451</v>
       </c>
       <c r="B165" t="n">
         <v>98443</v>
@@ -18435,7 +18440,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -18454,10 +18459,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>553416</v>
+        <v>553427</v>
       </c>
       <c r="R165" t="n">
-        <v>6704816</v>
+        <v>6704914</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18490,11 +18495,6 @@
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19396,45 +19396,50 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127314355</v>
+        <v>127314392</v>
       </c>
       <c r="B174" t="n">
-        <v>91684</v>
+        <v>57657</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P174" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>553451</v>
+        <v>553395</v>
       </c>
       <c r="R174" t="n">
-        <v>6705503</v>
+        <v>6704765</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19467,6 +19472,11 @@
       <c r="AA174" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19493,50 +19503,45 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127314392</v>
+        <v>127314355</v>
       </c>
       <c r="B175" t="n">
-        <v>57657</v>
+        <v>91684</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P175" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>553395</v>
+        <v>553451</v>
       </c>
       <c r="R175" t="n">
-        <v>6704765</v>
+        <v>6705503</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19569,11 +19574,6 @@
       <c r="AA175" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -22877,59 +22877,40 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>127314412</v>
+        <v>127314406</v>
       </c>
       <c r="B207" t="n">
-        <v>98443</v>
+        <v>91733</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>553337</v>
+        <v>553517</v>
       </c>
       <c r="R207" t="n">
-        <v>6704813</v>
+        <v>6705421</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22988,7 +22969,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>127314431</v>
+        <v>127314412</v>
       </c>
       <c r="B208" t="n">
         <v>98443</v>
@@ -23018,7 +22999,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -23026,16 +23007,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P208" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>553442</v>
+        <v>553337</v>
       </c>
       <c r="R208" t="n">
-        <v>6705095</v>
+        <v>6704813</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23094,40 +23080,54 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>127314406</v>
+        <v>127314431</v>
       </c>
       <c r="B209" t="n">
-        <v>91733</v>
+        <v>98443</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P209" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>553517</v>
+        <v>553442</v>
       </c>
       <c r="R209" t="n">
-        <v>6705421</v>
+        <v>6705095</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23699,32 +23699,32 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>127314396</v>
+        <v>127314351</v>
       </c>
       <c r="B215" t="n">
-        <v>97321</v>
+        <v>91326</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -23734,10 +23734,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>553521</v>
+        <v>553533</v>
       </c>
       <c r="R215" t="n">
-        <v>6705212</v>
+        <v>6705296</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -23796,7 +23796,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>127314351</v>
+        <v>127314348</v>
       </c>
       <c r="B216" t="n">
         <v>91326</v>
@@ -23831,10 +23831,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>553533</v>
+        <v>553499</v>
       </c>
       <c r="R216" t="n">
-        <v>6705296</v>
+        <v>6705218</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -23893,32 +23893,32 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>127314348</v>
+        <v>127314396</v>
       </c>
       <c r="B217" t="n">
-        <v>91326</v>
+        <v>97321</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -23928,10 +23928,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>553499</v>
+        <v>553521</v>
       </c>
       <c r="R217" t="n">
-        <v>6705218</v>
+        <v>6705212</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24092,10 +24092,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127314422</v>
+        <v>127314337</v>
       </c>
       <c r="B219" t="n">
-        <v>98443</v>
+        <v>91684</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24103,48 +24103,34 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J219" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>553445</v>
+        <v>553419</v>
       </c>
       <c r="R219" t="n">
-        <v>6704996</v>
+        <v>6705073</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24177,6 +24163,11 @@
       <c r="AA219" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>Eventuellt S. delicata</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -24203,59 +24194,45 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127314437</v>
+        <v>127314471</v>
       </c>
       <c r="B220" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J220" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>553333</v>
+        <v>553406</v>
       </c>
       <c r="R220" t="n">
-        <v>6704814</v>
+        <v>6705479</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24314,7 +24291,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>127314456</v>
+        <v>127314422</v>
       </c>
       <c r="B221" t="n">
         <v>98443</v>
@@ -24344,7 +24321,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -24363,10 +24340,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>553437</v>
+        <v>553445</v>
       </c>
       <c r="R221" t="n">
-        <v>6704997</v>
+        <v>6704996</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24399,11 +24376,6 @@
       <c r="AA221" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC221" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -24430,7 +24402,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>127314457</v>
+        <v>127314437</v>
       </c>
       <c r="B222" t="n">
         <v>98443</v>
@@ -24460,7 +24432,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -24468,16 +24440,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P222" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>553442</v>
+        <v>553333</v>
       </c>
       <c r="R222" t="n">
-        <v>6705078</v>
+        <v>6704814</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24536,7 +24513,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>127314463</v>
+        <v>127314456</v>
       </c>
       <c r="B223" t="n">
         <v>98443</v>
@@ -24566,7 +24543,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -24574,16 +24551,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>553433</v>
+        <v>553437</v>
       </c>
       <c r="R223" t="n">
-        <v>6704902</v>
+        <v>6704997</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24616,6 +24598,11 @@
       <c r="AA223" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -24642,7 +24629,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127314458</v>
+        <v>127314457</v>
       </c>
       <c r="B224" t="n">
         <v>98443</v>
@@ -24686,10 +24673,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>553526</v>
+        <v>553442</v>
       </c>
       <c r="R224" t="n">
-        <v>6705245</v>
+        <v>6705078</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24748,45 +24735,54 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127314394</v>
+        <v>127314463</v>
       </c>
       <c r="B225" t="n">
-        <v>97321</v>
+        <v>98443</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P225" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>553498</v>
+        <v>553433</v>
       </c>
       <c r="R225" t="n">
-        <v>6705418</v>
+        <v>6704902</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24845,10 +24841,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127314337</v>
+        <v>127314458</v>
       </c>
       <c r="B226" t="n">
-        <v>91684</v>
+        <v>98443</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -24856,34 +24852,43 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P226" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>553419</v>
+        <v>553526</v>
       </c>
       <c r="R226" t="n">
-        <v>6705073</v>
+        <v>6705245</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24916,11 +24921,6 @@
       <c r="AA226" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC226" t="inlineStr">
-        <is>
-          <t>Eventuellt S. delicata</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -24947,32 +24947,32 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127314471</v>
+        <v>127314394</v>
       </c>
       <c r="B227" t="n">
-        <v>79014</v>
+        <v>97321</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -24982,10 +24982,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>553406</v>
+        <v>553498</v>
       </c>
       <c r="R227" t="n">
-        <v>6705479</v>
+        <v>6705418</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>

--- a/artfynd/A 18040-2021 artfynd.xlsx
+++ b/artfynd/A 18040-2021 artfynd.xlsx
@@ -13776,50 +13776,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127314375</v>
+        <v>127314388</v>
       </c>
       <c r="B121" t="n">
-        <v>57654</v>
+        <v>91780</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>553537</v>
+        <v>553411</v>
       </c>
       <c r="R121" t="n">
-        <v>6705403</v>
+        <v>6705072</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13878,45 +13873,50 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127314388</v>
+        <v>127314375</v>
       </c>
       <c r="B122" t="n">
-        <v>91780</v>
+        <v>57654</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>553411</v>
+        <v>553537</v>
       </c>
       <c r="R122" t="n">
-        <v>6705072</v>
+        <v>6705403</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14832,7 +14832,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127314347</v>
+        <v>127314350</v>
       </c>
       <c r="B131" t="n">
         <v>91326</v>
@@ -14867,10 +14867,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>553419</v>
+        <v>553465</v>
       </c>
       <c r="R131" t="n">
-        <v>6705073</v>
+        <v>6705219</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14929,32 +14929,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127314345</v>
+        <v>127314336</v>
       </c>
       <c r="B132" t="n">
-        <v>91326</v>
+        <v>91684</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14964,10 +14964,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>553386</v>
+        <v>553429</v>
       </c>
       <c r="R132" t="n">
-        <v>6704777</v>
+        <v>6705077</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15026,7 +15026,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127314341</v>
+        <v>127314347</v>
       </c>
       <c r="B133" t="n">
         <v>91326</v>
@@ -15061,10 +15061,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>553429</v>
+        <v>553419</v>
       </c>
       <c r="R133" t="n">
-        <v>6705077</v>
+        <v>6705073</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15097,11 +15097,6 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15128,7 +15123,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127314350</v>
+        <v>127314345</v>
       </c>
       <c r="B134" t="n">
         <v>91326</v>
@@ -15163,10 +15158,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>553465</v>
+        <v>553386</v>
       </c>
       <c r="R134" t="n">
-        <v>6705219</v>
+        <v>6704777</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15225,32 +15220,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127314468</v>
+        <v>127314341</v>
       </c>
       <c r="B135" t="n">
-        <v>91913</v>
+        <v>91326</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1179</v>
+        <v>1202</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15260,10 +15255,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>553482</v>
+        <v>553429</v>
       </c>
       <c r="R135" t="n">
-        <v>6705183</v>
+        <v>6705077</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15300,7 +15295,7 @@
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>Återfynd</t>
+          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15327,10 +15322,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127314452</v>
+        <v>127314468</v>
       </c>
       <c r="B136" t="n">
-        <v>98443</v>
+        <v>91913</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15338,48 +15333,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220787</v>
+        <v>1179</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Peck) Donk</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>553418</v>
+        <v>553482</v>
       </c>
       <c r="R136" t="n">
-        <v>6705084</v>
+        <v>6705183</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15412,6 +15393,11 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Återfynd</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15438,7 +15424,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127314410</v>
+        <v>127314452</v>
       </c>
       <c r="B137" t="n">
         <v>98443</v>
@@ -15468,7 +15454,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -15476,16 +15462,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>553422</v>
+        <v>553418</v>
       </c>
       <c r="R137" t="n">
-        <v>6705072</v>
+        <v>6705084</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15544,7 +15535,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127314465</v>
+        <v>127314410</v>
       </c>
       <c r="B138" t="n">
         <v>98443</v>
@@ -15574,7 +15565,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15588,10 +15579,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>553488</v>
+        <v>553422</v>
       </c>
       <c r="R138" t="n">
-        <v>6705263</v>
+        <v>6705072</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15650,10 +15641,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127314336</v>
+        <v>127314465</v>
       </c>
       <c r="B139" t="n">
-        <v>91684</v>
+        <v>98443</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15661,34 +15652,43 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>553429</v>
+        <v>553488</v>
       </c>
       <c r="R139" t="n">
-        <v>6705077</v>
+        <v>6705263</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -17352,45 +17352,53 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127314387</v>
+        <v>127314374</v>
       </c>
       <c r="B155" t="n">
-        <v>91780</v>
+        <v>57654</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>553517</v>
+        <v>553523</v>
       </c>
       <c r="R155" t="n">
-        <v>6705421</v>
+        <v>6705404</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17449,47 +17457,38 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127314447</v>
+        <v>127314391</v>
       </c>
       <c r="B156" t="n">
-        <v>98443</v>
+        <v>57657</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -17498,10 +17497,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>553387</v>
+        <v>553375</v>
       </c>
       <c r="R156" t="n">
-        <v>6704938</v>
+        <v>6705433</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17534,6 +17533,11 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17560,10 +17564,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127314433</v>
+        <v>127314387</v>
       </c>
       <c r="B157" t="n">
-        <v>98443</v>
+        <v>91780</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17571,43 +17575,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>553366</v>
+        <v>553517</v>
       </c>
       <c r="R157" t="n">
-        <v>6704886</v>
+        <v>6705421</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17763,53 +17758,50 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127314374</v>
+        <v>127314362</v>
       </c>
       <c r="B159" t="n">
-        <v>57654</v>
+        <v>4772</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100049</v>
+        <v>100299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
       <c r="M159" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N159" t="inlineStr"/>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>553523</v>
+        <v>553526</v>
       </c>
       <c r="R159" t="n">
-        <v>6705404</v>
+        <v>6705221</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17868,38 +17860,47 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127314391</v>
+        <v>127314447</v>
       </c>
       <c r="B160" t="n">
-        <v>57657</v>
+        <v>98443</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -17908,10 +17909,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>553375</v>
+        <v>553387</v>
       </c>
       <c r="R160" t="n">
-        <v>6705433</v>
+        <v>6704938</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17944,11 +17945,6 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17975,38 +17971,42 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127314362</v>
+        <v>127314433</v>
       </c>
       <c r="B161" t="n">
-        <v>4772</v>
+        <v>98443</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
@@ -18015,10 +18015,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>553526</v>
+        <v>553366</v>
       </c>
       <c r="R161" t="n">
-        <v>6705221</v>
+        <v>6704886</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18961,42 +18961,42 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>127314386</v>
+        <v>127314426</v>
       </c>
       <c r="B170" t="n">
-        <v>92628</v>
+        <v>98443</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
@@ -19005,10 +19005,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>553414</v>
+        <v>553452</v>
       </c>
       <c r="R170" t="n">
-        <v>6704970</v>
+        <v>6705056</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19067,38 +19067,47 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127314393</v>
+        <v>127314455</v>
       </c>
       <c r="B171" t="n">
-        <v>57657</v>
+        <v>98443</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
@@ -19107,10 +19116,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>553521</v>
+        <v>553431</v>
       </c>
       <c r="R171" t="n">
-        <v>6705364</v>
+        <v>6704842</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19147,7 +19156,7 @@
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19174,42 +19183,42 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>127314426</v>
+        <v>127314386</v>
       </c>
       <c r="B172" t="n">
-        <v>98443</v>
+        <v>92628</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
@@ -19218,10 +19227,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>553452</v>
+        <v>553414</v>
       </c>
       <c r="R172" t="n">
-        <v>6705056</v>
+        <v>6704970</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19280,47 +19289,38 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127314455</v>
+        <v>127314393</v>
       </c>
       <c r="B173" t="n">
-        <v>98443</v>
+        <v>57657</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
@@ -19329,10 +19329,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>553431</v>
+        <v>553521</v>
       </c>
       <c r="R173" t="n">
-        <v>6704842</v>
+        <v>6705364</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19369,7 +19369,7 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>3 blomstjälkar</t>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19396,50 +19396,45 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127314392</v>
+        <v>127314355</v>
       </c>
       <c r="B174" t="n">
-        <v>57657</v>
+        <v>91684</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P174" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>553395</v>
+        <v>553451</v>
       </c>
       <c r="R174" t="n">
-        <v>6704765</v>
+        <v>6705503</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19472,11 +19467,6 @@
       <c r="AA174" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19503,45 +19493,50 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127314355</v>
+        <v>127314392</v>
       </c>
       <c r="B175" t="n">
-        <v>91684</v>
+        <v>57657</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P175" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>553451</v>
+        <v>553395</v>
       </c>
       <c r="R175" t="n">
-        <v>6705503</v>
+        <v>6704765</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19574,6 +19569,11 @@
       <c r="AA175" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -20762,45 +20762,59 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>127314390</v>
+        <v>127314436</v>
       </c>
       <c r="B187" t="n">
-        <v>91622</v>
+        <v>98443</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P187" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>553386</v>
+        <v>553571</v>
       </c>
       <c r="R187" t="n">
-        <v>6704777</v>
+        <v>6705315</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20833,6 +20847,11 @@
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20859,7 +20878,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>127314436</v>
+        <v>127314453</v>
       </c>
       <c r="B188" t="n">
         <v>98443</v>
@@ -20889,7 +20908,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -20908,10 +20927,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>553571</v>
+        <v>553477</v>
       </c>
       <c r="R188" t="n">
-        <v>6705315</v>
+        <v>6705197</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20944,11 +20963,6 @@
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC188" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20975,7 +20989,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>127314453</v>
+        <v>127314461</v>
       </c>
       <c r="B189" t="n">
         <v>98443</v>
@@ -21013,21 +21027,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P189" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>553477</v>
+        <v>553335</v>
       </c>
       <c r="R189" t="n">
-        <v>6705197</v>
+        <v>6704846</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21086,7 +21095,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>127314461</v>
+        <v>127314464</v>
       </c>
       <c r="B190" t="n">
         <v>98443</v>
@@ -21130,10 +21139,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>553335</v>
+        <v>553470</v>
       </c>
       <c r="R190" t="n">
-        <v>6704846</v>
+        <v>6705234</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21192,54 +21201,45 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>127314464</v>
+        <v>127314390</v>
       </c>
       <c r="B191" t="n">
-        <v>98443</v>
+        <v>91622</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>553470</v>
+        <v>553386</v>
       </c>
       <c r="R191" t="n">
-        <v>6705234</v>
+        <v>6704777</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -22877,40 +22877,59 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>127314406</v>
+        <v>127314412</v>
       </c>
       <c r="B207" t="n">
-        <v>91733</v>
+        <v>98443</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P207" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>553517</v>
+        <v>553337</v>
       </c>
       <c r="R207" t="n">
-        <v>6705421</v>
+        <v>6704813</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22969,7 +22988,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>127314412</v>
+        <v>127314431</v>
       </c>
       <c r="B208" t="n">
         <v>98443</v>
@@ -22999,7 +23018,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -23007,21 +23026,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P208" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>553337</v>
+        <v>553442</v>
       </c>
       <c r="R208" t="n">
-        <v>6704813</v>
+        <v>6705095</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23080,54 +23094,40 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>127314431</v>
+        <v>127314406</v>
       </c>
       <c r="B209" t="n">
-        <v>98443</v>
+        <v>91733</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J209" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>553442</v>
+        <v>553517</v>
       </c>
       <c r="R209" t="n">
-        <v>6705095</v>
+        <v>6705421</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>

--- a/artfynd/A 18040-2021 artfynd.xlsx
+++ b/artfynd/A 18040-2021 artfynd.xlsx
@@ -13779,7 +13779,7 @@
         <v>127314388</v>
       </c>
       <c r="B121" t="n">
-        <v>91780</v>
+        <v>91784</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>127314375</v>
       </c>
       <c r="B122" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13975,50 +13975,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127314407</v>
+        <v>127314398</v>
       </c>
       <c r="B123" t="n">
-        <v>98443</v>
+        <v>97325</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>553477</v>
+        <v>553472</v>
       </c>
       <c r="R123" t="n">
-        <v>6705175</v>
+        <v>6705479</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14051,11 +14046,6 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>få synliga bladrosetter</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14082,10 +14072,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127314398</v>
+        <v>127314397</v>
       </c>
       <c r="B124" t="n">
-        <v>97321</v>
+        <v>97325</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14117,10 +14107,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>553472</v>
+        <v>553527</v>
       </c>
       <c r="R124" t="n">
-        <v>6705479</v>
+        <v>6705221</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14179,45 +14169,50 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127314397</v>
+        <v>127314407</v>
       </c>
       <c r="B125" t="n">
-        <v>97321</v>
+        <v>98447</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>553527</v>
+        <v>553477</v>
       </c>
       <c r="R125" t="n">
-        <v>6705221</v>
+        <v>6705175</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14250,6 +14245,11 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>få synliga bladrosetter</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14276,38 +14276,47 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127314372</v>
+        <v>127314416</v>
       </c>
       <c r="B126" t="n">
-        <v>57654</v>
+        <v>98447</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -14316,10 +14325,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>553488</v>
+        <v>553356</v>
       </c>
       <c r="R126" t="n">
-        <v>6705460</v>
+        <v>6704786</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14352,6 +14361,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14378,10 +14392,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127314416</v>
+        <v>127314432</v>
       </c>
       <c r="B127" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14408,7 +14422,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -14416,21 +14430,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>553356</v>
+        <v>553508</v>
       </c>
       <c r="R127" t="n">
-        <v>6704786</v>
+        <v>6705194</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14463,11 +14472,6 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14497,7 +14501,7 @@
         <v>127314435</v>
       </c>
       <c r="B128" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14613,7 +14617,7 @@
         <v>127314415</v>
       </c>
       <c r="B129" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14726,42 +14730,38 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127314432</v>
+        <v>127314372</v>
       </c>
       <c r="B130" t="n">
-        <v>98443</v>
+        <v>57658</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -14770,10 +14770,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>553508</v>
+        <v>553488</v>
       </c>
       <c r="R130" t="n">
-        <v>6705194</v>
+        <v>6705460</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14832,45 +14832,59 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127314350</v>
+        <v>127314452</v>
       </c>
       <c r="B131" t="n">
-        <v>91326</v>
+        <v>98447</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>553465</v>
+        <v>553418</v>
       </c>
       <c r="R131" t="n">
-        <v>6705219</v>
+        <v>6705084</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14929,10 +14943,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127314336</v>
+        <v>127314410</v>
       </c>
       <c r="B132" t="n">
-        <v>91684</v>
+        <v>98447</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14940,34 +14954,43 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>553429</v>
+        <v>553422</v>
       </c>
       <c r="R132" t="n">
-        <v>6705077</v>
+        <v>6705072</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15026,45 +15049,54 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127314347</v>
+        <v>127314465</v>
       </c>
       <c r="B133" t="n">
-        <v>91326</v>
+        <v>98447</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>553419</v>
+        <v>553488</v>
       </c>
       <c r="R133" t="n">
-        <v>6705073</v>
+        <v>6705263</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15123,10 +15155,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127314345</v>
+        <v>127314347</v>
       </c>
       <c r="B134" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15158,10 +15190,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>553386</v>
+        <v>553419</v>
       </c>
       <c r="R134" t="n">
-        <v>6704777</v>
+        <v>6705073</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15220,32 +15252,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127314341</v>
+        <v>127314336</v>
       </c>
       <c r="B135" t="n">
-        <v>91326</v>
+        <v>91688</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15291,11 +15323,6 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15322,32 +15349,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127314468</v>
+        <v>127314345</v>
       </c>
       <c r="B136" t="n">
-        <v>91913</v>
+        <v>91330</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1179</v>
+        <v>1202</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15357,10 +15384,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>553482</v>
+        <v>553386</v>
       </c>
       <c r="R136" t="n">
-        <v>6705183</v>
+        <v>6704777</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15393,11 +15420,6 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Återfynd</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15424,59 +15446,45 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127314452</v>
+        <v>127314341</v>
       </c>
       <c r="B137" t="n">
-        <v>98443</v>
+        <v>91330</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>553418</v>
+        <v>553429</v>
       </c>
       <c r="R137" t="n">
-        <v>6705084</v>
+        <v>6705077</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15509,6 +15517,11 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15535,54 +15548,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127314410</v>
+        <v>127314350</v>
       </c>
       <c r="B138" t="n">
-        <v>98443</v>
+        <v>91330</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>553422</v>
+        <v>553465</v>
       </c>
       <c r="R138" t="n">
-        <v>6705072</v>
+        <v>6705219</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15641,10 +15645,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127314465</v>
+        <v>127314468</v>
       </c>
       <c r="B139" t="n">
-        <v>98443</v>
+        <v>91917</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15652,43 +15656,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220787</v>
+        <v>1179</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Peck) Donk</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>553488</v>
+        <v>553482</v>
       </c>
       <c r="R139" t="n">
-        <v>6705263</v>
+        <v>6705183</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15721,6 +15716,11 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Återfynd</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15747,10 +15747,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127314473</v>
+        <v>127314370</v>
       </c>
       <c r="B140" t="n">
-        <v>57578</v>
+        <v>57658</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15758,16 +15758,16 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100001</v>
+        <v>100049</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -15776,21 +15776,24 @@
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>553415</v>
+        <v>553311</v>
       </c>
       <c r="R140" t="n">
-        <v>6705462</v>
+        <v>6704717</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15823,11 +15826,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Fjädrar på "slaktbord"</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15854,10 +15852,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127314370</v>
+        <v>127314473</v>
       </c>
       <c r="B141" t="n">
-        <v>57654</v>
+        <v>57582</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15865,16 +15863,16 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -15883,24 +15881,21 @@
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>553311</v>
+        <v>553415</v>
       </c>
       <c r="R141" t="n">
-        <v>6704717</v>
+        <v>6705462</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15933,6 +15928,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Fjädrar på "slaktbord"</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15962,7 +15962,7 @@
         <v>127314441</v>
       </c>
       <c r="B142" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         <v>127314442</v>
       </c>
       <c r="B143" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>127314417</v>
       </c>
       <c r="B144" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16287,47 +16287,38 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127314424</v>
+        <v>127314380</v>
       </c>
       <c r="B145" t="n">
-        <v>98443</v>
+        <v>57658</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -16336,10 +16327,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>553422</v>
+        <v>553479</v>
       </c>
       <c r="R145" t="n">
-        <v>6704824</v>
+        <v>6705480</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16398,47 +16389,38 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127314454</v>
+        <v>127314376</v>
       </c>
       <c r="B146" t="n">
-        <v>98443</v>
+        <v>57658</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -16447,10 +16429,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>553347</v>
+        <v>553380</v>
       </c>
       <c r="R146" t="n">
-        <v>6705040</v>
+        <v>6704935</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16483,11 +16465,6 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>7 blomstjälkar</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16514,38 +16491,47 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127314376</v>
+        <v>127314424</v>
       </c>
       <c r="B147" t="n">
-        <v>57654</v>
+        <v>98447</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -16554,10 +16540,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>553380</v>
+        <v>553422</v>
       </c>
       <c r="R147" t="n">
-        <v>6704935</v>
+        <v>6704824</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16616,38 +16602,47 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127314380</v>
+        <v>127314454</v>
       </c>
       <c r="B148" t="n">
-        <v>57654</v>
+        <v>98447</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -16656,10 +16651,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>553479</v>
+        <v>553347</v>
       </c>
       <c r="R148" t="n">
-        <v>6705480</v>
+        <v>6705040</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16692,6 +16687,11 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>7 blomstjälkar</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16721,7 +16721,7 @@
         <v>127314343</v>
       </c>
       <c r="B149" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16818,7 +16818,7 @@
         <v>127314342</v>
       </c>
       <c r="B150" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16915,7 +16915,7 @@
         <v>127314405</v>
       </c>
       <c r="B151" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17017,7 +17017,7 @@
         <v>127314411</v>
       </c>
       <c r="B152" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17128,7 +17128,7 @@
         <v>127314419</v>
       </c>
       <c r="B153" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17244,7 +17244,7 @@
         <v>127314450</v>
       </c>
       <c r="B154" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17352,53 +17352,59 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127314374</v>
+        <v>127314447</v>
       </c>
       <c r="B155" t="n">
-        <v>57654</v>
+        <v>98447</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N155" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>553523</v>
+        <v>553387</v>
       </c>
       <c r="R155" t="n">
-        <v>6705404</v>
+        <v>6704938</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17457,38 +17463,42 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127314391</v>
+        <v>127314433</v>
       </c>
       <c r="B156" t="n">
-        <v>57657</v>
+        <v>98447</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -17497,10 +17507,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>553375</v>
+        <v>553366</v>
       </c>
       <c r="R156" t="n">
-        <v>6705433</v>
+        <v>6704886</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17533,11 +17543,6 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17564,32 +17569,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127314387</v>
+        <v>127314385</v>
       </c>
       <c r="B157" t="n">
-        <v>91780</v>
+        <v>56957</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1209</v>
+        <v>100038</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17599,10 +17604,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>553517</v>
+        <v>553426</v>
       </c>
       <c r="R157" t="n">
-        <v>6705421</v>
+        <v>6704786</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17661,45 +17666,50 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127314385</v>
+        <v>127314391</v>
       </c>
       <c r="B158" t="n">
-        <v>56953</v>
+        <v>57661</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100038</v>
+        <v>100109</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>553426</v>
+        <v>553375</v>
       </c>
       <c r="R158" t="n">
-        <v>6704786</v>
+        <v>6705433</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17732,6 +17742,11 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17758,50 +17773,45 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127314362</v>
+        <v>127314387</v>
       </c>
       <c r="B159" t="n">
-        <v>4772</v>
+        <v>91784</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100299</v>
+        <v>1209</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>553526</v>
+        <v>553517</v>
       </c>
       <c r="R159" t="n">
-        <v>6705221</v>
+        <v>6705421</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17860,59 +17870,53 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127314447</v>
+        <v>127314374</v>
       </c>
       <c r="B160" t="n">
-        <v>98443</v>
+        <v>57658</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>553387</v>
+        <v>553523</v>
       </c>
       <c r="R160" t="n">
-        <v>6704938</v>
+        <v>6705404</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17971,42 +17975,38 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127314433</v>
+        <v>127314362</v>
       </c>
       <c r="B161" t="n">
-        <v>98443</v>
+        <v>4773</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
@@ -18015,10 +18015,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>553366</v>
+        <v>553526</v>
       </c>
       <c r="R161" t="n">
-        <v>6704886</v>
+        <v>6705221</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18080,7 +18080,7 @@
         <v>127314443</v>
       </c>
       <c r="B162" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>127314448</v>
       </c>
       <c r="B163" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>127314434</v>
       </c>
       <c r="B164" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>127314451</v>
       </c>
       <c r="B165" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>127314421</v>
       </c>
       <c r="B166" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18635,7 +18635,7 @@
         <v>127314439</v>
       </c>
       <c r="B167" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18751,7 +18751,7 @@
         <v>127314409</v>
       </c>
       <c r="B168" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>127314460</v>
       </c>
       <c r="B169" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18961,42 +18961,42 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>127314426</v>
+        <v>127314386</v>
       </c>
       <c r="B170" t="n">
-        <v>98443</v>
+        <v>92632</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
@@ -19005,10 +19005,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>553452</v>
+        <v>553414</v>
       </c>
       <c r="R170" t="n">
-        <v>6705056</v>
+        <v>6704970</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19067,47 +19067,38 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127314455</v>
+        <v>127314393</v>
       </c>
       <c r="B171" t="n">
-        <v>98443</v>
+        <v>57661</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
@@ -19116,10 +19107,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>553431</v>
+        <v>553521</v>
       </c>
       <c r="R171" t="n">
-        <v>6704842</v>
+        <v>6705364</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19156,7 +19147,7 @@
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>3 blomstjälkar</t>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19183,42 +19174,42 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>127314386</v>
+        <v>127314426</v>
       </c>
       <c r="B172" t="n">
-        <v>92628</v>
+        <v>98447</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
@@ -19227,10 +19218,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>553414</v>
+        <v>553452</v>
       </c>
       <c r="R172" t="n">
-        <v>6704970</v>
+        <v>6705056</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19289,38 +19280,47 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127314393</v>
+        <v>127314455</v>
       </c>
       <c r="B173" t="n">
-        <v>57657</v>
+        <v>98447</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr"/>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
@@ -19329,10 +19329,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>553521</v>
+        <v>553431</v>
       </c>
       <c r="R173" t="n">
-        <v>6705364</v>
+        <v>6704842</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19369,7 +19369,7 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19396,45 +19396,50 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127314355</v>
+        <v>127314392</v>
       </c>
       <c r="B174" t="n">
-        <v>91684</v>
+        <v>57661</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P174" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>553451</v>
+        <v>553395</v>
       </c>
       <c r="R174" t="n">
-        <v>6705503</v>
+        <v>6704765</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19467,6 +19472,11 @@
       <c r="AA174" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19493,38 +19503,38 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127314392</v>
+        <v>127314482</v>
       </c>
       <c r="B175" t="n">
-        <v>57657</v>
+        <v>5177</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="M175" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
@@ -19533,10 +19543,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>553395</v>
+        <v>553322</v>
       </c>
       <c r="R175" t="n">
-        <v>6704765</v>
+        <v>6704727</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19569,11 +19579,6 @@
       <c r="AA175" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19600,50 +19605,45 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>127314482</v>
+        <v>127314355</v>
       </c>
       <c r="B176" t="n">
-        <v>5176</v>
+        <v>91688</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>100526</v>
+        <v>2062</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P176" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>553322</v>
+        <v>553451</v>
       </c>
       <c r="R176" t="n">
-        <v>6704727</v>
+        <v>6705503</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19705,7 +19705,7 @@
         <v>127314438</v>
       </c>
       <c r="B177" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>127314459</v>
       </c>
       <c r="B178" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19924,10 +19924,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>127314467</v>
+        <v>127314395</v>
       </c>
       <c r="B179" t="n">
-        <v>105478</v>
+        <v>97325</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19935,21 +19935,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19959,10 +19959,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>553468</v>
+        <v>553357</v>
       </c>
       <c r="R179" t="n">
-        <v>6705155</v>
+        <v>6704877</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20021,10 +20021,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>127314395</v>
+        <v>127314467</v>
       </c>
       <c r="B180" t="n">
-        <v>97321</v>
+        <v>105484</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20032,21 +20032,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -20056,10 +20056,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>553357</v>
+        <v>553468</v>
       </c>
       <c r="R180" t="n">
-        <v>6704877</v>
+        <v>6705155</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20118,38 +20118,38 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>127314484</v>
+        <v>127314378</v>
       </c>
       <c r="B181" t="n">
-        <v>5176</v>
+        <v>57658</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="M181" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
@@ -20158,10 +20158,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>553430</v>
+        <v>553468</v>
       </c>
       <c r="R181" t="n">
-        <v>6705087</v>
+        <v>6705210</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20220,47 +20220,38 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127314413</v>
+        <v>127314381</v>
       </c>
       <c r="B182" t="n">
-        <v>98443</v>
+        <v>57658</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
@@ -20269,10 +20260,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>553349</v>
+        <v>553468</v>
       </c>
       <c r="R182" t="n">
-        <v>6704994</v>
+        <v>6705451</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20305,11 +20296,6 @@
       <c r="AA182" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC182" t="inlineStr">
-        <is>
-          <t>5 blomstjälkar</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20336,47 +20322,38 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>127314418</v>
+        <v>127314484</v>
       </c>
       <c r="B183" t="n">
-        <v>98443</v>
+        <v>5177</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
@@ -20385,10 +20362,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>553496</v>
+        <v>553430</v>
       </c>
       <c r="R183" t="n">
-        <v>6705280</v>
+        <v>6705087</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20421,11 +20398,6 @@
       <c r="AA183" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -20452,10 +20424,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>127314430</v>
+        <v>127314413</v>
       </c>
       <c r="B184" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20482,7 +20454,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -20490,16 +20462,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P184" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>553358</v>
+        <v>553349</v>
       </c>
       <c r="R184" t="n">
-        <v>6705058</v>
+        <v>6704994</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20532,6 +20509,11 @@
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>5 blomstjälkar</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20558,38 +20540,47 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>127314381</v>
+        <v>127314418</v>
       </c>
       <c r="B185" t="n">
-        <v>57654</v>
+        <v>98447</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr"/>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
@@ -20598,10 +20589,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>553468</v>
+        <v>553496</v>
       </c>
       <c r="R185" t="n">
-        <v>6705451</v>
+        <v>6705280</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20634,6 +20625,11 @@
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -20660,38 +20656,42 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>127314378</v>
+        <v>127314430</v>
       </c>
       <c r="B186" t="n">
-        <v>57654</v>
+        <v>98447</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr"/>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
@@ -20700,10 +20700,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>553468</v>
+        <v>553358</v>
       </c>
       <c r="R186" t="n">
-        <v>6705210</v>
+        <v>6705058</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20765,7 +20765,7 @@
         <v>127314436</v>
       </c>
       <c r="B187" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>127314453</v>
       </c>
       <c r="B188" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20989,10 +20989,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>127314461</v>
+        <v>127314464</v>
       </c>
       <c r="B189" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21033,10 +21033,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>553335</v>
+        <v>553470</v>
       </c>
       <c r="R189" t="n">
-        <v>6704846</v>
+        <v>6705234</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21095,10 +21095,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>127314464</v>
+        <v>127314461</v>
       </c>
       <c r="B190" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21139,10 +21139,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>553470</v>
+        <v>553335</v>
       </c>
       <c r="R190" t="n">
-        <v>6705234</v>
+        <v>6704846</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21204,7 +21204,7 @@
         <v>127314390</v>
       </c>
       <c r="B191" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>127314339</v>
       </c>
       <c r="B192" t="n">
-        <v>91684</v>
+        <v>91688</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         <v>127310426</v>
       </c>
       <c r="B193" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
         <v>127314408</v>
       </c>
       <c r="B194" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21619,7 +21619,7 @@
         <v>127314423</v>
       </c>
       <c r="B195" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21727,45 +21727,54 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>127314389</v>
+        <v>127314425</v>
       </c>
       <c r="B196" t="n">
-        <v>91622</v>
+        <v>98447</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>553364</v>
+        <v>553466</v>
       </c>
       <c r="R196" t="n">
-        <v>6704790</v>
+        <v>6705077</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21824,53 +21833,59 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>127314363</v>
+        <v>127314420</v>
       </c>
       <c r="B197" t="n">
-        <v>57817</v>
+        <v>98447</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr"/>
-      <c r="K197" t="inlineStr"/>
-      <c r="L197" t="inlineStr"/>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N197" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>553336</v>
+        <v>553426</v>
       </c>
       <c r="R197" t="n">
-        <v>6704944</v>
+        <v>6704821</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21903,6 +21918,11 @@
       <c r="AA197" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21929,10 +21949,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>127314425</v>
+        <v>127314445</v>
       </c>
       <c r="B198" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21959,7 +21979,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -21967,16 +21987,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>553466</v>
+        <v>553364</v>
       </c>
       <c r="R198" t="n">
-        <v>6705077</v>
+        <v>6704996</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22035,10 +22060,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>127314420</v>
+        <v>127314429</v>
       </c>
       <c r="B199" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22073,21 +22098,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P199" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>553426</v>
+        <v>553414</v>
       </c>
       <c r="R199" t="n">
-        <v>6704821</v>
+        <v>6704864</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22120,11 +22140,6 @@
       <c r="AA199" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC199" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22151,42 +22166,38 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127314429</v>
+        <v>127314379</v>
       </c>
       <c r="B200" t="n">
-        <v>98443</v>
+        <v>57658</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -22195,10 +22206,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>553414</v>
+        <v>553485</v>
       </c>
       <c r="R200" t="n">
-        <v>6704864</v>
+        <v>6705230</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22257,47 +22268,38 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>127314445</v>
+        <v>127314382</v>
       </c>
       <c r="B201" t="n">
-        <v>98443</v>
+        <v>57311</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>220787</v>
+        <v>100063</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr"/>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
@@ -22306,10 +22308,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>553364</v>
+        <v>553494</v>
       </c>
       <c r="R201" t="n">
-        <v>6704996</v>
+        <v>6705461</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22368,10 +22370,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127314379</v>
+        <v>127314363</v>
       </c>
       <c r="B202" t="n">
-        <v>57654</v>
+        <v>57821</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22379,39 +22381,42 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
       <c r="M202" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>553485</v>
+        <v>553336</v>
       </c>
       <c r="R202" t="n">
-        <v>6705230</v>
+        <v>6704944</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22470,10 +22475,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>127314382</v>
+        <v>127314389</v>
       </c>
       <c r="B203" t="n">
-        <v>57307</v>
+        <v>91626</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22481,39 +22486,34 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>100063</v>
+        <v>658</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P203" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>553494</v>
+        <v>553364</v>
       </c>
       <c r="R203" t="n">
-        <v>6705461</v>
+        <v>6704790</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22575,7 +22575,7 @@
         <v>127314325</v>
       </c>
       <c r="B204" t="n">
-        <v>5196</v>
+        <v>5197</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>127314354</v>
       </c>
       <c r="B205" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>127314360</v>
       </c>
       <c r="B206" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -22880,7 +22880,7 @@
         <v>127314412</v>
       </c>
       <c r="B207" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -22991,7 +22991,7 @@
         <v>127314431</v>
       </c>
       <c r="B208" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23097,7 +23097,7 @@
         <v>127314406</v>
       </c>
       <c r="B209" t="n">
-        <v>91733</v>
+        <v>91737</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -23186,51 +23186,48 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>127310539</v>
+        <v>127314477</v>
       </c>
       <c r="B210" t="n">
-        <v>91538</v>
+        <v>92620</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>1106</v>
+        <v>4364</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
-      <c r="J210" t="inlineStr"/>
-      <c r="K210" t="inlineStr"/>
-      <c r="N210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
+          <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>553483</v>
+        <v>553371</v>
       </c>
       <c r="R210" t="n">
-        <v>6705051</v>
+        <v>6704731</v>
       </c>
       <c r="S210" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -23262,73 +23259,80 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>Många gamla fruktkroppar i häxring</t>
+        </is>
+      </c>
       <c r="AD210" t="b">
         <v>0</v>
       </c>
       <c r="AE210" t="b">
         <v>0</v>
       </c>
-      <c r="AF210" t="inlineStr"/>
       <c r="AG210" t="b">
         <v>0</v>
       </c>
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>127314477</v>
+        <v>127310539</v>
       </c>
       <c r="B211" t="n">
-        <v>92616</v>
+        <v>91542</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>4364</v>
+        <v>1106</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Morkullberget södra, Dlr</t>
+          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>553371</v>
+        <v>553483</v>
       </c>
       <c r="R211" t="n">
-        <v>6704731</v>
+        <v>6705051</v>
       </c>
       <c r="S211" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -23360,29 +23364,25 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC211" t="inlineStr">
-        <is>
-          <t>Många gamla fruktkroppar i häxring</t>
-        </is>
-      </c>
       <c r="AD211" t="b">
         <v>0</v>
       </c>
       <c r="AE211" t="b">
         <v>0</v>
       </c>
+      <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="b">
         <v>0</v>
       </c>
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
@@ -23392,7 +23392,7 @@
         <v>127314368</v>
       </c>
       <c r="B212" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -23494,7 +23494,7 @@
         <v>127314480</v>
       </c>
       <c r="B213" t="n">
-        <v>5176</v>
+        <v>5177</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -23596,7 +23596,7 @@
         <v>127314428</v>
       </c>
       <c r="B214" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>127314351</v>
       </c>
       <c r="B215" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>127314348</v>
       </c>
       <c r="B216" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>127314396</v>
       </c>
       <c r="B217" t="n">
-        <v>97321</v>
+        <v>97325</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -23990,50 +23990,45 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>127314377</v>
+        <v>127314337</v>
       </c>
       <c r="B218" t="n">
-        <v>57654</v>
+        <v>91688</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>100049</v>
+        <v>2062</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
-      <c r="M218" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P218" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>553336</v>
+        <v>553419</v>
       </c>
       <c r="R218" t="n">
-        <v>6704827</v>
+        <v>6705073</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24066,6 +24061,11 @@
       <c r="AA218" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>Eventuellt S. delicata</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24092,45 +24092,50 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127314337</v>
+        <v>127314377</v>
       </c>
       <c r="B219" t="n">
-        <v>91684</v>
+        <v>57658</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>2062</v>
+        <v>100049</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>553419</v>
+        <v>553336</v>
       </c>
       <c r="R219" t="n">
-        <v>6705073</v>
+        <v>6704827</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24163,11 +24168,6 @@
       <c r="AA219" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC219" t="inlineStr">
-        <is>
-          <t>Eventuellt S. delicata</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -24194,32 +24194,32 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127314471</v>
+        <v>127314394</v>
       </c>
       <c r="B220" t="n">
-        <v>79014</v>
+        <v>97325</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -24229,10 +24229,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>553406</v>
+        <v>553498</v>
       </c>
       <c r="R220" t="n">
-        <v>6705479</v>
+        <v>6705418</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24294,7 +24294,7 @@
         <v>127314422</v>
       </c>
       <c r="B221" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -24405,7 +24405,7 @@
         <v>127314437</v>
       </c>
       <c r="B222" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -24516,7 +24516,7 @@
         <v>127314456</v>
       </c>
       <c r="B223" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         <v>127314457</v>
       </c>
       <c r="B224" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -24735,54 +24735,45 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127314463</v>
+        <v>127314471</v>
       </c>
       <c r="B225" t="n">
-        <v>98443</v>
+        <v>79018</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J225" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>553433</v>
+        <v>553406</v>
       </c>
       <c r="R225" t="n">
-        <v>6704902</v>
+        <v>6705479</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24841,10 +24832,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127314458</v>
+        <v>127314463</v>
       </c>
       <c r="B226" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -24871,7 +24862,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -24885,10 +24876,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>553526</v>
+        <v>553433</v>
       </c>
       <c r="R226" t="n">
-        <v>6705245</v>
+        <v>6704902</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24947,45 +24938,54 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127314394</v>
+        <v>127314458</v>
       </c>
       <c r="B227" t="n">
-        <v>97321</v>
+        <v>98447</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>553498</v>
+        <v>553526</v>
       </c>
       <c r="R227" t="n">
-        <v>6705418</v>
+        <v>6705245</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25047,7 +25047,7 @@
         <v>127314371</v>
       </c>
       <c r="B228" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>127314479</v>
       </c>
       <c r="B229" t="n">
-        <v>5176</v>
+        <v>5177</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -25251,7 +25251,7 @@
         <v>127314326</v>
       </c>
       <c r="B230" t="n">
-        <v>5196</v>
+        <v>5197</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -25353,7 +25353,7 @@
         <v>127314414</v>
       </c>
       <c r="B231" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -25469,7 +25469,7 @@
         <v>127314444</v>
       </c>
       <c r="B232" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -25575,7 +25575,7 @@
         <v>127314440</v>
       </c>
       <c r="B233" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>127314486</v>
       </c>
       <c r="B234" t="n">
-        <v>91698</v>
+        <v>91702</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>

--- a/artfynd/A 18040-2021 artfynd.xlsx
+++ b/artfynd/A 18040-2021 artfynd.xlsx
@@ -13776,10 +13776,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127314388</v>
+        <v>127314407</v>
       </c>
       <c r="B121" t="n">
-        <v>91784</v>
+        <v>98447</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13787,34 +13787,39 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>553411</v>
+        <v>553477</v>
       </c>
       <c r="R121" t="n">
-        <v>6705072</v>
+        <v>6705175</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13847,6 +13852,11 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>få synliga bladrosetter</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14169,10 +14179,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127314407</v>
+        <v>127314388</v>
       </c>
       <c r="B125" t="n">
-        <v>98447</v>
+        <v>91784</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14180,39 +14190,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>553477</v>
+        <v>553411</v>
       </c>
       <c r="R125" t="n">
-        <v>6705175</v>
+        <v>6705072</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14245,11 +14250,6 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>få synliga bladrosetter</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14276,47 +14276,38 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127314416</v>
+        <v>127314372</v>
       </c>
       <c r="B126" t="n">
-        <v>98447</v>
+        <v>57658</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -14325,10 +14316,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>553356</v>
+        <v>553488</v>
       </c>
       <c r="R126" t="n">
-        <v>6704786</v>
+        <v>6705460</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14361,11 +14352,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14392,7 +14378,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127314432</v>
+        <v>127314416</v>
       </c>
       <c r="B127" t="n">
         <v>98447</v>
@@ -14422,7 +14408,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -14430,16 +14416,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>553508</v>
+        <v>553356</v>
       </c>
       <c r="R127" t="n">
-        <v>6705194</v>
+        <v>6704786</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14472,6 +14463,11 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14498,7 +14494,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127314435</v>
+        <v>127314432</v>
       </c>
       <c r="B128" t="n">
         <v>98447</v>
@@ -14528,7 +14524,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -14536,21 +14532,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>553476</v>
+        <v>553508</v>
       </c>
       <c r="R128" t="n">
-        <v>6705068</v>
+        <v>6705194</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14583,11 +14574,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>12 blomstjälkar</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14614,7 +14600,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127314415</v>
+        <v>127314435</v>
       </c>
       <c r="B129" t="n">
         <v>98447</v>
@@ -14644,7 +14630,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -14663,10 +14649,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>553463</v>
+        <v>553476</v>
       </c>
       <c r="R129" t="n">
-        <v>6705155</v>
+        <v>6705068</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14703,7 +14689,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>4 blomstjälkar</t>
+          <t>12 blomstjälkar</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14730,38 +14716,47 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127314372</v>
+        <v>127314415</v>
       </c>
       <c r="B130" t="n">
-        <v>57658</v>
+        <v>98447</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -14770,10 +14765,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>553488</v>
+        <v>553463</v>
       </c>
       <c r="R130" t="n">
-        <v>6705460</v>
+        <v>6705155</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14806,6 +14801,11 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14832,10 +14832,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127314452</v>
+        <v>127314336</v>
       </c>
       <c r="B131" t="n">
-        <v>98447</v>
+        <v>91688</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14843,48 +14843,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>553418</v>
+        <v>553429</v>
       </c>
       <c r="R131" t="n">
-        <v>6705084</v>
+        <v>6705077</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14943,54 +14929,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127314410</v>
+        <v>127314347</v>
       </c>
       <c r="B132" t="n">
-        <v>98447</v>
+        <v>91330</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>553422</v>
+        <v>553419</v>
       </c>
       <c r="R132" t="n">
-        <v>6705072</v>
+        <v>6705073</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15049,54 +15026,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127314465</v>
+        <v>127314345</v>
       </c>
       <c r="B133" t="n">
-        <v>98447</v>
+        <v>91330</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>553488</v>
+        <v>553386</v>
       </c>
       <c r="R133" t="n">
-        <v>6705263</v>
+        <v>6704777</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15155,7 +15123,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127314347</v>
+        <v>127314341</v>
       </c>
       <c r="B134" t="n">
         <v>91330</v>
@@ -15190,10 +15158,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>553419</v>
+        <v>553429</v>
       </c>
       <c r="R134" t="n">
-        <v>6705073</v>
+        <v>6705077</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15226,6 +15194,11 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15252,32 +15225,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127314336</v>
+        <v>127314350</v>
       </c>
       <c r="B135" t="n">
-        <v>91688</v>
+        <v>91330</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15287,10 +15260,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>553429</v>
+        <v>553465</v>
       </c>
       <c r="R135" t="n">
-        <v>6705077</v>
+        <v>6705219</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15349,32 +15322,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127314345</v>
+        <v>127314468</v>
       </c>
       <c r="B136" t="n">
-        <v>91330</v>
+        <v>91917</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1202</v>
+        <v>1179</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15384,10 +15357,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>553386</v>
+        <v>553482</v>
       </c>
       <c r="R136" t="n">
-        <v>6704777</v>
+        <v>6705183</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15420,6 +15393,11 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Återfynd</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15446,45 +15424,59 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127314341</v>
+        <v>127314452</v>
       </c>
       <c r="B137" t="n">
-        <v>91330</v>
+        <v>98447</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>553429</v>
+        <v>553418</v>
       </c>
       <c r="R137" t="n">
-        <v>6705077</v>
+        <v>6705084</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15517,11 +15509,6 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15548,45 +15535,54 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127314350</v>
+        <v>127314410</v>
       </c>
       <c r="B138" t="n">
-        <v>91330</v>
+        <v>98447</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>553465</v>
+        <v>553422</v>
       </c>
       <c r="R138" t="n">
-        <v>6705219</v>
+        <v>6705072</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15645,10 +15641,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127314468</v>
+        <v>127314465</v>
       </c>
       <c r="B139" t="n">
-        <v>91917</v>
+        <v>98447</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15656,34 +15652,43 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1179</v>
+        <v>220787</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>553482</v>
+        <v>553488</v>
       </c>
       <c r="R139" t="n">
-        <v>6705183</v>
+        <v>6705263</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15716,11 +15721,6 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Återfynd</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15852,38 +15852,42 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127314473</v>
+        <v>127314441</v>
       </c>
       <c r="B141" t="n">
-        <v>57582</v>
+        <v>98447</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -15892,10 +15896,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>553415</v>
+        <v>553422</v>
       </c>
       <c r="R141" t="n">
-        <v>6705462</v>
+        <v>6704986</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15928,11 +15932,6 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Fjädrar på "slaktbord"</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15959,7 +15958,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127314441</v>
+        <v>127314442</v>
       </c>
       <c r="B142" t="n">
         <v>98447</v>
@@ -16003,10 +16002,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>553422</v>
+        <v>553423</v>
       </c>
       <c r="R142" t="n">
-        <v>6704986</v>
+        <v>6704914</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16065,7 +16064,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127314442</v>
+        <v>127314417</v>
       </c>
       <c r="B143" t="n">
         <v>98447</v>
@@ -16095,7 +16094,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -16103,16 +16102,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>553423</v>
+        <v>553413</v>
       </c>
       <c r="R143" t="n">
-        <v>6704914</v>
+        <v>6704868</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16145,6 +16149,11 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16171,47 +16180,38 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127314417</v>
+        <v>127314473</v>
       </c>
       <c r="B144" t="n">
-        <v>98447</v>
+        <v>57582</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -16220,10 +16220,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>553413</v>
+        <v>553415</v>
       </c>
       <c r="R144" t="n">
-        <v>6704868</v>
+        <v>6705462</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16260,7 +16260,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>3 blomstjälkar</t>
+          <t>Fjädrar på "slaktbord"</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16287,38 +16287,47 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127314380</v>
+        <v>127314424</v>
       </c>
       <c r="B145" t="n">
-        <v>57658</v>
+        <v>98447</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -16327,10 +16336,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>553479</v>
+        <v>553422</v>
       </c>
       <c r="R145" t="n">
-        <v>6705480</v>
+        <v>6704824</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16389,38 +16398,47 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127314376</v>
+        <v>127314454</v>
       </c>
       <c r="B146" t="n">
-        <v>57658</v>
+        <v>98447</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -16429,10 +16447,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>553380</v>
+        <v>553347</v>
       </c>
       <c r="R146" t="n">
-        <v>6704935</v>
+        <v>6705040</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16465,6 +16483,11 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>7 blomstjälkar</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16491,47 +16514,38 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127314424</v>
+        <v>127314376</v>
       </c>
       <c r="B147" t="n">
-        <v>98447</v>
+        <v>57658</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -16540,10 +16554,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>553422</v>
+        <v>553380</v>
       </c>
       <c r="R147" t="n">
-        <v>6704824</v>
+        <v>6704935</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16602,47 +16616,38 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127314454</v>
+        <v>127314380</v>
       </c>
       <c r="B148" t="n">
-        <v>98447</v>
+        <v>57658</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -16651,10 +16656,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>553347</v>
+        <v>553479</v>
       </c>
       <c r="R148" t="n">
-        <v>6705040</v>
+        <v>6705480</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16687,11 +16692,6 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>7 blomstjälkar</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16718,45 +16718,59 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127314343</v>
+        <v>127314411</v>
       </c>
       <c r="B149" t="n">
-        <v>91330</v>
+        <v>98447</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>553388</v>
+        <v>553500</v>
       </c>
       <c r="R149" t="n">
-        <v>6704753</v>
+        <v>6705175</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16815,45 +16829,59 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127314342</v>
+        <v>127314419</v>
       </c>
       <c r="B150" t="n">
-        <v>91330</v>
+        <v>98447</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>553347</v>
+        <v>553343</v>
       </c>
       <c r="R150" t="n">
-        <v>6704783</v>
+        <v>6704786</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16886,6 +16914,11 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16912,38 +16945,47 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127314405</v>
+        <v>127314450</v>
       </c>
       <c r="B151" t="n">
-        <v>8450</v>
+        <v>98447</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -16952,10 +16994,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>553521</v>
+        <v>553340</v>
       </c>
       <c r="R151" t="n">
-        <v>6705364</v>
+        <v>6704784</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17014,59 +17056,45 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127314411</v>
+        <v>127314343</v>
       </c>
       <c r="B152" t="n">
-        <v>98447</v>
+        <v>91330</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>553500</v>
+        <v>553388</v>
       </c>
       <c r="R152" t="n">
-        <v>6705175</v>
+        <v>6704753</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17125,59 +17153,45 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>127314419</v>
+        <v>127314342</v>
       </c>
       <c r="B153" t="n">
-        <v>98447</v>
+        <v>91330</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>553343</v>
+        <v>553347</v>
       </c>
       <c r="R153" t="n">
-        <v>6704786</v>
+        <v>6704783</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17210,11 +17224,6 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17241,47 +17250,38 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127314450</v>
+        <v>127314405</v>
       </c>
       <c r="B154" t="n">
-        <v>98447</v>
+        <v>8450</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -17290,10 +17290,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>553340</v>
+        <v>553521</v>
       </c>
       <c r="R154" t="n">
-        <v>6704784</v>
+        <v>6705364</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17352,47 +17352,38 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127314447</v>
+        <v>127314391</v>
       </c>
       <c r="B155" t="n">
-        <v>98447</v>
+        <v>57661</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
@@ -17401,10 +17392,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>553387</v>
+        <v>553375</v>
       </c>
       <c r="R155" t="n">
-        <v>6704938</v>
+        <v>6705433</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17437,6 +17428,11 @@
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17463,54 +17459,53 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127314433</v>
+        <v>127314374</v>
       </c>
       <c r="B156" t="n">
-        <v>98447</v>
+        <v>57658</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>553366</v>
+        <v>553523</v>
       </c>
       <c r="R156" t="n">
-        <v>6704886</v>
+        <v>6705404</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17666,50 +17661,45 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127314391</v>
+        <v>127314387</v>
       </c>
       <c r="B158" t="n">
-        <v>57661</v>
+        <v>91784</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>553375</v>
+        <v>553517</v>
       </c>
       <c r="R158" t="n">
-        <v>6705433</v>
+        <v>6705421</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17742,11 +17732,6 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17773,45 +17758,50 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127314387</v>
+        <v>127314362</v>
       </c>
       <c r="B159" t="n">
-        <v>91784</v>
+        <v>4773</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1209</v>
+        <v>100299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>553517</v>
+        <v>553526</v>
       </c>
       <c r="R159" t="n">
-        <v>6705421</v>
+        <v>6705221</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17870,53 +17860,59 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127314374</v>
+        <v>127314447</v>
       </c>
       <c r="B160" t="n">
-        <v>57658</v>
+        <v>98447</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N160" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>553523</v>
+        <v>553387</v>
       </c>
       <c r="R160" t="n">
-        <v>6705404</v>
+        <v>6704938</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17975,38 +17971,42 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127314362</v>
+        <v>127314433</v>
       </c>
       <c r="B161" t="n">
-        <v>4773</v>
+        <v>98447</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
@@ -18015,10 +18015,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>553526</v>
+        <v>553366</v>
       </c>
       <c r="R161" t="n">
-        <v>6705221</v>
+        <v>6704886</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18961,42 +18961,38 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>127314386</v>
+        <v>127314393</v>
       </c>
       <c r="B170" t="n">
-        <v>92632</v>
+        <v>57661</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
@@ -19005,10 +19001,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>553414</v>
+        <v>553521</v>
       </c>
       <c r="R170" t="n">
-        <v>6704970</v>
+        <v>6705364</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19041,6 +19037,11 @@
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19067,38 +19068,42 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127314393</v>
+        <v>127314386</v>
       </c>
       <c r="B171" t="n">
-        <v>57661</v>
+        <v>92632</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
@@ -19107,10 +19112,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>553521</v>
+        <v>553414</v>
       </c>
       <c r="R171" t="n">
-        <v>6705364</v>
+        <v>6704970</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19143,11 +19148,6 @@
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19503,50 +19503,45 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127314482</v>
+        <v>127314355</v>
       </c>
       <c r="B175" t="n">
-        <v>5177</v>
+        <v>91688</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>100526</v>
+        <v>2062</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P175" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>553322</v>
+        <v>553451</v>
       </c>
       <c r="R175" t="n">
-        <v>6704727</v>
+        <v>6705503</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19605,45 +19600,50 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>127314355</v>
+        <v>127314482</v>
       </c>
       <c r="B176" t="n">
-        <v>91688</v>
+        <v>5177</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>2062</v>
+        <v>100526</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P176" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>553451</v>
+        <v>553322</v>
       </c>
       <c r="R176" t="n">
-        <v>6705503</v>
+        <v>6704727</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19924,10 +19924,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>127314395</v>
+        <v>127314484</v>
       </c>
       <c r="B179" t="n">
-        <v>97325</v>
+        <v>5177</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19935,34 +19935,39 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P179" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>553357</v>
+        <v>553430</v>
       </c>
       <c r="R179" t="n">
-        <v>6704877</v>
+        <v>6705087</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20021,45 +20026,59 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>127314467</v>
+        <v>127314413</v>
       </c>
       <c r="B180" t="n">
-        <v>105484</v>
+        <v>98447</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>553468</v>
+        <v>553349</v>
       </c>
       <c r="R180" t="n">
-        <v>6705155</v>
+        <v>6704994</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20092,6 +20111,11 @@
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>5 blomstjälkar</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20118,38 +20142,47 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>127314378</v>
+        <v>127314418</v>
       </c>
       <c r="B181" t="n">
-        <v>57658</v>
+        <v>98447</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr"/>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
@@ -20158,10 +20191,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>553468</v>
+        <v>553496</v>
       </c>
       <c r="R181" t="n">
-        <v>6705210</v>
+        <v>6705280</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20194,6 +20227,11 @@
       <c r="AA181" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20220,38 +20258,42 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127314381</v>
+        <v>127314430</v>
       </c>
       <c r="B182" t="n">
-        <v>57658</v>
+        <v>98447</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr"/>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
@@ -20260,10 +20302,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>553468</v>
+        <v>553358</v>
       </c>
       <c r="R182" t="n">
-        <v>6705451</v>
+        <v>6705058</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20322,10 +20364,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>127314484</v>
+        <v>127314395</v>
       </c>
       <c r="B183" t="n">
-        <v>5177</v>
+        <v>97325</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20333,39 +20375,34 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P183" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>553430</v>
+        <v>553357</v>
       </c>
       <c r="R183" t="n">
-        <v>6705087</v>
+        <v>6704877</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20424,47 +20461,38 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>127314413</v>
+        <v>127314381</v>
       </c>
       <c r="B184" t="n">
-        <v>98447</v>
+        <v>57658</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
@@ -20473,10 +20501,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>553349</v>
+        <v>553468</v>
       </c>
       <c r="R184" t="n">
-        <v>6704994</v>
+        <v>6705451</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20509,11 +20537,6 @@
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>5 blomstjälkar</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20540,47 +20563,38 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>127314418</v>
+        <v>127314378</v>
       </c>
       <c r="B185" t="n">
-        <v>98447</v>
+        <v>57658</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
@@ -20589,10 +20603,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>553496</v>
+        <v>553468</v>
       </c>
       <c r="R185" t="n">
-        <v>6705280</v>
+        <v>6705210</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20625,11 +20639,6 @@
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -20656,54 +20665,45 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>127314430</v>
+        <v>127314467</v>
       </c>
       <c r="B186" t="n">
-        <v>98447</v>
+        <v>105484</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J186" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>553358</v>
+        <v>553468</v>
       </c>
       <c r="R186" t="n">
-        <v>6705058</v>
+        <v>6705155</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20762,59 +20762,45 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>127314436</v>
+        <v>127314390</v>
       </c>
       <c r="B187" t="n">
-        <v>98447</v>
+        <v>91626</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J187" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>553571</v>
+        <v>553386</v>
       </c>
       <c r="R187" t="n">
-        <v>6705315</v>
+        <v>6704777</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20847,11 +20833,6 @@
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC187" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20878,7 +20859,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>127314453</v>
+        <v>127314436</v>
       </c>
       <c r="B188" t="n">
         <v>98447</v>
@@ -20908,7 +20889,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -20927,10 +20908,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>553477</v>
+        <v>553571</v>
       </c>
       <c r="R188" t="n">
-        <v>6705197</v>
+        <v>6705315</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20963,6 +20944,11 @@
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20989,7 +20975,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>127314464</v>
+        <v>127314453</v>
       </c>
       <c r="B189" t="n">
         <v>98447</v>
@@ -21027,16 +21013,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P189" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>553470</v>
+        <v>553477</v>
       </c>
       <c r="R189" t="n">
-        <v>6705234</v>
+        <v>6705197</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21095,7 +21086,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>127314461</v>
+        <v>127314464</v>
       </c>
       <c r="B190" t="n">
         <v>98447</v>
@@ -21139,10 +21130,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>553335</v>
+        <v>553470</v>
       </c>
       <c r="R190" t="n">
-        <v>6704846</v>
+        <v>6705234</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21201,45 +21192,54 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>127314390</v>
+        <v>127314461</v>
       </c>
       <c r="B191" t="n">
-        <v>91626</v>
+        <v>98447</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P191" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>553386</v>
+        <v>553335</v>
       </c>
       <c r="R191" t="n">
-        <v>6704777</v>
+        <v>6704846</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21727,54 +21727,45 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>127314425</v>
+        <v>127314389</v>
       </c>
       <c r="B196" t="n">
-        <v>98447</v>
+        <v>91626</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>553466</v>
+        <v>553364</v>
       </c>
       <c r="R196" t="n">
-        <v>6705077</v>
+        <v>6704790</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21833,59 +21824,53 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>127314420</v>
+        <v>127314363</v>
       </c>
       <c r="B197" t="n">
-        <v>98447</v>
+        <v>57821</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>553426</v>
+        <v>553336</v>
       </c>
       <c r="R197" t="n">
-        <v>6704821</v>
+        <v>6704944</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21918,11 +21903,6 @@
       <c r="AA197" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC197" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21949,47 +21929,38 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>127314445</v>
+        <v>127314379</v>
       </c>
       <c r="B198" t="n">
-        <v>98447</v>
+        <v>57658</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
@@ -21998,10 +21969,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>553364</v>
+        <v>553485</v>
       </c>
       <c r="R198" t="n">
-        <v>6704996</v>
+        <v>6705230</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22060,42 +22031,38 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>127314429</v>
+        <v>127314382</v>
       </c>
       <c r="B199" t="n">
-        <v>98447</v>
+        <v>57311</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>220787</v>
+        <v>100063</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
@@ -22104,10 +22071,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>553414</v>
+        <v>553494</v>
       </c>
       <c r="R199" t="n">
-        <v>6704864</v>
+        <v>6705461</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22166,27 +22133,27 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127314379</v>
+        <v>127314325</v>
       </c>
       <c r="B200" t="n">
-        <v>57658</v>
+        <v>5197</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -22197,7 +22164,7 @@
       <c r="I200" t="inlineStr"/>
       <c r="M200" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -22206,10 +22173,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>553485</v>
+        <v>553508</v>
       </c>
       <c r="R200" t="n">
-        <v>6705230</v>
+        <v>6705185</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22268,38 +22235,42 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>127314382</v>
+        <v>127314425</v>
       </c>
       <c r="B201" t="n">
-        <v>57311</v>
+        <v>98447</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>100063</v>
+        <v>220787</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr"/>
-      <c r="M201" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
@@ -22308,10 +22279,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>553494</v>
+        <v>553466</v>
       </c>
       <c r="R201" t="n">
-        <v>6705461</v>
+        <v>6705077</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22370,53 +22341,59 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127314363</v>
+        <v>127314420</v>
       </c>
       <c r="B202" t="n">
-        <v>57821</v>
+        <v>98447</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr"/>
-      <c r="K202" t="inlineStr"/>
-      <c r="L202" t="inlineStr"/>
-      <c r="M202" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N202" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P202" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>553336</v>
+        <v>553426</v>
       </c>
       <c r="R202" t="n">
-        <v>6704944</v>
+        <v>6704821</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22449,6 +22426,11 @@
       <c r="AA202" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22475,35 +22457,49 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>127314389</v>
+        <v>127314445</v>
       </c>
       <c r="B203" t="n">
-        <v>91626</v>
+        <v>98447</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P203" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
@@ -22513,7 +22509,7 @@
         <v>553364</v>
       </c>
       <c r="R203" t="n">
-        <v>6704790</v>
+        <v>6704996</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22572,38 +22568,42 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>127314325</v>
+        <v>127314429</v>
       </c>
       <c r="B204" t="n">
-        <v>5197</v>
+        <v>98447</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr"/>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
@@ -22612,10 +22612,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>553508</v>
+        <v>553414</v>
       </c>
       <c r="R204" t="n">
-        <v>6705185</v>
+        <v>6704864</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22771,32 +22771,32 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>127314360</v>
+        <v>127314412</v>
       </c>
       <c r="B206" t="n">
-        <v>56853</v>
+        <v>98447</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -22804,16 +22804,26 @@
           <t>5</t>
         </is>
       </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P206" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>553530</v>
+        <v>553337</v>
       </c>
       <c r="R206" t="n">
-        <v>6705203</v>
+        <v>6704813</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22846,11 +22856,6 @@
       <c r="AA206" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC206" t="inlineStr">
-        <is>
-          <t>Höna med minst fyra ungar</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22877,7 +22882,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>127314412</v>
+        <v>127314431</v>
       </c>
       <c r="B207" t="n">
         <v>98447</v>
@@ -22907,7 +22912,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -22915,21 +22920,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P207" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>553337</v>
+        <v>553442</v>
       </c>
       <c r="R207" t="n">
-        <v>6704813</v>
+        <v>6705095</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22988,54 +22988,40 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>127314431</v>
+        <v>127314406</v>
       </c>
       <c r="B208" t="n">
-        <v>98447</v>
+        <v>91737</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J208" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>553442</v>
+        <v>553517</v>
       </c>
       <c r="R208" t="n">
-        <v>6705095</v>
+        <v>6705421</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23094,40 +23080,49 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>127314406</v>
+        <v>127314360</v>
       </c>
       <c r="B209" t="n">
-        <v>91737</v>
+        <v>56853</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6040186</v>
+        <v>100138</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P209" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>553517</v>
+        <v>553530</v>
       </c>
       <c r="R209" t="n">
-        <v>6705421</v>
+        <v>6705203</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23160,6 +23155,11 @@
       <c r="AA209" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>Höna med minst fyra ungar</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -23288,51 +23288,53 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>127310539</v>
+        <v>127314480</v>
       </c>
       <c r="B211" t="n">
-        <v>91542</v>
+        <v>5177</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>1106</v>
+        <v>100526</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
-      <c r="J211" t="inlineStr"/>
-      <c r="K211" t="inlineStr"/>
-      <c r="N211" t="inlineStr"/>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
+          <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>553483</v>
+        <v>553399</v>
       </c>
       <c r="R211" t="n">
-        <v>6705051</v>
+        <v>6704947</v>
       </c>
       <c r="S211" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -23370,19 +23372,18 @@
       <c r="AE211" t="b">
         <v>0</v>
       </c>
-      <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="b">
         <v>0</v>
       </c>
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
@@ -23491,53 +23492,51 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>127314480</v>
+        <v>127310539</v>
       </c>
       <c r="B213" t="n">
-        <v>5177</v>
+        <v>91542</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>100526</v>
+        <v>1106</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
-      <c r="M213" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
+      <c r="N213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Morkullberget södra, Dlr</t>
+          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>553399</v>
+        <v>553483</v>
       </c>
       <c r="R213" t="n">
-        <v>6704947</v>
+        <v>6705051</v>
       </c>
       <c r="S213" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -23575,18 +23574,19 @@
       <c r="AE213" t="b">
         <v>0</v>
       </c>
+      <c r="AF213" t="inlineStr"/>
       <c r="AG213" t="b">
         <v>0</v>
       </c>
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
@@ -23990,32 +23990,32 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>127314337</v>
+        <v>127314471</v>
       </c>
       <c r="B218" t="n">
-        <v>91688</v>
+        <v>79018</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -24025,10 +24025,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>553419</v>
+        <v>553406</v>
       </c>
       <c r="R218" t="n">
-        <v>6705073</v>
+        <v>6705479</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24061,11 +24061,6 @@
       <c r="AA218" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC218" t="inlineStr">
-        <is>
-          <t>Eventuellt S. delicata</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24092,50 +24087,45 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127314377</v>
+        <v>127314337</v>
       </c>
       <c r="B219" t="n">
-        <v>57658</v>
+        <v>91688</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>100049</v>
+        <v>2062</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>553336</v>
+        <v>553419</v>
       </c>
       <c r="R219" t="n">
-        <v>6704827</v>
+        <v>6705073</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24168,6 +24158,11 @@
       <c r="AA219" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>Eventuellt S. delicata</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -24194,45 +24189,50 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127314394</v>
+        <v>127314377</v>
       </c>
       <c r="B220" t="n">
-        <v>97325</v>
+        <v>57658</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P220" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>553498</v>
+        <v>553336</v>
       </c>
       <c r="R220" t="n">
-        <v>6705418</v>
+        <v>6704827</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24735,45 +24735,54 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127314471</v>
+        <v>127314463</v>
       </c>
       <c r="B225" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P225" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>553406</v>
+        <v>553433</v>
       </c>
       <c r="R225" t="n">
-        <v>6705479</v>
+        <v>6704902</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24832,7 +24841,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127314463</v>
+        <v>127314458</v>
       </c>
       <c r="B226" t="n">
         <v>98447</v>
@@ -24862,7 +24871,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -24876,10 +24885,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>553433</v>
+        <v>553526</v>
       </c>
       <c r="R226" t="n">
-        <v>6704902</v>
+        <v>6705245</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24938,54 +24947,45 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127314458</v>
+        <v>127314394</v>
       </c>
       <c r="B227" t="n">
-        <v>98447</v>
+        <v>97325</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J227" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>553526</v>
+        <v>553498</v>
       </c>
       <c r="R227" t="n">
-        <v>6705245</v>
+        <v>6705418</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25044,38 +25044,38 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127314371</v>
+        <v>127314479</v>
       </c>
       <c r="B228" t="n">
-        <v>57658</v>
+        <v>5177</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
       <c r="M228" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
@@ -25084,10 +25084,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>553336</v>
+        <v>553496</v>
       </c>
       <c r="R228" t="n">
-        <v>6704723</v>
+        <v>6705218</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25146,38 +25146,38 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127314479</v>
+        <v>127314371</v>
       </c>
       <c r="B229" t="n">
-        <v>5177</v>
+        <v>57658</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
       <c r="M229" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -25186,10 +25186,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>553496</v>
+        <v>553336</v>
       </c>
       <c r="R229" t="n">
-        <v>6705218</v>
+        <v>6704723</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>

--- a/artfynd/A 18040-2021 artfynd.xlsx
+++ b/artfynd/A 18040-2021 artfynd.xlsx
@@ -13776,10 +13776,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127314407</v>
+        <v>127314388</v>
       </c>
       <c r="B121" t="n">
-        <v>98447</v>
+        <v>91784</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13787,39 +13787,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>553477</v>
+        <v>553411</v>
       </c>
       <c r="R121" t="n">
-        <v>6705175</v>
+        <v>6705072</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13852,11 +13847,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>få synliga bladrosetter</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14179,10 +14169,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127314388</v>
+        <v>127314407</v>
       </c>
       <c r="B125" t="n">
-        <v>91784</v>
+        <v>98447</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14190,34 +14180,39 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>553411</v>
+        <v>553477</v>
       </c>
       <c r="R125" t="n">
-        <v>6705072</v>
+        <v>6705175</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14250,6 +14245,11 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>få synliga bladrosetter</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14832,10 +14832,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127314336</v>
+        <v>127314452</v>
       </c>
       <c r="B131" t="n">
-        <v>91688</v>
+        <v>98447</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14843,34 +14843,48 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>553429</v>
+        <v>553418</v>
       </c>
       <c r="R131" t="n">
-        <v>6705077</v>
+        <v>6705084</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14929,45 +14943,54 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127314347</v>
+        <v>127314410</v>
       </c>
       <c r="B132" t="n">
-        <v>91330</v>
+        <v>98447</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>553419</v>
+        <v>553422</v>
       </c>
       <c r="R132" t="n">
-        <v>6705073</v>
+        <v>6705072</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15026,45 +15049,54 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127314345</v>
+        <v>127314465</v>
       </c>
       <c r="B133" t="n">
-        <v>91330</v>
+        <v>98447</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>553386</v>
+        <v>553488</v>
       </c>
       <c r="R133" t="n">
-        <v>6704777</v>
+        <v>6705263</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15123,7 +15155,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127314341</v>
+        <v>127314347</v>
       </c>
       <c r="B134" t="n">
         <v>91330</v>
@@ -15158,10 +15190,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>553429</v>
+        <v>553419</v>
       </c>
       <c r="R134" t="n">
-        <v>6705077</v>
+        <v>6705073</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15194,11 +15226,6 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15225,7 +15252,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127314350</v>
+        <v>127314345</v>
       </c>
       <c r="B135" t="n">
         <v>91330</v>
@@ -15260,10 +15287,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>553465</v>
+        <v>553386</v>
       </c>
       <c r="R135" t="n">
-        <v>6705219</v>
+        <v>6704777</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15322,32 +15349,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127314468</v>
+        <v>127314341</v>
       </c>
       <c r="B136" t="n">
-        <v>91917</v>
+        <v>91330</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1179</v>
+        <v>1202</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15357,10 +15384,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>553482</v>
+        <v>553429</v>
       </c>
       <c r="R136" t="n">
-        <v>6705183</v>
+        <v>6705077</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15397,7 +15424,7 @@
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>Återfynd</t>
+          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15424,59 +15451,45 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127314452</v>
+        <v>127314350</v>
       </c>
       <c r="B137" t="n">
-        <v>98447</v>
+        <v>91330</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>553418</v>
+        <v>553465</v>
       </c>
       <c r="R137" t="n">
-        <v>6705084</v>
+        <v>6705219</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15535,10 +15548,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127314410</v>
+        <v>127314468</v>
       </c>
       <c r="B138" t="n">
-        <v>98447</v>
+        <v>91917</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15546,43 +15559,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220787</v>
+        <v>1179</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Peck) Donk</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>553422</v>
+        <v>553482</v>
       </c>
       <c r="R138" t="n">
-        <v>6705072</v>
+        <v>6705183</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15615,6 +15619,11 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Återfynd</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15641,10 +15650,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127314465</v>
+        <v>127314336</v>
       </c>
       <c r="B139" t="n">
-        <v>98447</v>
+        <v>91688</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15652,43 +15661,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>553488</v>
+        <v>553429</v>
       </c>
       <c r="R139" t="n">
-        <v>6705263</v>
+        <v>6705077</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16287,47 +16287,38 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127314424</v>
+        <v>127314376</v>
       </c>
       <c r="B145" t="n">
-        <v>98447</v>
+        <v>57658</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -16336,10 +16327,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>553422</v>
+        <v>553380</v>
       </c>
       <c r="R145" t="n">
-        <v>6704824</v>
+        <v>6704935</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16398,47 +16389,38 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127314454</v>
+        <v>127314380</v>
       </c>
       <c r="B146" t="n">
-        <v>98447</v>
+        <v>57658</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -16447,10 +16429,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>553347</v>
+        <v>553479</v>
       </c>
       <c r="R146" t="n">
-        <v>6705040</v>
+        <v>6705480</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16483,11 +16465,6 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>7 blomstjälkar</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16514,38 +16491,47 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127314376</v>
+        <v>127314424</v>
       </c>
       <c r="B147" t="n">
-        <v>57658</v>
+        <v>98447</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -16554,10 +16540,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>553380</v>
+        <v>553422</v>
       </c>
       <c r="R147" t="n">
-        <v>6704935</v>
+        <v>6704824</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16616,38 +16602,47 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127314380</v>
+        <v>127314454</v>
       </c>
       <c r="B148" t="n">
-        <v>57658</v>
+        <v>98447</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -16656,10 +16651,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>553479</v>
+        <v>553347</v>
       </c>
       <c r="R148" t="n">
-        <v>6705480</v>
+        <v>6705040</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16692,6 +16687,11 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>7 blomstjälkar</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17352,50 +17352,45 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127314391</v>
+        <v>127314387</v>
       </c>
       <c r="B155" t="n">
-        <v>57661</v>
+        <v>91784</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>553375</v>
+        <v>553517</v>
       </c>
       <c r="R155" t="n">
-        <v>6705433</v>
+        <v>6705421</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17428,11 +17423,6 @@
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17459,10 +17449,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127314374</v>
+        <v>127314391</v>
       </c>
       <c r="B156" t="n">
-        <v>57658</v>
+        <v>57661</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17470,16 +17460,16 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -17488,24 +17478,21 @@
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
       <c r="M156" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N156" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>553523</v>
+        <v>553375</v>
       </c>
       <c r="R156" t="n">
-        <v>6705404</v>
+        <v>6705433</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17538,6 +17525,11 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17564,45 +17556,53 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127314385</v>
+        <v>127314374</v>
       </c>
       <c r="B157" t="n">
-        <v>56957</v>
+        <v>57658</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100038</v>
+        <v>100049</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>553426</v>
+        <v>553523</v>
       </c>
       <c r="R157" t="n">
-        <v>6704786</v>
+        <v>6705404</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17661,32 +17661,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127314387</v>
+        <v>127314385</v>
       </c>
       <c r="B158" t="n">
-        <v>91784</v>
+        <v>56957</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1209</v>
+        <v>100038</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17696,10 +17696,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>553517</v>
+        <v>553426</v>
       </c>
       <c r="R158" t="n">
-        <v>6705421</v>
+        <v>6704786</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -19924,38 +19924,38 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>127314484</v>
+        <v>127314381</v>
       </c>
       <c r="B179" t="n">
-        <v>5177</v>
+        <v>57658</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="M179" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
@@ -19964,10 +19964,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>553430</v>
+        <v>553468</v>
       </c>
       <c r="R179" t="n">
-        <v>6705087</v>
+        <v>6705451</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20026,47 +20026,38 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>127314413</v>
+        <v>127314378</v>
       </c>
       <c r="B180" t="n">
-        <v>98447</v>
+        <v>57658</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
@@ -20075,10 +20066,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>553349</v>
+        <v>553468</v>
       </c>
       <c r="R180" t="n">
-        <v>6704994</v>
+        <v>6705210</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20111,11 +20102,6 @@
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>5 blomstjälkar</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20142,47 +20128,38 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>127314418</v>
+        <v>127314484</v>
       </c>
       <c r="B181" t="n">
-        <v>98447</v>
+        <v>5177</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
@@ -20191,10 +20168,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>553496</v>
+        <v>553430</v>
       </c>
       <c r="R181" t="n">
-        <v>6705280</v>
+        <v>6705087</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20227,11 +20204,6 @@
       <c r="AA181" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20258,54 +20230,45 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127314430</v>
+        <v>127314395</v>
       </c>
       <c r="B182" t="n">
-        <v>98447</v>
+        <v>97325</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>553358</v>
+        <v>553357</v>
       </c>
       <c r="R182" t="n">
-        <v>6705058</v>
+        <v>6704877</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20364,10 +20327,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>127314395</v>
+        <v>127314467</v>
       </c>
       <c r="B183" t="n">
-        <v>97325</v>
+        <v>105484</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20375,21 +20338,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -20399,10 +20362,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>553357</v>
+        <v>553468</v>
       </c>
       <c r="R183" t="n">
-        <v>6704877</v>
+        <v>6705155</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20461,38 +20424,47 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>127314381</v>
+        <v>127314413</v>
       </c>
       <c r="B184" t="n">
-        <v>57658</v>
+        <v>98447</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr"/>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
@@ -20501,10 +20473,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>553468</v>
+        <v>553349</v>
       </c>
       <c r="R184" t="n">
-        <v>6705451</v>
+        <v>6704994</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20537,6 +20509,11 @@
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>5 blomstjälkar</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20563,38 +20540,47 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>127314378</v>
+        <v>127314418</v>
       </c>
       <c r="B185" t="n">
-        <v>57658</v>
+        <v>98447</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr"/>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
@@ -20603,10 +20589,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>553468</v>
+        <v>553496</v>
       </c>
       <c r="R185" t="n">
-        <v>6705210</v>
+        <v>6705280</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20639,6 +20625,11 @@
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -20665,45 +20656,54 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>127314467</v>
+        <v>127314430</v>
       </c>
       <c r="B186" t="n">
-        <v>105484</v>
+        <v>98447</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>553468</v>
+        <v>553358</v>
       </c>
       <c r="R186" t="n">
-        <v>6705155</v>
+        <v>6705058</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20762,45 +20762,59 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>127314390</v>
+        <v>127314436</v>
       </c>
       <c r="B187" t="n">
-        <v>91626</v>
+        <v>98447</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P187" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>553386</v>
+        <v>553571</v>
       </c>
       <c r="R187" t="n">
-        <v>6704777</v>
+        <v>6705315</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20833,6 +20847,11 @@
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20859,7 +20878,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>127314436</v>
+        <v>127314453</v>
       </c>
       <c r="B188" t="n">
         <v>98447</v>
@@ -20889,7 +20908,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -20908,10 +20927,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>553571</v>
+        <v>553477</v>
       </c>
       <c r="R188" t="n">
-        <v>6705315</v>
+        <v>6705197</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20944,11 +20963,6 @@
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC188" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20975,7 +20989,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>127314453</v>
+        <v>127314464</v>
       </c>
       <c r="B189" t="n">
         <v>98447</v>
@@ -21013,21 +21027,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P189" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>553477</v>
+        <v>553470</v>
       </c>
       <c r="R189" t="n">
-        <v>6705197</v>
+        <v>6705234</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21086,7 +21095,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>127314464</v>
+        <v>127314461</v>
       </c>
       <c r="B190" t="n">
         <v>98447</v>
@@ -21130,10 +21139,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>553470</v>
+        <v>553335</v>
       </c>
       <c r="R190" t="n">
-        <v>6705234</v>
+        <v>6704846</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21192,54 +21201,45 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>127314461</v>
+        <v>127314390</v>
       </c>
       <c r="B191" t="n">
-        <v>98447</v>
+        <v>91626</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>553335</v>
+        <v>553386</v>
       </c>
       <c r="R191" t="n">
-        <v>6704846</v>
+        <v>6704777</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21298,10 +21298,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>127314339</v>
+        <v>127310426</v>
       </c>
       <c r="B192" t="n">
-        <v>91688</v>
+        <v>98447</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21309,37 +21309,53 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Morkullberget södra, Dlr</t>
+          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>553347</v>
+        <v>553479</v>
       </c>
       <c r="R192" t="n">
-        <v>6704783</v>
+        <v>6705057</v>
       </c>
       <c r="S192" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -21377,25 +21393,26 @@
       <c r="AE192" t="b">
         <v>0</v>
       </c>
+      <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="b">
         <v>0</v>
       </c>
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>127310426</v>
+        <v>127314408</v>
       </c>
       <c r="B193" t="n">
         <v>98447</v>
@@ -21423,36 +21440,25 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
-      <c r="L193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
+          <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>553479</v>
+        <v>553400</v>
       </c>
       <c r="R193" t="n">
-        <v>6705057</v>
+        <v>6705072</v>
       </c>
       <c r="S193" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -21484,32 +21490,36 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>få synliga bladrosetter</t>
+        </is>
+      </c>
       <c r="AD193" t="b">
         <v>0</v>
       </c>
       <c r="AE193" t="b">
         <v>0</v>
       </c>
-      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>127314408</v>
+        <v>127314423</v>
       </c>
       <c r="B194" t="n">
         <v>98447</v>
@@ -21537,7 +21547,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K194" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -21549,10 +21568,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>553400</v>
+        <v>553338</v>
       </c>
       <c r="R194" t="n">
-        <v>6705072</v>
+        <v>6704806</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21585,11 +21604,6 @@
       <c r="AA194" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>få synliga bladrosetter</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21616,10 +21630,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>127314423</v>
+        <v>127314339</v>
       </c>
       <c r="B195" t="n">
-        <v>98447</v>
+        <v>91688</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21627,48 +21641,34 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>553338</v>
+        <v>553347</v>
       </c>
       <c r="R195" t="n">
-        <v>6704806</v>
+        <v>6704783</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21727,10 +21727,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>127314389</v>
+        <v>127314379</v>
       </c>
       <c r="B196" t="n">
-        <v>91626</v>
+        <v>57658</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21738,34 +21738,39 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>553364</v>
+        <v>553485</v>
       </c>
       <c r="R196" t="n">
-        <v>6704790</v>
+        <v>6705230</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21824,10 +21829,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>127314363</v>
+        <v>127314382</v>
       </c>
       <c r="B197" t="n">
-        <v>57821</v>
+        <v>57311</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21835,42 +21840,39 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>103021</v>
+        <v>100063</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
-      <c r="K197" t="inlineStr"/>
-      <c r="L197" t="inlineStr"/>
       <c r="M197" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N197" t="inlineStr"/>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>553336</v>
+        <v>553494</v>
       </c>
       <c r="R197" t="n">
-        <v>6704944</v>
+        <v>6705461</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21929,10 +21931,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>127314379</v>
+        <v>127314389</v>
       </c>
       <c r="B198" t="n">
-        <v>57658</v>
+        <v>91626</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21940,39 +21942,34 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>553485</v>
+        <v>553364</v>
       </c>
       <c r="R198" t="n">
-        <v>6705230</v>
+        <v>6704790</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22031,38 +22028,38 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>127314382</v>
+        <v>127314325</v>
       </c>
       <c r="B199" t="n">
-        <v>57311</v>
+        <v>5197</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>100063</v>
+        <v>105930</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
       <c r="M199" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
@@ -22071,10 +22068,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>553494</v>
+        <v>553508</v>
       </c>
       <c r="R199" t="n">
-        <v>6705461</v>
+        <v>6705185</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22133,38 +22130,42 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127314325</v>
+        <v>127314425</v>
       </c>
       <c r="B200" t="n">
-        <v>5197</v>
+        <v>98447</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr"/>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -22173,10 +22174,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>553508</v>
+        <v>553466</v>
       </c>
       <c r="R200" t="n">
-        <v>6705185</v>
+        <v>6705077</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22235,7 +22236,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>127314425</v>
+        <v>127314420</v>
       </c>
       <c r="B201" t="n">
         <v>98447</v>
@@ -22273,16 +22274,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P201" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>553466</v>
+        <v>553426</v>
       </c>
       <c r="R201" t="n">
-        <v>6705077</v>
+        <v>6704821</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22315,6 +22321,11 @@
       <c r="AA201" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22341,7 +22352,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127314420</v>
+        <v>127314445</v>
       </c>
       <c r="B202" t="n">
         <v>98447</v>
@@ -22371,7 +22382,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -22381,7 +22392,7 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
@@ -22390,10 +22401,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>553426</v>
+        <v>553364</v>
       </c>
       <c r="R202" t="n">
-        <v>6704821</v>
+        <v>6704996</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22426,11 +22437,6 @@
       <c r="AA202" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22457,7 +22463,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>127314445</v>
+        <v>127314429</v>
       </c>
       <c r="B203" t="n">
         <v>98447</v>
@@ -22487,7 +22493,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -22495,21 +22501,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P203" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>553364</v>
+        <v>553414</v>
       </c>
       <c r="R203" t="n">
-        <v>6704996</v>
+        <v>6704864</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22568,54 +22569,53 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>127314429</v>
+        <v>127314363</v>
       </c>
       <c r="B204" t="n">
-        <v>98447</v>
+        <v>57821</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>553414</v>
+        <v>553336</v>
       </c>
       <c r="R204" t="n">
-        <v>6704864</v>
+        <v>6704944</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22771,32 +22771,32 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>127314412</v>
+        <v>127314360</v>
       </c>
       <c r="B206" t="n">
-        <v>98447</v>
+        <v>56853</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -22804,26 +22804,16 @@
           <t>5</t>
         </is>
       </c>
-      <c r="J206" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P206" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>553337</v>
+        <v>553530</v>
       </c>
       <c r="R206" t="n">
-        <v>6704813</v>
+        <v>6705203</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22856,6 +22846,11 @@
       <c r="AA206" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>Höna med minst fyra ungar</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22882,7 +22877,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>127314431</v>
+        <v>127314412</v>
       </c>
       <c r="B207" t="n">
         <v>98447</v>
@@ -22912,7 +22907,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -22920,16 +22915,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P207" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>553442</v>
+        <v>553337</v>
       </c>
       <c r="R207" t="n">
-        <v>6705095</v>
+        <v>6704813</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22988,40 +22988,54 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>127314406</v>
+        <v>127314431</v>
       </c>
       <c r="B208" t="n">
-        <v>91737</v>
+        <v>98447</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P208" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>553517</v>
+        <v>553442</v>
       </c>
       <c r="R208" t="n">
-        <v>6705421</v>
+        <v>6705095</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23080,49 +23094,40 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>127314360</v>
+        <v>127314406</v>
       </c>
       <c r="B209" t="n">
-        <v>56853</v>
+        <v>91737</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>553530</v>
+        <v>553517</v>
       </c>
       <c r="R209" t="n">
-        <v>6705203</v>
+        <v>6705421</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23155,11 +23160,6 @@
       <c r="AA209" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>Höna med minst fyra ungar</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -23186,48 +23186,51 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>127314477</v>
+        <v>127310539</v>
       </c>
       <c r="B210" t="n">
-        <v>92620</v>
+        <v>91542</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>4364</v>
+        <v>1106</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr"/>
+      <c r="K210" t="inlineStr"/>
+      <c r="N210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Morkullberget södra, Dlr</t>
+          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>553371</v>
+        <v>553483</v>
       </c>
       <c r="R210" t="n">
-        <v>6704731</v>
+        <v>6705051</v>
       </c>
       <c r="S210" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -23259,29 +23262,25 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC210" t="inlineStr">
-        <is>
-          <t>Många gamla fruktkroppar i häxring</t>
-        </is>
-      </c>
       <c r="AD210" t="b">
         <v>0</v>
       </c>
       <c r="AE210" t="b">
         <v>0</v>
       </c>
+      <c r="AF210" t="inlineStr"/>
       <c r="AG210" t="b">
         <v>0</v>
       </c>
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
@@ -23390,38 +23389,42 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>127314368</v>
+        <v>127314428</v>
       </c>
       <c r="B212" t="n">
-        <v>57658</v>
+        <v>98447</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr"/>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
@@ -23430,10 +23433,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>553500</v>
+        <v>553336</v>
       </c>
       <c r="R212" t="n">
-        <v>6705249</v>
+        <v>6704827</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23492,51 +23495,53 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>127310539</v>
+        <v>127314368</v>
       </c>
       <c r="B213" t="n">
-        <v>91542</v>
+        <v>57658</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>1106</v>
+        <v>100049</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
-      <c r="J213" t="inlineStr"/>
-      <c r="K213" t="inlineStr"/>
-      <c r="N213" t="inlineStr"/>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
+          <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>553483</v>
+        <v>553500</v>
       </c>
       <c r="R213" t="n">
-        <v>6705051</v>
+        <v>6705249</v>
       </c>
       <c r="S213" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -23574,73 +23579,63 @@
       <c r="AE213" t="b">
         <v>0</v>
       </c>
-      <c r="AF213" t="inlineStr"/>
       <c r="AG213" t="b">
         <v>0</v>
       </c>
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>127314428</v>
+        <v>127314477</v>
       </c>
       <c r="B214" t="n">
-        <v>98447</v>
+        <v>92620</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J214" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>553336</v>
+        <v>553371</v>
       </c>
       <c r="R214" t="n">
-        <v>6704827</v>
+        <v>6704731</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23673,6 +23668,11 @@
       <c r="AA214" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>Många gamla fruktkroppar i häxring</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -23990,32 +23990,32 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>127314471</v>
+        <v>127314337</v>
       </c>
       <c r="B218" t="n">
-        <v>79018</v>
+        <v>91688</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -24025,10 +24025,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>553406</v>
+        <v>553419</v>
       </c>
       <c r="R218" t="n">
-        <v>6705479</v>
+        <v>6705073</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24061,6 +24061,11 @@
       <c r="AA218" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>Eventuellt S. delicata</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24087,45 +24092,50 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127314337</v>
+        <v>127314377</v>
       </c>
       <c r="B219" t="n">
-        <v>91688</v>
+        <v>57658</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>2062</v>
+        <v>100049</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>553419</v>
+        <v>553336</v>
       </c>
       <c r="R219" t="n">
-        <v>6705073</v>
+        <v>6704827</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24158,11 +24168,6 @@
       <c r="AA219" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC219" t="inlineStr">
-        <is>
-          <t>Eventuellt S. delicata</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -24189,10 +24194,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127314377</v>
+        <v>127314471</v>
       </c>
       <c r="B220" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24200,39 +24205,34 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P220" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>553336</v>
+        <v>553406</v>
       </c>
       <c r="R220" t="n">
-        <v>6704827</v>
+        <v>6705479</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>

--- a/artfynd/A 18040-2021 artfynd.xlsx
+++ b/artfynd/A 18040-2021 artfynd.xlsx
@@ -13873,38 +13873,38 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127314375</v>
+        <v>127314407</v>
       </c>
       <c r="B122" t="n">
-        <v>57658</v>
+        <v>98447</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -13913,10 +13913,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>553537</v>
+        <v>553477</v>
       </c>
       <c r="R122" t="n">
-        <v>6705403</v>
+        <v>6705175</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13949,6 +13949,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>få synliga bladrosetter</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13975,45 +13980,50 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127314398</v>
+        <v>127314375</v>
       </c>
       <c r="B123" t="n">
-        <v>97325</v>
+        <v>57658</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>553472</v>
+        <v>553537</v>
       </c>
       <c r="R123" t="n">
-        <v>6705479</v>
+        <v>6705403</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14072,7 +14082,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127314397</v>
+        <v>127314398</v>
       </c>
       <c r="B124" t="n">
         <v>97325</v>
@@ -14107,10 +14117,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>553527</v>
+        <v>553472</v>
       </c>
       <c r="R124" t="n">
-        <v>6705221</v>
+        <v>6705479</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14169,50 +14179,45 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127314407</v>
+        <v>127314397</v>
       </c>
       <c r="B125" t="n">
-        <v>98447</v>
+        <v>97325</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>553477</v>
+        <v>553527</v>
       </c>
       <c r="R125" t="n">
-        <v>6705175</v>
+        <v>6705221</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14245,11 +14250,6 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>få synliga bladrosetter</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -19924,38 +19924,38 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>127314381</v>
+        <v>127314484</v>
       </c>
       <c r="B179" t="n">
-        <v>57658</v>
+        <v>5177</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="M179" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
@@ -19964,10 +19964,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>553468</v>
+        <v>553430</v>
       </c>
       <c r="R179" t="n">
-        <v>6705451</v>
+        <v>6705087</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20026,38 +20026,47 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>127314378</v>
+        <v>127314413</v>
       </c>
       <c r="B180" t="n">
-        <v>57658</v>
+        <v>98447</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr"/>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
@@ -20066,10 +20075,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>553468</v>
+        <v>553349</v>
       </c>
       <c r="R180" t="n">
-        <v>6705210</v>
+        <v>6704994</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20102,6 +20111,11 @@
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>5 blomstjälkar</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20128,38 +20142,47 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>127314484</v>
+        <v>127314418</v>
       </c>
       <c r="B181" t="n">
-        <v>5177</v>
+        <v>98447</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr"/>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
@@ -20168,10 +20191,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>553430</v>
+        <v>553496</v>
       </c>
       <c r="R181" t="n">
-        <v>6705087</v>
+        <v>6705280</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20204,6 +20227,11 @@
       <c r="AA181" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20230,45 +20258,54 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127314395</v>
+        <v>127314430</v>
       </c>
       <c r="B182" t="n">
-        <v>97325</v>
+        <v>98447</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>553357</v>
+        <v>553358</v>
       </c>
       <c r="R182" t="n">
-        <v>6704877</v>
+        <v>6705058</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20327,10 +20364,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>127314467</v>
+        <v>127314395</v>
       </c>
       <c r="B183" t="n">
-        <v>105484</v>
+        <v>97325</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20338,21 +20375,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -20362,10 +20399,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>553468</v>
+        <v>553357</v>
       </c>
       <c r="R183" t="n">
-        <v>6705155</v>
+        <v>6704877</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20424,47 +20461,38 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>127314413</v>
+        <v>127314381</v>
       </c>
       <c r="B184" t="n">
-        <v>98447</v>
+        <v>57658</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
@@ -20473,10 +20501,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>553349</v>
+        <v>553468</v>
       </c>
       <c r="R184" t="n">
-        <v>6704994</v>
+        <v>6705451</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20509,11 +20537,6 @@
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>5 blomstjälkar</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20540,47 +20563,38 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>127314418</v>
+        <v>127314378</v>
       </c>
       <c r="B185" t="n">
-        <v>98447</v>
+        <v>57658</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
@@ -20589,10 +20603,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>553496</v>
+        <v>553468</v>
       </c>
       <c r="R185" t="n">
-        <v>6705280</v>
+        <v>6705210</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20625,11 +20639,6 @@
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -20656,54 +20665,45 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>127314430</v>
+        <v>127314467</v>
       </c>
       <c r="B186" t="n">
-        <v>98447</v>
+        <v>105484</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J186" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>553358</v>
+        <v>553468</v>
       </c>
       <c r="R186" t="n">
-        <v>6705058</v>
+        <v>6705155</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20762,59 +20762,45 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>127314436</v>
+        <v>127314390</v>
       </c>
       <c r="B187" t="n">
-        <v>98447</v>
+        <v>91626</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J187" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>553571</v>
+        <v>553386</v>
       </c>
       <c r="R187" t="n">
-        <v>6705315</v>
+        <v>6704777</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20847,11 +20833,6 @@
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC187" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20878,7 +20859,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>127314453</v>
+        <v>127314436</v>
       </c>
       <c r="B188" t="n">
         <v>98447</v>
@@ -20908,7 +20889,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -20927,10 +20908,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>553477</v>
+        <v>553571</v>
       </c>
       <c r="R188" t="n">
-        <v>6705197</v>
+        <v>6705315</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20963,6 +20944,11 @@
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20989,7 +20975,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>127314464</v>
+        <v>127314453</v>
       </c>
       <c r="B189" t="n">
         <v>98447</v>
@@ -21027,16 +21013,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P189" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>553470</v>
+        <v>553477</v>
       </c>
       <c r="R189" t="n">
-        <v>6705234</v>
+        <v>6705197</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21095,7 +21086,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>127314461</v>
+        <v>127314464</v>
       </c>
       <c r="B190" t="n">
         <v>98447</v>
@@ -21139,10 +21130,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>553335</v>
+        <v>553470</v>
       </c>
       <c r="R190" t="n">
-        <v>6704846</v>
+        <v>6705234</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21201,45 +21192,54 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>127314390</v>
+        <v>127314461</v>
       </c>
       <c r="B191" t="n">
-        <v>91626</v>
+        <v>98447</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P191" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>553386</v>
+        <v>553335</v>
       </c>
       <c r="R191" t="n">
-        <v>6704777</v>
+        <v>6704846</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21727,10 +21727,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>127314379</v>
+        <v>127314389</v>
       </c>
       <c r="B196" t="n">
-        <v>57658</v>
+        <v>91626</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21738,39 +21738,34 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>553485</v>
+        <v>553364</v>
       </c>
       <c r="R196" t="n">
-        <v>6705230</v>
+        <v>6704790</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21829,10 +21824,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>127314382</v>
+        <v>127314363</v>
       </c>
       <c r="B197" t="n">
-        <v>57311</v>
+        <v>57821</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21840,39 +21835,42 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>100063</v>
+        <v>103021</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
       <c r="M197" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>553494</v>
+        <v>553336</v>
       </c>
       <c r="R197" t="n">
-        <v>6705461</v>
+        <v>6704944</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21931,10 +21929,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>127314389</v>
+        <v>127314379</v>
       </c>
       <c r="B198" t="n">
-        <v>91626</v>
+        <v>57658</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21942,34 +21940,39 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>553364</v>
+        <v>553485</v>
       </c>
       <c r="R198" t="n">
-        <v>6704790</v>
+        <v>6705230</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22028,38 +22031,38 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>127314325</v>
+        <v>127314382</v>
       </c>
       <c r="B199" t="n">
-        <v>5197</v>
+        <v>57311</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>105930</v>
+        <v>100063</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
       <c r="M199" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
@@ -22068,10 +22071,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>553508</v>
+        <v>553494</v>
       </c>
       <c r="R199" t="n">
-        <v>6705185</v>
+        <v>6705461</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22130,42 +22133,38 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127314425</v>
+        <v>127314325</v>
       </c>
       <c r="B200" t="n">
-        <v>98447</v>
+        <v>5197</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -22174,10 +22173,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>553466</v>
+        <v>553508</v>
       </c>
       <c r="R200" t="n">
-        <v>6705077</v>
+        <v>6705185</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22236,7 +22235,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>127314420</v>
+        <v>127314425</v>
       </c>
       <c r="B201" t="n">
         <v>98447</v>
@@ -22274,21 +22273,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P201" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>553426</v>
+        <v>553466</v>
       </c>
       <c r="R201" t="n">
-        <v>6704821</v>
+        <v>6705077</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22321,11 +22315,6 @@
       <c r="AA201" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22352,7 +22341,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127314445</v>
+        <v>127314420</v>
       </c>
       <c r="B202" t="n">
         <v>98447</v>
@@ -22382,7 +22371,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -22392,7 +22381,7 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
@@ -22401,10 +22390,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>553364</v>
+        <v>553426</v>
       </c>
       <c r="R202" t="n">
-        <v>6704996</v>
+        <v>6704821</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22437,6 +22426,11 @@
       <c r="AA202" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22463,7 +22457,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>127314429</v>
+        <v>127314445</v>
       </c>
       <c r="B203" t="n">
         <v>98447</v>
@@ -22493,7 +22487,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -22501,16 +22495,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P203" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>553414</v>
+        <v>553364</v>
       </c>
       <c r="R203" t="n">
-        <v>6704864</v>
+        <v>6704996</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22569,53 +22568,54 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>127314363</v>
+        <v>127314429</v>
       </c>
       <c r="B204" t="n">
-        <v>57821</v>
+        <v>98447</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr"/>
-      <c r="K204" t="inlineStr"/>
-      <c r="L204" t="inlineStr"/>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N204" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P204" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>553336</v>
+        <v>553414</v>
       </c>
       <c r="R204" t="n">
-        <v>6704944</v>
+        <v>6704864</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>

--- a/artfynd/A 18040-2021 artfynd.xlsx
+++ b/artfynd/A 18040-2021 artfynd.xlsx
@@ -13776,45 +13776,50 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127314388</v>
+        <v>127314375</v>
       </c>
       <c r="B121" t="n">
-        <v>91784</v>
+        <v>57658</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>553411</v>
+        <v>553537</v>
       </c>
       <c r="R121" t="n">
-        <v>6705072</v>
+        <v>6705403</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13873,10 +13878,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127314407</v>
+        <v>127314388</v>
       </c>
       <c r="B122" t="n">
-        <v>98447</v>
+        <v>91784</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13884,39 +13889,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>553477</v>
+        <v>553411</v>
       </c>
       <c r="R122" t="n">
-        <v>6705175</v>
+        <v>6705072</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13949,11 +13949,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>få synliga bladrosetter</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13980,50 +13975,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127314375</v>
+        <v>127314398</v>
       </c>
       <c r="B123" t="n">
-        <v>57658</v>
+        <v>97325</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>553537</v>
+        <v>553472</v>
       </c>
       <c r="R123" t="n">
-        <v>6705403</v>
+        <v>6705479</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14082,7 +14072,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127314398</v>
+        <v>127314397</v>
       </c>
       <c r="B124" t="n">
         <v>97325</v>
@@ -14117,10 +14107,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>553472</v>
+        <v>553527</v>
       </c>
       <c r="R124" t="n">
-        <v>6705479</v>
+        <v>6705221</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14179,45 +14169,50 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127314397</v>
+        <v>127314407</v>
       </c>
       <c r="B125" t="n">
-        <v>97325</v>
+        <v>98448</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>553527</v>
+        <v>553477</v>
       </c>
       <c r="R125" t="n">
-        <v>6705221</v>
+        <v>6705175</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14250,6 +14245,11 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>få synliga bladrosetter</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14381,7 +14381,7 @@
         <v>127314416</v>
       </c>
       <c r="B127" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>127314432</v>
       </c>
       <c r="B128" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>127314435</v>
       </c>
       <c r="B129" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14719,7 +14719,7 @@
         <v>127314415</v>
       </c>
       <c r="B130" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14832,10 +14832,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127314452</v>
+        <v>127314468</v>
       </c>
       <c r="B131" t="n">
-        <v>98447</v>
+        <v>91917</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14843,48 +14843,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220787</v>
+        <v>1179</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Peck) Donk</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>553418</v>
+        <v>553482</v>
       </c>
       <c r="R131" t="n">
-        <v>6705084</v>
+        <v>6705183</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14917,6 +14903,11 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Återfynd</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14943,10 +14934,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127314410</v>
+        <v>127314452</v>
       </c>
       <c r="B132" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14973,7 +14964,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -14981,16 +14972,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>553422</v>
+        <v>553418</v>
       </c>
       <c r="R132" t="n">
-        <v>6705072</v>
+        <v>6705084</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15049,10 +15045,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127314465</v>
+        <v>127314410</v>
       </c>
       <c r="B133" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15079,7 +15075,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -15093,10 +15089,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>553488</v>
+        <v>553422</v>
       </c>
       <c r="R133" t="n">
-        <v>6705263</v>
+        <v>6705072</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15155,45 +15151,54 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127314347</v>
+        <v>127314465</v>
       </c>
       <c r="B134" t="n">
-        <v>91330</v>
+        <v>98448</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>553419</v>
+        <v>553488</v>
       </c>
       <c r="R134" t="n">
-        <v>6705073</v>
+        <v>6705263</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15252,32 +15257,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127314345</v>
+        <v>127314336</v>
       </c>
       <c r="B135" t="n">
-        <v>91330</v>
+        <v>91688</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15287,10 +15292,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>553386</v>
+        <v>553429</v>
       </c>
       <c r="R135" t="n">
-        <v>6704777</v>
+        <v>6705077</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15349,7 +15354,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127314341</v>
+        <v>127314347</v>
       </c>
       <c r="B136" t="n">
         <v>91330</v>
@@ -15384,10 +15389,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>553429</v>
+        <v>553419</v>
       </c>
       <c r="R136" t="n">
-        <v>6705077</v>
+        <v>6705073</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15420,11 +15425,6 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15451,7 +15451,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127314350</v>
+        <v>127314345</v>
       </c>
       <c r="B137" t="n">
         <v>91330</v>
@@ -15486,10 +15486,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>553465</v>
+        <v>553386</v>
       </c>
       <c r="R137" t="n">
-        <v>6705219</v>
+        <v>6704777</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15548,32 +15548,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127314468</v>
+        <v>127314341</v>
       </c>
       <c r="B138" t="n">
-        <v>91917</v>
+        <v>91330</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1179</v>
+        <v>1202</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15583,10 +15583,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>553482</v>
+        <v>553429</v>
       </c>
       <c r="R138" t="n">
-        <v>6705183</v>
+        <v>6705077</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15623,7 +15623,7 @@
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>Återfynd</t>
+          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15650,32 +15650,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127314336</v>
+        <v>127314350</v>
       </c>
       <c r="B139" t="n">
-        <v>91688</v>
+        <v>91330</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15685,10 +15685,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>553429</v>
+        <v>553465</v>
       </c>
       <c r="R139" t="n">
-        <v>6705077</v>
+        <v>6705219</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15747,53 +15747,59 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127314370</v>
+        <v>127314417</v>
       </c>
       <c r="B140" t="n">
-        <v>57658</v>
+        <v>98448</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>553311</v>
+        <v>553413</v>
       </c>
       <c r="R140" t="n">
-        <v>6704717</v>
+        <v>6704868</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15826,6 +15832,11 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15852,42 +15863,38 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127314441</v>
+        <v>127314473</v>
       </c>
       <c r="B141" t="n">
-        <v>98447</v>
+        <v>57582</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -15896,10 +15903,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>553422</v>
+        <v>553415</v>
       </c>
       <c r="R141" t="n">
-        <v>6704986</v>
+        <v>6705462</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15932,6 +15939,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Fjädrar på "slaktbord"</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15958,54 +15970,53 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127314442</v>
+        <v>127314370</v>
       </c>
       <c r="B142" t="n">
-        <v>98447</v>
+        <v>57658</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>553423</v>
+        <v>553311</v>
       </c>
       <c r="R142" t="n">
-        <v>6704914</v>
+        <v>6704717</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16064,10 +16075,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127314417</v>
+        <v>127314441</v>
       </c>
       <c r="B143" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16094,7 +16105,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -16102,21 +16113,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>553413</v>
+        <v>553422</v>
       </c>
       <c r="R143" t="n">
-        <v>6704868</v>
+        <v>6704986</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16149,11 +16155,6 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16180,38 +16181,42 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127314473</v>
+        <v>127314442</v>
       </c>
       <c r="B144" t="n">
-        <v>57582</v>
+        <v>98448</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -16220,10 +16225,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>553415</v>
+        <v>553423</v>
       </c>
       <c r="R144" t="n">
-        <v>6705462</v>
+        <v>6704914</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16256,11 +16261,6 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>Fjädrar på "slaktbord"</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16494,7 +16494,7 @@
         <v>127314424</v>
       </c>
       <c r="B147" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         <v>127314454</v>
       </c>
       <c r="B148" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16718,47 +16718,38 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127314411</v>
+        <v>127314405</v>
       </c>
       <c r="B149" t="n">
-        <v>98447</v>
+        <v>8450</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -16767,10 +16758,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>553500</v>
+        <v>553521</v>
       </c>
       <c r="R149" t="n">
-        <v>6705175</v>
+        <v>6705364</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16829,59 +16820,45 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127314419</v>
+        <v>127314343</v>
       </c>
       <c r="B150" t="n">
-        <v>98447</v>
+        <v>91330</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>553343</v>
+        <v>553388</v>
       </c>
       <c r="R150" t="n">
-        <v>6704786</v>
+        <v>6704753</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16914,11 +16891,6 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16945,59 +16917,45 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127314450</v>
+        <v>127314342</v>
       </c>
       <c r="B151" t="n">
-        <v>98447</v>
+        <v>91330</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>553340</v>
+        <v>553347</v>
       </c>
       <c r="R151" t="n">
-        <v>6704784</v>
+        <v>6704783</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17056,45 +17014,59 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127314343</v>
+        <v>127314411</v>
       </c>
       <c r="B152" t="n">
-        <v>91330</v>
+        <v>98448</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>553388</v>
+        <v>553500</v>
       </c>
       <c r="R152" t="n">
-        <v>6704753</v>
+        <v>6705175</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17153,45 +17125,59 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>127314342</v>
+        <v>127314419</v>
       </c>
       <c r="B153" t="n">
-        <v>91330</v>
+        <v>98448</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>553347</v>
+        <v>553343</v>
       </c>
       <c r="R153" t="n">
-        <v>6704783</v>
+        <v>6704786</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17224,6 +17210,11 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17250,38 +17241,47 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127314405</v>
+        <v>127314450</v>
       </c>
       <c r="B154" t="n">
-        <v>8450</v>
+        <v>98448</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr"/>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -17290,10 +17290,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>553521</v>
+        <v>553340</v>
       </c>
       <c r="R154" t="n">
-        <v>6705364</v>
+        <v>6704784</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17449,50 +17449,45 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127314391</v>
+        <v>127314385</v>
       </c>
       <c r="B156" t="n">
-        <v>57661</v>
+        <v>56957</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100109</v>
+        <v>100038</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>553375</v>
+        <v>553426</v>
       </c>
       <c r="R156" t="n">
-        <v>6705433</v>
+        <v>6704786</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17525,11 +17520,6 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17661,45 +17651,50 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127314385</v>
+        <v>127314391</v>
       </c>
       <c r="B158" t="n">
-        <v>56957</v>
+        <v>57661</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100038</v>
+        <v>100109</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>553426</v>
+        <v>553375</v>
       </c>
       <c r="R158" t="n">
-        <v>6704786</v>
+        <v>6705433</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17732,6 +17727,11 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17863,7 +17863,7 @@
         <v>127314447</v>
       </c>
       <c r="B160" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17974,7 +17974,7 @@
         <v>127314433</v>
       </c>
       <c r="B161" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>127314443</v>
       </c>
       <c r="B162" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>127314448</v>
       </c>
       <c r="B163" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>127314434</v>
       </c>
       <c r="B164" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>127314451</v>
       </c>
       <c r="B165" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>127314421</v>
       </c>
       <c r="B166" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18632,10 +18632,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>127314439</v>
+        <v>127314460</v>
       </c>
       <c r="B167" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -18670,21 +18670,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>553525</v>
+        <v>553444</v>
       </c>
       <c r="R167" t="n">
-        <v>6705250</v>
+        <v>6705056</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18717,11 +18712,6 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>6 blomstjälkar</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18748,10 +18738,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>127314409</v>
+        <v>127314439</v>
       </c>
       <c r="B168" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18776,7 +18766,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr"/>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K168" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -18788,10 +18787,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>553478</v>
+        <v>553525</v>
       </c>
       <c r="R168" t="n">
-        <v>6705174</v>
+        <v>6705250</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18828,7 +18827,7 @@
       </c>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>få synliga bladrosetter</t>
+          <t>6 blomstjälkar</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18855,10 +18854,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>127314460</v>
+        <v>127314409</v>
       </c>
       <c r="B169" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18883,14 +18882,10 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="I169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
@@ -18899,10 +18894,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>553444</v>
+        <v>553478</v>
       </c>
       <c r="R169" t="n">
-        <v>6705056</v>
+        <v>6705174</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18935,6 +18930,11 @@
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>få synliga bladrosetter</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18961,38 +18961,42 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>127314393</v>
+        <v>127314386</v>
       </c>
       <c r="B170" t="n">
-        <v>57661</v>
+        <v>92632</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
@@ -19001,10 +19005,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>553521</v>
+        <v>553414</v>
       </c>
       <c r="R170" t="n">
-        <v>6705364</v>
+        <v>6704970</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19037,11 +19041,6 @@
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19068,42 +19067,38 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127314386</v>
+        <v>127314393</v>
       </c>
       <c r="B171" t="n">
-        <v>92632</v>
+        <v>57661</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
@@ -19112,10 +19107,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>553414</v>
+        <v>553521</v>
       </c>
       <c r="R171" t="n">
-        <v>6704970</v>
+        <v>6705364</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19148,6 +19143,11 @@
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19177,7 +19177,7 @@
         <v>127314426</v>
       </c>
       <c r="B172" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>127314455</v>
       </c>
       <c r="B173" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19503,45 +19503,50 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127314355</v>
+        <v>127314482</v>
       </c>
       <c r="B175" t="n">
-        <v>91688</v>
+        <v>5177</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>2062</v>
+        <v>100526</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P175" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>553451</v>
+        <v>553322</v>
       </c>
       <c r="R175" t="n">
-        <v>6705503</v>
+        <v>6704727</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19600,38 +19605,47 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>127314482</v>
+        <v>127314438</v>
       </c>
       <c r="B176" t="n">
-        <v>5177</v>
+        <v>98448</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr"/>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
@@ -19640,10 +19654,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>553322</v>
+        <v>553407</v>
       </c>
       <c r="R176" t="n">
-        <v>6704727</v>
+        <v>6704816</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19676,6 +19690,11 @@
       <c r="AA176" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19702,10 +19721,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>127314438</v>
+        <v>127314459</v>
       </c>
       <c r="B177" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19732,7 +19751,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -19740,21 +19759,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P177" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>553407</v>
+        <v>553508</v>
       </c>
       <c r="R177" t="n">
-        <v>6704816</v>
+        <v>6705196</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19787,11 +19801,6 @@
       <c r="AA177" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19818,10 +19827,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>127314459</v>
+        <v>127314355</v>
       </c>
       <c r="B178" t="n">
-        <v>98447</v>
+        <v>91688</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19829,43 +19838,34 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>553508</v>
+        <v>553451</v>
       </c>
       <c r="R178" t="n">
-        <v>6705196</v>
+        <v>6705503</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19924,38 +19924,38 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>127314484</v>
+        <v>127314381</v>
       </c>
       <c r="B179" t="n">
-        <v>5177</v>
+        <v>57658</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="M179" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
@@ -19964,10 +19964,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>553430</v>
+        <v>553468</v>
       </c>
       <c r="R179" t="n">
-        <v>6705087</v>
+        <v>6705451</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20026,47 +20026,38 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>127314413</v>
+        <v>127314378</v>
       </c>
       <c r="B180" t="n">
-        <v>98447</v>
+        <v>57658</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
@@ -20075,10 +20066,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>553349</v>
+        <v>553468</v>
       </c>
       <c r="R180" t="n">
-        <v>6704994</v>
+        <v>6705210</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20111,11 +20102,6 @@
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>5 blomstjälkar</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20142,47 +20128,38 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>127314418</v>
+        <v>127314484</v>
       </c>
       <c r="B181" t="n">
-        <v>98447</v>
+        <v>5177</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
@@ -20191,10 +20168,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>553496</v>
+        <v>553430</v>
       </c>
       <c r="R181" t="n">
-        <v>6705280</v>
+        <v>6705087</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20227,11 +20204,6 @@
       <c r="AA181" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20258,54 +20230,45 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127314430</v>
+        <v>127314467</v>
       </c>
       <c r="B182" t="n">
-        <v>98447</v>
+        <v>105486</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>553358</v>
+        <v>553468</v>
       </c>
       <c r="R182" t="n">
-        <v>6705058</v>
+        <v>6705155</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20461,38 +20424,47 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>127314381</v>
+        <v>127314418</v>
       </c>
       <c r="B184" t="n">
-        <v>57658</v>
+        <v>98448</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr"/>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
@@ -20501,10 +20473,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>553468</v>
+        <v>553496</v>
       </c>
       <c r="R184" t="n">
-        <v>6705451</v>
+        <v>6705280</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20537,6 +20509,11 @@
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20563,38 +20540,42 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>127314378</v>
+        <v>127314430</v>
       </c>
       <c r="B185" t="n">
-        <v>57658</v>
+        <v>98448</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr"/>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
@@ -20603,10 +20584,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>553468</v>
+        <v>553358</v>
       </c>
       <c r="R185" t="n">
-        <v>6705210</v>
+        <v>6705058</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20665,45 +20646,59 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>127314467</v>
+        <v>127314413</v>
       </c>
       <c r="B186" t="n">
-        <v>105484</v>
+        <v>98448</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>553468</v>
+        <v>553349</v>
       </c>
       <c r="R186" t="n">
-        <v>6705155</v>
+        <v>6704994</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20736,6 +20731,11 @@
       <c r="AA186" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>5 blomstjälkar</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20762,45 +20762,54 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>127314390</v>
+        <v>127314461</v>
       </c>
       <c r="B187" t="n">
-        <v>91626</v>
+        <v>98448</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P187" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>553386</v>
+        <v>553335</v>
       </c>
       <c r="R187" t="n">
-        <v>6704777</v>
+        <v>6704846</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20862,7 +20871,7 @@
         <v>127314436</v>
       </c>
       <c r="B188" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20978,7 +20987,7 @@
         <v>127314453</v>
       </c>
       <c r="B189" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21089,7 +21098,7 @@
         <v>127314464</v>
       </c>
       <c r="B190" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21192,54 +21201,45 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>127314461</v>
+        <v>127314390</v>
       </c>
       <c r="B191" t="n">
-        <v>98447</v>
+        <v>91626</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>553335</v>
+        <v>553386</v>
       </c>
       <c r="R191" t="n">
-        <v>6704846</v>
+        <v>6704777</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21298,10 +21298,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>127310426</v>
+        <v>127314339</v>
       </c>
       <c r="B192" t="n">
-        <v>98447</v>
+        <v>91688</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21309,53 +21309,37 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J192" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
+          <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>553479</v>
+        <v>553347</v>
       </c>
       <c r="R192" t="n">
-        <v>6705057</v>
+        <v>6704783</v>
       </c>
       <c r="S192" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -21393,29 +21377,28 @@
       <c r="AE192" t="b">
         <v>0</v>
       </c>
-      <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="b">
         <v>0</v>
       </c>
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>127314408</v>
+        <v>127310426</v>
       </c>
       <c r="B193" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21440,25 +21423,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K193" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
+      <c r="L193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Morkullberget södra, Dlr</t>
+          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>553400</v>
+        <v>553479</v>
       </c>
       <c r="R193" t="n">
-        <v>6705072</v>
+        <v>6705057</v>
       </c>
       <c r="S193" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -21490,39 +21484,35 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>få synliga bladrosetter</t>
-        </is>
-      </c>
       <c r="AD193" t="b">
         <v>0</v>
       </c>
       <c r="AE193" t="b">
         <v>0</v>
       </c>
+      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>127314423</v>
+        <v>127314408</v>
       </c>
       <c r="B194" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21547,16 +21537,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -21568,10 +21549,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>553338</v>
+        <v>553400</v>
       </c>
       <c r="R194" t="n">
-        <v>6704806</v>
+        <v>6705072</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21604,6 +21585,11 @@
       <c r="AA194" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>få synliga bladrosetter</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21630,10 +21616,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>127314339</v>
+        <v>127314423</v>
       </c>
       <c r="B195" t="n">
-        <v>91688</v>
+        <v>98448</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21641,34 +21627,48 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P195" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>553347</v>
+        <v>553338</v>
       </c>
       <c r="R195" t="n">
-        <v>6704783</v>
+        <v>6704806</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21727,10 +21727,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>127314389</v>
+        <v>127314379</v>
       </c>
       <c r="B196" t="n">
-        <v>91626</v>
+        <v>57658</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21738,34 +21738,39 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>553364</v>
+        <v>553485</v>
       </c>
       <c r="R196" t="n">
-        <v>6704790</v>
+        <v>6705230</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21929,10 +21934,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>127314379</v>
+        <v>127314389</v>
       </c>
       <c r="B198" t="n">
-        <v>57658</v>
+        <v>91626</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21940,39 +21945,34 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>553485</v>
+        <v>553364</v>
       </c>
       <c r="R198" t="n">
-        <v>6705230</v>
+        <v>6704790</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22238,7 +22238,7 @@
         <v>127314425</v>
       </c>
       <c r="B201" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22344,7 +22344,7 @@
         <v>127314420</v>
       </c>
       <c r="B202" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22460,7 +22460,7 @@
         <v>127314445</v>
       </c>
       <c r="B203" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22571,7 +22571,7 @@
         <v>127314429</v>
       </c>
       <c r="B204" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -22877,59 +22877,40 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>127314412</v>
+        <v>127314406</v>
       </c>
       <c r="B207" t="n">
-        <v>98447</v>
+        <v>91737</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>553337</v>
+        <v>553517</v>
       </c>
       <c r="R207" t="n">
-        <v>6704813</v>
+        <v>6705421</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22988,10 +22969,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>127314431</v>
+        <v>127314412</v>
       </c>
       <c r="B208" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23018,7 +22999,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -23026,16 +23007,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P208" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>553442</v>
+        <v>553337</v>
       </c>
       <c r="R208" t="n">
-        <v>6705095</v>
+        <v>6704813</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23094,40 +23080,54 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>127314406</v>
+        <v>127314431</v>
       </c>
       <c r="B209" t="n">
-        <v>91737</v>
+        <v>98448</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P209" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>553517</v>
+        <v>553442</v>
       </c>
       <c r="R209" t="n">
-        <v>6705421</v>
+        <v>6705095</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23186,51 +23186,53 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>127310539</v>
+        <v>127314480</v>
       </c>
       <c r="B210" t="n">
-        <v>91542</v>
+        <v>5177</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>1106</v>
+        <v>100526</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
-      <c r="J210" t="inlineStr"/>
-      <c r="K210" t="inlineStr"/>
-      <c r="N210" t="inlineStr"/>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
+          <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>553483</v>
+        <v>553399</v>
       </c>
       <c r="R210" t="n">
-        <v>6705051</v>
+        <v>6704947</v>
       </c>
       <c r="S210" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -23268,57 +23270,60 @@
       <c r="AE210" t="b">
         <v>0</v>
       </c>
-      <c r="AF210" t="inlineStr"/>
       <c r="AG210" t="b">
         <v>0</v>
       </c>
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>127314480</v>
+        <v>127314428</v>
       </c>
       <c r="B211" t="n">
-        <v>5177</v>
+        <v>98448</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr"/>
-      <c r="M211" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
@@ -23327,10 +23332,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>553399</v>
+        <v>553336</v>
       </c>
       <c r="R211" t="n">
-        <v>6704947</v>
+        <v>6704827</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23389,54 +23394,45 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>127314428</v>
+        <v>127314477</v>
       </c>
       <c r="B212" t="n">
-        <v>98447</v>
+        <v>92620</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J212" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>553336</v>
+        <v>553371</v>
       </c>
       <c r="R212" t="n">
-        <v>6704827</v>
+        <v>6704731</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23469,6 +23465,11 @@
       <c r="AA212" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>Många gamla fruktkroppar i häxring</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -23495,53 +23496,51 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>127314368</v>
+        <v>127310539</v>
       </c>
       <c r="B213" t="n">
-        <v>57658</v>
+        <v>91542</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>100049</v>
+        <v>1106</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
-      <c r="M213" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
+      <c r="N213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Morkullberget södra, Dlr</t>
+          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>553500</v>
+        <v>553483</v>
       </c>
       <c r="R213" t="n">
-        <v>6705249</v>
+        <v>6705051</v>
       </c>
       <c r="S213" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -23579,63 +23578,69 @@
       <c r="AE213" t="b">
         <v>0</v>
       </c>
+      <c r="AF213" t="inlineStr"/>
       <c r="AG213" t="b">
         <v>0</v>
       </c>
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>127314477</v>
+        <v>127314368</v>
       </c>
       <c r="B214" t="n">
-        <v>92620</v>
+        <v>57658</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P214" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>553371</v>
+        <v>553500</v>
       </c>
       <c r="R214" t="n">
-        <v>6704731</v>
+        <v>6705249</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23668,11 +23673,6 @@
       <c r="AA214" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC214" t="inlineStr">
-        <is>
-          <t>Många gamla fruktkroppar i häxring</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -23990,32 +23990,32 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>127314337</v>
+        <v>127314394</v>
       </c>
       <c r="B218" t="n">
-        <v>91688</v>
+        <v>97325</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>2062</v>
+        <v>221945</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -24025,10 +24025,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>553419</v>
+        <v>553498</v>
       </c>
       <c r="R218" t="n">
-        <v>6705073</v>
+        <v>6705418</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24061,11 +24061,6 @@
       <c r="AA218" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC218" t="inlineStr">
-        <is>
-          <t>Eventuellt S. delicata</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24194,45 +24189,59 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127314471</v>
+        <v>127314456</v>
       </c>
       <c r="B220" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P220" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>553406</v>
+        <v>553437</v>
       </c>
       <c r="R220" t="n">
-        <v>6705479</v>
+        <v>6704997</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24265,6 +24274,11 @@
       <c r="AA220" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC220" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -24291,10 +24305,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>127314422</v>
+        <v>127314458</v>
       </c>
       <c r="B221" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -24321,7 +24335,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -24329,21 +24343,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>553445</v>
+        <v>553526</v>
       </c>
       <c r="R221" t="n">
-        <v>6704996</v>
+        <v>6705245</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24402,59 +24411,45 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>127314437</v>
+        <v>127314471</v>
       </c>
       <c r="B222" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J222" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>553333</v>
+        <v>553406</v>
       </c>
       <c r="R222" t="n">
-        <v>6704814</v>
+        <v>6705479</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24513,10 +24508,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>127314456</v>
+        <v>127314337</v>
       </c>
       <c r="B223" t="n">
-        <v>98447</v>
+        <v>91688</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -24524,48 +24519,34 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J223" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>553437</v>
+        <v>553419</v>
       </c>
       <c r="R223" t="n">
-        <v>6704997</v>
+        <v>6705073</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24602,7 +24583,7 @@
       </c>
       <c r="AC223" t="inlineStr">
         <is>
-          <t>2 blomstjälkar</t>
+          <t>Eventuellt S. delicata</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -24629,10 +24610,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127314457</v>
+        <v>127314422</v>
       </c>
       <c r="B224" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -24659,7 +24640,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -24667,16 +24648,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P224" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>553442</v>
+        <v>553445</v>
       </c>
       <c r="R224" t="n">
-        <v>6705078</v>
+        <v>6704996</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24735,10 +24721,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127314463</v>
+        <v>127314437</v>
       </c>
       <c r="B225" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -24765,7 +24751,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -24773,16 +24759,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P225" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>553433</v>
+        <v>553333</v>
       </c>
       <c r="R225" t="n">
-        <v>6704902</v>
+        <v>6704814</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24841,10 +24832,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127314458</v>
+        <v>127314457</v>
       </c>
       <c r="B226" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -24885,10 +24876,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>553526</v>
+        <v>553442</v>
       </c>
       <c r="R226" t="n">
-        <v>6705245</v>
+        <v>6705078</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24947,45 +24938,54 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127314394</v>
+        <v>127314463</v>
       </c>
       <c r="B227" t="n">
-        <v>97325</v>
+        <v>98448</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>553498</v>
+        <v>553433</v>
       </c>
       <c r="R227" t="n">
-        <v>6705418</v>
+        <v>6704902</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25044,38 +25044,38 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127314479</v>
+        <v>127314371</v>
       </c>
       <c r="B228" t="n">
-        <v>5177</v>
+        <v>57658</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
       <c r="M228" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
@@ -25084,10 +25084,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>553496</v>
+        <v>553336</v>
       </c>
       <c r="R228" t="n">
-        <v>6705218</v>
+        <v>6704723</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25146,27 +25146,27 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127314371</v>
+        <v>127314326</v>
       </c>
       <c r="B229" t="n">
-        <v>57658</v>
+        <v>5197</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -25177,7 +25177,7 @@
       <c r="I229" t="inlineStr"/>
       <c r="M229" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -25186,10 +25186,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>553336</v>
+        <v>553527</v>
       </c>
       <c r="R229" t="n">
-        <v>6704723</v>
+        <v>6705221</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25248,38 +25248,42 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>127314326</v>
+        <v>127314444</v>
       </c>
       <c r="B230" t="n">
-        <v>5197</v>
+        <v>98448</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr"/>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
@@ -25288,10 +25292,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>553527</v>
+        <v>553489</v>
       </c>
       <c r="R230" t="n">
-        <v>6705221</v>
+        <v>6705294</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -25353,7 +25357,7 @@
         <v>127314414</v>
       </c>
       <c r="B231" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -25466,10 +25470,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>127314444</v>
+        <v>127314440</v>
       </c>
       <c r="B232" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -25510,10 +25514,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>553489</v>
+        <v>553571</v>
       </c>
       <c r="R232" t="n">
-        <v>6705294</v>
+        <v>6705297</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -25572,42 +25576,38 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>127314440</v>
+        <v>127314479</v>
       </c>
       <c r="B233" t="n">
-        <v>98447</v>
+        <v>5177</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J233" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr"/>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
@@ -25616,10 +25616,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>553571</v>
+        <v>553496</v>
       </c>
       <c r="R233" t="n">
-        <v>6705297</v>
+        <v>6705218</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>

--- a/artfynd/A 18040-2021 artfynd.xlsx
+++ b/artfynd/A 18040-2021 artfynd.xlsx
@@ -14832,32 +14832,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127314468</v>
+        <v>127314350</v>
       </c>
       <c r="B131" t="n">
-        <v>91917</v>
+        <v>91330</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1179</v>
+        <v>1202</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14867,10 +14867,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>553482</v>
+        <v>553465</v>
       </c>
       <c r="R131" t="n">
-        <v>6705183</v>
+        <v>6705219</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14903,11 +14903,6 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Återfynd</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14934,10 +14929,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127314452</v>
+        <v>127314468</v>
       </c>
       <c r="B132" t="n">
-        <v>98448</v>
+        <v>91917</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14945,48 +14940,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220787</v>
+        <v>1179</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Peck) Donk</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>553418</v>
+        <v>553482</v>
       </c>
       <c r="R132" t="n">
-        <v>6705084</v>
+        <v>6705183</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15019,6 +15000,11 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Återfynd</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15045,10 +15031,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127314410</v>
+        <v>127314336</v>
       </c>
       <c r="B133" t="n">
-        <v>98448</v>
+        <v>91688</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15056,43 +15042,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>553422</v>
+        <v>553429</v>
       </c>
       <c r="R133" t="n">
-        <v>6705072</v>
+        <v>6705077</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15151,7 +15128,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127314465</v>
+        <v>127314452</v>
       </c>
       <c r="B134" t="n">
         <v>98448</v>
@@ -15189,16 +15166,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>553488</v>
+        <v>553418</v>
       </c>
       <c r="R134" t="n">
-        <v>6705263</v>
+        <v>6705084</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15257,10 +15239,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127314336</v>
+        <v>127314410</v>
       </c>
       <c r="B135" t="n">
-        <v>91688</v>
+        <v>98448</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15268,34 +15250,43 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>553429</v>
+        <v>553422</v>
       </c>
       <c r="R135" t="n">
-        <v>6705077</v>
+        <v>6705072</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15354,45 +15345,54 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127314347</v>
+        <v>127314465</v>
       </c>
       <c r="B136" t="n">
-        <v>91330</v>
+        <v>98448</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>553419</v>
+        <v>553488</v>
       </c>
       <c r="R136" t="n">
-        <v>6705073</v>
+        <v>6705263</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15451,7 +15451,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127314345</v>
+        <v>127314347</v>
       </c>
       <c r="B137" t="n">
         <v>91330</v>
@@ -15486,10 +15486,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>553386</v>
+        <v>553419</v>
       </c>
       <c r="R137" t="n">
-        <v>6704777</v>
+        <v>6705073</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15548,7 +15548,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127314341</v>
+        <v>127314345</v>
       </c>
       <c r="B138" t="n">
         <v>91330</v>
@@ -15583,10 +15583,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>553429</v>
+        <v>553386</v>
       </c>
       <c r="R138" t="n">
-        <v>6705077</v>
+        <v>6704777</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15619,11 +15619,6 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15650,7 +15645,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127314350</v>
+        <v>127314341</v>
       </c>
       <c r="B139" t="n">
         <v>91330</v>
@@ -15685,10 +15680,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>553465</v>
+        <v>553429</v>
       </c>
       <c r="R139" t="n">
-        <v>6705219</v>
+        <v>6705077</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15721,6 +15716,11 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15747,59 +15747,53 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127314417</v>
+        <v>127314370</v>
       </c>
       <c r="B140" t="n">
-        <v>98448</v>
+        <v>57658</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>553413</v>
+        <v>553311</v>
       </c>
       <c r="R140" t="n">
-        <v>6704868</v>
+        <v>6704717</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15832,11 +15826,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15970,53 +15959,59 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127314370</v>
+        <v>127314417</v>
       </c>
       <c r="B142" t="n">
-        <v>57658</v>
+        <v>98448</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N142" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>553311</v>
+        <v>553413</v>
       </c>
       <c r="R142" t="n">
-        <v>6704717</v>
+        <v>6704868</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16049,6 +16044,11 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16820,45 +16820,59 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127314343</v>
+        <v>127314411</v>
       </c>
       <c r="B150" t="n">
-        <v>91330</v>
+        <v>98448</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>553388</v>
+        <v>553500</v>
       </c>
       <c r="R150" t="n">
-        <v>6704753</v>
+        <v>6705175</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16917,45 +16931,59 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127314342</v>
+        <v>127314419</v>
       </c>
       <c r="B151" t="n">
-        <v>91330</v>
+        <v>98448</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>553347</v>
+        <v>553343</v>
       </c>
       <c r="R151" t="n">
-        <v>6704783</v>
+        <v>6704786</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16988,6 +17016,11 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17014,7 +17047,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127314411</v>
+        <v>127314450</v>
       </c>
       <c r="B152" t="n">
         <v>98448</v>
@@ -17044,7 +17077,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -17063,10 +17096,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>553500</v>
+        <v>553340</v>
       </c>
       <c r="R152" t="n">
-        <v>6705175</v>
+        <v>6704784</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17125,59 +17158,45 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>127314419</v>
+        <v>127314343</v>
       </c>
       <c r="B153" t="n">
-        <v>98448</v>
+        <v>91330</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>553343</v>
+        <v>553388</v>
       </c>
       <c r="R153" t="n">
-        <v>6704786</v>
+        <v>6704753</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17210,11 +17229,6 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17241,59 +17255,45 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127314450</v>
+        <v>127314342</v>
       </c>
       <c r="B154" t="n">
-        <v>98448</v>
+        <v>91330</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>553340</v>
+        <v>553347</v>
       </c>
       <c r="R154" t="n">
-        <v>6704784</v>
+        <v>6704783</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -19396,50 +19396,45 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127314392</v>
+        <v>127314355</v>
       </c>
       <c r="B174" t="n">
-        <v>57661</v>
+        <v>91688</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P174" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>553395</v>
+        <v>553451</v>
       </c>
       <c r="R174" t="n">
-        <v>6704765</v>
+        <v>6705503</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19472,11 +19467,6 @@
       <c r="AA174" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19827,45 +19817,50 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>127314355</v>
+        <v>127314392</v>
       </c>
       <c r="B178" t="n">
-        <v>91688</v>
+        <v>57661</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>553451</v>
+        <v>553395</v>
       </c>
       <c r="R178" t="n">
-        <v>6705503</v>
+        <v>6704765</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19898,6 +19893,11 @@
       <c r="AA178" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20128,10 +20128,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>127314484</v>
+        <v>127314395</v>
       </c>
       <c r="B181" t="n">
-        <v>5177</v>
+        <v>97325</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20139,39 +20139,34 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P181" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>553430</v>
+        <v>553357</v>
       </c>
       <c r="R181" t="n">
-        <v>6705087</v>
+        <v>6704877</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20230,10 +20225,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127314467</v>
+        <v>127314484</v>
       </c>
       <c r="B182" t="n">
-        <v>105486</v>
+        <v>5177</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20241,34 +20236,39 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>221144</v>
+        <v>100526</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>553468</v>
+        <v>553430</v>
       </c>
       <c r="R182" t="n">
-        <v>6705155</v>
+        <v>6705087</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20327,10 +20327,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>127314395</v>
+        <v>127314467</v>
       </c>
       <c r="B183" t="n">
-        <v>97325</v>
+        <v>105486</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20338,21 +20338,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -20362,10 +20362,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>553357</v>
+        <v>553468</v>
       </c>
       <c r="R183" t="n">
-        <v>6704877</v>
+        <v>6705155</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -21727,10 +21727,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>127314379</v>
+        <v>127314382</v>
       </c>
       <c r="B196" t="n">
-        <v>57658</v>
+        <v>57311</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21738,27 +21738,27 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>100049</v>
+        <v>100063</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="M196" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
@@ -21767,10 +21767,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>553485</v>
+        <v>553494</v>
       </c>
       <c r="R196" t="n">
-        <v>6705230</v>
+        <v>6705461</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21829,10 +21829,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>127314363</v>
+        <v>127314389</v>
       </c>
       <c r="B197" t="n">
-        <v>57821</v>
+        <v>91626</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21840,42 +21840,34 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
-      <c r="K197" t="inlineStr"/>
-      <c r="L197" t="inlineStr"/>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>553336</v>
+        <v>553364</v>
       </c>
       <c r="R197" t="n">
-        <v>6704944</v>
+        <v>6704790</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21934,10 +21926,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>127314389</v>
+        <v>127314379</v>
       </c>
       <c r="B198" t="n">
-        <v>91626</v>
+        <v>57658</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21945,34 +21937,39 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>553364</v>
+        <v>553485</v>
       </c>
       <c r="R198" t="n">
-        <v>6704790</v>
+        <v>6705230</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22031,10 +22028,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>127314382</v>
+        <v>127314363</v>
       </c>
       <c r="B199" t="n">
-        <v>57311</v>
+        <v>57821</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22042,39 +22039,42 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>100063</v>
+        <v>103021</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
       <c r="M199" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>553494</v>
+        <v>553336</v>
       </c>
       <c r="R199" t="n">
-        <v>6705461</v>
+        <v>6704944</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22674,45 +22674,49 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>127314354</v>
+        <v>127314360</v>
       </c>
       <c r="B205" t="n">
-        <v>91330</v>
+        <v>56853</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P205" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>553517</v>
+        <v>553530</v>
       </c>
       <c r="R205" t="n">
-        <v>6705421</v>
+        <v>6705203</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22745,6 +22749,11 @@
       <c r="AA205" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>Höna med minst fyra ungar</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -22771,32 +22780,32 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>127314360</v>
+        <v>127314412</v>
       </c>
       <c r="B206" t="n">
-        <v>56853</v>
+        <v>98448</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -22804,16 +22813,26 @@
           <t>5</t>
         </is>
       </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P206" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>553530</v>
+        <v>553337</v>
       </c>
       <c r="R206" t="n">
-        <v>6705203</v>
+        <v>6704813</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22846,11 +22865,6 @@
       <c r="AA206" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC206" t="inlineStr">
-        <is>
-          <t>Höna med minst fyra ungar</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22877,40 +22891,54 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>127314406</v>
+        <v>127314431</v>
       </c>
       <c r="B207" t="n">
-        <v>91737</v>
+        <v>98448</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P207" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>553517</v>
+        <v>553442</v>
       </c>
       <c r="R207" t="n">
-        <v>6705421</v>
+        <v>6705095</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22969,59 +22997,40 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>127314412</v>
+        <v>127314406</v>
       </c>
       <c r="B208" t="n">
-        <v>98448</v>
+        <v>91737</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J208" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K208" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>553337</v>
+        <v>553517</v>
       </c>
       <c r="R208" t="n">
-        <v>6704813</v>
+        <v>6705421</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23080,54 +23089,45 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>127314431</v>
+        <v>127314354</v>
       </c>
       <c r="B209" t="n">
-        <v>98448</v>
+        <v>91330</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J209" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>553442</v>
+        <v>553517</v>
       </c>
       <c r="R209" t="n">
-        <v>6705095</v>
+        <v>6705421</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23186,53 +23186,51 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>127314480</v>
+        <v>127310539</v>
       </c>
       <c r="B210" t="n">
-        <v>5177</v>
+        <v>91542</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>100526</v>
+        <v>1106</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J210" t="inlineStr"/>
+      <c r="K210" t="inlineStr"/>
+      <c r="N210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Morkullberget södra, Dlr</t>
+          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>553399</v>
+        <v>553483</v>
       </c>
       <c r="R210" t="n">
-        <v>6704947</v>
+        <v>6705051</v>
       </c>
       <c r="S210" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -23270,60 +23268,57 @@
       <c r="AE210" t="b">
         <v>0</v>
       </c>
+      <c r="AF210" t="inlineStr"/>
       <c r="AG210" t="b">
         <v>0</v>
       </c>
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>127314428</v>
+        <v>127314368</v>
       </c>
       <c r="B211" t="n">
-        <v>98448</v>
+        <v>57658</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J211" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr"/>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
@@ -23332,10 +23327,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>553336</v>
+        <v>553500</v>
       </c>
       <c r="R211" t="n">
-        <v>6704827</v>
+        <v>6705249</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23394,10 +23389,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>127314477</v>
+        <v>127314480</v>
       </c>
       <c r="B212" t="n">
-        <v>92620</v>
+        <v>5177</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -23405,34 +23400,39 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>4364</v>
+        <v>100526</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P212" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>553371</v>
+        <v>553399</v>
       </c>
       <c r="R212" t="n">
-        <v>6704731</v>
+        <v>6704947</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23465,11 +23465,6 @@
       <c r="AA212" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC212" t="inlineStr">
-        <is>
-          <t>Många gamla fruktkroppar i häxring</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -23496,10 +23491,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>127310539</v>
+        <v>127314428</v>
       </c>
       <c r="B213" t="n">
-        <v>91542</v>
+        <v>98448</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -23507,40 +23502,46 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>1106</v>
+        <v>220787</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr"/>
-      <c r="J213" t="inlineStr"/>
-      <c r="K213" t="inlineStr"/>
-      <c r="N213" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
+          <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>553483</v>
+        <v>553336</v>
       </c>
       <c r="R213" t="n">
-        <v>6705051</v>
+        <v>6704827</v>
       </c>
       <c r="S213" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -23578,69 +23579,63 @@
       <c r="AE213" t="b">
         <v>0</v>
       </c>
-      <c r="AF213" t="inlineStr"/>
       <c r="AG213" t="b">
         <v>0</v>
       </c>
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>127314368</v>
+        <v>127314477</v>
       </c>
       <c r="B214" t="n">
-        <v>57658</v>
+        <v>92620</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P214" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>553500</v>
+        <v>553371</v>
       </c>
       <c r="R214" t="n">
-        <v>6705249</v>
+        <v>6704731</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23673,6 +23668,11 @@
       <c r="AA214" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>Många gamla fruktkroppar i häxring</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -23699,32 +23699,32 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>127314351</v>
+        <v>127314396</v>
       </c>
       <c r="B215" t="n">
-        <v>91330</v>
+        <v>97325</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -23734,10 +23734,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>553533</v>
+        <v>553521</v>
       </c>
       <c r="R215" t="n">
-        <v>6705296</v>
+        <v>6705212</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -23796,7 +23796,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>127314348</v>
+        <v>127314351</v>
       </c>
       <c r="B216" t="n">
         <v>91330</v>
@@ -23831,10 +23831,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>553499</v>
+        <v>553533</v>
       </c>
       <c r="R216" t="n">
-        <v>6705218</v>
+        <v>6705296</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -23893,32 +23893,32 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>127314396</v>
+        <v>127314348</v>
       </c>
       <c r="B217" t="n">
-        <v>97325</v>
+        <v>91330</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -23928,10 +23928,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>553521</v>
+        <v>553499</v>
       </c>
       <c r="R217" t="n">
-        <v>6705212</v>
+        <v>6705218</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -23990,32 +23990,32 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>127314394</v>
+        <v>127314471</v>
       </c>
       <c r="B218" t="n">
-        <v>97325</v>
+        <v>79018</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -24025,10 +24025,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>553498</v>
+        <v>553406</v>
       </c>
       <c r="R218" t="n">
-        <v>6705418</v>
+        <v>6705479</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24087,50 +24087,45 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127314377</v>
+        <v>127314337</v>
       </c>
       <c r="B219" t="n">
-        <v>57658</v>
+        <v>91688</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>100049</v>
+        <v>2062</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>553336</v>
+        <v>553419</v>
       </c>
       <c r="R219" t="n">
-        <v>6704827</v>
+        <v>6705073</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24163,6 +24158,11 @@
       <c r="AA219" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>Eventuellt S. delicata</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -24189,47 +24189,38 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127314456</v>
+        <v>127314377</v>
       </c>
       <c r="B220" t="n">
-        <v>98448</v>
+        <v>57658</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J220" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr"/>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -24238,10 +24229,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>553437</v>
+        <v>553336</v>
       </c>
       <c r="R220" t="n">
-        <v>6704997</v>
+        <v>6704827</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24274,11 +24265,6 @@
       <c r="AA220" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC220" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -24305,54 +24291,45 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>127314458</v>
+        <v>127314394</v>
       </c>
       <c r="B221" t="n">
-        <v>98448</v>
+        <v>97325</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J221" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>553526</v>
+        <v>553498</v>
       </c>
       <c r="R221" t="n">
-        <v>6705245</v>
+        <v>6705418</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24411,45 +24388,59 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>127314471</v>
+        <v>127314456</v>
       </c>
       <c r="B222" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P222" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>553406</v>
+        <v>553437</v>
       </c>
       <c r="R222" t="n">
-        <v>6705479</v>
+        <v>6704997</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24482,6 +24473,11 @@
       <c r="AA222" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -24508,10 +24504,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>127314337</v>
+        <v>127314458</v>
       </c>
       <c r="B223" t="n">
-        <v>91688</v>
+        <v>98448</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -24519,34 +24515,43 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>553419</v>
+        <v>553526</v>
       </c>
       <c r="R223" t="n">
-        <v>6705073</v>
+        <v>6705245</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24579,11 +24584,6 @@
       <c r="AA223" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC223" t="inlineStr">
-        <is>
-          <t>Eventuellt S. delicata</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -25044,27 +25044,27 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127314371</v>
+        <v>127314326</v>
       </c>
       <c r="B228" t="n">
-        <v>57658</v>
+        <v>5197</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -25075,7 +25075,7 @@
       <c r="I228" t="inlineStr"/>
       <c r="M228" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
@@ -25084,10 +25084,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>553336</v>
+        <v>553527</v>
       </c>
       <c r="R228" t="n">
-        <v>6704723</v>
+        <v>6705221</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25146,27 +25146,27 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127314326</v>
+        <v>127314371</v>
       </c>
       <c r="B229" t="n">
-        <v>5197</v>
+        <v>57658</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -25177,7 +25177,7 @@
       <c r="I229" t="inlineStr"/>
       <c r="M229" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -25186,10 +25186,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>553527</v>
+        <v>553336</v>
       </c>
       <c r="R229" t="n">
-        <v>6705221</v>
+        <v>6704723</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25248,42 +25248,38 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>127314444</v>
+        <v>127314479</v>
       </c>
       <c r="B230" t="n">
-        <v>98448</v>
+        <v>5177</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J230" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr"/>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
@@ -25292,10 +25288,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>553489</v>
+        <v>553496</v>
       </c>
       <c r="R230" t="n">
-        <v>6705294</v>
+        <v>6705218</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -25354,7 +25350,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>127314414</v>
+        <v>127314444</v>
       </c>
       <c r="B231" t="n">
         <v>98448</v>
@@ -25384,7 +25380,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -25392,21 +25388,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P231" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>553341</v>
+        <v>553489</v>
       </c>
       <c r="R231" t="n">
-        <v>6704994</v>
+        <v>6705294</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -25439,11 +25430,6 @@
       <c r="AA231" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC231" t="inlineStr">
-        <is>
-          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -25470,7 +25456,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>127314440</v>
+        <v>127314414</v>
       </c>
       <c r="B232" t="n">
         <v>98448</v>
@@ -25500,7 +25486,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -25508,16 +25494,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P232" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>553571</v>
+        <v>553341</v>
       </c>
       <c r="R232" t="n">
-        <v>6705297</v>
+        <v>6704994</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -25550,6 +25541,11 @@
       <c r="AA232" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -25576,38 +25572,42 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>127314479</v>
+        <v>127314440</v>
       </c>
       <c r="B233" t="n">
-        <v>5177</v>
+        <v>98448</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr"/>
-      <c r="M233" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
@@ -25616,10 +25616,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>553496</v>
+        <v>553571</v>
       </c>
       <c r="R233" t="n">
-        <v>6705218</v>
+        <v>6705297</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>

--- a/artfynd/A 18040-2021 artfynd.xlsx
+++ b/artfynd/A 18040-2021 artfynd.xlsx
@@ -13779,7 +13779,7 @@
         <v>127314375</v>
       </c>
       <c r="B121" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13878,32 +13878,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127314388</v>
+        <v>127314398</v>
       </c>
       <c r="B122" t="n">
-        <v>91784</v>
+        <v>97327</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1209</v>
+        <v>221945</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13913,10 +13913,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>553411</v>
+        <v>553472</v>
       </c>
       <c r="R122" t="n">
-        <v>6705072</v>
+        <v>6705479</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13975,10 +13975,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127314398</v>
+        <v>127314397</v>
       </c>
       <c r="B123" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14010,10 +14010,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>553472</v>
+        <v>553527</v>
       </c>
       <c r="R123" t="n">
-        <v>6705479</v>
+        <v>6705221</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14072,32 +14072,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127314397</v>
+        <v>127314388</v>
       </c>
       <c r="B124" t="n">
-        <v>97325</v>
+        <v>91786</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>221945</v>
+        <v>1209</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14107,10 +14107,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>553527</v>
+        <v>553411</v>
       </c>
       <c r="R124" t="n">
-        <v>6705221</v>
+        <v>6705072</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14172,7 +14172,7 @@
         <v>127314407</v>
       </c>
       <c r="B125" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>127314372</v>
       </c>
       <c r="B126" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>127314416</v>
       </c>
       <c r="B127" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>127314432</v>
       </c>
       <c r="B128" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>127314435</v>
       </c>
       <c r="B129" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14719,7 +14719,7 @@
         <v>127314415</v>
       </c>
       <c r="B130" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14832,10 +14832,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127314350</v>
+        <v>127314347</v>
       </c>
       <c r="B131" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14867,10 +14867,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>553465</v>
+        <v>553419</v>
       </c>
       <c r="R131" t="n">
-        <v>6705219</v>
+        <v>6705073</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14929,10 +14929,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127314468</v>
+        <v>127314336</v>
       </c>
       <c r="B132" t="n">
-        <v>91917</v>
+        <v>91690</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14940,21 +14940,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1179</v>
+        <v>2062</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14964,10 +14964,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>553482</v>
+        <v>553429</v>
       </c>
       <c r="R132" t="n">
-        <v>6705183</v>
+        <v>6705077</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15000,11 +15000,6 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Återfynd</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15031,32 +15026,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127314336</v>
+        <v>127314345</v>
       </c>
       <c r="B133" t="n">
-        <v>91688</v>
+        <v>91332</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -15066,10 +15061,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>553429</v>
+        <v>553386</v>
       </c>
       <c r="R133" t="n">
-        <v>6705077</v>
+        <v>6704777</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15128,59 +15123,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127314452</v>
+        <v>127314341</v>
       </c>
       <c r="B134" t="n">
-        <v>98448</v>
+        <v>91332</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>553418</v>
+        <v>553429</v>
       </c>
       <c r="R134" t="n">
-        <v>6705084</v>
+        <v>6705077</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15213,6 +15194,11 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15239,54 +15225,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127314410</v>
+        <v>127314350</v>
       </c>
       <c r="B135" t="n">
-        <v>98448</v>
+        <v>91332</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>553422</v>
+        <v>553465</v>
       </c>
       <c r="R135" t="n">
-        <v>6705072</v>
+        <v>6705219</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15345,10 +15322,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127314465</v>
+        <v>127314468</v>
       </c>
       <c r="B136" t="n">
-        <v>98448</v>
+        <v>91919</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15356,43 +15333,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220787</v>
+        <v>1179</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Peck) Donk</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>553488</v>
+        <v>553482</v>
       </c>
       <c r="R136" t="n">
-        <v>6705263</v>
+        <v>6705183</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15427,6 +15395,11 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Återfynd</t>
+        </is>
+      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
@@ -15444,52 +15417,66 @@
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127314347</v>
+        <v>127314452</v>
       </c>
       <c r="B137" t="n">
-        <v>91330</v>
+        <v>98450</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>553419</v>
+        <v>553418</v>
       </c>
       <c r="R137" t="n">
-        <v>6705073</v>
+        <v>6705084</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15541,52 +15528,61 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127314345</v>
+        <v>127314410</v>
       </c>
       <c r="B138" t="n">
-        <v>91330</v>
+        <v>98450</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>553386</v>
+        <v>553422</v>
       </c>
       <c r="R138" t="n">
-        <v>6704777</v>
+        <v>6705072</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15645,45 +15641,54 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127314341</v>
+        <v>127314465</v>
       </c>
       <c r="B139" t="n">
-        <v>91330</v>
+        <v>98450</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>553429</v>
+        <v>553488</v>
       </c>
       <c r="R139" t="n">
-        <v>6705077</v>
+        <v>6705263</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15718,11 +15723,6 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
-        </is>
-      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
@@ -15740,17 +15740,17 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127314370</v>
+        <v>127314473</v>
       </c>
       <c r="B140" t="n">
-        <v>57658</v>
+        <v>57584</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15758,16 +15758,16 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -15776,24 +15776,21 @@
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>553311</v>
+        <v>553415</v>
       </c>
       <c r="R140" t="n">
-        <v>6704717</v>
+        <v>6705462</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15828,6 +15825,11 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Fjädrar på "slaktbord"</t>
+        </is>
+      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
@@ -15845,17 +15847,17 @@
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127314473</v>
+        <v>127314370</v>
       </c>
       <c r="B141" t="n">
-        <v>57582</v>
+        <v>57660</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15863,16 +15865,16 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100001</v>
+        <v>100049</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -15881,21 +15883,24 @@
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>553415</v>
+        <v>553311</v>
       </c>
       <c r="R141" t="n">
-        <v>6705462</v>
+        <v>6704717</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15928,11 +15933,6 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Fjädrar på "slaktbord"</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15959,10 +15959,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127314417</v>
+        <v>127314441</v>
       </c>
       <c r="B142" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -15997,21 +15997,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>553413</v>
+        <v>553422</v>
       </c>
       <c r="R142" t="n">
-        <v>6704868</v>
+        <v>6704986</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16044,11 +16039,6 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16075,10 +16065,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127314441</v>
+        <v>127314442</v>
       </c>
       <c r="B143" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16119,10 +16109,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>553422</v>
+        <v>553423</v>
       </c>
       <c r="R143" t="n">
-        <v>6704986</v>
+        <v>6704914</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16181,10 +16171,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127314442</v>
+        <v>127314417</v>
       </c>
       <c r="B144" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16211,7 +16201,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -16219,16 +16209,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>553423</v>
+        <v>553413</v>
       </c>
       <c r="R144" t="n">
-        <v>6704914</v>
+        <v>6704868</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16261,6 +16256,11 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16287,10 +16287,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127314376</v>
+        <v>127314380</v>
       </c>
       <c r="B145" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16327,10 +16327,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>553380</v>
+        <v>553479</v>
       </c>
       <c r="R145" t="n">
-        <v>6704935</v>
+        <v>6705480</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16389,10 +16389,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127314380</v>
+        <v>127314376</v>
       </c>
       <c r="B146" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16429,10 +16429,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>553479</v>
+        <v>553380</v>
       </c>
       <c r="R146" t="n">
-        <v>6705480</v>
+        <v>6704935</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16494,7 +16494,7 @@
         <v>127314424</v>
       </c>
       <c r="B147" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         <v>127314454</v>
       </c>
       <c r="B148" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16711,57 +16711,52 @@
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127314405</v>
+        <v>127314343</v>
       </c>
       <c r="B149" t="n">
-        <v>8450</v>
+        <v>91332</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>553521</v>
+        <v>553388</v>
       </c>
       <c r="R149" t="n">
-        <v>6705364</v>
+        <v>6704753</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16820,59 +16815,45 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127314411</v>
+        <v>127314342</v>
       </c>
       <c r="B150" t="n">
-        <v>98448</v>
+        <v>91332</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>553500</v>
+        <v>553347</v>
       </c>
       <c r="R150" t="n">
-        <v>6705175</v>
+        <v>6704783</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16931,47 +16912,38 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127314419</v>
+        <v>127314405</v>
       </c>
       <c r="B151" t="n">
-        <v>98448</v>
+        <v>8450</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -16980,10 +16952,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>553343</v>
+        <v>553521</v>
       </c>
       <c r="R151" t="n">
-        <v>6704786</v>
+        <v>6705364</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17016,11 +16988,6 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17047,10 +17014,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127314450</v>
+        <v>127314411</v>
       </c>
       <c r="B152" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17077,7 +17044,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -17096,10 +17063,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>553340</v>
+        <v>553500</v>
       </c>
       <c r="R152" t="n">
-        <v>6704784</v>
+        <v>6705175</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17158,45 +17125,59 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>127314343</v>
+        <v>127314419</v>
       </c>
       <c r="B153" t="n">
-        <v>91330</v>
+        <v>98450</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>553388</v>
+        <v>553343</v>
       </c>
       <c r="R153" t="n">
-        <v>6704753</v>
+        <v>6704786</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17229,6 +17210,11 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17255,45 +17241,59 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127314342</v>
+        <v>127314450</v>
       </c>
       <c r="B154" t="n">
-        <v>91330</v>
+        <v>98450</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>553347</v>
+        <v>553340</v>
       </c>
       <c r="R154" t="n">
-        <v>6704783</v>
+        <v>6704784</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17345,39 +17345,39 @@
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127314387</v>
+        <v>127314385</v>
       </c>
       <c r="B155" t="n">
-        <v>91784</v>
+        <v>56959</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1209</v>
+        <v>100038</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17387,10 +17387,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>553517</v>
+        <v>553426</v>
       </c>
       <c r="R155" t="n">
-        <v>6705421</v>
+        <v>6704786</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17449,45 +17449,53 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127314385</v>
+        <v>127314374</v>
       </c>
       <c r="B156" t="n">
-        <v>56957</v>
+        <v>57660</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100038</v>
+        <v>100049</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>553426</v>
+        <v>553523</v>
       </c>
       <c r="R156" t="n">
-        <v>6704786</v>
+        <v>6705404</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17546,53 +17554,45 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127314374</v>
+        <v>127314387</v>
       </c>
       <c r="B157" t="n">
-        <v>57658</v>
+        <v>91786</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>553523</v>
+        <v>553517</v>
       </c>
       <c r="R157" t="n">
-        <v>6705404</v>
+        <v>6705421</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17654,7 +17654,7 @@
         <v>127314391</v>
       </c>
       <c r="B158" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17758,38 +17758,47 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127314362</v>
+        <v>127314447</v>
       </c>
       <c r="B159" t="n">
-        <v>4773</v>
+        <v>98450</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
@@ -17798,10 +17807,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>553526</v>
+        <v>553387</v>
       </c>
       <c r="R159" t="n">
-        <v>6705221</v>
+        <v>6704938</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17853,17 +17862,17 @@
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127314447</v>
+        <v>127314433</v>
       </c>
       <c r="B160" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17890,7 +17899,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -17898,21 +17907,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>553387</v>
+        <v>553366</v>
       </c>
       <c r="R160" t="n">
-        <v>6704938</v>
+        <v>6704886</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17971,42 +17975,38 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127314433</v>
+        <v>127314362</v>
       </c>
       <c r="B161" t="n">
-        <v>98448</v>
+        <v>4773</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
@@ -18015,10 +18015,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>553366</v>
+        <v>553526</v>
       </c>
       <c r="R161" t="n">
-        <v>6704886</v>
+        <v>6705221</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18080,7 +18080,7 @@
         <v>127314443</v>
       </c>
       <c r="B162" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>127314448</v>
       </c>
       <c r="B163" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18287,7 +18287,7 @@
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
@@ -18297,7 +18297,7 @@
         <v>127314434</v>
       </c>
       <c r="B164" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>127314451</v>
       </c>
       <c r="B165" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
@@ -18524,7 +18524,7 @@
         <v>127314421</v>
       </c>
       <c r="B166" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18632,10 +18632,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>127314460</v>
+        <v>127314439</v>
       </c>
       <c r="B167" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -18670,16 +18670,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>553444</v>
+        <v>553525</v>
       </c>
       <c r="R167" t="n">
-        <v>6705056</v>
+        <v>6705250</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18712,6 +18717,11 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>6 blomstjälkar</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18738,10 +18748,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>127314439</v>
+        <v>127314409</v>
       </c>
       <c r="B168" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18766,16 +18776,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I168" t="inlineStr"/>
       <c r="K168" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -18787,10 +18788,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>553525</v>
+        <v>553478</v>
       </c>
       <c r="R168" t="n">
-        <v>6705250</v>
+        <v>6705174</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18827,7 +18828,7 @@
       </c>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>6 blomstjälkar</t>
+          <t>få synliga bladrosetter</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18854,10 +18855,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>127314409</v>
+        <v>127314460</v>
       </c>
       <c r="B169" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18882,10 +18883,14 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr"/>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
@@ -18894,10 +18899,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>553478</v>
+        <v>553444</v>
       </c>
       <c r="R169" t="n">
-        <v>6705174</v>
+        <v>6705056</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18932,11 +18937,6 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>få synliga bladrosetter</t>
-        </is>
-      </c>
       <c r="AD169" t="b">
         <v>0</v>
       </c>
@@ -18954,7 +18954,7 @@
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
@@ -18964,7 +18964,7 @@
         <v>127314386</v>
       </c>
       <c r="B170" t="n">
-        <v>92632</v>
+        <v>92634</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19070,7 +19070,7 @@
         <v>127314393</v>
       </c>
       <c r="B171" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19177,7 +19177,7 @@
         <v>127314426</v>
       </c>
       <c r="B172" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>127314455</v>
       </c>
       <c r="B173" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19389,7 +19389,7 @@
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
@@ -19399,7 +19399,7 @@
         <v>127314355</v>
       </c>
       <c r="B174" t="n">
-        <v>91688</v>
+        <v>91690</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19588,54 +19588,45 @@
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>127314438</v>
+        <v>127314392</v>
       </c>
       <c r="B176" t="n">
-        <v>98448</v>
+        <v>57663</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
@@ -19644,10 +19635,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>553407</v>
+        <v>553395</v>
       </c>
       <c r="R176" t="n">
-        <v>6704816</v>
+        <v>6704765</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19684,7 +19675,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>4 blomstjälkar</t>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19711,10 +19702,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>127314459</v>
+        <v>127314438</v>
       </c>
       <c r="B177" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19741,7 +19732,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -19749,16 +19740,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P177" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>553508</v>
+        <v>553407</v>
       </c>
       <c r="R177" t="n">
-        <v>6705196</v>
+        <v>6704816</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19791,6 +19787,11 @@
       <c r="AA177" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19817,38 +19818,42 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>127314392</v>
+        <v>127314459</v>
       </c>
       <c r="B178" t="n">
-        <v>57661</v>
+        <v>98450</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr"/>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
@@ -19857,10 +19862,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>553395</v>
+        <v>553508</v>
       </c>
       <c r="R178" t="n">
-        <v>6704765</v>
+        <v>6705196</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19895,11 +19900,6 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
-        </is>
-      </c>
       <c r="AD178" t="b">
         <v>0</v>
       </c>
@@ -19917,17 +19917,17 @@
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>127314381</v>
+        <v>127314378</v>
       </c>
       <c r="B179" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>553468</v>
       </c>
       <c r="R179" t="n">
-        <v>6705451</v>
+        <v>6705210</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20026,10 +20026,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>127314378</v>
+        <v>127314381</v>
       </c>
       <c r="B180" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20069,7 +20069,7 @@
         <v>553468</v>
       </c>
       <c r="R180" t="n">
-        <v>6705210</v>
+        <v>6705451</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20128,10 +20128,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>127314395</v>
+        <v>127314484</v>
       </c>
       <c r="B181" t="n">
-        <v>97325</v>
+        <v>5177</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20139,34 +20139,39 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P181" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>553357</v>
+        <v>553430</v>
       </c>
       <c r="R181" t="n">
-        <v>6704877</v>
+        <v>6705087</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20218,17 +20223,17 @@
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127314484</v>
+        <v>127314395</v>
       </c>
       <c r="B182" t="n">
-        <v>5177</v>
+        <v>97327</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20236,39 +20241,34 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>553430</v>
+        <v>553357</v>
       </c>
       <c r="R182" t="n">
-        <v>6705087</v>
+        <v>6704877</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20330,7 +20330,7 @@
         <v>127314467</v>
       </c>
       <c r="B183" t="n">
-        <v>105486</v>
+        <v>105488</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20417,17 +20417,17 @@
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>127314418</v>
+        <v>127314413</v>
       </c>
       <c r="B184" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -20473,10 +20473,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>553496</v>
+        <v>553349</v>
       </c>
       <c r="R184" t="n">
-        <v>6705280</v>
+        <v>6704994</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20513,7 +20513,7 @@
       </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>3 blomstjälkar</t>
+          <t>5 blomstjälkar</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20540,10 +20540,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>127314430</v>
+        <v>127314418</v>
       </c>
       <c r="B185" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20578,16 +20578,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P185" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>553358</v>
+        <v>553496</v>
       </c>
       <c r="R185" t="n">
-        <v>6705058</v>
+        <v>6705280</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20620,6 +20625,11 @@
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -20646,10 +20656,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>127314413</v>
+        <v>127314430</v>
       </c>
       <c r="B186" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20676,7 +20686,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -20684,21 +20694,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P186" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>553349</v>
+        <v>553358</v>
       </c>
       <c r="R186" t="n">
-        <v>6704994</v>
+        <v>6705058</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20731,11 +20736,6 @@
       <c r="AA186" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>5 blomstjälkar</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20762,54 +20762,45 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>127314461</v>
+        <v>127314390</v>
       </c>
       <c r="B187" t="n">
-        <v>98448</v>
+        <v>91628</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J187" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>553335</v>
+        <v>553386</v>
       </c>
       <c r="R187" t="n">
-        <v>6704846</v>
+        <v>6704777</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20871,7 +20862,7 @@
         <v>127314436</v>
       </c>
       <c r="B188" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20987,7 +20978,7 @@
         <v>127314453</v>
       </c>
       <c r="B189" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21088,7 +21079,7 @@
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
@@ -21098,7 +21089,7 @@
         <v>127314464</v>
       </c>
       <c r="B190" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21194,52 +21185,61 @@
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>127314390</v>
+        <v>127314461</v>
       </c>
       <c r="B191" t="n">
-        <v>91626</v>
+        <v>98450</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P191" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>553386</v>
+        <v>553335</v>
       </c>
       <c r="R191" t="n">
-        <v>6704777</v>
+        <v>6704846</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21291,17 +21291,17 @@
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>127314339</v>
+        <v>127310426</v>
       </c>
       <c r="B192" t="n">
-        <v>91688</v>
+        <v>98450</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21309,37 +21309,53 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Morkullberget södra, Dlr</t>
+          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>553347</v>
+        <v>553479</v>
       </c>
       <c r="R192" t="n">
-        <v>6704783</v>
+        <v>6705057</v>
       </c>
       <c r="S192" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -21377,28 +21393,29 @@
       <c r="AE192" t="b">
         <v>0</v>
       </c>
+      <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="b">
         <v>0</v>
       </c>
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>127310426</v>
+        <v>127314408</v>
       </c>
       <c r="B193" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21423,36 +21440,25 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
-      <c r="L193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
+          <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>553479</v>
+        <v>553400</v>
       </c>
       <c r="R193" t="n">
-        <v>6705057</v>
+        <v>6705072</v>
       </c>
       <c r="S193" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -21484,35 +21490,39 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>få synliga bladrosetter</t>
+        </is>
+      </c>
       <c r="AD193" t="b">
         <v>0</v>
       </c>
       <c r="AE193" t="b">
         <v>0</v>
       </c>
-      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>127314408</v>
+        <v>127314423</v>
       </c>
       <c r="B194" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21537,7 +21547,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K194" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -21549,10 +21568,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>553400</v>
+        <v>553338</v>
       </c>
       <c r="R194" t="n">
-        <v>6705072</v>
+        <v>6704806</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21585,11 +21604,6 @@
       <c r="AA194" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>få synliga bladrosetter</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21616,10 +21630,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>127314423</v>
+        <v>127314339</v>
       </c>
       <c r="B195" t="n">
-        <v>98448</v>
+        <v>91690</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21627,48 +21641,34 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>553338</v>
+        <v>553347</v>
       </c>
       <c r="R195" t="n">
-        <v>6704806</v>
+        <v>6704783</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21730,7 +21730,7 @@
         <v>127314382</v>
       </c>
       <c r="B196" t="n">
-        <v>57311</v>
+        <v>57313</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21829,10 +21829,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>127314389</v>
+        <v>127314379</v>
       </c>
       <c r="B197" t="n">
-        <v>91626</v>
+        <v>57660</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21840,34 +21840,39 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>553364</v>
+        <v>553485</v>
       </c>
       <c r="R197" t="n">
-        <v>6704790</v>
+        <v>6705230</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21926,10 +21931,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>127314379</v>
+        <v>127314389</v>
       </c>
       <c r="B198" t="n">
-        <v>57658</v>
+        <v>91628</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21937,39 +21942,34 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>553485</v>
+        <v>553364</v>
       </c>
       <c r="R198" t="n">
-        <v>6705230</v>
+        <v>6704790</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22031,7 +22031,7 @@
         <v>127314363</v>
       </c>
       <c r="B199" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22238,7 +22238,7 @@
         <v>127314425</v>
       </c>
       <c r="B201" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22344,7 +22344,7 @@
         <v>127314420</v>
       </c>
       <c r="B202" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22460,7 +22460,7 @@
         <v>127314445</v>
       </c>
       <c r="B203" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22561,7 +22561,7 @@
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
@@ -22571,7 +22571,7 @@
         <v>127314429</v>
       </c>
       <c r="B204" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -22674,49 +22674,45 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>127314360</v>
+        <v>127314354</v>
       </c>
       <c r="B205" t="n">
-        <v>56853</v>
+        <v>91332</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>553530</v>
+        <v>553517</v>
       </c>
       <c r="R205" t="n">
-        <v>6705203</v>
+        <v>6705421</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22749,11 +22745,6 @@
       <c r="AA205" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC205" t="inlineStr">
-        <is>
-          <t>Höna med minst fyra ungar</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -22783,7 +22774,7 @@
         <v>127314412</v>
       </c>
       <c r="B206" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -22894,7 +22885,7 @@
         <v>127314431</v>
       </c>
       <c r="B207" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23000,7 +22991,7 @@
         <v>127314406</v>
       </c>
       <c r="B208" t="n">
-        <v>91737</v>
+        <v>91739</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23089,45 +23080,49 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>127314354</v>
+        <v>127314360</v>
       </c>
       <c r="B209" t="n">
-        <v>91330</v>
+        <v>56855</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P209" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>553517</v>
+        <v>553530</v>
       </c>
       <c r="R209" t="n">
-        <v>6705421</v>
+        <v>6705203</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23160,6 +23155,11 @@
       <c r="AA209" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>Höna med minst fyra ungar</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -23186,51 +23186,53 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>127310539</v>
+        <v>127314368</v>
       </c>
       <c r="B210" t="n">
-        <v>91542</v>
+        <v>57660</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>1106</v>
+        <v>100049</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
-      <c r="J210" t="inlineStr"/>
-      <c r="K210" t="inlineStr"/>
-      <c r="N210" t="inlineStr"/>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
+          <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>553483</v>
+        <v>553500</v>
       </c>
       <c r="R210" t="n">
-        <v>6705051</v>
+        <v>6705249</v>
       </c>
       <c r="S210" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -23268,57 +23270,56 @@
       <c r="AE210" t="b">
         <v>0</v>
       </c>
-      <c r="AF210" t="inlineStr"/>
       <c r="AG210" t="b">
         <v>0</v>
       </c>
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>127314368</v>
+        <v>127314480</v>
       </c>
       <c r="B211" t="n">
-        <v>57658</v>
+        <v>5177</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
       <c r="M211" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
@@ -23327,10 +23328,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>553500</v>
+        <v>553399</v>
       </c>
       <c r="R211" t="n">
-        <v>6705249</v>
+        <v>6704947</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23382,17 +23383,17 @@
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>127314480</v>
+        <v>127314477</v>
       </c>
       <c r="B212" t="n">
-        <v>5177</v>
+        <v>92622</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -23400,39 +23401,34 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P212" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>553399</v>
+        <v>553371</v>
       </c>
       <c r="R212" t="n">
-        <v>6704947</v>
+        <v>6704731</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23467,6 +23463,11 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>Många gamla fruktkroppar i häxring</t>
+        </is>
+      </c>
       <c r="AD212" t="b">
         <v>0</v>
       </c>
@@ -23484,17 +23485,17 @@
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>127314428</v>
+        <v>127310539</v>
       </c>
       <c r="B213" t="n">
-        <v>98448</v>
+        <v>91544</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -23502,46 +23503,40 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>220787</v>
+        <v>1106</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J213" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
+      <c r="N213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Morkullberget södra, Dlr</t>
+          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>553336</v>
+        <v>553483</v>
       </c>
       <c r="R213" t="n">
-        <v>6704827</v>
+        <v>6705051</v>
       </c>
       <c r="S213" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -23579,63 +23574,73 @@
       <c r="AE213" t="b">
         <v>0</v>
       </c>
+      <c r="AF213" t="inlineStr"/>
       <c r="AG213" t="b">
         <v>0</v>
       </c>
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>127314477</v>
+        <v>127314428</v>
       </c>
       <c r="B214" t="n">
-        <v>92620</v>
+        <v>98450</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P214" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>553371</v>
+        <v>553336</v>
       </c>
       <c r="R214" t="n">
-        <v>6704731</v>
+        <v>6704827</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23668,11 +23673,6 @@
       <c r="AA214" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC214" t="inlineStr">
-        <is>
-          <t>Många gamla fruktkroppar i häxring</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -23699,32 +23699,32 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>127314396</v>
+        <v>127314351</v>
       </c>
       <c r="B215" t="n">
-        <v>97325</v>
+        <v>91332</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -23734,10 +23734,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>553521</v>
+        <v>553533</v>
       </c>
       <c r="R215" t="n">
-        <v>6705212</v>
+        <v>6705296</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -23796,10 +23796,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>127314351</v>
+        <v>127314348</v>
       </c>
       <c r="B216" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -23831,10 +23831,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>553533</v>
+        <v>553499</v>
       </c>
       <c r="R216" t="n">
-        <v>6705296</v>
+        <v>6705218</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -23893,32 +23893,32 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>127314348</v>
+        <v>127314396</v>
       </c>
       <c r="B217" t="n">
-        <v>91330</v>
+        <v>97327</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -23928,10 +23928,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>553499</v>
+        <v>553521</v>
       </c>
       <c r="R217" t="n">
-        <v>6705218</v>
+        <v>6705212</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -23990,32 +23990,32 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>127314471</v>
+        <v>127314337</v>
       </c>
       <c r="B218" t="n">
-        <v>79018</v>
+        <v>91690</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -24025,10 +24025,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>553406</v>
+        <v>553419</v>
       </c>
       <c r="R218" t="n">
-        <v>6705479</v>
+        <v>6705073</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24061,6 +24061,11 @@
       <c r="AA218" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>Eventuellt S. delicata</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24087,10 +24092,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127314337</v>
+        <v>127314463</v>
       </c>
       <c r="B219" t="n">
-        <v>91688</v>
+        <v>98450</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24098,34 +24103,43 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>553419</v>
+        <v>553433</v>
       </c>
       <c r="R219" t="n">
-        <v>6705073</v>
+        <v>6704902</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24160,11 +24174,6 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC219" t="inlineStr">
-        <is>
-          <t>Eventuellt S. delicata</t>
-        </is>
-      </c>
       <c r="AD219" t="b">
         <v>0</v>
       </c>
@@ -24182,45 +24191,49 @@
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127314377</v>
+        <v>127314458</v>
       </c>
       <c r="B220" t="n">
-        <v>57658</v>
+        <v>98450</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr"/>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -24229,10 +24242,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>553336</v>
+        <v>553526</v>
       </c>
       <c r="R220" t="n">
-        <v>6704827</v>
+        <v>6705245</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24284,7 +24297,7 @@
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
@@ -24294,7 +24307,7 @@
         <v>127314394</v>
       </c>
       <c r="B221" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -24388,10 +24401,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>127314456</v>
+        <v>127314422</v>
       </c>
       <c r="B222" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -24418,7 +24431,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -24437,10 +24450,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>553437</v>
+        <v>553445</v>
       </c>
       <c r="R222" t="n">
-        <v>6704997</v>
+        <v>6704996</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24473,11 +24486,6 @@
       <c r="AA222" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC222" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -24504,10 +24512,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>127314458</v>
+        <v>127314437</v>
       </c>
       <c r="B223" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -24534,7 +24542,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -24542,16 +24550,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>553526</v>
+        <v>553333</v>
       </c>
       <c r="R223" t="n">
-        <v>6705245</v>
+        <v>6704814</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24610,10 +24623,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127314422</v>
+        <v>127314456</v>
       </c>
       <c r="B224" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -24640,7 +24653,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -24659,10 +24672,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>553445</v>
+        <v>553437</v>
       </c>
       <c r="R224" t="n">
-        <v>6704996</v>
+        <v>6704997</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24697,6 +24710,11 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD224" t="b">
         <v>0</v>
       </c>
@@ -24714,17 +24732,17 @@
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127314437</v>
+        <v>127314457</v>
       </c>
       <c r="B225" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -24751,7 +24769,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -24759,21 +24777,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P225" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>553333</v>
+        <v>553442</v>
       </c>
       <c r="R225" t="n">
-        <v>6704814</v>
+        <v>6705078</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24825,61 +24838,52 @@
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127314457</v>
+        <v>127314471</v>
       </c>
       <c r="B226" t="n">
-        <v>98448</v>
+        <v>79020</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J226" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>553442</v>
+        <v>553406</v>
       </c>
       <c r="R226" t="n">
-        <v>6705078</v>
+        <v>6705479</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24931,49 +24935,45 @@
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127314463</v>
+        <v>127314377</v>
       </c>
       <c r="B227" t="n">
-        <v>98448</v>
+        <v>57660</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J227" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr"/>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
@@ -24982,10 +24982,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>553433</v>
+        <v>553336</v>
       </c>
       <c r="R227" t="n">
-        <v>6704902</v>
+        <v>6704827</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25044,10 +25044,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127314326</v>
+        <v>127314479</v>
       </c>
       <c r="B228" t="n">
-        <v>5197</v>
+        <v>5177</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -25055,27 +25055,27 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
       <c r="M228" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
@@ -25084,10 +25084,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>553527</v>
+        <v>553496</v>
       </c>
       <c r="R228" t="n">
-        <v>6705221</v>
+        <v>6705218</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25139,34 +25139,34 @@
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127314371</v>
+        <v>127314326</v>
       </c>
       <c r="B229" t="n">
-        <v>57658</v>
+        <v>5197</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -25177,7 +25177,7 @@
       <c r="I229" t="inlineStr"/>
       <c r="M229" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -25186,10 +25186,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>553336</v>
+        <v>553527</v>
       </c>
       <c r="R229" t="n">
-        <v>6704723</v>
+        <v>6705221</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25248,38 +25248,47 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>127314479</v>
+        <v>127314414</v>
       </c>
       <c r="B230" t="n">
-        <v>5177</v>
+        <v>98450</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr"/>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
@@ -25288,10 +25297,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>553496</v>
+        <v>553341</v>
       </c>
       <c r="R230" t="n">
-        <v>6705218</v>
+        <v>6704994</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -25324,6 +25333,11 @@
       <c r="AA230" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC230" t="inlineStr">
+        <is>
+          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -25353,7 +25367,7 @@
         <v>127314444</v>
       </c>
       <c r="B231" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -25449,17 +25463,17 @@
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>127314414</v>
+        <v>127314440</v>
       </c>
       <c r="B232" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -25486,7 +25500,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -25494,21 +25508,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P232" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>553341</v>
+        <v>553571</v>
       </c>
       <c r="R232" t="n">
-        <v>6704994</v>
+        <v>6705297</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -25541,11 +25550,6 @@
       <c r="AA232" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC232" t="inlineStr">
-        <is>
-          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -25572,42 +25576,38 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>127314440</v>
+        <v>127314371</v>
       </c>
       <c r="B233" t="n">
-        <v>98448</v>
+        <v>57660</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J233" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr"/>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
@@ -25616,10 +25616,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>553571</v>
+        <v>553336</v>
       </c>
       <c r="R233" t="n">
-        <v>6705297</v>
+        <v>6704723</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -25681,7 +25681,7 @@
         <v>127314486</v>
       </c>
       <c r="B234" t="n">
-        <v>91702</v>
+        <v>91704</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -25774,7 +25774,7 @@
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>

--- a/artfynd/A 18040-2021 artfynd.xlsx
+++ b/artfynd/A 18040-2021 artfynd.xlsx
@@ -13776,50 +13776,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127314375</v>
+        <v>127314388</v>
       </c>
       <c r="B121" t="n">
-        <v>57660</v>
+        <v>91786</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>553537</v>
+        <v>553411</v>
       </c>
       <c r="R121" t="n">
-        <v>6705403</v>
+        <v>6705072</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13878,45 +13873,50 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127314398</v>
+        <v>127314375</v>
       </c>
       <c r="B122" t="n">
-        <v>97327</v>
+        <v>57660</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>553472</v>
+        <v>553537</v>
       </c>
       <c r="R122" t="n">
-        <v>6705479</v>
+        <v>6705403</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13975,7 +13975,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127314397</v>
+        <v>127314398</v>
       </c>
       <c r="B123" t="n">
         <v>97327</v>
@@ -14010,10 +14010,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>553527</v>
+        <v>553472</v>
       </c>
       <c r="R123" t="n">
-        <v>6705221</v>
+        <v>6705479</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14072,32 +14072,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127314388</v>
+        <v>127314397</v>
       </c>
       <c r="B124" t="n">
-        <v>91786</v>
+        <v>97327</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1209</v>
+        <v>221945</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14107,10 +14107,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>553411</v>
+        <v>553527</v>
       </c>
       <c r="R124" t="n">
-        <v>6705072</v>
+        <v>6705221</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14494,7 +14494,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127314432</v>
+        <v>127314415</v>
       </c>
       <c r="B128" t="n">
         <v>98450</v>
@@ -14524,7 +14524,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -14532,16 +14532,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>553508</v>
+        <v>553463</v>
       </c>
       <c r="R128" t="n">
-        <v>6705194</v>
+        <v>6705155</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14574,6 +14579,11 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14600,7 +14610,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127314435</v>
+        <v>127314432</v>
       </c>
       <c r="B129" t="n">
         <v>98450</v>
@@ -14630,7 +14640,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -14638,21 +14648,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>553476</v>
+        <v>553508</v>
       </c>
       <c r="R129" t="n">
-        <v>6705068</v>
+        <v>6705194</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14685,11 +14690,6 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>12 blomstjälkar</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14716,7 +14716,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127314415</v>
+        <v>127314435</v>
       </c>
       <c r="B130" t="n">
         <v>98450</v>
@@ -14746,7 +14746,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -14765,10 +14765,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>553463</v>
+        <v>553476</v>
       </c>
       <c r="R130" t="n">
-        <v>6705155</v>
+        <v>6705068</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14805,7 +14805,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>4 blomstjälkar</t>
+          <t>12 blomstjälkar</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14832,32 +14832,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127314347</v>
+        <v>127314336</v>
       </c>
       <c r="B131" t="n">
-        <v>91332</v>
+        <v>91690</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14867,10 +14867,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>553419</v>
+        <v>553429</v>
       </c>
       <c r="R131" t="n">
-        <v>6705073</v>
+        <v>6705077</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14929,32 +14929,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127314336</v>
+        <v>127314347</v>
       </c>
       <c r="B132" t="n">
-        <v>91690</v>
+        <v>91332</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14964,10 +14964,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>553429</v>
+        <v>553419</v>
       </c>
       <c r="R132" t="n">
-        <v>6705077</v>
+        <v>6705073</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15747,10 +15747,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127314473</v>
+        <v>127314370</v>
       </c>
       <c r="B140" t="n">
-        <v>57584</v>
+        <v>57660</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15758,16 +15758,16 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100001</v>
+        <v>100049</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -15776,21 +15776,24 @@
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>553415</v>
+        <v>553311</v>
       </c>
       <c r="R140" t="n">
-        <v>6705462</v>
+        <v>6704717</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15825,11 +15828,6 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Fjädrar på "slaktbord"</t>
-        </is>
-      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
@@ -15847,60 +15845,61 @@
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127314370</v>
+        <v>127314441</v>
       </c>
       <c r="B141" t="n">
-        <v>57660</v>
+        <v>98450</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>553311</v>
+        <v>553422</v>
       </c>
       <c r="R141" t="n">
-        <v>6704717</v>
+        <v>6704986</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15959,7 +15958,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127314441</v>
+        <v>127314442</v>
       </c>
       <c r="B142" t="n">
         <v>98450</v>
@@ -16003,10 +16002,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>553422</v>
+        <v>553423</v>
       </c>
       <c r="R142" t="n">
-        <v>6704986</v>
+        <v>6704914</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16065,7 +16064,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127314442</v>
+        <v>127314417</v>
       </c>
       <c r="B143" t="n">
         <v>98450</v>
@@ -16095,7 +16094,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -16103,16 +16102,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>553423</v>
+        <v>553413</v>
       </c>
       <c r="R143" t="n">
-        <v>6704914</v>
+        <v>6704868</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16145,6 +16149,11 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16171,47 +16180,38 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127314417</v>
+        <v>127314473</v>
       </c>
       <c r="B144" t="n">
-        <v>98450</v>
+        <v>57584</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -16220,10 +16220,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>553413</v>
+        <v>553415</v>
       </c>
       <c r="R144" t="n">
-        <v>6704868</v>
+        <v>6705462</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16260,7 +16260,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>3 blomstjälkar</t>
+          <t>Fjädrar på "slaktbord"</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16280,14 +16280,14 @@
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127314380</v>
+        <v>127314376</v>
       </c>
       <c r="B145" t="n">
         <v>57660</v>
@@ -16327,10 +16327,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>553479</v>
+        <v>553380</v>
       </c>
       <c r="R145" t="n">
-        <v>6705480</v>
+        <v>6704935</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16389,7 +16389,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127314376</v>
+        <v>127314380</v>
       </c>
       <c r="B146" t="n">
         <v>57660</v>
@@ -16429,10 +16429,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>553380</v>
+        <v>553479</v>
       </c>
       <c r="R146" t="n">
-        <v>6704935</v>
+        <v>6705480</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16718,45 +16718,50 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127314343</v>
+        <v>127314405</v>
       </c>
       <c r="B149" t="n">
-        <v>91332</v>
+        <v>8450</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>553388</v>
+        <v>553521</v>
       </c>
       <c r="R149" t="n">
-        <v>6704753</v>
+        <v>6705364</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16815,45 +16820,59 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127314342</v>
+        <v>127314411</v>
       </c>
       <c r="B150" t="n">
-        <v>91332</v>
+        <v>98450</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>553347</v>
+        <v>553500</v>
       </c>
       <c r="R150" t="n">
-        <v>6704783</v>
+        <v>6705175</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16912,38 +16931,47 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127314405</v>
+        <v>127314450</v>
       </c>
       <c r="B151" t="n">
-        <v>8450</v>
+        <v>98450</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -16952,10 +16980,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>553521</v>
+        <v>553340</v>
       </c>
       <c r="R151" t="n">
-        <v>6705364</v>
+        <v>6704784</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17007,66 +17035,52 @@
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127314411</v>
+        <v>127314343</v>
       </c>
       <c r="B152" t="n">
-        <v>98450</v>
+        <v>91332</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>553500</v>
+        <v>553388</v>
       </c>
       <c r="R152" t="n">
-        <v>6705175</v>
+        <v>6704753</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17125,59 +17139,45 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>127314419</v>
+        <v>127314342</v>
       </c>
       <c r="B153" t="n">
-        <v>98450</v>
+        <v>91332</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>553343</v>
+        <v>553347</v>
       </c>
       <c r="R153" t="n">
-        <v>6704786</v>
+        <v>6704783</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17210,11 +17210,6 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17241,7 +17236,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127314450</v>
+        <v>127314419</v>
       </c>
       <c r="B154" t="n">
         <v>98450</v>
@@ -17271,7 +17266,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -17290,10 +17285,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>553340</v>
+        <v>553343</v>
       </c>
       <c r="R154" t="n">
-        <v>6704784</v>
+        <v>6704786</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17328,6 +17323,11 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD154" t="b">
         <v>0</v>
       </c>
@@ -17345,52 +17345,57 @@
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127314385</v>
+        <v>127314391</v>
       </c>
       <c r="B155" t="n">
-        <v>56959</v>
+        <v>57663</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100038</v>
+        <v>100109</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>553426</v>
+        <v>553375</v>
       </c>
       <c r="R155" t="n">
-        <v>6704786</v>
+        <v>6705433</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17423,6 +17428,11 @@
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17449,53 +17459,50 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127314374</v>
+        <v>127314362</v>
       </c>
       <c r="B156" t="n">
-        <v>57660</v>
+        <v>4773</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100049</v>
+        <v>100299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
       <c r="M156" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N156" t="inlineStr"/>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>553523</v>
+        <v>553526</v>
       </c>
       <c r="R156" t="n">
-        <v>6705404</v>
+        <v>6705221</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17651,10 +17658,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127314391</v>
+        <v>127314374</v>
       </c>
       <c r="B158" t="n">
-        <v>57663</v>
+        <v>57660</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17662,16 +17669,16 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -17680,21 +17687,24 @@
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>553375</v>
+        <v>553523</v>
       </c>
       <c r="R158" t="n">
-        <v>6705433</v>
+        <v>6705404</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17727,11 +17737,6 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17758,59 +17763,45 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127314447</v>
+        <v>127314385</v>
       </c>
       <c r="B159" t="n">
-        <v>98450</v>
+        <v>56959</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>220787</v>
+        <v>100038</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>553387</v>
+        <v>553426</v>
       </c>
       <c r="R159" t="n">
-        <v>6704938</v>
+        <v>6704786</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17862,14 +17853,14 @@
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127314433</v>
+        <v>127314447</v>
       </c>
       <c r="B160" t="n">
         <v>98450</v>
@@ -17899,7 +17890,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -17907,16 +17898,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>553366</v>
+        <v>553387</v>
       </c>
       <c r="R160" t="n">
-        <v>6704886</v>
+        <v>6704938</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17968,45 +17964,49 @@
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127314362</v>
+        <v>127314433</v>
       </c>
       <c r="B161" t="n">
-        <v>4773</v>
+        <v>98450</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
@@ -18015,10 +18015,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>553526</v>
+        <v>553366</v>
       </c>
       <c r="R161" t="n">
-        <v>6705221</v>
+        <v>6704886</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18077,7 +18077,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127314443</v>
+        <v>127314434</v>
       </c>
       <c r="B162" t="n">
         <v>98450</v>
@@ -18107,7 +18107,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -18115,16 +18115,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>553338</v>
+        <v>553416</v>
       </c>
       <c r="R162" t="n">
-        <v>6705039</v>
+        <v>6704816</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18157,6 +18162,11 @@
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18183,7 +18193,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>127314448</v>
+        <v>127314443</v>
       </c>
       <c r="B163" t="n">
         <v>98450</v>
@@ -18213,7 +18223,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -18221,21 +18231,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P163" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>553342</v>
+        <v>553338</v>
       </c>
       <c r="R163" t="n">
-        <v>6704852</v>
+        <v>6705039</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18287,14 +18292,14 @@
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>127314434</v>
+        <v>127314448</v>
       </c>
       <c r="B164" t="n">
         <v>98450</v>
@@ -18324,7 +18329,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -18343,10 +18348,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>553416</v>
+        <v>553342</v>
       </c>
       <c r="R164" t="n">
-        <v>6704816</v>
+        <v>6704852</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18381,11 +18386,6 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
@@ -18403,7 +18403,7 @@
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
@@ -18961,42 +18961,42 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>127314386</v>
+        <v>127314426</v>
       </c>
       <c r="B170" t="n">
-        <v>92634</v>
+        <v>98450</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
@@ -19005,10 +19005,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>553414</v>
+        <v>553452</v>
       </c>
       <c r="R170" t="n">
-        <v>6704970</v>
+        <v>6705056</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19067,38 +19067,47 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127314393</v>
+        <v>127314455</v>
       </c>
       <c r="B171" t="n">
-        <v>57663</v>
+        <v>98450</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
@@ -19107,10 +19116,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>553521</v>
+        <v>553431</v>
       </c>
       <c r="R171" t="n">
-        <v>6705364</v>
+        <v>6704842</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19147,7 +19156,7 @@
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19167,49 +19176,49 @@
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>127314426</v>
+        <v>127314386</v>
       </c>
       <c r="B172" t="n">
-        <v>98450</v>
+        <v>92634</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
@@ -19218,10 +19227,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>553452</v>
+        <v>553414</v>
       </c>
       <c r="R172" t="n">
-        <v>6705056</v>
+        <v>6704970</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19280,47 +19289,38 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127314455</v>
+        <v>127314393</v>
       </c>
       <c r="B173" t="n">
-        <v>98450</v>
+        <v>57663</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
@@ -19329,10 +19329,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>553431</v>
+        <v>553521</v>
       </c>
       <c r="R173" t="n">
-        <v>6704842</v>
+        <v>6705364</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19369,7 +19369,7 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>3 blomstjälkar</t>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19389,7 +19389,7 @@
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
@@ -19493,38 +19493,38 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127314482</v>
+        <v>127314392</v>
       </c>
       <c r="B175" t="n">
-        <v>5177</v>
+        <v>57663</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="M175" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
@@ -19533,10 +19533,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>553322</v>
+        <v>553395</v>
       </c>
       <c r="R175" t="n">
-        <v>6704727</v>
+        <v>6704765</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19571,6 +19571,11 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
+        </is>
+      </c>
       <c r="AD175" t="b">
         <v>0</v>
       </c>
@@ -19588,45 +19593,49 @@
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>127314392</v>
+        <v>127314459</v>
       </c>
       <c r="B176" t="n">
-        <v>57663</v>
+        <v>98450</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr"/>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
@@ -19635,10 +19644,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>553395</v>
+        <v>553508</v>
       </c>
       <c r="R176" t="n">
-        <v>6704765</v>
+        <v>6705196</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19673,11 +19682,6 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
-        </is>
-      </c>
       <c r="AD176" t="b">
         <v>0</v>
       </c>
@@ -19695,54 +19699,45 @@
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>127314438</v>
+        <v>127314482</v>
       </c>
       <c r="B177" t="n">
-        <v>98450</v>
+        <v>5177</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
@@ -19751,10 +19746,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>553407</v>
+        <v>553322</v>
       </c>
       <c r="R177" t="n">
-        <v>6704816</v>
+        <v>6704727</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19789,11 +19784,6 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>4 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD177" t="b">
         <v>0</v>
       </c>
@@ -19811,14 +19801,14 @@
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>127314459</v>
+        <v>127314438</v>
       </c>
       <c r="B178" t="n">
         <v>98450</v>
@@ -19848,7 +19838,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -19856,16 +19846,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>553508</v>
+        <v>553407</v>
       </c>
       <c r="R178" t="n">
-        <v>6705196</v>
+        <v>6704816</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19900,6 +19895,11 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>4 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD178" t="b">
         <v>0</v>
       </c>
@@ -19917,14 +19917,14 @@
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>127314378</v>
+        <v>127314381</v>
       </c>
       <c r="B179" t="n">
         <v>57660</v>
@@ -19967,7 +19967,7 @@
         <v>553468</v>
       </c>
       <c r="R179" t="n">
-        <v>6705210</v>
+        <v>6705451</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20026,40 +20026,35 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>127314381</v>
+        <v>127314467</v>
       </c>
       <c r="B180" t="n">
-        <v>57660</v>
+        <v>105488</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P180" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
@@ -20069,7 +20064,7 @@
         <v>553468</v>
       </c>
       <c r="R180" t="n">
-        <v>6705451</v>
+        <v>6705155</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20121,45 +20116,54 @@
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>127314484</v>
+        <v>127314418</v>
       </c>
       <c r="B181" t="n">
-        <v>5177</v>
+        <v>98450</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr"/>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
@@ -20168,10 +20172,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>553430</v>
+        <v>553496</v>
       </c>
       <c r="R181" t="n">
-        <v>6705087</v>
+        <v>6705280</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20206,6 +20210,11 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD181" t="b">
         <v>0</v>
       </c>
@@ -20223,52 +20232,66 @@
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127314395</v>
+        <v>127314413</v>
       </c>
       <c r="B182" t="n">
-        <v>97327</v>
+        <v>98450</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>553357</v>
+        <v>553349</v>
       </c>
       <c r="R182" t="n">
-        <v>6704877</v>
+        <v>6704994</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20301,6 +20324,11 @@
       <c r="AA182" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>5 blomstjälkar</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20327,45 +20355,54 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>127314467</v>
+        <v>127314430</v>
       </c>
       <c r="B183" t="n">
-        <v>105488</v>
+        <v>98450</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P183" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>553468</v>
+        <v>553358</v>
       </c>
       <c r="R183" t="n">
-        <v>6705155</v>
+        <v>6705058</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20417,54 +20454,45 @@
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>127314413</v>
+        <v>127314378</v>
       </c>
       <c r="B184" t="n">
-        <v>98450</v>
+        <v>57660</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
@@ -20473,10 +20501,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>553349</v>
+        <v>553468</v>
       </c>
       <c r="R184" t="n">
-        <v>6704994</v>
+        <v>6705210</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20509,11 +20537,6 @@
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>5 blomstjälkar</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20540,47 +20563,38 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>127314418</v>
+        <v>127314484</v>
       </c>
       <c r="B185" t="n">
-        <v>98450</v>
+        <v>5177</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
@@ -20589,10 +20603,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>553496</v>
+        <v>553430</v>
       </c>
       <c r="R185" t="n">
-        <v>6705280</v>
+        <v>6705087</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20627,11 +20641,6 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD185" t="b">
         <v>0</v>
       </c>
@@ -20649,61 +20658,52 @@
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>127314430</v>
+        <v>127314395</v>
       </c>
       <c r="B186" t="n">
-        <v>98450</v>
+        <v>97327</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J186" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>553358</v>
+        <v>553357</v>
       </c>
       <c r="R186" t="n">
-        <v>6705058</v>
+        <v>6704877</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -21298,10 +21298,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>127310426</v>
+        <v>127314339</v>
       </c>
       <c r="B192" t="n">
-        <v>98450</v>
+        <v>91690</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21309,53 +21309,37 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J192" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
+          <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>553479</v>
+        <v>553347</v>
       </c>
       <c r="R192" t="n">
-        <v>6705057</v>
+        <v>6704783</v>
       </c>
       <c r="S192" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -21393,26 +21377,25 @@
       <c r="AE192" t="b">
         <v>0</v>
       </c>
-      <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="b">
         <v>0</v>
       </c>
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>127314408</v>
+        <v>127310426</v>
       </c>
       <c r="B193" t="n">
         <v>98450</v>
@@ -21440,25 +21423,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K193" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
+      <c r="L193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Morkullberget södra, Dlr</t>
+          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>553400</v>
+        <v>553479</v>
       </c>
       <c r="R193" t="n">
-        <v>6705072</v>
+        <v>6705057</v>
       </c>
       <c r="S193" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -21490,36 +21484,32 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>få synliga bladrosetter</t>
-        </is>
-      </c>
       <c r="AD193" t="b">
         <v>0</v>
       </c>
       <c r="AE193" t="b">
         <v>0</v>
       </c>
+      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>127314423</v>
+        <v>127314408</v>
       </c>
       <c r="B194" t="n">
         <v>98450</v>
@@ -21547,16 +21537,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -21568,10 +21549,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>553338</v>
+        <v>553400</v>
       </c>
       <c r="R194" t="n">
-        <v>6704806</v>
+        <v>6705072</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21604,6 +21585,11 @@
       <c r="AA194" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>få synliga bladrosetter</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21630,10 +21616,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>127314339</v>
+        <v>127314423</v>
       </c>
       <c r="B195" t="n">
-        <v>91690</v>
+        <v>98450</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21641,34 +21627,48 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P195" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>553347</v>
+        <v>553338</v>
       </c>
       <c r="R195" t="n">
-        <v>6704783</v>
+        <v>6704806</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21727,10 +21727,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>127314382</v>
+        <v>127314379</v>
       </c>
       <c r="B196" t="n">
-        <v>57313</v>
+        <v>57660</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21738,27 +21738,27 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>100063</v>
+        <v>100049</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="M196" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
@@ -21767,10 +21767,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>553494</v>
+        <v>553485</v>
       </c>
       <c r="R196" t="n">
-        <v>6705461</v>
+        <v>6705230</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21829,38 +21829,47 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>127314379</v>
+        <v>127314445</v>
       </c>
       <c r="B197" t="n">
-        <v>57660</v>
+        <v>98450</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr"/>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
@@ -21869,10 +21878,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>553485</v>
+        <v>553364</v>
       </c>
       <c r="R197" t="n">
-        <v>6705230</v>
+        <v>6704996</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21924,52 +21933,61 @@
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>127314389</v>
+        <v>127314429</v>
       </c>
       <c r="B198" t="n">
-        <v>91628</v>
+        <v>98450</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>553364</v>
+        <v>553414</v>
       </c>
       <c r="R198" t="n">
-        <v>6704790</v>
+        <v>6704864</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22028,53 +22046,54 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>127314363</v>
+        <v>127314425</v>
       </c>
       <c r="B199" t="n">
-        <v>57823</v>
+        <v>98450</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr"/>
-      <c r="K199" t="inlineStr"/>
-      <c r="L199" t="inlineStr"/>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N199" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P199" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>553336</v>
+        <v>553466</v>
       </c>
       <c r="R199" t="n">
-        <v>6704944</v>
+        <v>6705077</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22133,38 +22152,47 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127314325</v>
+        <v>127314420</v>
       </c>
       <c r="B200" t="n">
-        <v>5197</v>
+        <v>98450</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr"/>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -22173,10 +22201,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>553508</v>
+        <v>553426</v>
       </c>
       <c r="R200" t="n">
-        <v>6705185</v>
+        <v>6704821</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22209,6 +22237,11 @@
       <c r="AA200" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22235,54 +22268,45 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>127314425</v>
+        <v>127314389</v>
       </c>
       <c r="B201" t="n">
-        <v>98450</v>
+        <v>91628</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>553466</v>
+        <v>553364</v>
       </c>
       <c r="R201" t="n">
-        <v>6705077</v>
+        <v>6704790</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22341,47 +22365,38 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127314420</v>
+        <v>127314382</v>
       </c>
       <c r="B202" t="n">
-        <v>98450</v>
+        <v>57313</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>220787</v>
+        <v>100063</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
@@ -22390,10 +22405,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>553426</v>
+        <v>553494</v>
       </c>
       <c r="R202" t="n">
-        <v>6704821</v>
+        <v>6705461</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22426,11 +22441,6 @@
       <c r="AA202" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22457,59 +22467,53 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>127314445</v>
+        <v>127314363</v>
       </c>
       <c r="B203" t="n">
-        <v>98450</v>
+        <v>57823</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>553364</v>
+        <v>553336</v>
       </c>
       <c r="R203" t="n">
-        <v>6704996</v>
+        <v>6704944</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22561,49 +22565,45 @@
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>127314429</v>
+        <v>127314325</v>
       </c>
       <c r="B204" t="n">
-        <v>98450</v>
+        <v>5197</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
@@ -22612,10 +22612,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>553414</v>
+        <v>553508</v>
       </c>
       <c r="R204" t="n">
-        <v>6704864</v>
+        <v>6705185</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22771,32 +22771,32 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>127314412</v>
+        <v>127314360</v>
       </c>
       <c r="B206" t="n">
-        <v>98450</v>
+        <v>56855</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -22804,26 +22804,16 @@
           <t>5</t>
         </is>
       </c>
-      <c r="J206" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P206" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>553337</v>
+        <v>553530</v>
       </c>
       <c r="R206" t="n">
-        <v>6704813</v>
+        <v>6705203</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22856,6 +22846,11 @@
       <c r="AA206" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>Höna med minst fyra ungar</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22988,40 +22983,59 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>127314406</v>
+        <v>127314412</v>
       </c>
       <c r="B208" t="n">
-        <v>91739</v>
+        <v>98450</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P208" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>553517</v>
+        <v>553337</v>
       </c>
       <c r="R208" t="n">
-        <v>6705421</v>
+        <v>6704813</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23080,49 +23094,40 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>127314360</v>
+        <v>127314406</v>
       </c>
       <c r="B209" t="n">
-        <v>56855</v>
+        <v>91739</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>553530</v>
+        <v>553517</v>
       </c>
       <c r="R209" t="n">
-        <v>6705203</v>
+        <v>6705421</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23155,11 +23160,6 @@
       <c r="AA209" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>Höna med minst fyra ungar</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -23288,10 +23288,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>127314480</v>
+        <v>127314477</v>
       </c>
       <c r="B211" t="n">
-        <v>5177</v>
+        <v>92622</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23299,39 +23299,34 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
-      <c r="M211" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P211" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>553399</v>
+        <v>553371</v>
       </c>
       <c r="R211" t="n">
-        <v>6704947</v>
+        <v>6704731</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23364,6 +23359,11 @@
       <c r="AA211" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>Många gamla fruktkroppar i häxring</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -23390,48 +23390,51 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>127314477</v>
+        <v>127310539</v>
       </c>
       <c r="B212" t="n">
-        <v>92622</v>
+        <v>91544</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>4364</v>
+        <v>1106</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr"/>
+      <c r="N212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Morkullberget södra, Dlr</t>
+          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>553371</v>
+        <v>553483</v>
       </c>
       <c r="R212" t="n">
-        <v>6704731</v>
+        <v>6705051</v>
       </c>
       <c r="S212" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -23463,24 +23466,20 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC212" t="inlineStr">
-        <is>
-          <t>Många gamla fruktkroppar i häxring</t>
-        </is>
-      </c>
       <c r="AD212" t="b">
         <v>0</v>
       </c>
       <c r="AE212" t="b">
         <v>0</v>
       </c>
+      <c r="AF212" t="inlineStr"/>
       <c r="AG212" t="b">
         <v>0</v>
       </c>
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
@@ -23492,51 +23491,53 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>127310539</v>
+        <v>127314480</v>
       </c>
       <c r="B213" t="n">
-        <v>91544</v>
+        <v>5177</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>1106</v>
+        <v>100526</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
-      <c r="J213" t="inlineStr"/>
-      <c r="K213" t="inlineStr"/>
-      <c r="N213" t="inlineStr"/>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
+          <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>553483</v>
+        <v>553399</v>
       </c>
       <c r="R213" t="n">
-        <v>6705051</v>
+        <v>6704947</v>
       </c>
       <c r="S213" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -23574,14 +23575,13 @@
       <c r="AE213" t="b">
         <v>0</v>
       </c>
-      <c r="AF213" t="inlineStr"/>
       <c r="AG213" t="b">
         <v>0</v>
       </c>
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
@@ -24092,54 +24092,45 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127314463</v>
+        <v>127314471</v>
       </c>
       <c r="B219" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J219" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>553433</v>
+        <v>553406</v>
       </c>
       <c r="R219" t="n">
-        <v>6704902</v>
+        <v>6705479</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24198,42 +24189,38 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127314458</v>
+        <v>127314377</v>
       </c>
       <c r="B220" t="n">
-        <v>98450</v>
+        <v>57660</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J220" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr"/>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -24242,10 +24229,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>553526</v>
+        <v>553336</v>
       </c>
       <c r="R220" t="n">
-        <v>6705245</v>
+        <v>6704827</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24297,52 +24284,61 @@
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>127314394</v>
+        <v>127314457</v>
       </c>
       <c r="B221" t="n">
-        <v>97327</v>
+        <v>98450</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>553498</v>
+        <v>553442</v>
       </c>
       <c r="R221" t="n">
-        <v>6705418</v>
+        <v>6705078</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24394,14 +24390,14 @@
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>127314422</v>
+        <v>127314458</v>
       </c>
       <c r="B222" t="n">
         <v>98450</v>
@@ -24431,7 +24427,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -24439,21 +24435,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P222" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>553445</v>
+        <v>553526</v>
       </c>
       <c r="R222" t="n">
-        <v>6704996</v>
+        <v>6705245</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24505,66 +24496,52 @@
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>127314437</v>
+        <v>127314394</v>
       </c>
       <c r="B223" t="n">
-        <v>98450</v>
+        <v>97327</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J223" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>553333</v>
+        <v>553498</v>
       </c>
       <c r="R223" t="n">
-        <v>6704814</v>
+        <v>6705418</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24623,7 +24600,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127314456</v>
+        <v>127314422</v>
       </c>
       <c r="B224" t="n">
         <v>98450</v>
@@ -24653,7 +24630,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -24672,10 +24649,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>553437</v>
+        <v>553445</v>
       </c>
       <c r="R224" t="n">
-        <v>6704997</v>
+        <v>6704996</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24710,11 +24687,6 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC224" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD224" t="b">
         <v>0</v>
       </c>
@@ -24732,14 +24704,14 @@
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127314457</v>
+        <v>127314437</v>
       </c>
       <c r="B225" t="n">
         <v>98450</v>
@@ -24769,7 +24741,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -24777,16 +24749,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P225" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>553442</v>
+        <v>553333</v>
       </c>
       <c r="R225" t="n">
-        <v>6705078</v>
+        <v>6704814</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24838,52 +24815,66 @@
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127314471</v>
+        <v>127314456</v>
       </c>
       <c r="B226" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P226" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>553406</v>
+        <v>553437</v>
       </c>
       <c r="R226" t="n">
-        <v>6705479</v>
+        <v>6704997</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24916,6 +24907,11 @@
       <c r="AA226" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -24942,38 +24938,42 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127314377</v>
+        <v>127314463</v>
       </c>
       <c r="B227" t="n">
-        <v>57660</v>
+        <v>98450</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr"/>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
@@ -24982,10 +24982,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>553336</v>
+        <v>553433</v>
       </c>
       <c r="R227" t="n">
-        <v>6704827</v>
+        <v>6704902</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25037,45 +25037,49 @@
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127314479</v>
+        <v>127314444</v>
       </c>
       <c r="B228" t="n">
-        <v>5177</v>
+        <v>98450</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr"/>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
@@ -25084,10 +25088,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>553496</v>
+        <v>553489</v>
       </c>
       <c r="R228" t="n">
-        <v>6705218</v>
+        <v>6705294</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25146,38 +25150,42 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127314326</v>
+        <v>127314440</v>
       </c>
       <c r="B229" t="n">
-        <v>5197</v>
+        <v>98450</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I229" t="inlineStr"/>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -25186,10 +25194,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>553527</v>
+        <v>553571</v>
       </c>
       <c r="R229" t="n">
-        <v>6705221</v>
+        <v>6705297</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25248,47 +25256,38 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>127314414</v>
+        <v>127314371</v>
       </c>
       <c r="B230" t="n">
-        <v>98450</v>
+        <v>57660</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J230" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K230" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr"/>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
@@ -25297,10 +25296,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>553341</v>
+        <v>553336</v>
       </c>
       <c r="R230" t="n">
-        <v>6704994</v>
+        <v>6704723</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -25333,11 +25332,6 @@
       <c r="AA230" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC230" t="inlineStr">
-        <is>
-          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -25364,42 +25358,38 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>127314444</v>
+        <v>127314326</v>
       </c>
       <c r="B231" t="n">
-        <v>98450</v>
+        <v>5197</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I231" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J231" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr"/>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P231" t="inlineStr">
@@ -25408,10 +25398,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>553489</v>
+        <v>553527</v>
       </c>
       <c r="R231" t="n">
-        <v>6705294</v>
+        <v>6705221</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -25463,49 +25453,45 @@
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>127314440</v>
+        <v>127314479</v>
       </c>
       <c r="B232" t="n">
-        <v>98450</v>
+        <v>5177</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I232" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J232" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr"/>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P232" t="inlineStr">
@@ -25514,10 +25500,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>553571</v>
+        <v>553496</v>
       </c>
       <c r="R232" t="n">
-        <v>6705297</v>
+        <v>6705218</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -25569,45 +25555,54 @@
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>127314371</v>
+        <v>127314414</v>
       </c>
       <c r="B233" t="n">
-        <v>57660</v>
+        <v>98450</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr"/>
-      <c r="M233" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
@@ -25616,10 +25611,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>553336</v>
+        <v>553341</v>
       </c>
       <c r="R233" t="n">
-        <v>6704723</v>
+        <v>6704994</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -25652,6 +25647,11 @@
       <c r="AA233" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD233" t="b">

--- a/artfynd/A 18040-2021 artfynd.xlsx
+++ b/artfynd/A 18040-2021 artfynd.xlsx
@@ -14276,38 +14276,42 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127314372</v>
+        <v>127314432</v>
       </c>
       <c r="B126" t="n">
-        <v>57660</v>
+        <v>98450</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -14316,10 +14320,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>553488</v>
+        <v>553508</v>
       </c>
       <c r="R126" t="n">
-        <v>6705460</v>
+        <v>6705194</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14378,7 +14382,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127314416</v>
+        <v>127314435</v>
       </c>
       <c r="B127" t="n">
         <v>98450</v>
@@ -14408,7 +14412,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -14427,10 +14431,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>553356</v>
+        <v>553476</v>
       </c>
       <c r="R127" t="n">
-        <v>6704786</v>
+        <v>6705068</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14467,7 +14471,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>3 blomstjälkar</t>
+          <t>12 blomstjälkar</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14494,7 +14498,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127314415</v>
+        <v>127314416</v>
       </c>
       <c r="B128" t="n">
         <v>98450</v>
@@ -14543,10 +14547,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>553463</v>
+        <v>553356</v>
       </c>
       <c r="R128" t="n">
-        <v>6705155</v>
+        <v>6704786</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14583,7 +14587,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>4 blomstjälkar</t>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14610,7 +14614,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127314432</v>
+        <v>127314415</v>
       </c>
       <c r="B129" t="n">
         <v>98450</v>
@@ -14640,7 +14644,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -14648,16 +14652,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>553508</v>
+        <v>553463</v>
       </c>
       <c r="R129" t="n">
-        <v>6705194</v>
+        <v>6705155</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14690,6 +14699,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14716,47 +14730,38 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127314435</v>
+        <v>127314372</v>
       </c>
       <c r="B130" t="n">
-        <v>98450</v>
+        <v>57660</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -14765,10 +14770,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>553476</v>
+        <v>553488</v>
       </c>
       <c r="R130" t="n">
-        <v>6705068</v>
+        <v>6705460</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14801,11 +14806,6 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>12 blomstjälkar</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15747,53 +15747,54 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127314370</v>
+        <v>127314442</v>
       </c>
       <c r="B140" t="n">
-        <v>57660</v>
+        <v>98450</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>553311</v>
+        <v>553423</v>
       </c>
       <c r="R140" t="n">
-        <v>6704717</v>
+        <v>6704914</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15852,7 +15853,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127314441</v>
+        <v>127314417</v>
       </c>
       <c r="B141" t="n">
         <v>98450</v>
@@ -15882,7 +15883,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -15890,16 +15891,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>553422</v>
+        <v>553413</v>
       </c>
       <c r="R141" t="n">
-        <v>6704986</v>
+        <v>6704868</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15932,6 +15938,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15958,42 +15969,38 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127314442</v>
+        <v>127314473</v>
       </c>
       <c r="B142" t="n">
-        <v>98450</v>
+        <v>57584</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -16002,10 +16009,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>553423</v>
+        <v>553415</v>
       </c>
       <c r="R142" t="n">
-        <v>6704914</v>
+        <v>6705462</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16040,6 +16047,11 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Fjädrar på "slaktbord"</t>
+        </is>
+      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
@@ -16057,66 +16069,60 @@
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127314417</v>
+        <v>127314370</v>
       </c>
       <c r="B143" t="n">
-        <v>98450</v>
+        <v>57660</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>553413</v>
+        <v>553311</v>
       </c>
       <c r="R143" t="n">
-        <v>6704868</v>
+        <v>6704717</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16149,11 +16155,6 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16180,38 +16181,42 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127314473</v>
+        <v>127314441</v>
       </c>
       <c r="B144" t="n">
-        <v>57584</v>
+        <v>98450</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -16220,10 +16225,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>553415</v>
+        <v>553422</v>
       </c>
       <c r="R144" t="n">
-        <v>6705462</v>
+        <v>6704986</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16258,11 +16263,6 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>Fjädrar på "slaktbord"</t>
-        </is>
-      </c>
       <c r="AD144" t="b">
         <v>0</v>
       </c>
@@ -16280,7 +16280,7 @@
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
@@ -16718,50 +16718,45 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127314405</v>
+        <v>127314343</v>
       </c>
       <c r="B149" t="n">
-        <v>8450</v>
+        <v>91332</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>553521</v>
+        <v>553388</v>
       </c>
       <c r="R149" t="n">
-        <v>6705364</v>
+        <v>6704753</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16820,59 +16815,45 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127314411</v>
+        <v>127314342</v>
       </c>
       <c r="B150" t="n">
-        <v>98450</v>
+        <v>91332</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>553500</v>
+        <v>553347</v>
       </c>
       <c r="R150" t="n">
-        <v>6705175</v>
+        <v>6704783</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16931,47 +16912,38 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127314450</v>
+        <v>127314405</v>
       </c>
       <c r="B151" t="n">
-        <v>98450</v>
+        <v>8450</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -16980,10 +16952,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>553340</v>
+        <v>553521</v>
       </c>
       <c r="R151" t="n">
-        <v>6704784</v>
+        <v>6705364</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17035,52 +17007,66 @@
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127314343</v>
+        <v>127314419</v>
       </c>
       <c r="B152" t="n">
-        <v>91332</v>
+        <v>98450</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>553388</v>
+        <v>553343</v>
       </c>
       <c r="R152" t="n">
-        <v>6704753</v>
+        <v>6704786</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17113,6 +17099,11 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17139,45 +17130,59 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>127314342</v>
+        <v>127314411</v>
       </c>
       <c r="B153" t="n">
-        <v>91332</v>
+        <v>98450</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>553347</v>
+        <v>553500</v>
       </c>
       <c r="R153" t="n">
-        <v>6704783</v>
+        <v>6705175</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17236,7 +17241,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127314419</v>
+        <v>127314450</v>
       </c>
       <c r="B154" t="n">
         <v>98450</v>
@@ -17266,7 +17271,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -17285,10 +17290,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>553343</v>
+        <v>553340</v>
       </c>
       <c r="R154" t="n">
-        <v>6704786</v>
+        <v>6704784</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17323,11 +17328,6 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD154" t="b">
         <v>0</v>
       </c>
@@ -17345,57 +17345,52 @@
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127314391</v>
+        <v>127314385</v>
       </c>
       <c r="B155" t="n">
-        <v>57663</v>
+        <v>56959</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100109</v>
+        <v>100038</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>553375</v>
+        <v>553426</v>
       </c>
       <c r="R155" t="n">
-        <v>6705433</v>
+        <v>6704786</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17428,11 +17423,6 @@
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17561,10 +17551,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127314387</v>
+        <v>127314447</v>
       </c>
       <c r="B157" t="n">
-        <v>91786</v>
+        <v>98450</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17572,34 +17562,48 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>553517</v>
+        <v>553387</v>
       </c>
       <c r="R157" t="n">
-        <v>6705421</v>
+        <v>6704938</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17651,60 +17655,61 @@
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127314374</v>
+        <v>127314433</v>
       </c>
       <c r="B158" t="n">
-        <v>57660</v>
+        <v>98450</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N158" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>553523</v>
+        <v>553366</v>
       </c>
       <c r="R158" t="n">
-        <v>6705404</v>
+        <v>6704886</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17763,32 +17768,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127314385</v>
+        <v>127314387</v>
       </c>
       <c r="B159" t="n">
-        <v>56959</v>
+        <v>91786</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100038</v>
+        <v>1209</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17798,10 +17803,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>553426</v>
+        <v>553517</v>
       </c>
       <c r="R159" t="n">
-        <v>6704786</v>
+        <v>6705421</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17860,59 +17865,53 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127314447</v>
+        <v>127314374</v>
       </c>
       <c r="B160" t="n">
-        <v>98450</v>
+        <v>57660</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>553387</v>
+        <v>553523</v>
       </c>
       <c r="R160" t="n">
-        <v>6704938</v>
+        <v>6705404</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17964,49 +17963,45 @@
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127314433</v>
+        <v>127314391</v>
       </c>
       <c r="B161" t="n">
-        <v>98450</v>
+        <v>57663</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
@@ -18015,10 +18010,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>553366</v>
+        <v>553375</v>
       </c>
       <c r="R161" t="n">
-        <v>6704886</v>
+        <v>6705433</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18051,6 +18046,11 @@
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18077,7 +18077,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127314434</v>
+        <v>127314443</v>
       </c>
       <c r="B162" t="n">
         <v>98450</v>
@@ -18107,7 +18107,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -18115,21 +18115,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>553416</v>
+        <v>553338</v>
       </c>
       <c r="R162" t="n">
-        <v>6704816</v>
+        <v>6705039</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18162,11 +18157,6 @@
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18193,7 +18183,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>127314443</v>
+        <v>127314448</v>
       </c>
       <c r="B163" t="n">
         <v>98450</v>
@@ -18223,7 +18213,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -18231,16 +18221,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>553338</v>
+        <v>553342</v>
       </c>
       <c r="R163" t="n">
-        <v>6705039</v>
+        <v>6704852</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18292,14 +18287,14 @@
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>127314448</v>
+        <v>127314451</v>
       </c>
       <c r="B164" t="n">
         <v>98450</v>
@@ -18348,10 +18343,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>553342</v>
+        <v>553427</v>
       </c>
       <c r="R164" t="n">
-        <v>6704852</v>
+        <v>6704914</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18410,7 +18405,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>127314451</v>
+        <v>127314434</v>
       </c>
       <c r="B165" t="n">
         <v>98450</v>
@@ -18440,7 +18435,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -18459,10 +18454,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>553427</v>
+        <v>553416</v>
       </c>
       <c r="R165" t="n">
-        <v>6704914</v>
+        <v>6704816</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18497,6 +18492,11 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD165" t="b">
         <v>0</v>
       </c>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
@@ -21829,59 +21829,53 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>127314445</v>
+        <v>127314363</v>
       </c>
       <c r="B197" t="n">
-        <v>98450</v>
+        <v>57823</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>553364</v>
+        <v>553336</v>
       </c>
       <c r="R197" t="n">
-        <v>6704996</v>
+        <v>6704944</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21933,61 +21927,52 @@
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>127314429</v>
+        <v>127314389</v>
       </c>
       <c r="B198" t="n">
-        <v>98450</v>
+        <v>91628</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>553414</v>
+        <v>553364</v>
       </c>
       <c r="R198" t="n">
-        <v>6704864</v>
+        <v>6704790</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22046,42 +22031,38 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>127314425</v>
+        <v>127314382</v>
       </c>
       <c r="B199" t="n">
-        <v>98450</v>
+        <v>57313</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>220787</v>
+        <v>100063</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
@@ -22090,10 +22071,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>553466</v>
+        <v>553494</v>
       </c>
       <c r="R199" t="n">
-        <v>6705077</v>
+        <v>6705461</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22152,47 +22133,38 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127314420</v>
+        <v>127314325</v>
       </c>
       <c r="B200" t="n">
-        <v>98450</v>
+        <v>5197</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -22201,10 +22173,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>553426</v>
+        <v>553508</v>
       </c>
       <c r="R200" t="n">
-        <v>6704821</v>
+        <v>6705185</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22237,11 +22209,6 @@
       <c r="AA200" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22268,35 +22235,49 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>127314389</v>
+        <v>127314445</v>
       </c>
       <c r="B201" t="n">
-        <v>91628</v>
+        <v>98450</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P201" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
@@ -22306,7 +22287,7 @@
         <v>553364</v>
       </c>
       <c r="R201" t="n">
-        <v>6704790</v>
+        <v>6704996</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22358,45 +22339,49 @@
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127314382</v>
+        <v>127314429</v>
       </c>
       <c r="B202" t="n">
-        <v>57313</v>
+        <v>98450</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>100063</v>
+        <v>220787</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr"/>
-      <c r="M202" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
@@ -22405,10 +22390,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>553494</v>
+        <v>553414</v>
       </c>
       <c r="R202" t="n">
-        <v>6705461</v>
+        <v>6704864</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22467,53 +22452,54 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>127314363</v>
+        <v>127314425</v>
       </c>
       <c r="B203" t="n">
-        <v>57823</v>
+        <v>98450</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr"/>
-      <c r="K203" t="inlineStr"/>
-      <c r="L203" t="inlineStr"/>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N203" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P203" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>553336</v>
+        <v>553466</v>
       </c>
       <c r="R203" t="n">
-        <v>6704944</v>
+        <v>6705077</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22572,38 +22558,47 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>127314325</v>
+        <v>127314420</v>
       </c>
       <c r="B204" t="n">
-        <v>5197</v>
+        <v>98450</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr"/>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
@@ -22612,10 +22607,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>553508</v>
+        <v>553426</v>
       </c>
       <c r="R204" t="n">
-        <v>6705185</v>
+        <v>6704821</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22648,6 +22643,11 @@
       <c r="AA204" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -23186,50 +23186,45 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>127314368</v>
+        <v>127314477</v>
       </c>
       <c r="B210" t="n">
-        <v>57660</v>
+        <v>92622</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P210" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>553500</v>
+        <v>553371</v>
       </c>
       <c r="R210" t="n">
-        <v>6705249</v>
+        <v>6704731</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23264,6 +23259,11 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>Många gamla fruktkroppar i häxring</t>
+        </is>
+      </c>
       <c r="AD210" t="b">
         <v>0</v>
       </c>
@@ -23281,55 +23281,58 @@
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>127314477</v>
+        <v>127310539</v>
       </c>
       <c r="B211" t="n">
-        <v>92622</v>
+        <v>91544</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>4364</v>
+        <v>1106</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Morkullberget södra, Dlr</t>
+          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>553371</v>
+        <v>553483</v>
       </c>
       <c r="R211" t="n">
-        <v>6704731</v>
+        <v>6705051</v>
       </c>
       <c r="S211" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -23361,24 +23364,20 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC211" t="inlineStr">
-        <is>
-          <t>Många gamla fruktkroppar i häxring</t>
-        </is>
-      </c>
       <c r="AD211" t="b">
         <v>0</v>
       </c>
       <c r="AE211" t="b">
         <v>0</v>
       </c>
+      <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="b">
         <v>0</v>
       </c>
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
@@ -23390,51 +23389,53 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>127310539</v>
+        <v>127314480</v>
       </c>
       <c r="B212" t="n">
-        <v>91544</v>
+        <v>5177</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>1106</v>
+        <v>100526</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
-      <c r="J212" t="inlineStr"/>
-      <c r="K212" t="inlineStr"/>
-      <c r="N212" t="inlineStr"/>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
+          <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>553483</v>
+        <v>553399</v>
       </c>
       <c r="R212" t="n">
-        <v>6705051</v>
+        <v>6704947</v>
       </c>
       <c r="S212" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -23472,14 +23473,13 @@
       <c r="AE212" t="b">
         <v>0</v>
       </c>
-      <c r="AF212" t="inlineStr"/>
       <c r="AG212" t="b">
         <v>0</v>
       </c>
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
@@ -23491,38 +23491,38 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>127314480</v>
+        <v>127314368</v>
       </c>
       <c r="B213" t="n">
-        <v>5177</v>
+        <v>57660</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
       <c r="M213" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -23531,10 +23531,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>553399</v>
+        <v>553500</v>
       </c>
       <c r="R213" t="n">
-        <v>6704947</v>
+        <v>6705249</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -23586,7 +23586,7 @@
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
@@ -23699,32 +23699,32 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>127314351</v>
+        <v>127314396</v>
       </c>
       <c r="B215" t="n">
-        <v>91332</v>
+        <v>97327</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -23734,10 +23734,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>553533</v>
+        <v>553521</v>
       </c>
       <c r="R215" t="n">
-        <v>6705296</v>
+        <v>6705212</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -23796,7 +23796,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>127314348</v>
+        <v>127314351</v>
       </c>
       <c r="B216" t="n">
         <v>91332</v>
@@ -23831,10 +23831,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>553499</v>
+        <v>553533</v>
       </c>
       <c r="R216" t="n">
-        <v>6705218</v>
+        <v>6705296</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -23893,32 +23893,32 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>127314396</v>
+        <v>127314348</v>
       </c>
       <c r="B217" t="n">
-        <v>97327</v>
+        <v>91332</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -23928,10 +23928,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>553521</v>
+        <v>553499</v>
       </c>
       <c r="R217" t="n">
-        <v>6705212</v>
+        <v>6705218</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -25044,42 +25044,38 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127314444</v>
+        <v>127314371</v>
       </c>
       <c r="B228" t="n">
-        <v>98450</v>
+        <v>57660</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J228" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr"/>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
@@ -25088,10 +25084,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>553489</v>
+        <v>553336</v>
       </c>
       <c r="R228" t="n">
-        <v>6705294</v>
+        <v>6704723</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25143,49 +25139,45 @@
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127314440</v>
+        <v>127314479</v>
       </c>
       <c r="B229" t="n">
-        <v>98450</v>
+        <v>5177</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I229" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J229" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr"/>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -25194,10 +25186,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>553571</v>
+        <v>553496</v>
       </c>
       <c r="R229" t="n">
-        <v>6705297</v>
+        <v>6705218</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25249,34 +25241,34 @@
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>127314371</v>
+        <v>127314326</v>
       </c>
       <c r="B230" t="n">
-        <v>57660</v>
+        <v>5197</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -25287,7 +25279,7 @@
       <c r="I230" t="inlineStr"/>
       <c r="M230" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
@@ -25296,10 +25288,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>553336</v>
+        <v>553527</v>
       </c>
       <c r="R230" t="n">
-        <v>6704723</v>
+        <v>6705221</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -25358,38 +25350,47 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>127314326</v>
+        <v>127314414</v>
       </c>
       <c r="B231" t="n">
-        <v>5197</v>
+        <v>98450</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I231" t="inlineStr"/>
-      <c r="M231" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P231" t="inlineStr">
@@ -25398,10 +25399,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>553527</v>
+        <v>553341</v>
       </c>
       <c r="R231" t="n">
-        <v>6705221</v>
+        <v>6704994</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -25434,6 +25435,11 @@
       <c r="AA231" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -25460,38 +25466,42 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>127314479</v>
+        <v>127314444</v>
       </c>
       <c r="B232" t="n">
-        <v>5177</v>
+        <v>98450</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I232" t="inlineStr"/>
-      <c r="M232" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P232" t="inlineStr">
@@ -25500,10 +25510,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>553496</v>
+        <v>553489</v>
       </c>
       <c r="R232" t="n">
-        <v>6705218</v>
+        <v>6705294</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -25562,7 +25572,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>127314414</v>
+        <v>127314440</v>
       </c>
       <c r="B233" t="n">
         <v>98450</v>
@@ -25592,7 +25602,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -25600,21 +25610,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P233" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>553341</v>
+        <v>553571</v>
       </c>
       <c r="R233" t="n">
-        <v>6704994</v>
+        <v>6705297</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -25647,11 +25652,6 @@
       <c r="AA233" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC233" t="inlineStr">
-        <is>
-          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD233" t="b">

--- a/artfynd/A 18040-2021 artfynd.xlsx
+++ b/artfynd/A 18040-2021 artfynd.xlsx
@@ -13776,32 +13776,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127314388</v>
+        <v>127314398</v>
       </c>
       <c r="B121" t="n">
-        <v>91786</v>
+        <v>97327</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1209</v>
+        <v>221945</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13811,10 +13811,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>553411</v>
+        <v>553472</v>
       </c>
       <c r="R121" t="n">
-        <v>6705072</v>
+        <v>6705479</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13873,50 +13873,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127314375</v>
+        <v>127314397</v>
       </c>
       <c r="B122" t="n">
-        <v>57660</v>
+        <v>97327</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>553537</v>
+        <v>553527</v>
       </c>
       <c r="R122" t="n">
-        <v>6705403</v>
+        <v>6705221</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13975,32 +13970,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127314398</v>
+        <v>127314388</v>
       </c>
       <c r="B123" t="n">
-        <v>97327</v>
+        <v>91786</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>221945</v>
+        <v>1209</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14010,10 +14005,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>553472</v>
+        <v>553411</v>
       </c>
       <c r="R123" t="n">
-        <v>6705479</v>
+        <v>6705072</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14072,45 +14067,50 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127314397</v>
+        <v>127314375</v>
       </c>
       <c r="B124" t="n">
-        <v>97327</v>
+        <v>57660</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>553527</v>
+        <v>553537</v>
       </c>
       <c r="R124" t="n">
-        <v>6705221</v>
+        <v>6705403</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14276,42 +14276,38 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127314432</v>
+        <v>127314372</v>
       </c>
       <c r="B126" t="n">
-        <v>98450</v>
+        <v>57660</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -14320,10 +14316,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>553508</v>
+        <v>553488</v>
       </c>
       <c r="R126" t="n">
-        <v>6705194</v>
+        <v>6705460</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14382,7 +14378,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127314435</v>
+        <v>127314416</v>
       </c>
       <c r="B127" t="n">
         <v>98450</v>
@@ -14412,7 +14408,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -14431,10 +14427,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>553476</v>
+        <v>553356</v>
       </c>
       <c r="R127" t="n">
-        <v>6705068</v>
+        <v>6704786</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14471,7 +14467,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>12 blomstjälkar</t>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14498,7 +14494,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127314416</v>
+        <v>127314432</v>
       </c>
       <c r="B128" t="n">
         <v>98450</v>
@@ -14528,7 +14524,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -14536,21 +14532,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>553356</v>
+        <v>553508</v>
       </c>
       <c r="R128" t="n">
-        <v>6704786</v>
+        <v>6705194</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14583,11 +14574,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14614,7 +14600,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127314415</v>
+        <v>127314435</v>
       </c>
       <c r="B129" t="n">
         <v>98450</v>
@@ -14644,7 +14630,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -14663,10 +14649,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>553463</v>
+        <v>553476</v>
       </c>
       <c r="R129" t="n">
-        <v>6705155</v>
+        <v>6705068</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14703,7 +14689,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>4 blomstjälkar</t>
+          <t>12 blomstjälkar</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14730,38 +14716,47 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127314372</v>
+        <v>127314415</v>
       </c>
       <c r="B130" t="n">
-        <v>57660</v>
+        <v>98450</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -14770,10 +14765,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>553488</v>
+        <v>553463</v>
       </c>
       <c r="R130" t="n">
-        <v>6705460</v>
+        <v>6705155</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14806,6 +14801,11 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14832,32 +14832,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127314336</v>
+        <v>127314347</v>
       </c>
       <c r="B131" t="n">
-        <v>91690</v>
+        <v>91332</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14867,10 +14867,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>553429</v>
+        <v>553419</v>
       </c>
       <c r="R131" t="n">
-        <v>6705077</v>
+        <v>6705073</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14929,32 +14929,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127314347</v>
+        <v>127314336</v>
       </c>
       <c r="B132" t="n">
-        <v>91332</v>
+        <v>91690</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14964,10 +14964,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>553419</v>
+        <v>553429</v>
       </c>
       <c r="R132" t="n">
-        <v>6705073</v>
+        <v>6705077</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15417,7 +15417,7 @@
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
@@ -15740,14 +15740,14 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127314442</v>
+        <v>127314441</v>
       </c>
       <c r="B140" t="n">
         <v>98450</v>
@@ -15791,10 +15791,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>553423</v>
+        <v>553422</v>
       </c>
       <c r="R140" t="n">
-        <v>6704914</v>
+        <v>6704986</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15853,7 +15853,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127314417</v>
+        <v>127314442</v>
       </c>
       <c r="B141" t="n">
         <v>98450</v>
@@ -15883,7 +15883,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -15891,21 +15891,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>553413</v>
+        <v>553423</v>
       </c>
       <c r="R141" t="n">
-        <v>6704868</v>
+        <v>6704914</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15938,11 +15933,6 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15969,38 +15959,47 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127314473</v>
+        <v>127314417</v>
       </c>
       <c r="B142" t="n">
-        <v>57584</v>
+        <v>98450</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -16009,10 +16008,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>553415</v>
+        <v>553413</v>
       </c>
       <c r="R142" t="n">
-        <v>6705462</v>
+        <v>6704868</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16049,7 +16048,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>Fjädrar på "slaktbord"</t>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16069,17 +16068,17 @@
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127314370</v>
+        <v>127314473</v>
       </c>
       <c r="B143" t="n">
-        <v>57660</v>
+        <v>57584</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16087,16 +16086,16 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -16105,24 +16104,21 @@
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>553311</v>
+        <v>553415</v>
       </c>
       <c r="R143" t="n">
-        <v>6704717</v>
+        <v>6705462</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16155,6 +16151,11 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Fjädrar på "slaktbord"</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16181,54 +16182,53 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127314441</v>
+        <v>127314370</v>
       </c>
       <c r="B144" t="n">
-        <v>98450</v>
+        <v>57660</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>553422</v>
+        <v>553311</v>
       </c>
       <c r="R144" t="n">
-        <v>6704986</v>
+        <v>6704717</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16711,52 +16711,57 @@
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127314343</v>
+        <v>127314405</v>
       </c>
       <c r="B149" t="n">
-        <v>91332</v>
+        <v>8450</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>553388</v>
+        <v>553521</v>
       </c>
       <c r="R149" t="n">
-        <v>6704753</v>
+        <v>6705364</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16815,45 +16820,59 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127314342</v>
+        <v>127314411</v>
       </c>
       <c r="B150" t="n">
-        <v>91332</v>
+        <v>98450</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>553347</v>
+        <v>553500</v>
       </c>
       <c r="R150" t="n">
-        <v>6704783</v>
+        <v>6705175</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16912,38 +16931,47 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127314405</v>
+        <v>127314419</v>
       </c>
       <c r="B151" t="n">
-        <v>8450</v>
+        <v>98450</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -16952,10 +16980,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>553521</v>
+        <v>553343</v>
       </c>
       <c r="R151" t="n">
-        <v>6705364</v>
+        <v>6704786</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16988,6 +17016,11 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17014,7 +17047,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127314419</v>
+        <v>127314450</v>
       </c>
       <c r="B152" t="n">
         <v>98450</v>
@@ -17044,7 +17077,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -17063,10 +17096,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>553343</v>
+        <v>553340</v>
       </c>
       <c r="R152" t="n">
-        <v>6704786</v>
+        <v>6704784</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17099,11 +17132,6 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17130,59 +17158,45 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>127314411</v>
+        <v>127314343</v>
       </c>
       <c r="B153" t="n">
-        <v>98450</v>
+        <v>91332</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>553500</v>
+        <v>553388</v>
       </c>
       <c r="R153" t="n">
-        <v>6705175</v>
+        <v>6704753</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17241,59 +17255,45 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127314450</v>
+        <v>127314342</v>
       </c>
       <c r="B154" t="n">
-        <v>98450</v>
+        <v>91332</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>553340</v>
+        <v>553347</v>
       </c>
       <c r="R154" t="n">
-        <v>6704784</v>
+        <v>6704783</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17345,39 +17345,39 @@
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127314385</v>
+        <v>127314387</v>
       </c>
       <c r="B155" t="n">
-        <v>56959</v>
+        <v>91786</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100038</v>
+        <v>1209</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17387,10 +17387,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>553426</v>
+        <v>553517</v>
       </c>
       <c r="R155" t="n">
-        <v>6704786</v>
+        <v>6705421</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17449,38 +17449,38 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127314362</v>
+        <v>127314391</v>
       </c>
       <c r="B156" t="n">
-        <v>4773</v>
+        <v>57663</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100299</v>
+        <v>100109</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="M156" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -17489,10 +17489,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>553526</v>
+        <v>553375</v>
       </c>
       <c r="R156" t="n">
-        <v>6705221</v>
+        <v>6705433</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17525,6 +17525,11 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17551,47 +17556,38 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127314447</v>
+        <v>127314362</v>
       </c>
       <c r="B157" t="n">
-        <v>98450</v>
+        <v>4773</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
@@ -17600,10 +17596,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>553387</v>
+        <v>553526</v>
       </c>
       <c r="R157" t="n">
-        <v>6704938</v>
+        <v>6705221</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17655,14 +17651,14 @@
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127314433</v>
+        <v>127314447</v>
       </c>
       <c r="B158" t="n">
         <v>98450</v>
@@ -17692,7 +17688,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -17700,16 +17696,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>553366</v>
+        <v>553387</v>
       </c>
       <c r="R158" t="n">
-        <v>6704886</v>
+        <v>6704938</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17768,10 +17769,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127314387</v>
+        <v>127314433</v>
       </c>
       <c r="B159" t="n">
-        <v>91786</v>
+        <v>98450</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17779,34 +17780,43 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>553517</v>
+        <v>553366</v>
       </c>
       <c r="R159" t="n">
-        <v>6705421</v>
+        <v>6704886</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17865,53 +17875,45 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127314374</v>
+        <v>127314385</v>
       </c>
       <c r="B160" t="n">
-        <v>57660</v>
+        <v>56959</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100049</v>
+        <v>100038</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>553523</v>
+        <v>553426</v>
       </c>
       <c r="R160" t="n">
-        <v>6705404</v>
+        <v>6704786</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17970,10 +17972,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127314391</v>
+        <v>127314374</v>
       </c>
       <c r="B161" t="n">
-        <v>57663</v>
+        <v>57660</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17981,16 +17983,16 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -17999,21 +18001,24 @@
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>553375</v>
+        <v>553523</v>
       </c>
       <c r="R161" t="n">
-        <v>6705433</v>
+        <v>6705404</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18046,11 +18051,6 @@
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18287,14 +18287,14 @@
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>127314451</v>
+        <v>127314434</v>
       </c>
       <c r="B164" t="n">
         <v>98450</v>
@@ -18324,7 +18324,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -18343,10 +18343,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>553427</v>
+        <v>553416</v>
       </c>
       <c r="R164" t="n">
-        <v>6704914</v>
+        <v>6704816</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18381,6 +18381,11 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
@@ -18398,14 +18403,14 @@
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>127314434</v>
+        <v>127314451</v>
       </c>
       <c r="B165" t="n">
         <v>98450</v>
@@ -18435,7 +18440,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -18454,10 +18459,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>553416</v>
+        <v>553427</v>
       </c>
       <c r="R165" t="n">
-        <v>6704816</v>
+        <v>6704914</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18490,11 +18495,6 @@
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18954,49 +18954,45 @@
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>127314426</v>
+        <v>127314393</v>
       </c>
       <c r="B170" t="n">
-        <v>98450</v>
+        <v>57663</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
@@ -19005,10 +19001,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>553452</v>
+        <v>553521</v>
       </c>
       <c r="R170" t="n">
-        <v>6705056</v>
+        <v>6705364</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19041,6 +19037,11 @@
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19067,7 +19068,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127314455</v>
+        <v>127314426</v>
       </c>
       <c r="B171" t="n">
         <v>98450</v>
@@ -19097,7 +19098,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -19105,21 +19106,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>553431</v>
+        <v>553452</v>
       </c>
       <c r="R171" t="n">
-        <v>6704842</v>
+        <v>6705056</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19154,11 +19150,6 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD171" t="b">
         <v>0</v>
       </c>
@@ -19176,49 +19167,54 @@
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>127314386</v>
+        <v>127314455</v>
       </c>
       <c r="B172" t="n">
-        <v>92634</v>
+        <v>98450</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
@@ -19227,10 +19223,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>553414</v>
+        <v>553431</v>
       </c>
       <c r="R172" t="n">
-        <v>6704970</v>
+        <v>6704842</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19263,6 +19259,11 @@
       <c r="AA172" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19289,38 +19290,42 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127314393</v>
+        <v>127314386</v>
       </c>
       <c r="B173" t="n">
-        <v>57663</v>
+        <v>92634</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr"/>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
@@ -19329,10 +19334,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>553521</v>
+        <v>553414</v>
       </c>
       <c r="R173" t="n">
-        <v>6705364</v>
+        <v>6704970</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19365,11 +19370,6 @@
       <c r="AA173" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19396,45 +19396,50 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127314355</v>
+        <v>127314392</v>
       </c>
       <c r="B174" t="n">
-        <v>91690</v>
+        <v>57663</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P174" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>553451</v>
+        <v>553395</v>
       </c>
       <c r="R174" t="n">
-        <v>6705503</v>
+        <v>6704765</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19467,6 +19472,11 @@
       <c r="AA174" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19493,38 +19503,38 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127314392</v>
+        <v>127314482</v>
       </c>
       <c r="B175" t="n">
-        <v>57663</v>
+        <v>5177</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="M175" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
@@ -19533,10 +19543,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>553395</v>
+        <v>553322</v>
       </c>
       <c r="R175" t="n">
-        <v>6704765</v>
+        <v>6704727</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19569,11 +19579,6 @@
       <c r="AA175" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19699,57 +19704,52 @@
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>127314482</v>
+        <v>127314355</v>
       </c>
       <c r="B177" t="n">
-        <v>5177</v>
+        <v>91690</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>100526</v>
+        <v>2062</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P177" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>553322</v>
+        <v>553451</v>
       </c>
       <c r="R177" t="n">
-        <v>6704727</v>
+        <v>6705503</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19801,7 +19801,7 @@
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
@@ -19924,50 +19924,45 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>127314381</v>
+        <v>127314395</v>
       </c>
       <c r="B179" t="n">
-        <v>57660</v>
+        <v>97327</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P179" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>553468</v>
+        <v>553357</v>
       </c>
       <c r="R179" t="n">
-        <v>6705451</v>
+        <v>6704877</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20026,35 +20021,40 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>127314467</v>
+        <v>127314381</v>
       </c>
       <c r="B180" t="n">
-        <v>105488</v>
+        <v>57660</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
@@ -20064,7 +20064,7 @@
         <v>553468</v>
       </c>
       <c r="R180" t="n">
-        <v>6705155</v>
+        <v>6705451</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20116,54 +20116,45 @@
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>127314418</v>
+        <v>127314378</v>
       </c>
       <c r="B181" t="n">
-        <v>98450</v>
+        <v>57660</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
@@ -20172,10 +20163,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>553496</v>
+        <v>553468</v>
       </c>
       <c r="R181" t="n">
-        <v>6705280</v>
+        <v>6705210</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20208,11 +20199,6 @@
       <c r="AA181" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20239,47 +20225,38 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127314413</v>
+        <v>127314484</v>
       </c>
       <c r="B182" t="n">
-        <v>98450</v>
+        <v>5177</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
@@ -20288,10 +20265,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>553349</v>
+        <v>553430</v>
       </c>
       <c r="R182" t="n">
-        <v>6704994</v>
+        <v>6705087</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20324,11 +20301,6 @@
       <c r="AA182" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC182" t="inlineStr">
-        <is>
-          <t>5 blomstjälkar</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20355,7 +20327,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>127314430</v>
+        <v>127314413</v>
       </c>
       <c r="B183" t="n">
         <v>98450</v>
@@ -20385,7 +20357,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -20393,16 +20365,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P183" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>553358</v>
+        <v>553349</v>
       </c>
       <c r="R183" t="n">
-        <v>6705058</v>
+        <v>6704994</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20435,6 +20412,11 @@
       <c r="AA183" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>5 blomstjälkar</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -20461,38 +20443,47 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>127314378</v>
+        <v>127314418</v>
       </c>
       <c r="B184" t="n">
-        <v>57660</v>
+        <v>98450</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr"/>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
@@ -20501,10 +20492,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>553468</v>
+        <v>553496</v>
       </c>
       <c r="R184" t="n">
-        <v>6705210</v>
+        <v>6705280</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20537,6 +20528,11 @@
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20563,38 +20559,42 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>127314484</v>
+        <v>127314430</v>
       </c>
       <c r="B185" t="n">
-        <v>5177</v>
+        <v>98450</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr"/>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
@@ -20603,10 +20603,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>553430</v>
+        <v>553358</v>
       </c>
       <c r="R185" t="n">
-        <v>6705087</v>
+        <v>6705058</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20658,17 +20658,17 @@
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>127314395</v>
+        <v>127314467</v>
       </c>
       <c r="B186" t="n">
-        <v>97327</v>
+        <v>105488</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20676,21 +20676,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -20700,10 +20700,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>553357</v>
+        <v>553468</v>
       </c>
       <c r="R186" t="n">
-        <v>6704877</v>
+        <v>6705155</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -21079,7 +21079,7 @@
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
@@ -21185,7 +21185,7 @@
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
@@ -21291,17 +21291,17 @@
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>127314339</v>
+        <v>127310426</v>
       </c>
       <c r="B192" t="n">
-        <v>91690</v>
+        <v>98450</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21309,37 +21309,53 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Morkullberget södra, Dlr</t>
+          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>553347</v>
+        <v>553479</v>
       </c>
       <c r="R192" t="n">
-        <v>6704783</v>
+        <v>6705057</v>
       </c>
       <c r="S192" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -21377,25 +21393,26 @@
       <c r="AE192" t="b">
         <v>0</v>
       </c>
+      <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="b">
         <v>0</v>
       </c>
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>127310426</v>
+        <v>127314408</v>
       </c>
       <c r="B193" t="n">
         <v>98450</v>
@@ -21423,36 +21440,25 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
-      <c r="L193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
+          <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>553479</v>
+        <v>553400</v>
       </c>
       <c r="R193" t="n">
-        <v>6705057</v>
+        <v>6705072</v>
       </c>
       <c r="S193" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -21484,32 +21490,36 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>få synliga bladrosetter</t>
+        </is>
+      </c>
       <c r="AD193" t="b">
         <v>0</v>
       </c>
       <c r="AE193" t="b">
         <v>0</v>
       </c>
-      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>127314408</v>
+        <v>127314423</v>
       </c>
       <c r="B194" t="n">
         <v>98450</v>
@@ -21537,7 +21547,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K194" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -21549,10 +21568,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>553400</v>
+        <v>553338</v>
       </c>
       <c r="R194" t="n">
-        <v>6705072</v>
+        <v>6704806</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21585,11 +21604,6 @@
       <c r="AA194" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>få synliga bladrosetter</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21616,10 +21630,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>127314423</v>
+        <v>127314339</v>
       </c>
       <c r="B195" t="n">
-        <v>98450</v>
+        <v>91690</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21627,48 +21641,34 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>553338</v>
+        <v>553347</v>
       </c>
       <c r="R195" t="n">
-        <v>6704806</v>
+        <v>6704783</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21727,27 +21727,27 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>127314379</v>
+        <v>127314325</v>
       </c>
       <c r="B196" t="n">
-        <v>57660</v>
+        <v>5197</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -21758,7 +21758,7 @@
       <c r="I196" t="inlineStr"/>
       <c r="M196" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
@@ -21767,10 +21767,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>553485</v>
+        <v>553508</v>
       </c>
       <c r="R196" t="n">
-        <v>6705230</v>
+        <v>6705185</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21829,53 +21829,54 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>127314363</v>
+        <v>127314425</v>
       </c>
       <c r="B197" t="n">
-        <v>57823</v>
+        <v>98450</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr"/>
-      <c r="K197" t="inlineStr"/>
-      <c r="L197" t="inlineStr"/>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N197" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>553336</v>
+        <v>553466</v>
       </c>
       <c r="R197" t="n">
-        <v>6704944</v>
+        <v>6705077</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21934,45 +21935,59 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>127314389</v>
+        <v>127314420</v>
       </c>
       <c r="B198" t="n">
-        <v>91628</v>
+        <v>98450</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>553364</v>
+        <v>553426</v>
       </c>
       <c r="R198" t="n">
-        <v>6704790</v>
+        <v>6704821</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22005,6 +22020,11 @@
       <c r="AA198" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -22031,38 +22051,47 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>127314382</v>
+        <v>127314445</v>
       </c>
       <c r="B199" t="n">
-        <v>57313</v>
+        <v>98450</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>100063</v>
+        <v>220787</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr"/>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
@@ -22071,10 +22100,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>553494</v>
+        <v>553364</v>
       </c>
       <c r="R199" t="n">
-        <v>6705461</v>
+        <v>6704996</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22133,38 +22162,42 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127314325</v>
+        <v>127314429</v>
       </c>
       <c r="B200" t="n">
-        <v>5197</v>
+        <v>98450</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr"/>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -22173,10 +22206,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>553508</v>
+        <v>553414</v>
       </c>
       <c r="R200" t="n">
-        <v>6705185</v>
+        <v>6704864</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22235,47 +22268,38 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>127314445</v>
+        <v>127314382</v>
       </c>
       <c r="B201" t="n">
-        <v>98450</v>
+        <v>57313</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>220787</v>
+        <v>100063</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr"/>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
@@ -22284,10 +22308,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>553364</v>
+        <v>553494</v>
       </c>
       <c r="R201" t="n">
-        <v>6704996</v>
+        <v>6705461</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22339,61 +22363,52 @@
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127314429</v>
+        <v>127314389</v>
       </c>
       <c r="B202" t="n">
-        <v>98450</v>
+        <v>91628</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>553414</v>
+        <v>553364</v>
       </c>
       <c r="R202" t="n">
-        <v>6704864</v>
+        <v>6704790</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22452,42 +22467,38 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>127314425</v>
+        <v>127314379</v>
       </c>
       <c r="B203" t="n">
-        <v>98450</v>
+        <v>57660</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr"/>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
@@ -22496,10 +22507,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>553466</v>
+        <v>553485</v>
       </c>
       <c r="R203" t="n">
-        <v>6705077</v>
+        <v>6705230</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22558,59 +22569,53 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>127314420</v>
+        <v>127314363</v>
       </c>
       <c r="B204" t="n">
-        <v>98450</v>
+        <v>57823</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>553426</v>
+        <v>553336</v>
       </c>
       <c r="R204" t="n">
-        <v>6704821</v>
+        <v>6704944</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22643,11 +22648,6 @@
       <c r="AA204" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -22877,7 +22877,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>127314431</v>
+        <v>127314412</v>
       </c>
       <c r="B207" t="n">
         <v>98450</v>
@@ -22907,7 +22907,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -22915,16 +22915,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P207" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>553442</v>
+        <v>553337</v>
       </c>
       <c r="R207" t="n">
-        <v>6705095</v>
+        <v>6704813</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22983,7 +22988,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>127314412</v>
+        <v>127314431</v>
       </c>
       <c r="B208" t="n">
         <v>98450</v>
@@ -23013,7 +23018,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -23021,21 +23026,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P208" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>553337</v>
+        <v>553442</v>
       </c>
       <c r="R208" t="n">
-        <v>6704813</v>
+        <v>6705095</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23186,48 +23186,51 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>127314477</v>
+        <v>127310539</v>
       </c>
       <c r="B210" t="n">
-        <v>92622</v>
+        <v>91544</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>4364</v>
+        <v>1106</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr"/>
+      <c r="K210" t="inlineStr"/>
+      <c r="N210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Morkullberget södra, Dlr</t>
+          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>553371</v>
+        <v>553483</v>
       </c>
       <c r="R210" t="n">
-        <v>6704731</v>
+        <v>6705051</v>
       </c>
       <c r="S210" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -23259,24 +23262,20 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC210" t="inlineStr">
-        <is>
-          <t>Många gamla fruktkroppar i häxring</t>
-        </is>
-      </c>
       <c r="AD210" t="b">
         <v>0</v>
       </c>
       <c r="AE210" t="b">
         <v>0</v>
       </c>
+      <c r="AF210" t="inlineStr"/>
       <c r="AG210" t="b">
         <v>0</v>
       </c>
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
@@ -23288,51 +23287,48 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>127310539</v>
+        <v>127314477</v>
       </c>
       <c r="B211" t="n">
-        <v>91544</v>
+        <v>92622</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>1106</v>
+        <v>4364</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
-      <c r="J211" t="inlineStr"/>
-      <c r="K211" t="inlineStr"/>
-      <c r="N211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
+          <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>553483</v>
+        <v>553371</v>
       </c>
       <c r="R211" t="n">
-        <v>6705051</v>
+        <v>6704731</v>
       </c>
       <c r="S211" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -23364,63 +23360,67 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>Många gamla fruktkroppar i häxring</t>
+        </is>
+      </c>
       <c r="AD211" t="b">
         <v>0</v>
       </c>
       <c r="AE211" t="b">
         <v>0</v>
       </c>
-      <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="b">
         <v>0</v>
       </c>
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>127314480</v>
+        <v>127314368</v>
       </c>
       <c r="B212" t="n">
-        <v>5177</v>
+        <v>57660</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
       <c r="M212" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
@@ -23429,10 +23429,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>553399</v>
+        <v>553500</v>
       </c>
       <c r="R212" t="n">
-        <v>6704947</v>
+        <v>6705249</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23484,45 +23484,45 @@
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>127314368</v>
+        <v>127314480</v>
       </c>
       <c r="B213" t="n">
-        <v>57660</v>
+        <v>5177</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
       <c r="M213" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -23531,10 +23531,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>553500</v>
+        <v>553399</v>
       </c>
       <c r="R213" t="n">
-        <v>6705249</v>
+        <v>6704947</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -23699,32 +23699,32 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>127314396</v>
+        <v>127314351</v>
       </c>
       <c r="B215" t="n">
-        <v>97327</v>
+        <v>91332</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -23734,10 +23734,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>553521</v>
+        <v>553533</v>
       </c>
       <c r="R215" t="n">
-        <v>6705212</v>
+        <v>6705296</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -23796,7 +23796,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>127314351</v>
+        <v>127314348</v>
       </c>
       <c r="B216" t="n">
         <v>91332</v>
@@ -23831,10 +23831,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>553533</v>
+        <v>553499</v>
       </c>
       <c r="R216" t="n">
-        <v>6705296</v>
+        <v>6705218</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -23893,32 +23893,32 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>127314348</v>
+        <v>127314396</v>
       </c>
       <c r="B217" t="n">
-        <v>91332</v>
+        <v>97327</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -23928,10 +23928,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>553499</v>
+        <v>553521</v>
       </c>
       <c r="R217" t="n">
-        <v>6705218</v>
+        <v>6705212</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24092,10 +24092,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127314471</v>
+        <v>127314377</v>
       </c>
       <c r="B219" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24103,34 +24103,39 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>553406</v>
+        <v>553336</v>
       </c>
       <c r="R219" t="n">
-        <v>6705479</v>
+        <v>6704827</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24182,45 +24187,54 @@
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127314377</v>
+        <v>127314422</v>
       </c>
       <c r="B220" t="n">
-        <v>57660</v>
+        <v>98450</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr"/>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -24229,10 +24243,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>553336</v>
+        <v>553445</v>
       </c>
       <c r="R220" t="n">
-        <v>6704827</v>
+        <v>6704996</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24291,7 +24305,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>127314457</v>
+        <v>127314437</v>
       </c>
       <c r="B221" t="n">
         <v>98450</v>
@@ -24321,7 +24335,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -24329,16 +24343,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>553442</v>
+        <v>553333</v>
       </c>
       <c r="R221" t="n">
-        <v>6705078</v>
+        <v>6704814</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24390,14 +24409,14 @@
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>127314458</v>
+        <v>127314456</v>
       </c>
       <c r="B222" t="n">
         <v>98450</v>
@@ -24435,16 +24454,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P222" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>553526</v>
+        <v>553437</v>
       </c>
       <c r="R222" t="n">
-        <v>6705245</v>
+        <v>6704997</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24479,6 +24503,11 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD222" t="b">
         <v>0</v>
       </c>
@@ -24496,52 +24525,61 @@
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>127314394</v>
+        <v>127314457</v>
       </c>
       <c r="B223" t="n">
-        <v>97327</v>
+        <v>98450</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>553498</v>
+        <v>553442</v>
       </c>
       <c r="R223" t="n">
-        <v>6705418</v>
+        <v>6705078</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24600,7 +24638,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127314422</v>
+        <v>127314463</v>
       </c>
       <c r="B224" t="n">
         <v>98450</v>
@@ -24630,7 +24668,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -24638,21 +24676,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P224" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>553445</v>
+        <v>553433</v>
       </c>
       <c r="R224" t="n">
-        <v>6704996</v>
+        <v>6704902</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24711,7 +24744,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127314437</v>
+        <v>127314458</v>
       </c>
       <c r="B225" t="n">
         <v>98450</v>
@@ -24741,7 +24774,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -24749,21 +24782,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P225" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>553333</v>
+        <v>553526</v>
       </c>
       <c r="R225" t="n">
-        <v>6704814</v>
+        <v>6705245</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24822,59 +24850,45 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127314456</v>
+        <v>127314471</v>
       </c>
       <c r="B226" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J226" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K226" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>553437</v>
+        <v>553406</v>
       </c>
       <c r="R226" t="n">
-        <v>6704997</v>
+        <v>6705479</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24909,11 +24923,6 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC226" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD226" t="b">
         <v>0</v>
       </c>
@@ -24931,61 +24940,52 @@
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127314463</v>
+        <v>127314394</v>
       </c>
       <c r="B227" t="n">
-        <v>98450</v>
+        <v>97327</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J227" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>553433</v>
+        <v>553498</v>
       </c>
       <c r="R227" t="n">
-        <v>6704902</v>
+        <v>6705418</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25037,45 +25037,45 @@
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127314371</v>
+        <v>127314479</v>
       </c>
       <c r="B228" t="n">
-        <v>57660</v>
+        <v>5177</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
       <c r="M228" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
@@ -25084,10 +25084,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>553336</v>
+        <v>553496</v>
       </c>
       <c r="R228" t="n">
-        <v>6704723</v>
+        <v>6705218</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25146,38 +25146,47 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127314479</v>
+        <v>127314414</v>
       </c>
       <c r="B229" t="n">
-        <v>5177</v>
+        <v>98450</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I229" t="inlineStr"/>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -25186,10 +25195,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>553496</v>
+        <v>553341</v>
       </c>
       <c r="R229" t="n">
-        <v>6705218</v>
+        <v>6704994</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25224,6 +25233,11 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC229" t="inlineStr">
+        <is>
+          <t>4 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD229" t="b">
         <v>0</v>
       </c>
@@ -25241,45 +25255,49 @@
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>127314326</v>
+        <v>127314444</v>
       </c>
       <c r="B230" t="n">
-        <v>5197</v>
+        <v>98450</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr"/>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
@@ -25288,10 +25306,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>553527</v>
+        <v>553489</v>
       </c>
       <c r="R230" t="n">
-        <v>6705221</v>
+        <v>6705294</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -25350,7 +25368,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>127314414</v>
+        <v>127314440</v>
       </c>
       <c r="B231" t="n">
         <v>98450</v>
@@ -25380,7 +25398,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -25388,21 +25406,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P231" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>553341</v>
+        <v>553571</v>
       </c>
       <c r="R231" t="n">
-        <v>6704994</v>
+        <v>6705297</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -25435,11 +25448,6 @@
       <c r="AA231" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC231" t="inlineStr">
-        <is>
-          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -25466,42 +25474,38 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>127314444</v>
+        <v>127314371</v>
       </c>
       <c r="B232" t="n">
-        <v>98450</v>
+        <v>57660</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I232" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J232" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr"/>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P232" t="inlineStr">
@@ -25510,10 +25514,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>553489</v>
+        <v>553336</v>
       </c>
       <c r="R232" t="n">
-        <v>6705294</v>
+        <v>6704723</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -25565,49 +25569,45 @@
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>127314440</v>
+        <v>127314326</v>
       </c>
       <c r="B233" t="n">
-        <v>98450</v>
+        <v>5197</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J233" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr"/>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
@@ -25616,10 +25616,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>553571</v>
+        <v>553527</v>
       </c>
       <c r="R233" t="n">
-        <v>6705297</v>
+        <v>6705221</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -25774,7 +25774,7 @@
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>

--- a/artfynd/A 18040-2021 artfynd.xlsx
+++ b/artfynd/A 18040-2021 artfynd.xlsx
@@ -13776,45 +13776,50 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127314398</v>
+        <v>127314375</v>
       </c>
       <c r="B121" t="n">
-        <v>97327</v>
+        <v>57660</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>553472</v>
+        <v>553537</v>
       </c>
       <c r="R121" t="n">
-        <v>6705479</v>
+        <v>6705403</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13873,32 +13878,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127314397</v>
+        <v>127314388</v>
       </c>
       <c r="B122" t="n">
-        <v>97327</v>
+        <v>91792</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>221945</v>
+        <v>1209</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13908,10 +13913,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>553527</v>
+        <v>553411</v>
       </c>
       <c r="R122" t="n">
-        <v>6705221</v>
+        <v>6705072</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13970,32 +13975,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127314388</v>
+        <v>127314398</v>
       </c>
       <c r="B123" t="n">
-        <v>91786</v>
+        <v>97333</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1209</v>
+        <v>221945</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14005,10 +14010,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>553411</v>
+        <v>553472</v>
       </c>
       <c r="R123" t="n">
-        <v>6705072</v>
+        <v>6705479</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14067,50 +14072,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127314375</v>
+        <v>127314397</v>
       </c>
       <c r="B124" t="n">
-        <v>57660</v>
+        <v>97333</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>553537</v>
+        <v>553527</v>
       </c>
       <c r="R124" t="n">
-        <v>6705403</v>
+        <v>6705221</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14172,7 +14172,7 @@
         <v>127314407</v>
       </c>
       <c r="B125" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>127314416</v>
       </c>
       <c r="B127" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>127314432</v>
       </c>
       <c r="B128" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>127314435</v>
       </c>
       <c r="B129" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14719,7 +14719,7 @@
         <v>127314415</v>
       </c>
       <c r="B130" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14832,45 +14832,59 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127314347</v>
+        <v>127314452</v>
       </c>
       <c r="B131" t="n">
-        <v>91332</v>
+        <v>98456</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>553419</v>
+        <v>553418</v>
       </c>
       <c r="R131" t="n">
-        <v>6705073</v>
+        <v>6705084</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14929,10 +14943,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127314336</v>
+        <v>127314410</v>
       </c>
       <c r="B132" t="n">
-        <v>91690</v>
+        <v>98456</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14940,34 +14954,43 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>553429</v>
+        <v>553422</v>
       </c>
       <c r="R132" t="n">
-        <v>6705077</v>
+        <v>6705072</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15026,45 +15049,54 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127314345</v>
+        <v>127314465</v>
       </c>
       <c r="B133" t="n">
-        <v>91332</v>
+        <v>98456</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>553386</v>
+        <v>553488</v>
       </c>
       <c r="R133" t="n">
-        <v>6704777</v>
+        <v>6705263</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15123,10 +15155,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127314341</v>
+        <v>127314350</v>
       </c>
       <c r="B134" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15158,10 +15190,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>553429</v>
+        <v>553465</v>
       </c>
       <c r="R134" t="n">
-        <v>6705077</v>
+        <v>6705219</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15194,11 +15226,6 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15225,32 +15252,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127314350</v>
+        <v>127314468</v>
       </c>
       <c r="B135" t="n">
-        <v>91332</v>
+        <v>91925</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1202</v>
+        <v>1179</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15260,10 +15287,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>553465</v>
+        <v>553482</v>
       </c>
       <c r="R135" t="n">
-        <v>6705219</v>
+        <v>6705183</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15296,6 +15323,11 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Återfynd</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15322,32 +15354,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127314468</v>
+        <v>127314347</v>
       </c>
       <c r="B136" t="n">
-        <v>91919</v>
+        <v>91338</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1179</v>
+        <v>1202</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15357,10 +15389,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>553482</v>
+        <v>553419</v>
       </c>
       <c r="R136" t="n">
-        <v>6705183</v>
+        <v>6705073</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15393,11 +15425,6 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Återfynd</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15424,10 +15451,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127314452</v>
+        <v>127314336</v>
       </c>
       <c r="B137" t="n">
-        <v>98450</v>
+        <v>91696</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15435,48 +15462,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>553418</v>
+        <v>553429</v>
       </c>
       <c r="R137" t="n">
-        <v>6705084</v>
+        <v>6705077</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15535,54 +15548,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127314410</v>
+        <v>127314345</v>
       </c>
       <c r="B138" t="n">
-        <v>98450</v>
+        <v>91338</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>553422</v>
+        <v>553386</v>
       </c>
       <c r="R138" t="n">
-        <v>6705072</v>
+        <v>6704777</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15641,54 +15645,45 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127314465</v>
+        <v>127314341</v>
       </c>
       <c r="B139" t="n">
-        <v>98450</v>
+        <v>91338</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>553488</v>
+        <v>553429</v>
       </c>
       <c r="R139" t="n">
-        <v>6705263</v>
+        <v>6705077</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15721,6 +15716,11 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15747,54 +15747,53 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127314441</v>
+        <v>127314370</v>
       </c>
       <c r="B140" t="n">
-        <v>98450</v>
+        <v>57660</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>553422</v>
+        <v>553311</v>
       </c>
       <c r="R140" t="n">
-        <v>6704986</v>
+        <v>6704717</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15853,10 +15852,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127314442</v>
+        <v>127314441</v>
       </c>
       <c r="B141" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15897,10 +15896,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>553423</v>
+        <v>553422</v>
       </c>
       <c r="R141" t="n">
-        <v>6704914</v>
+        <v>6704986</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15959,10 +15958,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127314417</v>
+        <v>127314442</v>
       </c>
       <c r="B142" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15989,7 +15988,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -15997,21 +15996,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>553413</v>
+        <v>553423</v>
       </c>
       <c r="R142" t="n">
-        <v>6704868</v>
+        <v>6704914</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16044,11 +16038,6 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16075,38 +16064,47 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127314473</v>
+        <v>127314417</v>
       </c>
       <c r="B143" t="n">
-        <v>57584</v>
+        <v>98456</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -16115,10 +16113,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>553415</v>
+        <v>553413</v>
       </c>
       <c r="R143" t="n">
-        <v>6705462</v>
+        <v>6704868</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16155,7 +16153,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Fjädrar på "slaktbord"</t>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16182,10 +16180,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127314370</v>
+        <v>127314473</v>
       </c>
       <c r="B144" t="n">
-        <v>57660</v>
+        <v>57584</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16193,16 +16191,16 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -16211,24 +16209,21 @@
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N144" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>553311</v>
+        <v>553415</v>
       </c>
       <c r="R144" t="n">
-        <v>6704717</v>
+        <v>6705462</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16261,6 +16256,11 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Fjädrar på "slaktbord"</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16494,7 +16494,7 @@
         <v>127314424</v>
       </c>
       <c r="B147" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         <v>127314454</v>
       </c>
       <c r="B148" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16718,50 +16718,45 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127314405</v>
+        <v>127314342</v>
       </c>
       <c r="B149" t="n">
-        <v>8450</v>
+        <v>91338</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>553521</v>
+        <v>553347</v>
       </c>
       <c r="R149" t="n">
-        <v>6705364</v>
+        <v>6704783</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16820,59 +16815,45 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127314411</v>
+        <v>127314343</v>
       </c>
       <c r="B150" t="n">
-        <v>98450</v>
+        <v>91338</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>553500</v>
+        <v>553388</v>
       </c>
       <c r="R150" t="n">
-        <v>6705175</v>
+        <v>6704753</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16931,47 +16912,38 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127314419</v>
+        <v>127314405</v>
       </c>
       <c r="B151" t="n">
-        <v>98450</v>
+        <v>8450</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -16980,10 +16952,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>553343</v>
+        <v>553521</v>
       </c>
       <c r="R151" t="n">
-        <v>6704786</v>
+        <v>6705364</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17016,11 +16988,6 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17047,10 +17014,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127314450</v>
+        <v>127314411</v>
       </c>
       <c r="B152" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17077,7 +17044,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -17096,10 +17063,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>553340</v>
+        <v>553500</v>
       </c>
       <c r="R152" t="n">
-        <v>6704784</v>
+        <v>6705175</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17158,45 +17125,59 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>127314343</v>
+        <v>127314419</v>
       </c>
       <c r="B153" t="n">
-        <v>91332</v>
+        <v>98456</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>553388</v>
+        <v>553343</v>
       </c>
       <c r="R153" t="n">
-        <v>6704753</v>
+        <v>6704786</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17229,6 +17210,11 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17255,45 +17241,59 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127314342</v>
+        <v>127314450</v>
       </c>
       <c r="B154" t="n">
-        <v>91332</v>
+        <v>98456</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>553347</v>
+        <v>553340</v>
       </c>
       <c r="R154" t="n">
-        <v>6704783</v>
+        <v>6704784</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17352,32 +17352,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127314387</v>
+        <v>127314385</v>
       </c>
       <c r="B155" t="n">
-        <v>91786</v>
+        <v>56959</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1209</v>
+        <v>100038</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17387,10 +17387,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>553517</v>
+        <v>553426</v>
       </c>
       <c r="R155" t="n">
-        <v>6705421</v>
+        <v>6704786</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17449,10 +17449,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127314391</v>
+        <v>127314374</v>
       </c>
       <c r="B156" t="n">
-        <v>57663</v>
+        <v>57660</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17460,16 +17460,16 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -17478,21 +17478,24 @@
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
       <c r="M156" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>553375</v>
+        <v>553523</v>
       </c>
       <c r="R156" t="n">
-        <v>6705433</v>
+        <v>6705404</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17525,11 +17528,6 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17556,38 +17554,38 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127314362</v>
+        <v>127314391</v>
       </c>
       <c r="B157" t="n">
-        <v>4773</v>
+        <v>57663</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100299</v>
+        <v>100109</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="M157" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
@@ -17596,10 +17594,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>553526</v>
+        <v>553375</v>
       </c>
       <c r="R157" t="n">
-        <v>6705221</v>
+        <v>6705433</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17632,6 +17630,11 @@
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17658,10 +17661,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127314447</v>
+        <v>127314387</v>
       </c>
       <c r="B158" t="n">
-        <v>98450</v>
+        <v>91792</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17669,48 +17672,34 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>553387</v>
+        <v>553517</v>
       </c>
       <c r="R158" t="n">
-        <v>6704938</v>
+        <v>6705421</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17769,10 +17758,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127314433</v>
+        <v>127314447</v>
       </c>
       <c r="B159" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17799,7 +17788,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -17807,16 +17796,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>553366</v>
+        <v>553387</v>
       </c>
       <c r="R159" t="n">
-        <v>6704886</v>
+        <v>6704938</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17875,45 +17869,54 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127314385</v>
+        <v>127314433</v>
       </c>
       <c r="B160" t="n">
-        <v>56959</v>
+        <v>98456</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100038</v>
+        <v>220787</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>553426</v>
+        <v>553366</v>
       </c>
       <c r="R160" t="n">
-        <v>6704786</v>
+        <v>6704886</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17972,53 +17975,50 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127314374</v>
+        <v>127314362</v>
       </c>
       <c r="B161" t="n">
-        <v>57660</v>
+        <v>4773</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100049</v>
+        <v>100299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N161" t="inlineStr"/>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>553523</v>
+        <v>553526</v>
       </c>
       <c r="R161" t="n">
-        <v>6705404</v>
+        <v>6705221</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18080,7 +18080,7 @@
         <v>127314443</v>
       </c>
       <c r="B162" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>127314448</v>
       </c>
       <c r="B163" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>127314434</v>
       </c>
       <c r="B164" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>127314451</v>
       </c>
       <c r="B165" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>127314421</v>
       </c>
       <c r="B166" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18635,7 +18635,7 @@
         <v>127314439</v>
       </c>
       <c r="B167" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18751,7 +18751,7 @@
         <v>127314409</v>
       </c>
       <c r="B168" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>127314460</v>
       </c>
       <c r="B169" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19068,42 +19068,42 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127314426</v>
+        <v>127314386</v>
       </c>
       <c r="B171" t="n">
-        <v>98450</v>
+        <v>92640</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
@@ -19112,10 +19112,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>553452</v>
+        <v>553414</v>
       </c>
       <c r="R171" t="n">
-        <v>6705056</v>
+        <v>6704970</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19174,10 +19174,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>127314455</v>
+        <v>127314426</v>
       </c>
       <c r="B172" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -19212,21 +19212,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P172" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>553431</v>
+        <v>553452</v>
       </c>
       <c r="R172" t="n">
-        <v>6704842</v>
+        <v>6705056</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19259,11 +19254,6 @@
       <c r="AA172" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC172" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19290,42 +19280,47 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127314386</v>
+        <v>127314455</v>
       </c>
       <c r="B173" t="n">
-        <v>92634</v>
+        <v>98456</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
@@ -19334,10 +19329,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>553414</v>
+        <v>553431</v>
       </c>
       <c r="R173" t="n">
-        <v>6704970</v>
+        <v>6704842</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19370,6 +19365,11 @@
       <c r="AA173" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19396,38 +19396,38 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127314392</v>
+        <v>127314482</v>
       </c>
       <c r="B174" t="n">
-        <v>57663</v>
+        <v>5177</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
       <c r="M174" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
@@ -19436,10 +19436,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>553395</v>
+        <v>553322</v>
       </c>
       <c r="R174" t="n">
-        <v>6704765</v>
+        <v>6704727</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19472,11 +19472,6 @@
       <c r="AA174" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19503,38 +19498,47 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127314482</v>
+        <v>127314438</v>
       </c>
       <c r="B175" t="n">
-        <v>5177</v>
+        <v>98456</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr"/>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
@@ -19543,10 +19547,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>553322</v>
+        <v>553407</v>
       </c>
       <c r="R175" t="n">
-        <v>6704727</v>
+        <v>6704816</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19579,6 +19583,11 @@
       <c r="AA175" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19608,7 +19617,7 @@
         <v>127314459</v>
       </c>
       <c r="B176" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19711,45 +19720,50 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>127314355</v>
+        <v>127314392</v>
       </c>
       <c r="B177" t="n">
-        <v>91690</v>
+        <v>57663</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P177" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>553451</v>
+        <v>553395</v>
       </c>
       <c r="R177" t="n">
-        <v>6705503</v>
+        <v>6704765</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19782,6 +19796,11 @@
       <c r="AA177" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19808,10 +19827,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>127314438</v>
+        <v>127314355</v>
       </c>
       <c r="B178" t="n">
-        <v>98450</v>
+        <v>91696</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19819,48 +19838,34 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>553407</v>
+        <v>553451</v>
       </c>
       <c r="R178" t="n">
-        <v>6704816</v>
+        <v>6705503</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19893,11 +19898,6 @@
       <c r="AA178" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19924,45 +19924,50 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>127314395</v>
+        <v>127314381</v>
       </c>
       <c r="B179" t="n">
-        <v>97327</v>
+        <v>57660</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P179" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>553357</v>
+        <v>553468</v>
       </c>
       <c r="R179" t="n">
-        <v>6704877</v>
+        <v>6705451</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20021,7 +20026,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>127314381</v>
+        <v>127314378</v>
       </c>
       <c r="B180" t="n">
         <v>57660</v>
@@ -20064,7 +20069,7 @@
         <v>553468</v>
       </c>
       <c r="R180" t="n">
-        <v>6705451</v>
+        <v>6705210</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20123,38 +20128,38 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>127314378</v>
+        <v>127314484</v>
       </c>
       <c r="B181" t="n">
-        <v>57660</v>
+        <v>5177</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="M181" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
@@ -20163,10 +20168,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>553468</v>
+        <v>553430</v>
       </c>
       <c r="R181" t="n">
-        <v>6705210</v>
+        <v>6705087</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20225,10 +20230,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127314484</v>
+        <v>127314395</v>
       </c>
       <c r="B182" t="n">
-        <v>5177</v>
+        <v>97333</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20236,39 +20241,34 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>553430</v>
+        <v>553357</v>
       </c>
       <c r="R182" t="n">
-        <v>6705087</v>
+        <v>6704877</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20327,59 +20327,45 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>127314413</v>
+        <v>127314467</v>
       </c>
       <c r="B183" t="n">
-        <v>98450</v>
+        <v>105494</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>553349</v>
+        <v>553468</v>
       </c>
       <c r="R183" t="n">
-        <v>6704994</v>
+        <v>6705155</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20412,11 +20398,6 @@
       <c r="AA183" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>5 blomstjälkar</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -20443,10 +20424,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>127314418</v>
+        <v>127314413</v>
       </c>
       <c r="B184" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20473,7 +20454,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -20492,10 +20473,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>553496</v>
+        <v>553349</v>
       </c>
       <c r="R184" t="n">
-        <v>6705280</v>
+        <v>6704994</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20532,7 +20513,7 @@
       </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>3 blomstjälkar</t>
+          <t>5 blomstjälkar</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20559,10 +20540,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>127314430</v>
+        <v>127314418</v>
       </c>
       <c r="B185" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20597,16 +20578,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P185" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>553358</v>
+        <v>553496</v>
       </c>
       <c r="R185" t="n">
-        <v>6705058</v>
+        <v>6705280</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20639,6 +20625,11 @@
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -20665,45 +20656,54 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>127314467</v>
+        <v>127314430</v>
       </c>
       <c r="B186" t="n">
-        <v>105488</v>
+        <v>98456</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>553468</v>
+        <v>553358</v>
       </c>
       <c r="R186" t="n">
-        <v>6705155</v>
+        <v>6705058</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20762,45 +20762,59 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>127314390</v>
+        <v>127314436</v>
       </c>
       <c r="B187" t="n">
-        <v>91628</v>
+        <v>98456</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P187" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>553386</v>
+        <v>553571</v>
       </c>
       <c r="R187" t="n">
-        <v>6704777</v>
+        <v>6705315</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20833,6 +20847,11 @@
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20859,10 +20878,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>127314436</v>
+        <v>127314453</v>
       </c>
       <c r="B188" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20889,7 +20908,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -20908,10 +20927,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>553571</v>
+        <v>553477</v>
       </c>
       <c r="R188" t="n">
-        <v>6705315</v>
+        <v>6705197</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20944,11 +20963,6 @@
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC188" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20975,10 +20989,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>127314453</v>
+        <v>127314464</v>
       </c>
       <c r="B189" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21013,21 +21027,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P189" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>553477</v>
+        <v>553470</v>
       </c>
       <c r="R189" t="n">
-        <v>6705197</v>
+        <v>6705234</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21086,10 +21095,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>127314464</v>
+        <v>127314461</v>
       </c>
       <c r="B190" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21130,10 +21139,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>553470</v>
+        <v>553335</v>
       </c>
       <c r="R190" t="n">
-        <v>6705234</v>
+        <v>6704846</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21192,54 +21201,45 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>127314461</v>
+        <v>127314390</v>
       </c>
       <c r="B191" t="n">
-        <v>98450</v>
+        <v>91634</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>553335</v>
+        <v>553386</v>
       </c>
       <c r="R191" t="n">
-        <v>6704846</v>
+        <v>6704777</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21298,10 +21298,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>127310426</v>
+        <v>127314339</v>
       </c>
       <c r="B192" t="n">
-        <v>98450</v>
+        <v>91696</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21309,53 +21309,37 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J192" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
+          <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>553479</v>
+        <v>553347</v>
       </c>
       <c r="R192" t="n">
-        <v>6705057</v>
+        <v>6704783</v>
       </c>
       <c r="S192" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -21393,29 +21377,28 @@
       <c r="AE192" t="b">
         <v>0</v>
       </c>
-      <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="b">
         <v>0</v>
       </c>
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>127314408</v>
+        <v>127310426</v>
       </c>
       <c r="B193" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21440,25 +21423,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K193" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
+      <c r="L193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Morkullberget södra, Dlr</t>
+          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>553400</v>
+        <v>553479</v>
       </c>
       <c r="R193" t="n">
-        <v>6705072</v>
+        <v>6705057</v>
       </c>
       <c r="S193" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -21490,39 +21484,35 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>få synliga bladrosetter</t>
-        </is>
-      </c>
       <c r="AD193" t="b">
         <v>0</v>
       </c>
       <c r="AE193" t="b">
         <v>0</v>
       </c>
+      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>127314423</v>
+        <v>127314408</v>
       </c>
       <c r="B194" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21547,16 +21537,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -21568,10 +21549,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>553338</v>
+        <v>553400</v>
       </c>
       <c r="R194" t="n">
-        <v>6704806</v>
+        <v>6705072</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21604,6 +21585,11 @@
       <c r="AA194" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>få synliga bladrosetter</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21630,10 +21616,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>127314339</v>
+        <v>127314423</v>
       </c>
       <c r="B195" t="n">
-        <v>91690</v>
+        <v>98456</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21641,34 +21627,48 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P195" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>553347</v>
+        <v>553338</v>
       </c>
       <c r="R195" t="n">
-        <v>6704783</v>
+        <v>6704806</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21727,50 +21727,45 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>127314325</v>
+        <v>127314389</v>
       </c>
       <c r="B196" t="n">
-        <v>5197</v>
+        <v>91634</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>105930</v>
+        <v>658</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>553508</v>
+        <v>553364</v>
       </c>
       <c r="R196" t="n">
-        <v>6705185</v>
+        <v>6704790</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21829,42 +21824,38 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>127314425</v>
+        <v>127314379</v>
       </c>
       <c r="B197" t="n">
-        <v>98450</v>
+        <v>57660</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
@@ -21873,10 +21864,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>553466</v>
+        <v>553485</v>
       </c>
       <c r="R197" t="n">
-        <v>6705077</v>
+        <v>6705230</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21935,47 +21926,38 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>127314420</v>
+        <v>127314382</v>
       </c>
       <c r="B198" t="n">
-        <v>98450</v>
+        <v>57313</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>220787</v>
+        <v>100063</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
@@ -21984,10 +21966,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>553426</v>
+        <v>553494</v>
       </c>
       <c r="R198" t="n">
-        <v>6704821</v>
+        <v>6705461</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22020,11 +22002,6 @@
       <c r="AA198" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC198" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -22051,47 +22028,38 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>127314445</v>
+        <v>127314325</v>
       </c>
       <c r="B199" t="n">
-        <v>98450</v>
+        <v>5197</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
@@ -22100,10 +22068,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>553364</v>
+        <v>553508</v>
       </c>
       <c r="R199" t="n">
-        <v>6704996</v>
+        <v>6705185</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22162,54 +22130,53 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127314429</v>
+        <v>127314363</v>
       </c>
       <c r="B200" t="n">
-        <v>98450</v>
+        <v>57823</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>553414</v>
+        <v>553336</v>
       </c>
       <c r="R200" t="n">
-        <v>6704864</v>
+        <v>6704944</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22268,38 +22235,42 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>127314382</v>
+        <v>127314425</v>
       </c>
       <c r="B201" t="n">
-        <v>57313</v>
+        <v>98456</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>100063</v>
+        <v>220787</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr"/>
-      <c r="M201" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
@@ -22308,10 +22279,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>553494</v>
+        <v>553466</v>
       </c>
       <c r="R201" t="n">
-        <v>6705461</v>
+        <v>6705077</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22370,45 +22341,59 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127314389</v>
+        <v>127314420</v>
       </c>
       <c r="B202" t="n">
-        <v>91628</v>
+        <v>98456</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P202" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>553364</v>
+        <v>553426</v>
       </c>
       <c r="R202" t="n">
-        <v>6704790</v>
+        <v>6704821</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22441,6 +22426,11 @@
       <c r="AA202" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22467,38 +22457,47 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>127314379</v>
+        <v>127314445</v>
       </c>
       <c r="B203" t="n">
-        <v>57660</v>
+        <v>98456</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr"/>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
@@ -22507,10 +22506,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>553485</v>
+        <v>553364</v>
       </c>
       <c r="R203" t="n">
-        <v>6705230</v>
+        <v>6704996</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22569,53 +22568,54 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>127314363</v>
+        <v>127314429</v>
       </c>
       <c r="B204" t="n">
-        <v>57823</v>
+        <v>98456</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr"/>
-      <c r="K204" t="inlineStr"/>
-      <c r="L204" t="inlineStr"/>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N204" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P204" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>553336</v>
+        <v>553414</v>
       </c>
       <c r="R204" t="n">
-        <v>6704944</v>
+        <v>6704864</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22677,7 +22677,7 @@
         <v>127314354</v>
       </c>
       <c r="B205" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -22880,7 +22880,7 @@
         <v>127314412</v>
       </c>
       <c r="B207" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -22991,7 +22991,7 @@
         <v>127314431</v>
       </c>
       <c r="B208" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23097,7 +23097,7 @@
         <v>127314406</v>
       </c>
       <c r="B209" t="n">
-        <v>91739</v>
+        <v>91745</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -23186,51 +23186,53 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>127310539</v>
+        <v>127314368</v>
       </c>
       <c r="B210" t="n">
-        <v>91544</v>
+        <v>57660</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>1106</v>
+        <v>100049</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
-      <c r="J210" t="inlineStr"/>
-      <c r="K210" t="inlineStr"/>
-      <c r="N210" t="inlineStr"/>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
+          <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>553483</v>
+        <v>553500</v>
       </c>
       <c r="R210" t="n">
-        <v>6705051</v>
+        <v>6705249</v>
       </c>
       <c r="S210" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -23268,67 +23270,69 @@
       <c r="AE210" t="b">
         <v>0</v>
       </c>
-      <c r="AF210" t="inlineStr"/>
       <c r="AG210" t="b">
         <v>0</v>
       </c>
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>127314477</v>
+        <v>127310539</v>
       </c>
       <c r="B211" t="n">
-        <v>92622</v>
+        <v>91550</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>4364</v>
+        <v>1106</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Morkullberget södra, Dlr</t>
+          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>553371</v>
+        <v>553483</v>
       </c>
       <c r="R211" t="n">
-        <v>6704731</v>
+        <v>6705051</v>
       </c>
       <c r="S211" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -23360,79 +23364,70 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC211" t="inlineStr">
-        <is>
-          <t>Många gamla fruktkroppar i häxring</t>
-        </is>
-      </c>
       <c r="AD211" t="b">
         <v>0</v>
       </c>
       <c r="AE211" t="b">
         <v>0</v>
       </c>
+      <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="b">
         <v>0</v>
       </c>
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>127314368</v>
+        <v>127314477</v>
       </c>
       <c r="B212" t="n">
-        <v>57660</v>
+        <v>92628</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P212" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>553500</v>
+        <v>553371</v>
       </c>
       <c r="R212" t="n">
-        <v>6705249</v>
+        <v>6704731</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23465,6 +23460,11 @@
       <c r="AA212" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>Många gamla fruktkroppar i häxring</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -23491,38 +23491,42 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>127314480</v>
+        <v>127314428</v>
       </c>
       <c r="B213" t="n">
-        <v>5177</v>
+        <v>98456</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr"/>
-      <c r="M213" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -23531,10 +23535,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>553399</v>
+        <v>553336</v>
       </c>
       <c r="R213" t="n">
-        <v>6704947</v>
+        <v>6704827</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -23593,42 +23597,38 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>127314428</v>
+        <v>127314480</v>
       </c>
       <c r="B214" t="n">
-        <v>98450</v>
+        <v>5177</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J214" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr"/>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
@@ -23637,10 +23637,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>553336</v>
+        <v>553399</v>
       </c>
       <c r="R214" t="n">
-        <v>6704827</v>
+        <v>6704947</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23702,7 +23702,7 @@
         <v>127314351</v>
       </c>
       <c r="B215" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>127314348</v>
       </c>
       <c r="B216" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>127314396</v>
       </c>
       <c r="B217" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -23990,32 +23990,32 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>127314337</v>
+        <v>127314471</v>
       </c>
       <c r="B218" t="n">
-        <v>91690</v>
+        <v>79020</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -24025,10 +24025,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>553419</v>
+        <v>553406</v>
       </c>
       <c r="R218" t="n">
-        <v>6705073</v>
+        <v>6705479</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24061,11 +24061,6 @@
       <c r="AA218" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC218" t="inlineStr">
-        <is>
-          <t>Eventuellt S. delicata</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24194,10 +24189,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127314422</v>
+        <v>127314337</v>
       </c>
       <c r="B220" t="n">
-        <v>98450</v>
+        <v>91696</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24205,48 +24200,34 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J220" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>553445</v>
+        <v>553419</v>
       </c>
       <c r="R220" t="n">
-        <v>6704996</v>
+        <v>6705073</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24279,6 +24260,11 @@
       <c r="AA220" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC220" t="inlineStr">
+        <is>
+          <t>Eventuellt S. delicata</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -24305,59 +24291,45 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>127314437</v>
+        <v>127314394</v>
       </c>
       <c r="B221" t="n">
-        <v>98450</v>
+        <v>97333</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J221" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K221" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>553333</v>
+        <v>553498</v>
       </c>
       <c r="R221" t="n">
-        <v>6704814</v>
+        <v>6705418</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24416,10 +24388,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>127314456</v>
+        <v>127314422</v>
       </c>
       <c r="B222" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -24446,7 +24418,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -24465,10 +24437,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>553437</v>
+        <v>553445</v>
       </c>
       <c r="R222" t="n">
-        <v>6704997</v>
+        <v>6704996</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24501,11 +24473,6 @@
       <c r="AA222" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC222" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -24532,10 +24499,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>127314457</v>
+        <v>127314437</v>
       </c>
       <c r="B223" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -24562,7 +24529,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -24570,16 +24537,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>553442</v>
+        <v>553333</v>
       </c>
       <c r="R223" t="n">
-        <v>6705078</v>
+        <v>6704814</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24638,10 +24610,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127314463</v>
+        <v>127314456</v>
       </c>
       <c r="B224" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -24668,7 +24640,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -24676,16 +24648,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P224" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>553433</v>
+        <v>553437</v>
       </c>
       <c r="R224" t="n">
-        <v>6704902</v>
+        <v>6704997</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24718,6 +24695,11 @@
       <c r="AA224" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -24744,10 +24726,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127314458</v>
+        <v>127314457</v>
       </c>
       <c r="B225" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -24788,10 +24770,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>553526</v>
+        <v>553442</v>
       </c>
       <c r="R225" t="n">
-        <v>6705245</v>
+        <v>6705078</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24850,45 +24832,54 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127314471</v>
+        <v>127314463</v>
       </c>
       <c r="B226" t="n">
-        <v>79020</v>
+        <v>98456</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P226" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>553406</v>
+        <v>553433</v>
       </c>
       <c r="R226" t="n">
-        <v>6705479</v>
+        <v>6704902</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24947,45 +24938,54 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127314394</v>
+        <v>127314458</v>
       </c>
       <c r="B227" t="n">
-        <v>97327</v>
+        <v>98456</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>553498</v>
+        <v>553526</v>
       </c>
       <c r="R227" t="n">
-        <v>6705418</v>
+        <v>6705245</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25044,38 +25044,38 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127314479</v>
+        <v>127314371</v>
       </c>
       <c r="B228" t="n">
-        <v>5177</v>
+        <v>57660</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
       <c r="M228" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
@@ -25084,10 +25084,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>553496</v>
+        <v>553336</v>
       </c>
       <c r="R228" t="n">
-        <v>6705218</v>
+        <v>6704723</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25146,47 +25146,38 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127314414</v>
+        <v>127314479</v>
       </c>
       <c r="B229" t="n">
-        <v>98450</v>
+        <v>5177</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I229" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J229" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K229" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr"/>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -25195,10 +25186,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>553341</v>
+        <v>553496</v>
       </c>
       <c r="R229" t="n">
-        <v>6704994</v>
+        <v>6705218</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25231,11 +25222,6 @@
       <c r="AA229" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC229" t="inlineStr">
-        <is>
-          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -25262,42 +25248,38 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>127314444</v>
+        <v>127314326</v>
       </c>
       <c r="B230" t="n">
-        <v>98450</v>
+        <v>5197</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J230" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr"/>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
@@ -25306,10 +25288,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>553489</v>
+        <v>553527</v>
       </c>
       <c r="R230" t="n">
-        <v>6705294</v>
+        <v>6705221</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -25368,10 +25350,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>127314440</v>
+        <v>127314414</v>
       </c>
       <c r="B231" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -25398,7 +25380,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -25406,16 +25388,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P231" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>553571</v>
+        <v>553341</v>
       </c>
       <c r="R231" t="n">
-        <v>6705297</v>
+        <v>6704994</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -25448,6 +25435,11 @@
       <c r="AA231" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -25474,38 +25466,42 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>127314371</v>
+        <v>127314444</v>
       </c>
       <c r="B232" t="n">
-        <v>57660</v>
+        <v>98456</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I232" t="inlineStr"/>
-      <c r="M232" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P232" t="inlineStr">
@@ -25514,10 +25510,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>553336</v>
+        <v>553489</v>
       </c>
       <c r="R232" t="n">
-        <v>6704723</v>
+        <v>6705294</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -25576,38 +25572,42 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>127314326</v>
+        <v>127314440</v>
       </c>
       <c r="B233" t="n">
-        <v>5197</v>
+        <v>98456</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr"/>
-      <c r="M233" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
@@ -25616,10 +25616,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>553527</v>
+        <v>553571</v>
       </c>
       <c r="R233" t="n">
-        <v>6705221</v>
+        <v>6705297</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -25681,7 +25681,7 @@
         <v>127314486</v>
       </c>
       <c r="B234" t="n">
-        <v>91704</v>
+        <v>91710</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>

--- a/artfynd/A 18040-2021 artfynd.xlsx
+++ b/artfynd/A 18040-2021 artfynd.xlsx
@@ -13776,50 +13776,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127314375</v>
+        <v>127314388</v>
       </c>
       <c r="B121" t="n">
-        <v>57660</v>
+        <v>91795</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>553537</v>
+        <v>553411</v>
       </c>
       <c r="R121" t="n">
-        <v>6705403</v>
+        <v>6705072</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13878,45 +13873,50 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127314388</v>
+        <v>127314375</v>
       </c>
       <c r="B122" t="n">
-        <v>91792</v>
+        <v>57663</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>553411</v>
+        <v>553537</v>
       </c>
       <c r="R122" t="n">
-        <v>6705072</v>
+        <v>6705403</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13978,7 +13978,7 @@
         <v>127314398</v>
       </c>
       <c r="B123" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14075,7 +14075,7 @@
         <v>127314397</v>
       </c>
       <c r="B124" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>127314407</v>
       </c>
       <c r="B125" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14276,38 +14276,47 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127314372</v>
+        <v>127314416</v>
       </c>
       <c r="B126" t="n">
-        <v>57660</v>
+        <v>98459</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -14316,10 +14325,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>553488</v>
+        <v>553356</v>
       </c>
       <c r="R126" t="n">
-        <v>6705460</v>
+        <v>6704786</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14352,6 +14361,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14378,10 +14392,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127314416</v>
+        <v>127314432</v>
       </c>
       <c r="B127" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14408,7 +14422,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -14416,21 +14430,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>553356</v>
+        <v>553508</v>
       </c>
       <c r="R127" t="n">
-        <v>6704786</v>
+        <v>6705194</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14463,11 +14472,6 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14494,10 +14498,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127314432</v>
+        <v>127314435</v>
       </c>
       <c r="B128" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14524,7 +14528,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -14532,16 +14536,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>553508</v>
+        <v>553476</v>
       </c>
       <c r="R128" t="n">
-        <v>6705194</v>
+        <v>6705068</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14574,6 +14583,11 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>12 blomstjälkar</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14600,10 +14614,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127314435</v>
+        <v>127314415</v>
       </c>
       <c r="B129" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14630,7 +14644,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -14649,10 +14663,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>553476</v>
+        <v>553463</v>
       </c>
       <c r="R129" t="n">
-        <v>6705068</v>
+        <v>6705155</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14689,7 +14703,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>12 blomstjälkar</t>
+          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14716,47 +14730,38 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127314415</v>
+        <v>127314372</v>
       </c>
       <c r="B130" t="n">
-        <v>98456</v>
+        <v>57663</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -14765,10 +14770,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>553463</v>
+        <v>553488</v>
       </c>
       <c r="R130" t="n">
-        <v>6705155</v>
+        <v>6705460</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14801,11 +14806,6 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14832,59 +14832,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127314452</v>
+        <v>127314347</v>
       </c>
       <c r="B131" t="n">
-        <v>98456</v>
+        <v>91341</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>553418</v>
+        <v>553419</v>
       </c>
       <c r="R131" t="n">
-        <v>6705084</v>
+        <v>6705073</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14943,54 +14929,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127314410</v>
+        <v>127314345</v>
       </c>
       <c r="B132" t="n">
-        <v>98456</v>
+        <v>91341</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>553422</v>
+        <v>553386</v>
       </c>
       <c r="R132" t="n">
-        <v>6705072</v>
+        <v>6704777</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15049,54 +15026,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127314465</v>
+        <v>127314350</v>
       </c>
       <c r="B133" t="n">
-        <v>98456</v>
+        <v>91341</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>553488</v>
+        <v>553465</v>
       </c>
       <c r="R133" t="n">
-        <v>6705263</v>
+        <v>6705219</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15155,32 +15123,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127314350</v>
+        <v>127314468</v>
       </c>
       <c r="B134" t="n">
-        <v>91338</v>
+        <v>91928</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1202</v>
+        <v>1179</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15190,10 +15158,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>553465</v>
+        <v>553482</v>
       </c>
       <c r="R134" t="n">
-        <v>6705219</v>
+        <v>6705183</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15226,6 +15194,11 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Återfynd</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15252,10 +15225,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127314468</v>
+        <v>127314336</v>
       </c>
       <c r="B135" t="n">
-        <v>91925</v>
+        <v>91699</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15263,21 +15236,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1179</v>
+        <v>2062</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15287,10 +15260,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>553482</v>
+        <v>553429</v>
       </c>
       <c r="R135" t="n">
-        <v>6705183</v>
+        <v>6705077</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15323,11 +15296,6 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Återfynd</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15354,10 +15322,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127314347</v>
+        <v>127314341</v>
       </c>
       <c r="B136" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15389,10 +15357,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>553419</v>
+        <v>553429</v>
       </c>
       <c r="R136" t="n">
-        <v>6705073</v>
+        <v>6705077</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15425,6 +15393,11 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15451,10 +15424,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127314336</v>
+        <v>127314452</v>
       </c>
       <c r="B137" t="n">
-        <v>91696</v>
+        <v>98459</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15462,34 +15435,48 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>553429</v>
+        <v>553418</v>
       </c>
       <c r="R137" t="n">
-        <v>6705077</v>
+        <v>6705084</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15548,45 +15535,54 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127314345</v>
+        <v>127314410</v>
       </c>
       <c r="B138" t="n">
-        <v>91338</v>
+        <v>98459</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>553386</v>
+        <v>553422</v>
       </c>
       <c r="R138" t="n">
-        <v>6704777</v>
+        <v>6705072</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15645,45 +15641,54 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127314341</v>
+        <v>127314465</v>
       </c>
       <c r="B139" t="n">
-        <v>91338</v>
+        <v>98459</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>553429</v>
+        <v>553488</v>
       </c>
       <c r="R139" t="n">
-        <v>6705077</v>
+        <v>6705263</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15716,11 +15721,6 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15747,53 +15747,54 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127314370</v>
+        <v>127314441</v>
       </c>
       <c r="B140" t="n">
-        <v>57660</v>
+        <v>98459</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>553311</v>
+        <v>553422</v>
       </c>
       <c r="R140" t="n">
-        <v>6704717</v>
+        <v>6704986</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15852,10 +15853,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127314441</v>
+        <v>127314442</v>
       </c>
       <c r="B141" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15896,10 +15897,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>553422</v>
+        <v>553423</v>
       </c>
       <c r="R141" t="n">
-        <v>6704986</v>
+        <v>6704914</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15958,10 +15959,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127314442</v>
+        <v>127314417</v>
       </c>
       <c r="B142" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15988,7 +15989,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -15996,16 +15997,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>553423</v>
+        <v>553413</v>
       </c>
       <c r="R142" t="n">
-        <v>6704914</v>
+        <v>6704868</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16038,6 +16044,11 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16064,47 +16075,38 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127314417</v>
+        <v>127314473</v>
       </c>
       <c r="B143" t="n">
-        <v>98456</v>
+        <v>57587</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -16113,10 +16115,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>553413</v>
+        <v>553415</v>
       </c>
       <c r="R143" t="n">
-        <v>6704868</v>
+        <v>6705462</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16153,7 +16155,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>3 blomstjälkar</t>
+          <t>Fjädrar på "slaktbord"</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16180,10 +16182,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127314473</v>
+        <v>127314370</v>
       </c>
       <c r="B144" t="n">
-        <v>57584</v>
+        <v>57663</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16191,16 +16193,16 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100001</v>
+        <v>100049</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -16209,21 +16211,24 @@
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>553415</v>
+        <v>553311</v>
       </c>
       <c r="R144" t="n">
-        <v>6705462</v>
+        <v>6704717</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16256,11 +16261,6 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>Fjädrar på "slaktbord"</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16290,7 +16290,7 @@
         <v>127314376</v>
       </c>
       <c r="B145" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>127314380</v>
       </c>
       <c r="B146" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>127314424</v>
       </c>
       <c r="B147" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         <v>127314454</v>
       </c>
       <c r="B148" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16718,10 +16718,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127314342</v>
+        <v>127314343</v>
       </c>
       <c r="B149" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16753,10 +16753,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>553347</v>
+        <v>553388</v>
       </c>
       <c r="R149" t="n">
-        <v>6704783</v>
+        <v>6704753</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16815,10 +16815,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127314343</v>
+        <v>127314342</v>
       </c>
       <c r="B150" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16850,10 +16850,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>553388</v>
+        <v>553347</v>
       </c>
       <c r="R150" t="n">
-        <v>6704753</v>
+        <v>6704783</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17017,7 +17017,7 @@
         <v>127314411</v>
       </c>
       <c r="B152" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17128,7 +17128,7 @@
         <v>127314419</v>
       </c>
       <c r="B153" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17244,7 +17244,7 @@
         <v>127314450</v>
       </c>
       <c r="B154" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17352,45 +17352,59 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127314385</v>
+        <v>127314447</v>
       </c>
       <c r="B155" t="n">
-        <v>56959</v>
+        <v>98459</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100038</v>
+        <v>220787</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>553426</v>
+        <v>553387</v>
       </c>
       <c r="R155" t="n">
-        <v>6704786</v>
+        <v>6704938</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17449,53 +17463,54 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127314374</v>
+        <v>127314433</v>
       </c>
       <c r="B156" t="n">
-        <v>57660</v>
+        <v>98459</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N156" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>553523</v>
+        <v>553366</v>
       </c>
       <c r="R156" t="n">
-        <v>6705404</v>
+        <v>6704886</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17554,50 +17569,45 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127314391</v>
+        <v>127314387</v>
       </c>
       <c r="B157" t="n">
-        <v>57663</v>
+        <v>91795</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>553375</v>
+        <v>553517</v>
       </c>
       <c r="R157" t="n">
-        <v>6705433</v>
+        <v>6705421</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17630,11 +17640,6 @@
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17661,32 +17666,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127314387</v>
+        <v>127314385</v>
       </c>
       <c r="B158" t="n">
-        <v>91792</v>
+        <v>56962</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1209</v>
+        <v>100038</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17696,10 +17701,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>553517</v>
+        <v>553426</v>
       </c>
       <c r="R158" t="n">
-        <v>6705421</v>
+        <v>6704786</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17758,59 +17763,53 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127314447</v>
+        <v>127314374</v>
       </c>
       <c r="B159" t="n">
-        <v>98456</v>
+        <v>57663</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>553387</v>
+        <v>553523</v>
       </c>
       <c r="R159" t="n">
-        <v>6704938</v>
+        <v>6705404</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17869,42 +17868,38 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127314433</v>
+        <v>127314362</v>
       </c>
       <c r="B160" t="n">
-        <v>98456</v>
+        <v>4773</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -17913,10 +17908,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>553366</v>
+        <v>553526</v>
       </c>
       <c r="R160" t="n">
-        <v>6704886</v>
+        <v>6705221</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17975,38 +17970,38 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127314362</v>
+        <v>127314391</v>
       </c>
       <c r="B161" t="n">
-        <v>4773</v>
+        <v>57666</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100299</v>
+        <v>100109</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="M161" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
@@ -18015,10 +18010,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>553526</v>
+        <v>553375</v>
       </c>
       <c r="R161" t="n">
-        <v>6705221</v>
+        <v>6705433</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18051,6 +18046,11 @@
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18080,7 +18080,7 @@
         <v>127314443</v>
       </c>
       <c r="B162" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>127314448</v>
       </c>
       <c r="B163" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>127314434</v>
       </c>
       <c r="B164" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>127314451</v>
       </c>
       <c r="B165" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18521,10 +18521,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>127314421</v>
+        <v>127314439</v>
       </c>
       <c r="B166" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18551,7 +18551,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -18570,10 +18570,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>553457</v>
+        <v>553525</v>
       </c>
       <c r="R166" t="n">
-        <v>6705062</v>
+        <v>6705250</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18606,6 +18606,11 @@
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>6 blomstjälkar</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18632,10 +18637,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>127314439</v>
+        <v>127314421</v>
       </c>
       <c r="B167" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18662,7 +18667,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -18681,10 +18686,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>553525</v>
+        <v>553457</v>
       </c>
       <c r="R167" t="n">
-        <v>6705250</v>
+        <v>6705062</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18717,11 +18722,6 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>6 blomstjälkar</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18751,7 +18751,7 @@
         <v>127314409</v>
       </c>
       <c r="B168" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>127314460</v>
       </c>
       <c r="B169" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18961,38 +18961,42 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>127314393</v>
+        <v>127314386</v>
       </c>
       <c r="B170" t="n">
-        <v>57663</v>
+        <v>92643</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
@@ -19001,10 +19005,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>553521</v>
+        <v>553414</v>
       </c>
       <c r="R170" t="n">
-        <v>6705364</v>
+        <v>6704970</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19037,11 +19041,6 @@
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19068,42 +19067,38 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127314386</v>
+        <v>127314393</v>
       </c>
       <c r="B171" t="n">
-        <v>92640</v>
+        <v>57666</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
@@ -19112,10 +19107,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>553414</v>
+        <v>553521</v>
       </c>
       <c r="R171" t="n">
-        <v>6704970</v>
+        <v>6705364</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19148,6 +19143,11 @@
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19177,7 +19177,7 @@
         <v>127314426</v>
       </c>
       <c r="B172" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>127314455</v>
       </c>
       <c r="B173" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19396,50 +19396,45 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127314482</v>
+        <v>127314355</v>
       </c>
       <c r="B174" t="n">
-        <v>5177</v>
+        <v>91699</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>100526</v>
+        <v>2062</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P174" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>553322</v>
+        <v>553451</v>
       </c>
       <c r="R174" t="n">
-        <v>6704727</v>
+        <v>6705503</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19498,47 +19493,38 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127314438</v>
+        <v>127314392</v>
       </c>
       <c r="B175" t="n">
-        <v>98456</v>
+        <v>57666</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
@@ -19547,10 +19533,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>553407</v>
+        <v>553395</v>
       </c>
       <c r="R175" t="n">
-        <v>6704816</v>
+        <v>6704765</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19587,7 +19573,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>4 blomstjälkar</t>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19614,42 +19600,38 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>127314459</v>
+        <v>127314482</v>
       </c>
       <c r="B176" t="n">
-        <v>98456</v>
+        <v>5177</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
@@ -19658,10 +19640,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>553508</v>
+        <v>553322</v>
       </c>
       <c r="R176" t="n">
-        <v>6705196</v>
+        <v>6704727</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19720,38 +19702,47 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>127314392</v>
+        <v>127314438</v>
       </c>
       <c r="B177" t="n">
-        <v>57663</v>
+        <v>98459</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr"/>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
@@ -19760,10 +19751,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>553395</v>
+        <v>553407</v>
       </c>
       <c r="R177" t="n">
-        <v>6704765</v>
+        <v>6704816</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19800,7 +19791,7 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19827,10 +19818,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>127314355</v>
+        <v>127314459</v>
       </c>
       <c r="B178" t="n">
-        <v>91696</v>
+        <v>98459</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19838,34 +19829,43 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>553451</v>
+        <v>553508</v>
       </c>
       <c r="R178" t="n">
-        <v>6705503</v>
+        <v>6705196</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19924,40 +19924,35 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>127314381</v>
+        <v>127314467</v>
       </c>
       <c r="B179" t="n">
-        <v>57660</v>
+        <v>105497</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P179" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
@@ -19967,7 +19962,7 @@
         <v>553468</v>
       </c>
       <c r="R179" t="n">
-        <v>6705451</v>
+        <v>6705155</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20026,38 +20021,47 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>127314378</v>
+        <v>127314413</v>
       </c>
       <c r="B180" t="n">
-        <v>57660</v>
+        <v>98459</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr"/>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
@@ -20066,10 +20070,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>553468</v>
+        <v>553349</v>
       </c>
       <c r="R180" t="n">
-        <v>6705210</v>
+        <v>6704994</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20102,6 +20106,11 @@
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>5 blomstjälkar</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20128,38 +20137,47 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>127314484</v>
+        <v>127314418</v>
       </c>
       <c r="B181" t="n">
-        <v>5177</v>
+        <v>98459</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr"/>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
@@ -20168,10 +20186,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>553430</v>
+        <v>553496</v>
       </c>
       <c r="R181" t="n">
-        <v>6705087</v>
+        <v>6705280</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20204,6 +20222,11 @@
       <c r="AA181" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20230,45 +20253,50 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127314395</v>
+        <v>127314378</v>
       </c>
       <c r="B182" t="n">
-        <v>97333</v>
+        <v>57663</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>553357</v>
+        <v>553468</v>
       </c>
       <c r="R182" t="n">
-        <v>6704877</v>
+        <v>6705210</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20327,45 +20355,54 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>127314467</v>
+        <v>127314430</v>
       </c>
       <c r="B183" t="n">
-        <v>105494</v>
+        <v>98459</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P183" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>553468</v>
+        <v>553358</v>
       </c>
       <c r="R183" t="n">
-        <v>6705155</v>
+        <v>6705058</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20424,59 +20461,45 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>127314413</v>
+        <v>127314395</v>
       </c>
       <c r="B184" t="n">
-        <v>98456</v>
+        <v>97336</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>553349</v>
+        <v>553357</v>
       </c>
       <c r="R184" t="n">
-        <v>6704994</v>
+        <v>6704877</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20509,11 +20532,6 @@
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>5 blomstjälkar</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20540,47 +20558,38 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>127314418</v>
+        <v>127314381</v>
       </c>
       <c r="B185" t="n">
-        <v>98456</v>
+        <v>57663</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
@@ -20589,10 +20598,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>553496</v>
+        <v>553468</v>
       </c>
       <c r="R185" t="n">
-        <v>6705280</v>
+        <v>6705451</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20625,11 +20634,6 @@
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -20656,42 +20660,38 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>127314430</v>
+        <v>127314484</v>
       </c>
       <c r="B186" t="n">
-        <v>98456</v>
+        <v>5177</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J186" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
@@ -20700,10 +20700,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>553358</v>
+        <v>553430</v>
       </c>
       <c r="R186" t="n">
-        <v>6705058</v>
+        <v>6705087</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20762,59 +20762,45 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>127314436</v>
+        <v>127314390</v>
       </c>
       <c r="B187" t="n">
-        <v>98456</v>
+        <v>91637</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J187" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>553571</v>
+        <v>553386</v>
       </c>
       <c r="R187" t="n">
-        <v>6705315</v>
+        <v>6704777</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20847,11 +20833,6 @@
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC187" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20878,10 +20859,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>127314453</v>
+        <v>127314436</v>
       </c>
       <c r="B188" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20908,7 +20889,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -20927,10 +20908,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>553477</v>
+        <v>553571</v>
       </c>
       <c r="R188" t="n">
-        <v>6705197</v>
+        <v>6705315</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20963,6 +20944,11 @@
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20989,10 +20975,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>127314464</v>
+        <v>127314453</v>
       </c>
       <c r="B189" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21027,16 +21013,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P189" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>553470</v>
+        <v>553477</v>
       </c>
       <c r="R189" t="n">
-        <v>6705234</v>
+        <v>6705197</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21095,10 +21086,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>127314461</v>
+        <v>127314464</v>
       </c>
       <c r="B190" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21139,10 +21130,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>553335</v>
+        <v>553470</v>
       </c>
       <c r="R190" t="n">
-        <v>6704846</v>
+        <v>6705234</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21201,45 +21192,54 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>127314390</v>
+        <v>127314461</v>
       </c>
       <c r="B191" t="n">
-        <v>91634</v>
+        <v>98459</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P191" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>553386</v>
+        <v>553335</v>
       </c>
       <c r="R191" t="n">
-        <v>6704777</v>
+        <v>6704846</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21301,7 +21301,7 @@
         <v>127314339</v>
       </c>
       <c r="B192" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         <v>127310426</v>
       </c>
       <c r="B193" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
         <v>127314408</v>
       </c>
       <c r="B194" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21619,7 +21619,7 @@
         <v>127314423</v>
       </c>
       <c r="B195" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21727,10 +21727,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>127314389</v>
+        <v>127314379</v>
       </c>
       <c r="B196" t="n">
-        <v>91634</v>
+        <v>57663</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21738,34 +21738,39 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>553364</v>
+        <v>553485</v>
       </c>
       <c r="R196" t="n">
-        <v>6704790</v>
+        <v>6705230</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21824,10 +21829,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>127314379</v>
+        <v>127314389</v>
       </c>
       <c r="B197" t="n">
-        <v>57660</v>
+        <v>91637</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21835,39 +21840,34 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>553485</v>
+        <v>553364</v>
       </c>
       <c r="R197" t="n">
-        <v>6705230</v>
+        <v>6704790</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21926,38 +21926,42 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>127314382</v>
+        <v>127314425</v>
       </c>
       <c r="B198" t="n">
-        <v>57313</v>
+        <v>98459</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>100063</v>
+        <v>220787</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr"/>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
@@ -21966,10 +21970,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>553494</v>
+        <v>553466</v>
       </c>
       <c r="R198" t="n">
-        <v>6705461</v>
+        <v>6705077</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22028,38 +22032,47 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>127314325</v>
+        <v>127314420</v>
       </c>
       <c r="B199" t="n">
-        <v>5197</v>
+        <v>98459</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr"/>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
@@ -22068,10 +22081,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>553508</v>
+        <v>553426</v>
       </c>
       <c r="R199" t="n">
-        <v>6705185</v>
+        <v>6704821</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22104,6 +22117,11 @@
       <c r="AA199" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22130,53 +22148,59 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127314363</v>
+        <v>127314445</v>
       </c>
       <c r="B200" t="n">
-        <v>57823</v>
+        <v>98459</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr"/>
-      <c r="K200" t="inlineStr"/>
-      <c r="L200" t="inlineStr"/>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N200" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P200" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>553336</v>
+        <v>553364</v>
       </c>
       <c r="R200" t="n">
-        <v>6704944</v>
+        <v>6704996</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22235,10 +22259,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>127314425</v>
+        <v>127314429</v>
       </c>
       <c r="B201" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22279,10 +22303,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>553466</v>
+        <v>553414</v>
       </c>
       <c r="R201" t="n">
-        <v>6705077</v>
+        <v>6704864</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22341,47 +22365,38 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127314420</v>
+        <v>127314382</v>
       </c>
       <c r="B202" t="n">
-        <v>98456</v>
+        <v>57316</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>220787</v>
+        <v>100063</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
@@ -22390,10 +22405,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>553426</v>
+        <v>553494</v>
       </c>
       <c r="R202" t="n">
-        <v>6704821</v>
+        <v>6705461</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22426,11 +22441,6 @@
       <c r="AA202" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22457,59 +22467,53 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>127314445</v>
+        <v>127314363</v>
       </c>
       <c r="B203" t="n">
-        <v>98456</v>
+        <v>57826</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>553364</v>
+        <v>553336</v>
       </c>
       <c r="R203" t="n">
-        <v>6704996</v>
+        <v>6704944</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22568,42 +22572,38 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>127314429</v>
+        <v>127314325</v>
       </c>
       <c r="B204" t="n">
-        <v>98456</v>
+        <v>5197</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
@@ -22612,10 +22612,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>553414</v>
+        <v>553508</v>
       </c>
       <c r="R204" t="n">
-        <v>6704864</v>
+        <v>6705185</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22674,45 +22674,54 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>127314354</v>
+        <v>127314431</v>
       </c>
       <c r="B205" t="n">
-        <v>91338</v>
+        <v>98459</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P205" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>553517</v>
+        <v>553442</v>
       </c>
       <c r="R205" t="n">
-        <v>6705421</v>
+        <v>6705095</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22771,32 +22780,32 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>127314360</v>
+        <v>127314412</v>
       </c>
       <c r="B206" t="n">
-        <v>56855</v>
+        <v>98459</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -22804,16 +22813,26 @@
           <t>5</t>
         </is>
       </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P206" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>553530</v>
+        <v>553337</v>
       </c>
       <c r="R206" t="n">
-        <v>6705203</v>
+        <v>6704813</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22846,11 +22865,6 @@
       <c r="AA206" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC206" t="inlineStr">
-        <is>
-          <t>Höna med minst fyra ungar</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22877,59 +22891,40 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>127314412</v>
+        <v>127314406</v>
       </c>
       <c r="B207" t="n">
-        <v>98456</v>
+        <v>91748</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>553337</v>
+        <v>553517</v>
       </c>
       <c r="R207" t="n">
-        <v>6704813</v>
+        <v>6705421</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22988,54 +22983,45 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>127314431</v>
+        <v>127314354</v>
       </c>
       <c r="B208" t="n">
-        <v>98456</v>
+        <v>91341</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J208" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>553442</v>
+        <v>553517</v>
       </c>
       <c r="R208" t="n">
-        <v>6705095</v>
+        <v>6705421</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23094,40 +23080,49 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>127314406</v>
+        <v>127314360</v>
       </c>
       <c r="B209" t="n">
-        <v>91745</v>
+        <v>56858</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6040186</v>
+        <v>100138</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P209" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>553517</v>
+        <v>553530</v>
       </c>
       <c r="R209" t="n">
-        <v>6705421</v>
+        <v>6705203</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23160,6 +23155,11 @@
       <c r="AA209" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>Höna med minst fyra ungar</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -23186,53 +23186,51 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>127314368</v>
+        <v>127310539</v>
       </c>
       <c r="B210" t="n">
-        <v>57660</v>
+        <v>91553</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>100049</v>
+        <v>1106</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="J210" t="inlineStr"/>
+      <c r="K210" t="inlineStr"/>
+      <c r="N210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Morkullberget södra, Dlr</t>
+          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>553500</v>
+        <v>553483</v>
       </c>
       <c r="R210" t="n">
-        <v>6705249</v>
+        <v>6705051</v>
       </c>
       <c r="S210" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -23270,69 +23268,72 @@
       <c r="AE210" t="b">
         <v>0</v>
       </c>
+      <c r="AF210" t="inlineStr"/>
       <c r="AG210" t="b">
         <v>0</v>
       </c>
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>127310539</v>
+        <v>127314368</v>
       </c>
       <c r="B211" t="n">
-        <v>91550</v>
+        <v>57663</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>1106</v>
+        <v>100049</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
-      <c r="J211" t="inlineStr"/>
-      <c r="K211" t="inlineStr"/>
-      <c r="N211" t="inlineStr"/>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
+          <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>553483</v>
+        <v>553500</v>
       </c>
       <c r="R211" t="n">
-        <v>6705051</v>
+        <v>6705249</v>
       </c>
       <c r="S211" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -23370,19 +23371,18 @@
       <c r="AE211" t="b">
         <v>0</v>
       </c>
-      <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="b">
         <v>0</v>
       </c>
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
@@ -23392,7 +23392,7 @@
         <v>127314477</v>
       </c>
       <c r="B212" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -23491,42 +23491,38 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>127314428</v>
+        <v>127314480</v>
       </c>
       <c r="B213" t="n">
-        <v>98456</v>
+        <v>5177</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J213" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr"/>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -23535,10 +23531,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>553336</v>
+        <v>553399</v>
       </c>
       <c r="R213" t="n">
-        <v>6704827</v>
+        <v>6704947</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -23597,38 +23593,42 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>127314480</v>
+        <v>127314428</v>
       </c>
       <c r="B214" t="n">
-        <v>5177</v>
+        <v>98459</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr"/>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
@@ -23637,10 +23637,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>553399</v>
+        <v>553336</v>
       </c>
       <c r="R214" t="n">
-        <v>6704947</v>
+        <v>6704827</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23702,7 +23702,7 @@
         <v>127314351</v>
       </c>
       <c r="B215" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>127314348</v>
       </c>
       <c r="B216" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>127314396</v>
       </c>
       <c r="B217" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -23990,45 +23990,59 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>127314471</v>
+        <v>127314437</v>
       </c>
       <c r="B218" t="n">
-        <v>79020</v>
+        <v>98459</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I218" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P218" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>553406</v>
+        <v>553333</v>
       </c>
       <c r="R218" t="n">
-        <v>6705479</v>
+        <v>6704814</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24087,38 +24101,42 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127314377</v>
+        <v>127314463</v>
       </c>
       <c r="B219" t="n">
-        <v>57660</v>
+        <v>98459</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr"/>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
@@ -24127,10 +24145,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>553336</v>
+        <v>553433</v>
       </c>
       <c r="R219" t="n">
-        <v>6704827</v>
+        <v>6704902</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24189,10 +24207,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127314337</v>
+        <v>127314422</v>
       </c>
       <c r="B220" t="n">
-        <v>91696</v>
+        <v>98459</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24200,34 +24218,48 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P220" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>553419</v>
+        <v>553445</v>
       </c>
       <c r="R220" t="n">
-        <v>6705073</v>
+        <v>6704996</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24260,11 +24292,6 @@
       <c r="AA220" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC220" t="inlineStr">
-        <is>
-          <t>Eventuellt S. delicata</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -24291,45 +24318,59 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>127314394</v>
+        <v>127314456</v>
       </c>
       <c r="B221" t="n">
-        <v>97333</v>
+        <v>98459</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>553498</v>
+        <v>553437</v>
       </c>
       <c r="R221" t="n">
-        <v>6705418</v>
+        <v>6704997</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24362,6 +24403,11 @@
       <c r="AA221" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -24388,10 +24434,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>127314422</v>
+        <v>127314457</v>
       </c>
       <c r="B222" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -24418,7 +24464,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -24426,21 +24472,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P222" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>553445</v>
+        <v>553442</v>
       </c>
       <c r="R222" t="n">
-        <v>6704996</v>
+        <v>6705078</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24499,10 +24540,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>127314437</v>
+        <v>127314458</v>
       </c>
       <c r="B223" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -24529,7 +24570,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -24537,21 +24578,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>553333</v>
+        <v>553526</v>
       </c>
       <c r="R223" t="n">
-        <v>6704814</v>
+        <v>6705245</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24610,59 +24646,45 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127314456</v>
+        <v>127314394</v>
       </c>
       <c r="B224" t="n">
-        <v>98456</v>
+        <v>97336</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I224" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J224" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K224" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>553437</v>
+        <v>553498</v>
       </c>
       <c r="R224" t="n">
-        <v>6704997</v>
+        <v>6705418</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24695,11 +24717,6 @@
       <c r="AA224" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC224" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -24726,42 +24743,38 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127314457</v>
+        <v>127314377</v>
       </c>
       <c r="B225" t="n">
-        <v>98456</v>
+        <v>57663</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J225" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr"/>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
@@ -24770,10 +24783,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>553442</v>
+        <v>553336</v>
       </c>
       <c r="R225" t="n">
-        <v>6705078</v>
+        <v>6704827</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24832,54 +24845,45 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127314463</v>
+        <v>127314471</v>
       </c>
       <c r="B226" t="n">
-        <v>98456</v>
+        <v>79023</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J226" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>553433</v>
+        <v>553406</v>
       </c>
       <c r="R226" t="n">
-        <v>6704902</v>
+        <v>6705479</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24938,10 +24942,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127314458</v>
+        <v>127314337</v>
       </c>
       <c r="B227" t="n">
-        <v>98456</v>
+        <v>91699</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -24949,43 +24953,34 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J227" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>553526</v>
+        <v>553419</v>
       </c>
       <c r="R227" t="n">
-        <v>6705245</v>
+        <v>6705073</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25018,6 +25013,11 @@
       <c r="AA227" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC227" t="inlineStr">
+        <is>
+          <t>Eventuellt S. delicata</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -25047,7 +25047,7 @@
         <v>127314371</v>
       </c>
       <c r="B228" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -25146,38 +25146,42 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127314479</v>
+        <v>127314440</v>
       </c>
       <c r="B229" t="n">
-        <v>5177</v>
+        <v>98459</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I229" t="inlineStr"/>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -25186,10 +25190,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>553496</v>
+        <v>553571</v>
       </c>
       <c r="R229" t="n">
-        <v>6705218</v>
+        <v>6705297</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25248,10 +25252,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>127314326</v>
+        <v>127314479</v>
       </c>
       <c r="B230" t="n">
-        <v>5197</v>
+        <v>5177</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -25259,27 +25263,27 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
       <c r="M230" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
@@ -25288,10 +25292,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>553527</v>
+        <v>553496</v>
       </c>
       <c r="R230" t="n">
-        <v>6705221</v>
+        <v>6705218</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -25350,47 +25354,38 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>127314414</v>
+        <v>127314326</v>
       </c>
       <c r="B231" t="n">
-        <v>98456</v>
+        <v>5197</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I231" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J231" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K231" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr"/>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P231" t="inlineStr">
@@ -25399,10 +25394,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>553341</v>
+        <v>553527</v>
       </c>
       <c r="R231" t="n">
-        <v>6704994</v>
+        <v>6705221</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -25435,11 +25430,6 @@
       <c r="AA231" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC231" t="inlineStr">
-        <is>
-          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -25466,10 +25456,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>127314444</v>
+        <v>127314414</v>
       </c>
       <c r="B232" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -25496,7 +25486,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -25504,16 +25494,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P232" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>553489</v>
+        <v>553341</v>
       </c>
       <c r="R232" t="n">
-        <v>6705294</v>
+        <v>6704994</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -25546,6 +25541,11 @@
       <c r="AA232" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -25572,10 +25572,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>127314440</v>
+        <v>127314444</v>
       </c>
       <c r="B233" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -25616,10 +25616,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>553571</v>
+        <v>553489</v>
       </c>
       <c r="R233" t="n">
-        <v>6705297</v>
+        <v>6705294</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -25681,7 +25681,7 @@
         <v>127314486</v>
       </c>
       <c r="B234" t="n">
-        <v>91710</v>
+        <v>91713</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>

--- a/artfynd/A 18040-2021 artfynd.xlsx
+++ b/artfynd/A 18040-2021 artfynd.xlsx
@@ -13776,32 +13776,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127314388</v>
+        <v>127314398</v>
       </c>
       <c r="B121" t="n">
-        <v>91795</v>
+        <v>97344</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1209</v>
+        <v>221945</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13811,10 +13811,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>553411</v>
+        <v>553472</v>
       </c>
       <c r="R121" t="n">
-        <v>6705072</v>
+        <v>6705479</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13873,50 +13873,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127314375</v>
+        <v>127314397</v>
       </c>
       <c r="B122" t="n">
-        <v>57663</v>
+        <v>97344</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>553537</v>
+        <v>553527</v>
       </c>
       <c r="R122" t="n">
-        <v>6705403</v>
+        <v>6705221</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13975,32 +13970,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127314398</v>
+        <v>127314388</v>
       </c>
       <c r="B123" t="n">
-        <v>97336</v>
+        <v>91803</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>221945</v>
+        <v>1209</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14010,10 +14005,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>553472</v>
+        <v>553411</v>
       </c>
       <c r="R123" t="n">
-        <v>6705479</v>
+        <v>6705072</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14072,45 +14067,50 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127314397</v>
+        <v>127314375</v>
       </c>
       <c r="B124" t="n">
-        <v>97336</v>
+        <v>57669</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>553527</v>
+        <v>553537</v>
       </c>
       <c r="R124" t="n">
-        <v>6705221</v>
+        <v>6705403</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14172,7 +14172,7 @@
         <v>127314407</v>
       </c>
       <c r="B125" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14276,47 +14276,38 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127314416</v>
+        <v>127314372</v>
       </c>
       <c r="B126" t="n">
-        <v>98459</v>
+        <v>57669</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -14325,10 +14316,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>553356</v>
+        <v>553488</v>
       </c>
       <c r="R126" t="n">
-        <v>6704786</v>
+        <v>6705460</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14361,11 +14352,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14392,10 +14378,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127314432</v>
+        <v>127314435</v>
       </c>
       <c r="B127" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14422,7 +14408,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -14430,16 +14416,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>553508</v>
+        <v>553476</v>
       </c>
       <c r="R127" t="n">
-        <v>6705194</v>
+        <v>6705068</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14472,6 +14463,11 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>12 blomstjälkar</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14498,10 +14494,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127314435</v>
+        <v>127314416</v>
       </c>
       <c r="B128" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14528,7 +14524,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -14547,10 +14543,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>553476</v>
+        <v>553356</v>
       </c>
       <c r="R128" t="n">
-        <v>6705068</v>
+        <v>6704786</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14587,7 +14583,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>12 blomstjälkar</t>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14614,10 +14610,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127314415</v>
+        <v>127314432</v>
       </c>
       <c r="B129" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14644,7 +14640,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -14652,21 +14648,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>553463</v>
+        <v>553508</v>
       </c>
       <c r="R129" t="n">
-        <v>6705155</v>
+        <v>6705194</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14699,11 +14690,6 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14730,38 +14716,47 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127314372</v>
+        <v>127314415</v>
       </c>
       <c r="B130" t="n">
-        <v>57663</v>
+        <v>98467</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -14770,10 +14765,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>553488</v>
+        <v>553463</v>
       </c>
       <c r="R130" t="n">
-        <v>6705460</v>
+        <v>6705155</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14806,6 +14801,11 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14832,45 +14832,54 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127314347</v>
+        <v>127314465</v>
       </c>
       <c r="B131" t="n">
-        <v>91341</v>
+        <v>98467</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>553419</v>
+        <v>553488</v>
       </c>
       <c r="R131" t="n">
-        <v>6705073</v>
+        <v>6705263</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14929,45 +14938,59 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127314345</v>
+        <v>127314452</v>
       </c>
       <c r="B132" t="n">
-        <v>91341</v>
+        <v>98467</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>553386</v>
+        <v>553418</v>
       </c>
       <c r="R132" t="n">
-        <v>6704777</v>
+        <v>6705084</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15026,45 +15049,54 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127314350</v>
+        <v>127314410</v>
       </c>
       <c r="B133" t="n">
-        <v>91341</v>
+        <v>98467</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>553465</v>
+        <v>553422</v>
       </c>
       <c r="R133" t="n">
-        <v>6705219</v>
+        <v>6705072</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15123,10 +15155,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127314468</v>
+        <v>127314336</v>
       </c>
       <c r="B134" t="n">
-        <v>91928</v>
+        <v>91707</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15134,21 +15166,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1179</v>
+        <v>2062</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15158,10 +15190,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>553482</v>
+        <v>553429</v>
       </c>
       <c r="R134" t="n">
-        <v>6705183</v>
+        <v>6705077</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15194,11 +15226,6 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Återfynd</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15225,32 +15252,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127314336</v>
+        <v>127314341</v>
       </c>
       <c r="B135" t="n">
-        <v>91699</v>
+        <v>91349</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15296,6 +15323,11 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15322,10 +15354,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127314341</v>
+        <v>127314345</v>
       </c>
       <c r="B136" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15357,10 +15389,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>553429</v>
+        <v>553386</v>
       </c>
       <c r="R136" t="n">
-        <v>6705077</v>
+        <v>6704777</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15393,11 +15425,6 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15424,10 +15451,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127314452</v>
+        <v>127314468</v>
       </c>
       <c r="B137" t="n">
-        <v>98459</v>
+        <v>91936</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15435,48 +15462,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220787</v>
+        <v>1179</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Peck) Donk</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>553418</v>
+        <v>553482</v>
       </c>
       <c r="R137" t="n">
-        <v>6705084</v>
+        <v>6705183</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15509,6 +15522,11 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Återfynd</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15535,54 +15553,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127314410</v>
+        <v>127314347</v>
       </c>
       <c r="B138" t="n">
-        <v>98459</v>
+        <v>91349</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>553422</v>
+        <v>553419</v>
       </c>
       <c r="R138" t="n">
-        <v>6705072</v>
+        <v>6705073</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15641,54 +15650,45 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127314465</v>
+        <v>127314350</v>
       </c>
       <c r="B139" t="n">
-        <v>98459</v>
+        <v>91349</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>553488</v>
+        <v>553465</v>
       </c>
       <c r="R139" t="n">
-        <v>6705263</v>
+        <v>6705219</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15747,54 +15747,53 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127314441</v>
+        <v>127314370</v>
       </c>
       <c r="B140" t="n">
-        <v>98459</v>
+        <v>57669</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>553422</v>
+        <v>553311</v>
       </c>
       <c r="R140" t="n">
-        <v>6704986</v>
+        <v>6704717</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15853,42 +15852,38 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127314442</v>
+        <v>127314473</v>
       </c>
       <c r="B141" t="n">
-        <v>98459</v>
+        <v>57593</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -15897,10 +15892,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>553423</v>
+        <v>553415</v>
       </c>
       <c r="R141" t="n">
-        <v>6704914</v>
+        <v>6705462</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15933,6 +15928,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Fjädrar på "slaktbord"</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15959,10 +15959,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127314417</v>
+        <v>127314442</v>
       </c>
       <c r="B142" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -15997,21 +15997,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>553413</v>
+        <v>553423</v>
       </c>
       <c r="R142" t="n">
-        <v>6704868</v>
+        <v>6704914</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16044,11 +16039,6 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16075,38 +16065,42 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127314473</v>
+        <v>127314441</v>
       </c>
       <c r="B143" t="n">
-        <v>57587</v>
+        <v>98467</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -16115,10 +16109,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>553415</v>
+        <v>553422</v>
       </c>
       <c r="R143" t="n">
-        <v>6705462</v>
+        <v>6704986</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16151,11 +16145,6 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Fjädrar på "slaktbord"</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16182,53 +16171,59 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127314370</v>
+        <v>127314417</v>
       </c>
       <c r="B144" t="n">
-        <v>57663</v>
+        <v>98467</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N144" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>553311</v>
+        <v>553413</v>
       </c>
       <c r="R144" t="n">
-        <v>6704717</v>
+        <v>6704868</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16261,6 +16256,11 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16290,7 +16290,7 @@
         <v>127314376</v>
       </c>
       <c r="B145" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>127314380</v>
       </c>
       <c r="B146" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16491,10 +16491,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127314424</v>
+        <v>127314454</v>
       </c>
       <c r="B147" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -16540,10 +16540,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>553422</v>
+        <v>553347</v>
       </c>
       <c r="R147" t="n">
-        <v>6704824</v>
+        <v>6705040</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16576,6 +16576,11 @@
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>7 blomstjälkar</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16602,10 +16607,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127314454</v>
+        <v>127314424</v>
       </c>
       <c r="B148" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16632,7 +16637,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -16651,10 +16656,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>553347</v>
+        <v>553422</v>
       </c>
       <c r="R148" t="n">
-        <v>6705040</v>
+        <v>6704824</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16687,11 +16692,6 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>7 blomstjälkar</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16718,45 +16718,50 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127314343</v>
+        <v>127314405</v>
       </c>
       <c r="B149" t="n">
-        <v>91341</v>
+        <v>8450</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>553388</v>
+        <v>553521</v>
       </c>
       <c r="R149" t="n">
-        <v>6704753</v>
+        <v>6705364</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16815,45 +16820,59 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127314342</v>
+        <v>127314450</v>
       </c>
       <c r="B150" t="n">
-        <v>91341</v>
+        <v>98467</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>553347</v>
+        <v>553340</v>
       </c>
       <c r="R150" t="n">
-        <v>6704783</v>
+        <v>6704784</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16912,38 +16931,47 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127314405</v>
+        <v>127314411</v>
       </c>
       <c r="B151" t="n">
-        <v>8450</v>
+        <v>98467</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -16952,10 +16980,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>553521</v>
+        <v>553500</v>
       </c>
       <c r="R151" t="n">
-        <v>6705364</v>
+        <v>6705175</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17014,10 +17042,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127314411</v>
+        <v>127314419</v>
       </c>
       <c r="B152" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17044,7 +17072,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -17063,10 +17091,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>553500</v>
+        <v>553343</v>
       </c>
       <c r="R152" t="n">
-        <v>6705175</v>
+        <v>6704786</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17099,6 +17127,11 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17125,59 +17158,45 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>127314419</v>
+        <v>127314342</v>
       </c>
       <c r="B153" t="n">
-        <v>98459</v>
+        <v>91349</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>553343</v>
+        <v>553347</v>
       </c>
       <c r="R153" t="n">
-        <v>6704786</v>
+        <v>6704783</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17210,11 +17229,6 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17241,59 +17255,45 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127314450</v>
+        <v>127314343</v>
       </c>
       <c r="B154" t="n">
-        <v>98459</v>
+        <v>91349</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>553340</v>
+        <v>553388</v>
       </c>
       <c r="R154" t="n">
-        <v>6704784</v>
+        <v>6704753</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17352,59 +17352,53 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127314447</v>
+        <v>127314374</v>
       </c>
       <c r="B155" t="n">
-        <v>98459</v>
+        <v>57669</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>553387</v>
+        <v>553523</v>
       </c>
       <c r="R155" t="n">
-        <v>6704938</v>
+        <v>6705404</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17463,42 +17457,38 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127314433</v>
+        <v>127314391</v>
       </c>
       <c r="B156" t="n">
-        <v>98459</v>
+        <v>57672</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -17507,10 +17497,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>553366</v>
+        <v>553375</v>
       </c>
       <c r="R156" t="n">
-        <v>6704886</v>
+        <v>6705433</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17543,6 +17533,11 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17569,10 +17564,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127314387</v>
+        <v>127314433</v>
       </c>
       <c r="B157" t="n">
-        <v>91795</v>
+        <v>98467</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17580,34 +17575,43 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>553517</v>
+        <v>553366</v>
       </c>
       <c r="R157" t="n">
-        <v>6705421</v>
+        <v>6704886</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17666,45 +17670,59 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127314385</v>
+        <v>127314447</v>
       </c>
       <c r="B158" t="n">
-        <v>56962</v>
+        <v>98467</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100038</v>
+        <v>220787</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>553426</v>
+        <v>553387</v>
       </c>
       <c r="R158" t="n">
-        <v>6704786</v>
+        <v>6704938</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17763,53 +17781,45 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127314374</v>
+        <v>127314387</v>
       </c>
       <c r="B159" t="n">
-        <v>57663</v>
+        <v>91803</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>553523</v>
+        <v>553517</v>
       </c>
       <c r="R159" t="n">
-        <v>6705404</v>
+        <v>6705421</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17868,10 +17878,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127314362</v>
+        <v>127314385</v>
       </c>
       <c r="B160" t="n">
-        <v>4773</v>
+        <v>56968</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17879,39 +17889,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100299</v>
+        <v>100038</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>553526</v>
+        <v>553426</v>
       </c>
       <c r="R160" t="n">
-        <v>6705221</v>
+        <v>6704786</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17970,38 +17975,38 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127314391</v>
+        <v>127314362</v>
       </c>
       <c r="B161" t="n">
-        <v>57666</v>
+        <v>4773</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100109</v>
+        <v>100299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="M161" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
@@ -18010,10 +18015,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>553375</v>
+        <v>553526</v>
       </c>
       <c r="R161" t="n">
-        <v>6705433</v>
+        <v>6705221</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18046,11 +18051,6 @@
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18077,10 +18077,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127314443</v>
+        <v>127314448</v>
       </c>
       <c r="B162" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18107,7 +18107,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -18115,16 +18115,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>553338</v>
+        <v>553342</v>
       </c>
       <c r="R162" t="n">
-        <v>6705039</v>
+        <v>6704852</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18183,10 +18188,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>127314448</v>
+        <v>127314443</v>
       </c>
       <c r="B163" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18213,7 +18218,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -18221,21 +18226,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P163" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>553342</v>
+        <v>553338</v>
       </c>
       <c r="R163" t="n">
-        <v>6704852</v>
+        <v>6705039</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18297,7 +18297,7 @@
         <v>127314434</v>
       </c>
       <c r="B164" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>127314451</v>
       </c>
       <c r="B165" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18521,10 +18521,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>127314439</v>
+        <v>127314421</v>
       </c>
       <c r="B166" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18551,7 +18551,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -18570,10 +18570,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>553525</v>
+        <v>553457</v>
       </c>
       <c r="R166" t="n">
-        <v>6705250</v>
+        <v>6705062</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18606,11 +18606,6 @@
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>6 blomstjälkar</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18637,10 +18632,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>127314421</v>
+        <v>127314439</v>
       </c>
       <c r="B167" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18667,7 +18662,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -18686,10 +18681,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>553457</v>
+        <v>553525</v>
       </c>
       <c r="R167" t="n">
-        <v>6705062</v>
+        <v>6705250</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18722,6 +18717,11 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>6 blomstjälkar</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18751,7 +18751,7 @@
         <v>127314409</v>
       </c>
       <c r="B168" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>127314460</v>
       </c>
       <c r="B169" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18961,42 +18961,47 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>127314386</v>
+        <v>127314455</v>
       </c>
       <c r="B170" t="n">
-        <v>92643</v>
+        <v>98467</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
@@ -19005,10 +19010,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>553414</v>
+        <v>553431</v>
       </c>
       <c r="R170" t="n">
-        <v>6704970</v>
+        <v>6704842</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19041,6 +19046,11 @@
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19067,38 +19077,42 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127314393</v>
+        <v>127314426</v>
       </c>
       <c r="B171" t="n">
-        <v>57666</v>
+        <v>98467</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
@@ -19107,10 +19121,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>553521</v>
+        <v>553452</v>
       </c>
       <c r="R171" t="n">
-        <v>6705364</v>
+        <v>6705056</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19143,11 +19157,6 @@
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19174,42 +19183,42 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>127314426</v>
+        <v>127314386</v>
       </c>
       <c r="B172" t="n">
-        <v>98459</v>
+        <v>92651</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
@@ -19218,10 +19227,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>553452</v>
+        <v>553414</v>
       </c>
       <c r="R172" t="n">
-        <v>6705056</v>
+        <v>6704970</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19280,47 +19289,38 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127314455</v>
+        <v>127314393</v>
       </c>
       <c r="B173" t="n">
-        <v>98459</v>
+        <v>57672</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
@@ -19329,10 +19329,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>553431</v>
+        <v>553521</v>
       </c>
       <c r="R173" t="n">
-        <v>6704842</v>
+        <v>6705364</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19369,7 +19369,7 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>3 blomstjälkar</t>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19399,7 +19399,7 @@
         <v>127314355</v>
       </c>
       <c r="B174" t="n">
-        <v>91699</v>
+        <v>91707</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19496,7 +19496,7 @@
         <v>127314392</v>
       </c>
       <c r="B175" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19600,38 +19600,47 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>127314482</v>
+        <v>127314438</v>
       </c>
       <c r="B176" t="n">
-        <v>5177</v>
+        <v>98467</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr"/>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
@@ -19640,10 +19649,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>553322</v>
+        <v>553407</v>
       </c>
       <c r="R176" t="n">
-        <v>6704727</v>
+        <v>6704816</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19676,6 +19685,11 @@
       <c r="AA176" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19702,10 +19716,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>127314438</v>
+        <v>127314459</v>
       </c>
       <c r="B177" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19732,7 +19746,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -19740,21 +19754,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P177" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>553407</v>
+        <v>553508</v>
       </c>
       <c r="R177" t="n">
-        <v>6704816</v>
+        <v>6705196</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19787,11 +19796,6 @@
       <c r="AA177" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19818,42 +19822,38 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>127314459</v>
+        <v>127314482</v>
       </c>
       <c r="B178" t="n">
-        <v>98459</v>
+        <v>5177</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
@@ -19862,10 +19862,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>553508</v>
+        <v>553322</v>
       </c>
       <c r="R178" t="n">
-        <v>6705196</v>
+        <v>6704727</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19924,10 +19924,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>127314467</v>
+        <v>127314395</v>
       </c>
       <c r="B179" t="n">
-        <v>105497</v>
+        <v>97344</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19935,21 +19935,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19959,10 +19959,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>553468</v>
+        <v>553357</v>
       </c>
       <c r="R179" t="n">
-        <v>6705155</v>
+        <v>6704877</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20021,10 +20021,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>127314413</v>
+        <v>127314430</v>
       </c>
       <c r="B180" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -20059,21 +20059,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P180" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>553349</v>
+        <v>553358</v>
       </c>
       <c r="R180" t="n">
-        <v>6704994</v>
+        <v>6705058</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20106,11 +20101,6 @@
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>5 blomstjälkar</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20137,47 +20127,38 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>127314418</v>
+        <v>127314381</v>
       </c>
       <c r="B181" t="n">
-        <v>98459</v>
+        <v>57669</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
@@ -20186,10 +20167,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>553496</v>
+        <v>553468</v>
       </c>
       <c r="R181" t="n">
-        <v>6705280</v>
+        <v>6705451</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20222,11 +20203,6 @@
       <c r="AA181" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20256,7 +20232,7 @@
         <v>127314378</v>
       </c>
       <c r="B182" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20355,42 +20331,38 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>127314430</v>
+        <v>127314484</v>
       </c>
       <c r="B183" t="n">
-        <v>98459</v>
+        <v>5177</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
@@ -20399,10 +20371,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>553358</v>
+        <v>553430</v>
       </c>
       <c r="R183" t="n">
-        <v>6705058</v>
+        <v>6705087</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20461,10 +20433,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>127314395</v>
+        <v>127314467</v>
       </c>
       <c r="B184" t="n">
-        <v>97336</v>
+        <v>105505</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20472,21 +20444,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -20496,10 +20468,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>553357</v>
+        <v>553468</v>
       </c>
       <c r="R184" t="n">
-        <v>6704877</v>
+        <v>6705155</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20558,38 +20530,47 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>127314381</v>
+        <v>127314413</v>
       </c>
       <c r="B185" t="n">
-        <v>57663</v>
+        <v>98467</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr"/>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
@@ -20598,10 +20579,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>553468</v>
+        <v>553349</v>
       </c>
       <c r="R185" t="n">
-        <v>6705451</v>
+        <v>6704994</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20634,6 +20615,11 @@
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>5 blomstjälkar</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -20660,38 +20646,47 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>127314484</v>
+        <v>127314418</v>
       </c>
       <c r="B186" t="n">
-        <v>5177</v>
+        <v>98467</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr"/>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
@@ -20700,10 +20695,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>553430</v>
+        <v>553496</v>
       </c>
       <c r="R186" t="n">
-        <v>6705087</v>
+        <v>6705280</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20736,6 +20731,11 @@
       <c r="AA186" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20762,45 +20762,59 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>127314390</v>
+        <v>127314453</v>
       </c>
       <c r="B187" t="n">
-        <v>91637</v>
+        <v>98467</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P187" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>553386</v>
+        <v>553477</v>
       </c>
       <c r="R187" t="n">
-        <v>6704777</v>
+        <v>6705197</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20859,10 +20873,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>127314436</v>
+        <v>127314464</v>
       </c>
       <c r="B188" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20889,7 +20903,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -20897,21 +20911,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P188" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>553571</v>
+        <v>553470</v>
       </c>
       <c r="R188" t="n">
-        <v>6705315</v>
+        <v>6705234</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20944,11 +20953,6 @@
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC188" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20975,10 +20979,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>127314453</v>
+        <v>127314461</v>
       </c>
       <c r="B189" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21013,21 +21017,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P189" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>553477</v>
+        <v>553335</v>
       </c>
       <c r="R189" t="n">
-        <v>6705197</v>
+        <v>6704846</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21086,54 +21085,45 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>127314464</v>
+        <v>127314390</v>
       </c>
       <c r="B190" t="n">
-        <v>98459</v>
+        <v>91645</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>553470</v>
+        <v>553386</v>
       </c>
       <c r="R190" t="n">
-        <v>6705234</v>
+        <v>6704777</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21192,10 +21182,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>127314461</v>
+        <v>127314436</v>
       </c>
       <c r="B191" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21222,7 +21212,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -21230,16 +21220,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P191" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>553335</v>
+        <v>553571</v>
       </c>
       <c r="R191" t="n">
-        <v>6704846</v>
+        <v>6705315</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21272,6 +21267,11 @@
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21301,7 +21301,7 @@
         <v>127314339</v>
       </c>
       <c r="B192" t="n">
-        <v>91699</v>
+        <v>91707</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21395,10 +21395,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>127310426</v>
+        <v>127314408</v>
       </c>
       <c r="B193" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21423,36 +21423,25 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
-      <c r="L193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
+          <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>553479</v>
+        <v>553400</v>
       </c>
       <c r="R193" t="n">
-        <v>6705057</v>
+        <v>6705072</v>
       </c>
       <c r="S193" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -21484,35 +21473,39 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>få synliga bladrosetter</t>
+        </is>
+      </c>
       <c r="AD193" t="b">
         <v>0</v>
       </c>
       <c r="AE193" t="b">
         <v>0</v>
       </c>
-      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>127314408</v>
+        <v>127310426</v>
       </c>
       <c r="B194" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21537,25 +21530,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K194" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
+      <c r="L194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Morkullberget södra, Dlr</t>
+          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>553400</v>
+        <v>553479</v>
       </c>
       <c r="R194" t="n">
-        <v>6705072</v>
+        <v>6705057</v>
       </c>
       <c r="S194" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -21587,29 +21591,25 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>få synliga bladrosetter</t>
-        </is>
-      </c>
       <c r="AD194" t="b">
         <v>0</v>
       </c>
       <c r="AE194" t="b">
         <v>0</v>
       </c>
+      <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="b">
         <v>0</v>
       </c>
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
@@ -21619,7 +21619,7 @@
         <v>127314423</v>
       </c>
       <c r="B195" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21727,10 +21727,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>127314379</v>
+        <v>127314389</v>
       </c>
       <c r="B196" t="n">
-        <v>57663</v>
+        <v>91645</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21738,39 +21738,34 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>553485</v>
+        <v>553364</v>
       </c>
       <c r="R196" t="n">
-        <v>6705230</v>
+        <v>6704790</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21829,10 +21824,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>127314389</v>
+        <v>127314382</v>
       </c>
       <c r="B197" t="n">
-        <v>91637</v>
+        <v>57322</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21840,34 +21835,39 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>658</v>
+        <v>100063</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>553364</v>
+        <v>553494</v>
       </c>
       <c r="R197" t="n">
-        <v>6704790</v>
+        <v>6705461</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21926,42 +21926,38 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>127314425</v>
+        <v>127314379</v>
       </c>
       <c r="B198" t="n">
-        <v>98459</v>
+        <v>57669</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
@@ -21970,10 +21966,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>553466</v>
+        <v>553485</v>
       </c>
       <c r="R198" t="n">
-        <v>6705077</v>
+        <v>6705230</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22032,59 +22028,53 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>127314420</v>
+        <v>127314363</v>
       </c>
       <c r="B199" t="n">
-        <v>98459</v>
+        <v>57832</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>553426</v>
+        <v>553336</v>
       </c>
       <c r="R199" t="n">
-        <v>6704821</v>
+        <v>6704944</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22117,11 +22107,6 @@
       <c r="AA199" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC199" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22148,10 +22133,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127314445</v>
+        <v>127314425</v>
       </c>
       <c r="B200" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22178,7 +22163,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -22186,21 +22171,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P200" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>553364</v>
+        <v>553466</v>
       </c>
       <c r="R200" t="n">
-        <v>6704996</v>
+        <v>6705077</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22262,7 +22242,7 @@
         <v>127314429</v>
       </c>
       <c r="B201" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22365,38 +22345,47 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127314382</v>
+        <v>127314420</v>
       </c>
       <c r="B202" t="n">
-        <v>57316</v>
+        <v>98467</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>100063</v>
+        <v>220787</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr"/>
-      <c r="M202" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
@@ -22405,10 +22394,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>553494</v>
+        <v>553426</v>
       </c>
       <c r="R202" t="n">
-        <v>6705461</v>
+        <v>6704821</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22441,6 +22430,11 @@
       <c r="AA202" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22467,53 +22461,50 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>127314363</v>
+        <v>127314325</v>
       </c>
       <c r="B203" t="n">
-        <v>57826</v>
+        <v>5197</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>103021</v>
+        <v>105930</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
-      <c r="K203" t="inlineStr"/>
-      <c r="L203" t="inlineStr"/>
       <c r="M203" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N203" t="inlineStr"/>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P203" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>553336</v>
+        <v>553508</v>
       </c>
       <c r="R203" t="n">
-        <v>6704944</v>
+        <v>6705185</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22572,38 +22563,47 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>127314325</v>
+        <v>127314445</v>
       </c>
       <c r="B204" t="n">
-        <v>5197</v>
+        <v>98467</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr"/>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
@@ -22612,10 +22612,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>553508</v>
+        <v>553364</v>
       </c>
       <c r="R204" t="n">
-        <v>6705185</v>
+        <v>6704996</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22674,54 +22674,45 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>127314431</v>
+        <v>127314354</v>
       </c>
       <c r="B205" t="n">
-        <v>98459</v>
+        <v>91349</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J205" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>553442</v>
+        <v>553517</v>
       </c>
       <c r="R205" t="n">
-        <v>6705095</v>
+        <v>6705421</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22780,32 +22771,32 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>127314412</v>
+        <v>127314360</v>
       </c>
       <c r="B206" t="n">
-        <v>98459</v>
+        <v>56864</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -22813,26 +22804,16 @@
           <t>5</t>
         </is>
       </c>
-      <c r="J206" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P206" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>553337</v>
+        <v>553530</v>
       </c>
       <c r="R206" t="n">
-        <v>6704813</v>
+        <v>6705203</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22865,6 +22846,11 @@
       <c r="AA206" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>Höna med minst fyra ungar</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22891,40 +22877,59 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>127314406</v>
+        <v>127314412</v>
       </c>
       <c r="B207" t="n">
-        <v>91748</v>
+        <v>98467</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P207" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>553517</v>
+        <v>553337</v>
       </c>
       <c r="R207" t="n">
-        <v>6705421</v>
+        <v>6704813</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22983,45 +22988,54 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>127314354</v>
+        <v>127314431</v>
       </c>
       <c r="B208" t="n">
-        <v>91341</v>
+        <v>98467</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P208" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>553517</v>
+        <v>553442</v>
       </c>
       <c r="R208" t="n">
-        <v>6705421</v>
+        <v>6705095</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23080,49 +23094,40 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>127314360</v>
+        <v>127314406</v>
       </c>
       <c r="B209" t="n">
-        <v>56858</v>
+        <v>91756</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>553530</v>
+        <v>553517</v>
       </c>
       <c r="R209" t="n">
-        <v>6705203</v>
+        <v>6705421</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23155,11 +23160,6 @@
       <c r="AA209" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>Höna med minst fyra ungar</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -23186,51 +23186,48 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>127310539</v>
+        <v>127314477</v>
       </c>
       <c r="B210" t="n">
-        <v>91553</v>
+        <v>92639</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>1106</v>
+        <v>4364</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
-      <c r="J210" t="inlineStr"/>
-      <c r="K210" t="inlineStr"/>
-      <c r="N210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
+          <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>553483</v>
+        <v>553371</v>
       </c>
       <c r="R210" t="n">
-        <v>6705051</v>
+        <v>6704731</v>
       </c>
       <c r="S210" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -23262,25 +23259,29 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>Många gamla fruktkroppar i häxring</t>
+        </is>
+      </c>
       <c r="AD210" t="b">
         <v>0</v>
       </c>
       <c r="AE210" t="b">
         <v>0</v>
       </c>
-      <c r="AF210" t="inlineStr"/>
       <c r="AG210" t="b">
         <v>0</v>
       </c>
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
@@ -23290,7 +23291,7 @@
         <v>127314368</v>
       </c>
       <c r="B211" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23389,48 +23390,51 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>127314477</v>
+        <v>127310539</v>
       </c>
       <c r="B212" t="n">
-        <v>92631</v>
+        <v>91561</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>4364</v>
+        <v>1106</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr"/>
+      <c r="N212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Morkullberget södra, Dlr</t>
+          <t>Flyttjesundet, Flyttjesundet, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>553371</v>
+        <v>553483</v>
       </c>
       <c r="R212" t="n">
-        <v>6704731</v>
+        <v>6705051</v>
       </c>
       <c r="S212" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -23462,29 +23466,25 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC212" t="inlineStr">
-        <is>
-          <t>Många gamla fruktkroppar i häxring</t>
-        </is>
-      </c>
       <c r="AD212" t="b">
         <v>0</v>
       </c>
       <c r="AE212" t="b">
         <v>0</v>
       </c>
+      <c r="AF212" t="inlineStr"/>
       <c r="AG212" t="b">
         <v>0</v>
       </c>
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
@@ -23596,7 +23596,7 @@
         <v>127314428</v>
       </c>
       <c r="B214" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -23699,10 +23699,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>127314351</v>
+        <v>127314348</v>
       </c>
       <c r="B215" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -23734,10 +23734,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>553533</v>
+        <v>553499</v>
       </c>
       <c r="R215" t="n">
-        <v>6705296</v>
+        <v>6705218</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -23796,10 +23796,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>127314348</v>
+        <v>127314351</v>
       </c>
       <c r="B216" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -23831,10 +23831,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>553499</v>
+        <v>553533</v>
       </c>
       <c r="R216" t="n">
-        <v>6705218</v>
+        <v>6705296</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -23896,7 +23896,7 @@
         <v>127314396</v>
       </c>
       <c r="B217" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -23990,10 +23990,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>127314437</v>
+        <v>127314337</v>
       </c>
       <c r="B218" t="n">
-        <v>98459</v>
+        <v>91707</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24001,48 +24001,34 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J218" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>553333</v>
+        <v>553419</v>
       </c>
       <c r="R218" t="n">
-        <v>6704814</v>
+        <v>6705073</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24075,6 +24061,11 @@
       <c r="AA218" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>Eventuellt S. delicata</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24101,42 +24092,38 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127314463</v>
+        <v>127314377</v>
       </c>
       <c r="B219" t="n">
-        <v>98459</v>
+        <v>57669</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J219" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr"/>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
@@ -24145,10 +24132,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>553433</v>
+        <v>553336</v>
       </c>
       <c r="R219" t="n">
-        <v>6704902</v>
+        <v>6704827</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24207,59 +24194,45 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127314422</v>
+        <v>127314394</v>
       </c>
       <c r="B220" t="n">
-        <v>98459</v>
+        <v>97344</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J220" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>553445</v>
+        <v>553498</v>
       </c>
       <c r="R220" t="n">
-        <v>6704996</v>
+        <v>6705418</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24318,59 +24291,45 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>127314456</v>
+        <v>127314471</v>
       </c>
       <c r="B221" t="n">
-        <v>98459</v>
+        <v>79029</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J221" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K221" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>553437</v>
+        <v>553406</v>
       </c>
       <c r="R221" t="n">
-        <v>6704997</v>
+        <v>6705479</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24403,11 +24362,6 @@
       <c r="AA221" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC221" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -24434,10 +24388,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>127314457</v>
+        <v>127314463</v>
       </c>
       <c r="B222" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -24464,7 +24418,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -24478,10 +24432,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>553442</v>
+        <v>553433</v>
       </c>
       <c r="R222" t="n">
-        <v>6705078</v>
+        <v>6704902</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24540,10 +24494,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>127314458</v>
+        <v>127314437</v>
       </c>
       <c r="B223" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -24570,7 +24524,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -24578,16 +24532,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>553526</v>
+        <v>553333</v>
       </c>
       <c r="R223" t="n">
-        <v>6705245</v>
+        <v>6704814</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24646,45 +24605,54 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127314394</v>
+        <v>127314458</v>
       </c>
       <c r="B224" t="n">
-        <v>97336</v>
+        <v>98467</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I224" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P224" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>553498</v>
+        <v>553526</v>
       </c>
       <c r="R224" t="n">
-        <v>6705418</v>
+        <v>6705245</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24743,38 +24711,47 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127314377</v>
+        <v>127314422</v>
       </c>
       <c r="B225" t="n">
-        <v>57663</v>
+        <v>98467</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr"/>
-      <c r="M225" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
@@ -24783,10 +24760,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>553336</v>
+        <v>553445</v>
       </c>
       <c r="R225" t="n">
-        <v>6704827</v>
+        <v>6704996</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24845,45 +24822,59 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127314471</v>
+        <v>127314456</v>
       </c>
       <c r="B226" t="n">
-        <v>79023</v>
+        <v>98467</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P226" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>553406</v>
+        <v>553437</v>
       </c>
       <c r="R226" t="n">
-        <v>6705479</v>
+        <v>6704997</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24916,6 +24907,11 @@
       <c r="AA226" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -24942,10 +24938,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127314337</v>
+        <v>127314457</v>
       </c>
       <c r="B227" t="n">
-        <v>91699</v>
+        <v>98467</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -24953,34 +24949,43 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>553419</v>
+        <v>553442</v>
       </c>
       <c r="R227" t="n">
-        <v>6705073</v>
+        <v>6705078</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25013,11 +25018,6 @@
       <c r="AA227" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC227" t="inlineStr">
-        <is>
-          <t>Eventuellt S. delicata</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -25044,38 +25044,38 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127314371</v>
+        <v>127314479</v>
       </c>
       <c r="B228" t="n">
-        <v>57663</v>
+        <v>5177</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
       <c r="M228" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
@@ -25084,10 +25084,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>553336</v>
+        <v>553496</v>
       </c>
       <c r="R228" t="n">
-        <v>6704723</v>
+        <v>6705218</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25146,42 +25146,38 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127314440</v>
+        <v>127314371</v>
       </c>
       <c r="B229" t="n">
-        <v>98459</v>
+        <v>57669</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I229" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J229" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr"/>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -25190,10 +25186,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>553571</v>
+        <v>553336</v>
       </c>
       <c r="R229" t="n">
-        <v>6705297</v>
+        <v>6704723</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25252,10 +25248,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>127314479</v>
+        <v>127314326</v>
       </c>
       <c r="B230" t="n">
-        <v>5177</v>
+        <v>5197</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -25263,27 +25259,27 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
       <c r="M230" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
@@ -25292,10 +25288,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>553496</v>
+        <v>553527</v>
       </c>
       <c r="R230" t="n">
-        <v>6705218</v>
+        <v>6705221</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -25354,38 +25350,42 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>127314326</v>
+        <v>127314444</v>
       </c>
       <c r="B231" t="n">
-        <v>5197</v>
+        <v>98467</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I231" t="inlineStr"/>
-      <c r="M231" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P231" t="inlineStr">
@@ -25394,10 +25394,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>553527</v>
+        <v>553489</v>
       </c>
       <c r="R231" t="n">
-        <v>6705221</v>
+        <v>6705294</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -25459,7 +25459,7 @@
         <v>127314414</v>
       </c>
       <c r="B232" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -25572,10 +25572,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>127314444</v>
+        <v>127314440</v>
       </c>
       <c r="B233" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -25616,10 +25616,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>553489</v>
+        <v>553571</v>
       </c>
       <c r="R233" t="n">
-        <v>6705294</v>
+        <v>6705297</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -25681,7 +25681,7 @@
         <v>127314486</v>
       </c>
       <c r="B234" t="n">
-        <v>91713</v>
+        <v>91721</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>

--- a/artfynd/A 18040-2021 artfynd.xlsx
+++ b/artfynd/A 18040-2021 artfynd.xlsx
@@ -13776,32 +13776,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127314398</v>
+        <v>127314388</v>
       </c>
       <c r="B121" t="n">
-        <v>97344</v>
+        <v>91804</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>221945</v>
+        <v>1209</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13811,10 +13811,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>553472</v>
+        <v>553411</v>
       </c>
       <c r="R121" t="n">
-        <v>6705479</v>
+        <v>6705072</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13873,45 +13873,50 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127314397</v>
+        <v>127314407</v>
       </c>
       <c r="B122" t="n">
-        <v>97344</v>
+        <v>98468</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>553527</v>
+        <v>553477</v>
       </c>
       <c r="R122" t="n">
-        <v>6705221</v>
+        <v>6705175</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13944,6 +13949,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>få synliga bladrosetter</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13970,45 +13980,50 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127314388</v>
+        <v>127314375</v>
       </c>
       <c r="B123" t="n">
-        <v>91803</v>
+        <v>57669</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>553411</v>
+        <v>553537</v>
       </c>
       <c r="R123" t="n">
-        <v>6705072</v>
+        <v>6705403</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14067,50 +14082,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127314375</v>
+        <v>127314398</v>
       </c>
       <c r="B124" t="n">
-        <v>57669</v>
+        <v>97345</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>553537</v>
+        <v>553472</v>
       </c>
       <c r="R124" t="n">
-        <v>6705403</v>
+        <v>6705479</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14169,50 +14179,45 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127314407</v>
+        <v>127314397</v>
       </c>
       <c r="B125" t="n">
-        <v>98467</v>
+        <v>97345</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>553477</v>
+        <v>553527</v>
       </c>
       <c r="R125" t="n">
-        <v>6705175</v>
+        <v>6705221</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14245,11 +14250,6 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>få synliga bladrosetter</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14378,10 +14378,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127314435</v>
+        <v>127314416</v>
       </c>
       <c r="B127" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14408,7 +14408,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -14427,10 +14427,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>553476</v>
+        <v>553356</v>
       </c>
       <c r="R127" t="n">
-        <v>6705068</v>
+        <v>6704786</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14467,7 +14467,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>12 blomstjälkar</t>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14494,10 +14494,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127314416</v>
+        <v>127314432</v>
       </c>
       <c r="B128" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -14532,21 +14532,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>553356</v>
+        <v>553508</v>
       </c>
       <c r="R128" t="n">
-        <v>6704786</v>
+        <v>6705194</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14579,11 +14574,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14610,10 +14600,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127314432</v>
+        <v>127314415</v>
       </c>
       <c r="B129" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14640,7 +14630,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -14648,16 +14638,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>553508</v>
+        <v>553463</v>
       </c>
       <c r="R129" t="n">
-        <v>6705194</v>
+        <v>6705155</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14690,6 +14685,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>4 blomstjälkar</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14716,10 +14716,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127314415</v>
+        <v>127314435</v>
       </c>
       <c r="B130" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14746,7 +14746,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -14765,10 +14765,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>553463</v>
+        <v>553476</v>
       </c>
       <c r="R130" t="n">
-        <v>6705155</v>
+        <v>6705068</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14805,7 +14805,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>4 blomstjälkar</t>
+          <t>12 blomstjälkar</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14832,54 +14832,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127314465</v>
+        <v>127314347</v>
       </c>
       <c r="B131" t="n">
-        <v>98467</v>
+        <v>91350</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>553488</v>
+        <v>553419</v>
       </c>
       <c r="R131" t="n">
-        <v>6705263</v>
+        <v>6705073</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14938,10 +14929,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127314452</v>
+        <v>127314336</v>
       </c>
       <c r="B132" t="n">
-        <v>98467</v>
+        <v>91708</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14949,48 +14940,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>553418</v>
+        <v>553429</v>
       </c>
       <c r="R132" t="n">
-        <v>6705084</v>
+        <v>6705077</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15049,54 +15026,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127314410</v>
+        <v>127314345</v>
       </c>
       <c r="B133" t="n">
-        <v>98467</v>
+        <v>91350</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>553422</v>
+        <v>553386</v>
       </c>
       <c r="R133" t="n">
-        <v>6705072</v>
+        <v>6704777</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15155,32 +15123,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127314336</v>
+        <v>127314341</v>
       </c>
       <c r="B134" t="n">
-        <v>91707</v>
+        <v>91350</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15226,6 +15194,11 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15252,10 +15225,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127314341</v>
+        <v>127314350</v>
       </c>
       <c r="B135" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15287,10 +15260,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>553429</v>
+        <v>553465</v>
       </c>
       <c r="R135" t="n">
-        <v>6705077</v>
+        <v>6705219</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15323,11 +15296,6 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15354,32 +15322,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127314345</v>
+        <v>127314468</v>
       </c>
       <c r="B136" t="n">
-        <v>91349</v>
+        <v>91937</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1202</v>
+        <v>1179</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15389,10 +15357,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>553386</v>
+        <v>553482</v>
       </c>
       <c r="R136" t="n">
-        <v>6704777</v>
+        <v>6705183</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15427,6 +15395,11 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Återfynd</t>
+        </is>
+      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
@@ -15444,17 +15417,17 @@
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127314468</v>
+        <v>127314452</v>
       </c>
       <c r="B137" t="n">
-        <v>91936</v>
+        <v>98468</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15462,34 +15435,48 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1179</v>
+        <v>220787</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>553482</v>
+        <v>553418</v>
       </c>
       <c r="R137" t="n">
-        <v>6705183</v>
+        <v>6705084</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15524,11 +15511,6 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Återfynd</t>
-        </is>
-      </c>
       <c r="AD137" t="b">
         <v>0</v>
       </c>
@@ -15546,52 +15528,61 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127314347</v>
+        <v>127314410</v>
       </c>
       <c r="B138" t="n">
-        <v>91349</v>
+        <v>98468</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>553419</v>
+        <v>553422</v>
       </c>
       <c r="R138" t="n">
-        <v>6705073</v>
+        <v>6705072</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15650,45 +15641,54 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127314350</v>
+        <v>127314465</v>
       </c>
       <c r="B139" t="n">
-        <v>91349</v>
+        <v>98468</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>553465</v>
+        <v>553488</v>
       </c>
       <c r="R139" t="n">
-        <v>6705219</v>
+        <v>6705263</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15740,17 +15740,17 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127314370</v>
+        <v>127314473</v>
       </c>
       <c r="B140" t="n">
-        <v>57669</v>
+        <v>57593</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15758,16 +15758,16 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -15776,24 +15776,21 @@
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>553311</v>
+        <v>553415</v>
       </c>
       <c r="R140" t="n">
-        <v>6704717</v>
+        <v>6705462</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15828,6 +15825,11 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Fjädrar på "slaktbord"</t>
+        </is>
+      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
@@ -15845,17 +15847,17 @@
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127314473</v>
+        <v>127314370</v>
       </c>
       <c r="B141" t="n">
-        <v>57593</v>
+        <v>57669</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15863,16 +15865,16 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100001</v>
+        <v>100049</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -15881,21 +15883,24 @@
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>553415</v>
+        <v>553311</v>
       </c>
       <c r="R141" t="n">
-        <v>6705462</v>
+        <v>6704717</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15928,11 +15933,6 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Fjädrar på "slaktbord"</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15959,10 +15959,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127314442</v>
+        <v>127314441</v>
       </c>
       <c r="B142" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16003,10 +16003,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>553423</v>
+        <v>553422</v>
       </c>
       <c r="R142" t="n">
-        <v>6704914</v>
+        <v>6704986</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16065,10 +16065,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127314441</v>
+        <v>127314442</v>
       </c>
       <c r="B143" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16109,10 +16109,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>553422</v>
+        <v>553423</v>
       </c>
       <c r="R143" t="n">
-        <v>6704986</v>
+        <v>6704914</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16174,7 +16174,7 @@
         <v>127314417</v>
       </c>
       <c r="B144" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16491,10 +16491,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127314454</v>
+        <v>127314424</v>
       </c>
       <c r="B147" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -16540,10 +16540,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>553347</v>
+        <v>553422</v>
       </c>
       <c r="R147" t="n">
-        <v>6705040</v>
+        <v>6704824</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16576,11 +16576,6 @@
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>7 blomstjälkar</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16607,10 +16602,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127314424</v>
+        <v>127314454</v>
       </c>
       <c r="B148" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16637,7 +16632,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -16656,10 +16651,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>553422</v>
+        <v>553347</v>
       </c>
       <c r="R148" t="n">
-        <v>6704824</v>
+        <v>6705040</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16694,6 +16689,11 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>7 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD148" t="b">
         <v>0</v>
       </c>
@@ -16711,57 +16711,52 @@
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127314405</v>
+        <v>127314343</v>
       </c>
       <c r="B149" t="n">
-        <v>8450</v>
+        <v>91350</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>553521</v>
+        <v>553388</v>
       </c>
       <c r="R149" t="n">
-        <v>6705364</v>
+        <v>6704753</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16820,59 +16815,45 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127314450</v>
+        <v>127314342</v>
       </c>
       <c r="B150" t="n">
-        <v>98467</v>
+        <v>91350</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>553340</v>
+        <v>553347</v>
       </c>
       <c r="R150" t="n">
-        <v>6704784</v>
+        <v>6704783</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16934,7 +16915,7 @@
         <v>127314411</v>
       </c>
       <c r="B151" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17042,47 +17023,38 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127314419</v>
+        <v>127314405</v>
       </c>
       <c r="B152" t="n">
-        <v>98467</v>
+        <v>8450</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -17091,10 +17063,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>553343</v>
+        <v>553521</v>
       </c>
       <c r="R152" t="n">
-        <v>6704786</v>
+        <v>6705364</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17127,11 +17099,6 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17158,45 +17125,59 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>127314342</v>
+        <v>127314419</v>
       </c>
       <c r="B153" t="n">
-        <v>91349</v>
+        <v>98468</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>553347</v>
+        <v>553343</v>
       </c>
       <c r="R153" t="n">
-        <v>6704783</v>
+        <v>6704786</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17229,6 +17210,11 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17255,45 +17241,59 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127314343</v>
+        <v>127314450</v>
       </c>
       <c r="B154" t="n">
-        <v>91349</v>
+        <v>98468</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>553388</v>
+        <v>553340</v>
       </c>
       <c r="R154" t="n">
-        <v>6704753</v>
+        <v>6704784</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17345,60 +17345,52 @@
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127314374</v>
+        <v>127314385</v>
       </c>
       <c r="B155" t="n">
-        <v>57669</v>
+        <v>56968</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100049</v>
+        <v>100038</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>553523</v>
+        <v>553426</v>
       </c>
       <c r="R155" t="n">
-        <v>6705404</v>
+        <v>6704786</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17457,10 +17449,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127314391</v>
+        <v>127314374</v>
       </c>
       <c r="B156" t="n">
-        <v>57672</v>
+        <v>57669</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17468,16 +17460,16 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -17486,21 +17478,24 @@
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
       <c r="M156" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>553375</v>
+        <v>553523</v>
       </c>
       <c r="R156" t="n">
-        <v>6705433</v>
+        <v>6705404</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17533,11 +17528,6 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17564,10 +17554,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127314433</v>
+        <v>127314387</v>
       </c>
       <c r="B157" t="n">
-        <v>98467</v>
+        <v>91804</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17575,43 +17565,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Morkullberget södra, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>553366</v>
+        <v>553517</v>
       </c>
       <c r="R157" t="n">
-        <v>6704886</v>
+        <v>6705421</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17670,47 +17651,38 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127314447</v>
+        <v>127314391</v>
       </c>
       <c r="B158" t="n">
-        <v>98467</v>
+        <v>57672</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      